--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">CRES!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">HERMES!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">TRIUMPH!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">빠따!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="760">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,597 +84,597 @@
     <t>Scania 25</t>
   </si>
   <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>675경 8717조 9996억 6939만</t>
+  </si>
+  <si>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+  </si>
+  <si>
+    <t>설익은체리</t>
+  </si>
+  <si>
+    <t>2026.09.12</t>
+  </si>
+  <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>602경 2808조 3209억 1039만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN70위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.09.13</t>
+  </si>
+  <si>
+    <t>HERMES</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=HERMES</t>
+  </si>
+  <si>
+    <t>Scania 3</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>618경 1272조 9707억 7440만</t>
+  </si>
+  <si>
+    <t>No.1 HERMES</t>
+  </si>
+  <si>
+    <t>명탐젓코난</t>
+  </si>
+  <si>
+    <t>유니크</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9C%A0%EB%8B%88%ED%81%AC</t>
+  </si>
+  <si>
+    <t>Scania 1</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>592경 4343조 4147억 6600만</t>
+  </si>
+  <si>
+    <t>똥!</t>
+  </si>
+  <si>
+    <t>동땅이</t>
+  </si>
+  <si>
+    <t>빠따</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>541경 4853조 3239억 949만</t>
+  </si>
+  <si>
+    <t>매너친목아닌길드</t>
+  </si>
+  <si>
+    <t>o원기o</t>
+  </si>
+  <si>
+    <t>CRES</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=CRES</t>
+  </si>
+  <si>
+    <t>Scania 45</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>486경 6868조 2475억 4590만</t>
+  </si>
+  <si>
+    <t>by invitation only</t>
+  </si>
+  <si>
+    <t>라리c</t>
+  </si>
+  <si>
+    <t>TRIUMPH</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
+  </si>
+  <si>
+    <t>Scania 63</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>823경 131조 424억 1509만</t>
+  </si>
+  <si>
+    <t>퐁이츄</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>187경 9039조 7170억 6795만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>캐일리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>127경 9398조 8573억 4847만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>킹규봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>62경 4188조 2543억 3793만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>40경 9302조 8286억 6262만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>38경 977조 8938억 5636만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>34경 3801조 8477억 2219만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
+  </si>
+  <si>
+    <t>30경 3935조 631억 9583만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>27경 5354조 8887억 3874만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>시드리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>23경 4505조 3815억 9635만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>셀렘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>18경 4568조 198억 4901만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>졸귀탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>13경 4975조 4851억 7583만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>설딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
+  </si>
+  <si>
+    <t>12경 7975조 8170억 5111만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>11경 2284조 7629억 3908만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>슐아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>7경 2382조 7642억 9212만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>설름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>6경 8149조 5923억 707만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>경성2018</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>6경 3038조 8711억 1572만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>5경 2230조 4268억 1822만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>4경 5345조 1275억 983만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>4경 3643조 5234억 1086만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>우열무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%97%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>3경 2534조 9024억 7216만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>수상구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>2경 903조 2186억 8410만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>견아니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 6169조 6284억 1304만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>설앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1경 3569조 9243억 6675만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>설치지마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EC%A7%80%EB%A7%88</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1경 3284조 7758억 2759만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>공룡박사원이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%A3%A1%EB%B0%95%EC%82%AC%EC%9B%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1경 1008조 8977억 2613만</t>
+  </si>
+  <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>8896조 7359억 8277만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>8781조 4022억 5235만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>7510조 8126억 8889만</t>
+  </si>
+  <si>
+    <t>양촌마을</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B4%8C%EB%A7%88%EC%9D%84</t>
+  </si>
+  <si>
+    <t>6095조 9324억 3963만</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>636경 432조 3564억 5949만</t>
-  </si>
-  <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
-  </si>
-  <si>
-    <t>설익은체리</t>
-  </si>
-  <si>
-    <t>2026.09.12</t>
-  </si>
-  <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>590경 105조 2361억 5050만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN70위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>HERMES</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=HERMES</t>
-  </si>
-  <si>
-    <t>Scania 3</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>612경 1649조 3464억 6290만</t>
-  </si>
-  <si>
-    <t>No.1 HERMES</t>
-  </si>
-  <si>
-    <t>명탐젓코난</t>
-  </si>
-  <si>
-    <t>유니크</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9C%A0%EB%8B%88%ED%81%AC</t>
-  </si>
-  <si>
-    <t>Scania 1</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>590경 3861조 1539억 1239만</t>
-  </si>
-  <si>
-    <t>똥!</t>
-  </si>
-  <si>
-    <t>동땅이</t>
-  </si>
-  <si>
-    <t>빠따</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>530경 3702조 9820억 300만</t>
-  </si>
-  <si>
-    <t>매너친목아닌길드</t>
-  </si>
-  <si>
-    <t>o원기o</t>
-  </si>
-  <si>
-    <t>CRES</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=CRES</t>
-  </si>
-  <si>
-    <t>Scania 45</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>486경 6112조 4639억 8369만</t>
-  </si>
-  <si>
-    <t>by invitation only</t>
-  </si>
-  <si>
-    <t>라리c</t>
-  </si>
-  <si>
-    <t>TRIUMPH</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
-  </si>
-  <si>
-    <t>Scania 63</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>822경 8525조 4342억 5219만</t>
-  </si>
-  <si>
-    <t>퐁이츄</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>해물만두야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>150경 6569조 3334억 3234만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>캐일리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>126경 8689조 3653억 8759만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>킹규봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>62경 4188조 2543억 3793만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>설함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>40경 9302조 8286억 6262만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>38경 977조 8938억 5636만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>34경 3801조 8477억 2219만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>너굴얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
-  </si>
-  <si>
-    <t>30경 3909조 9713억 9733만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>루델밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>27경 5227조 9852억 8753만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>시드리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>23경 4505조 3815억 9635만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>셀렘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>17경 8367조 7896억 1374만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>졸귀탱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>13경 1638조 5691억 833만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>11경 1938조 3670억 2482만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>설딩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
-  </si>
-  <si>
-    <t>10경 7470조 3945억 2966만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>슐아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>7경 2382조 7642억 9212만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>설름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
-  </si>
-  <si>
-    <t>6경 8149조 5923억 707만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>경성2018</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>6경 3038조 8711억 1572만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>5경 2230조 4268억 1822만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>4경 5345조 1275억 983만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>4경 3643조 5234억 1086만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>우열무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%97%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>3경 2534조 9024억 7216만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>수상구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>1경 7774조 2386억 7106만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>견아니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 4775조 3794억 8133만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>설앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>1경 3569조 9243억 6675만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>설치지마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EC%A7%80%EB%A7%88</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1경 3284조 7758억 2759만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>공룡박사원이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%A3%A1%EB%B0%95%EC%82%AC%EC%9B%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1경 818조 7326억 8358만</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>8896조 7359억 8277만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>8781조 4022억 5235만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>7477조 9291억 6103만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>양촌마을</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B4%8C%EB%A7%88%EC%9D%84</t>
-  </si>
-  <si>
-    <t>6095조 9324억 3963만</t>
-  </si>
-  <si>
     <t>헤븐잉</t>
   </si>
   <si>
@@ -702,7 +702,7 @@
     <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
   </si>
   <si>
-    <t>56경 2380조 2927억 6127만</t>
+    <t>58경 4001조 2779억 5325만</t>
   </si>
   <si>
     <t>진자이</t>
@@ -711,7 +711,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>51경 8875조 2162억 6967만</t>
+    <t>53경 625조 5653억 3480만</t>
   </si>
   <si>
     <t>돈스</t>
@@ -729,7 +729,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>39경 4863조 5172억 8731만</t>
+    <t>40경 4809조 4569억 7661만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -750,7 +750,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
   </si>
   <si>
-    <t>22경 2656조 5088억 3487만</t>
+    <t>22경 2897조 9622억 4868만</t>
   </si>
   <si>
     <t>스타캐치</t>
@@ -759,7 +759,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
   </si>
   <si>
-    <t>22경 2273조 5626억 5080만</t>
+    <t>22경 2364조 9461억 5527만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -777,7 +777,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>9경 2858조 7659억 4585만</t>
+    <t>9경 3208조 1900억 1331만</t>
   </si>
   <si>
     <t>국의</t>
@@ -804,7 +804,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
   </si>
   <si>
-    <t>7경 7634조 1071억 4397만</t>
+    <t>7경 8521조 7245억 5404만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -825,6 +825,15 @@
     <t>7경 145조 793억 7358만</t>
   </si>
   <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>6경 7507조 6793억 8682만</t>
+  </si>
+  <si>
     <t>잼포즈</t>
   </si>
   <si>
@@ -834,7 +843,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>6경 5453조 148억 5508만</t>
+    <t>6경 5572조 9054억 2021만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -846,22 +855,22 @@
     <t>6경 4885조 3111억 7395만</t>
   </si>
   <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>6경 3278조 9460억 3057만</t>
-  </si>
-  <si>
     <t>킹몬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>5경 2700조 2571억 9886만</t>
+    <t>5경 6355조 5541억 4319만</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
     <t>김겨탱</t>
@@ -870,16 +879,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
   </si>
   <si>
-    <t>4경 5847조 8701억 7698만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>4경 332조 8806억 8276만</t>
+    <t>4경 6208조 3978억 9628만</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>1경 5432조 1524억 327만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -891,15 +900,6 @@
     <t>1경 5275조 752억 3008만</t>
   </si>
   <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1경 5210조 2553억 4869만</t>
-  </si>
-  <si>
     <t>할룽</t>
   </si>
   <si>
@@ -924,7 +924,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
   </si>
   <si>
-    <t>1경 58조 8286억 5389만</t>
+    <t>1경 84조 5679억 4324만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
@@ -942,7 +942,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>8487조 8465억 6014만</t>
+    <t>8488조 7335억 2631만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -951,7 +951,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>8199조 9891억 1409만</t>
+    <t>8263조 3641억 1604만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -969,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%A5%EC%BB%A4</t>
   </si>
   <si>
-    <t>156경 2339조 7753억 4418만</t>
+    <t>160경 368조 1168억 858만</t>
   </si>
   <si>
     <t>적금묶인린풍</t>
@@ -978,7 +978,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EA%B8%88%EB%AC%B6%EC%9D%B8%EB%A6%B0%ED%92%8D</t>
   </si>
   <si>
-    <t>112경 9843조 3480억 3863만</t>
+    <t>114경 187조 2032억 9841만</t>
   </si>
   <si>
     <t>야느</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%83%90%EC%A0%93%EC%BD%94%EB%82%9C</t>
   </si>
   <si>
-    <t>53경 5645조 8175억 4778만</t>
+    <t>53경 7558조 8546억 2362만</t>
   </si>
   <si>
     <t>닐쿵</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%89%EB%B0%9C%EC%A7%841</t>
   </si>
   <si>
-    <t>42경 95조 1694억 400만</t>
+    <t>44경 324조 7001억 2760만</t>
   </si>
   <si>
     <t>조평견</t>
@@ -1029,7 +1029,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A8%ED%99%98%EB%B6%88%ED%95%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>16경 5387조 7844억 7406만</t>
+    <t>16경 5740조 1366억 190만</t>
   </si>
   <si>
     <t>쁘헬</t>
@@ -1038,7 +1038,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%81%98%ED%97%AC</t>
   </si>
   <si>
-    <t>9경 1조 1347억 7737만</t>
+    <t>9경 265조 4706억 783만</t>
   </si>
   <si>
     <t>랍아</t>
@@ -1074,7 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%EC%9A%B4</t>
   </si>
   <si>
-    <t>4경 4216조 1625억 288만</t>
+    <t>4경 4379조 5496억 2571만</t>
   </si>
   <si>
     <t>육퇴한아빠</t>
@@ -1092,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%84%ED%8F%89</t>
   </si>
   <si>
-    <t>2경 9097조 1643억 3135만</t>
+    <t>3경 97조 803억 1885만</t>
   </si>
   <si>
     <t>노건</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A8%EC%94%A8</t>
   </si>
   <si>
-    <t>2경 2371조 3840억 2135만</t>
+    <t>2경 2620조 6420억 2041만</t>
   </si>
   <si>
     <t>수냬</t>
@@ -1137,7 +1137,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%ED%95%98</t>
   </si>
   <si>
-    <t>1경 6635조 9195억 1239만</t>
+    <t>1경 6666조 6912억 7835만</t>
   </si>
   <si>
     <t>딸기껌</t>
@@ -1155,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>1경 966조 2630억 3117만</t>
+    <t>1경 1152조 3255억 995만</t>
   </si>
   <si>
     <t>새콤달콤해</t>
@@ -1173,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%99%8D</t>
   </si>
   <si>
-    <t>8881조 8586억 5896만</t>
+    <t>8915조 9516억 22만</t>
   </si>
   <si>
     <t>칸델</t>
@@ -1182,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%B8%EB%8D%B8</t>
   </si>
   <si>
-    <t>7825조 9287억 7653만</t>
+    <t>7854조 5403억 3321만</t>
   </si>
   <si>
     <t>고양이확대범</t>
@@ -1266,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%ED%98%B8%EB%94%98</t>
   </si>
   <si>
-    <t>22경 1096조 4226억 3197만</t>
+    <t>22경 1380조 1868억 2011만</t>
   </si>
   <si>
     <t>우땨</t>
@@ -1293,7 +1293,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%ED%94%BD</t>
   </si>
   <si>
-    <t>11경 510조 7801억 7507만</t>
+    <t>11경 831조 2626억 6651만</t>
   </si>
   <si>
     <t>임씬</t>
@@ -1302,7 +1302,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%94%AC</t>
   </si>
   <si>
-    <t>7경 7941조 1023억 1221만</t>
+    <t>8경 540조 3712억 1485만</t>
   </si>
   <si>
     <t>겐미</t>
@@ -1311,7 +1311,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>5경 5640조 2221억 9760만</t>
+    <t>5경 6895조 3874억 1493만</t>
   </si>
   <si>
     <t>텨숍</t>
@@ -1320,7 +1320,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%85%A8%EC%88%8D</t>
   </si>
   <si>
-    <t>4경 1986조 3353억 2483만</t>
+    <t>4경 9694조 9731억 8905만</t>
+  </si>
+  <si>
+    <t>승질승</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%A7%88%EC%8A%B9</t>
+  </si>
+  <si>
+    <t>4경 239조 7442억 1924만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%95%85%EC%9D%B4</t>
@@ -1329,22 +1338,13 @@
     <t>3경 9265조 5752억 5679만</t>
   </si>
   <si>
-    <t>승질승</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%A7%88%EC%8A%B9</t>
-  </si>
-  <si>
-    <t>3경 8197조 7091억 6283만</t>
-  </si>
-  <si>
     <t>보레아스</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A0%88%EC%95%84%EC%8A%A4</t>
   </si>
   <si>
-    <t>2경 887조 1131억 39만</t>
+    <t>2경 947조 9879억 613만</t>
   </si>
   <si>
     <t>향연</t>
@@ -1380,7 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1경 9695조 8388억 6901만</t>
+    <t>1경 9730조 9484억 8556만</t>
   </si>
   <si>
     <t>정령성</t>
@@ -1389,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%A0%B9%EC%84%B1</t>
   </si>
   <si>
-    <t>1경 5737조 3904억 3701만</t>
+    <t>1경 6007조 4327억 1703만</t>
   </si>
   <si>
     <t>DAEBAK</t>
@@ -1398,7 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=DAEBAK</t>
   </si>
   <si>
-    <t>1경 2639조 9500억 3354만</t>
+    <t>1경 3538조 9525억 7635만</t>
   </si>
   <si>
     <t>벞벞</t>
@@ -1407,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%9E%EB%B2%9E</t>
   </si>
   <si>
-    <t>1경 1330조 3259억 7670만</t>
+    <t>1경 2189조 8683억 18만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -1434,7 +1434,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%B8</t>
   </si>
   <si>
-    <t>9613조 7340억 6917만</t>
+    <t>9631조 3747억 3263만</t>
   </si>
   <si>
     <t>퍌라딘</t>
@@ -1461,7 +1461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A5%98</t>
   </si>
   <si>
-    <t>5456조 9805억 7596만</t>
+    <t>5488조 1815억 1778만</t>
   </si>
   <si>
     <t>뚱뚱쉰</t>
@@ -1470,7 +1470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%EB%9A%B1%EC%89%B0</t>
   </si>
   <si>
-    <t>4756조 7286억 5926만</t>
+    <t>4760조 7160억 6436만</t>
   </si>
   <si>
     <t>댤타냥</t>
@@ -1479,7 +1479,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%A4%ED%83%80%EB%83%A5</t>
   </si>
   <si>
-    <t>4644조 6613억 4533만</t>
+    <t>4711조 5145억 248만</t>
   </si>
   <si>
     <t>컈컈</t>
@@ -1509,7 +1509,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%94%A8</t>
   </si>
   <si>
-    <t>209경 3114조 8435억 3445만</t>
+    <t>227경 441조 4254억 7501만</t>
   </si>
   <si>
     <t>라온MS</t>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%9F%EB%BF%A1%EC%95%BC</t>
   </si>
   <si>
-    <t>9경 9596조 6713억 15만</t>
+    <t>9경 9711조 7551억 1995만</t>
   </si>
   <si>
     <t>o엉댕o</t>
@@ -1569,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
   </si>
   <si>
-    <t>7경 2477조 6912억 4916만</t>
+    <t>7경 2882조 1295억 9353만</t>
   </si>
   <si>
     <t>매쵸맛</t>
@@ -1578,7 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%B5%B8%EB%A7%9B</t>
   </si>
   <si>
-    <t>4경 6447조 2325억 988만</t>
+    <t>4경 7149조 6273억 3016만</t>
   </si>
   <si>
     <t>설편</t>
@@ -1587,7 +1587,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%8E%B8</t>
   </si>
   <si>
-    <t>4경 4142조 6540억 9445만</t>
+    <t>4경 5420조 9162억 9652만</t>
+  </si>
+  <si>
+    <t>여수로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%88%98%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>2경 8646조 1583억 1624만</t>
   </si>
   <si>
     <t>o후국o</t>
@@ -1599,15 +1608,6 @@
     <t>2경 8526조 1391억 6769만</t>
   </si>
   <si>
-    <t>여수로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%88%98%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>2경 8319조 288억 7675만</t>
-  </si>
-  <si>
     <t>o진이o</t>
   </si>
   <si>
@@ -1650,7 +1650,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EC%9B%85</t>
   </si>
   <si>
-    <t>1경 7388조 1868억 6761만</t>
+    <t>1경 7465조 9577억 9299만</t>
+  </si>
+  <si>
+    <t>후니와동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>1경 5364조 8821억 4359만</t>
   </si>
   <si>
     <t>사단장님</t>
@@ -1662,13 +1671,13 @@
     <t>1경 5073조 4203억 9618만</t>
   </si>
   <si>
-    <t>후니와동동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
-  </si>
-  <si>
-    <t>1경 4948조 9921억 5901만</t>
+    <t>화욤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
+  </si>
+  <si>
+    <t>1경 4875조 1822억 2534만</t>
   </si>
   <si>
     <t>멩구v</t>
@@ -1680,15 +1689,6 @@
     <t>1경 4589조 2742억 1441만</t>
   </si>
   <si>
-    <t>화욤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
-  </si>
-  <si>
-    <t>1경 4343조 8810억 5756만</t>
-  </si>
-  <si>
     <t>호이호이포이</t>
   </si>
   <si>
@@ -1704,7 +1704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
   </si>
   <si>
-    <t>8485조 1043억 369만</t>
+    <t>8662조 7378억 2262만</t>
   </si>
   <si>
     <t>FFFK</t>
@@ -1713,7 +1713,7 @@
     <t>https://mgf.gg/contents/character.php?n=FFFK</t>
   </si>
   <si>
-    <t>8364조 5461억 2677만</t>
+    <t>8477조 3763억 8738만</t>
   </si>
   <si>
     <t>옹이잉</t>
@@ -1722,7 +1722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%9D%B4%EC%9E%89</t>
   </si>
   <si>
-    <t>7714조 4366억 3766만</t>
+    <t>7861조 2137억 6072만</t>
   </si>
   <si>
     <t>o아윤o</t>
@@ -1740,7 +1740,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
   </si>
   <si>
-    <t>4525조 2142억 8791만</t>
+    <t>4571조 4731억 4344만</t>
   </si>
   <si>
     <t>담훌</t>
@@ -1749,7 +1749,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
   </si>
   <si>
-    <t>4202조 1641억 8318만</t>
+    <t>4284조 7797억 2852만</t>
   </si>
   <si>
     <t>건들면혼남</t>
@@ -1758,7 +1758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%93%A4%EB%A9%B4%ED%98%BC%EB%82%A8</t>
   </si>
   <si>
-    <t>3499조 3832억 1667만</t>
+    <t>3536조 6744억 759만</t>
   </si>
   <si>
     <t>보마할래</t>
@@ -1767,13 +1767,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
   </si>
   <si>
-    <t>2960조 869억 2783만</t>
+    <t>2961조 4012억 1670만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A6%ACc</t>
   </si>
   <si>
-    <t>456경 4246조 8876억 4167만</t>
+    <t>126</t>
+  </si>
+  <si>
+    <t>470경 553조 4118억 9856만</t>
   </si>
   <si>
     <t>김승관</t>
@@ -1791,7 +1794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EC%84%9C%EC%A0%95</t>
   </si>
   <si>
-    <t>3경 8614조 2874억 4689만</t>
+    <t>3경 8661조 6767억 6273만</t>
   </si>
   <si>
     <t>yullmu</t>
@@ -1800,7 +1803,7 @@
     <t>https://mgf.gg/contents/character.php?n=yullmu</t>
   </si>
   <si>
-    <t>1경 1193조 6809억 4733만</t>
+    <t>1경 1346조 1232억 3236만</t>
   </si>
   <si>
     <t>황룹</t>
@@ -1809,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EB%A3%B9</t>
   </si>
   <si>
-    <t>8302조 2980억 8162만</t>
+    <t>8306조 1218억 3388만</t>
   </si>
   <si>
     <t>서공윤</t>
@@ -1827,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%81%AC%EC%98%A4%EB%B8%8C</t>
   </si>
   <si>
-    <t>4686조 6914억 1189만</t>
+    <t>5057조 3629억 8668만</t>
   </si>
   <si>
     <t>압러</t>
@@ -1836,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%95%EB%9F%AC</t>
   </si>
   <si>
-    <t>4331조 4917억 1117만</t>
+    <t>4384조 9103억 9361만</t>
   </si>
   <si>
     <t>라리v</t>
@@ -1845,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A6%ACv</t>
   </si>
   <si>
-    <t>3879조 1835억 5214만</t>
+    <t>3881조 8359억 5964만</t>
   </si>
   <si>
     <t>사랑보다깊은</t>
@@ -1866,6 +1869,15 @@
     <t>2227조 5185억 7197만</t>
   </si>
   <si>
+    <t>팍솔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8D%EC%86%94</t>
+  </si>
+  <si>
+    <t>2114조 6997억 5264만</t>
+  </si>
+  <si>
     <t>콜리콜리</t>
   </si>
   <si>
@@ -1878,13 +1890,22 @@
     <t>2094조 2516억 6756만</t>
   </si>
   <si>
-    <t>팍솔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8D%EC%86%94</t>
-  </si>
-  <si>
-    <t>2068조 5239억 2950만</t>
+    <t>유굥a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EA%B5%A5a</t>
+  </si>
+  <si>
+    <t>1338조 875억 1870만</t>
+  </si>
+  <si>
+    <t>융챠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%B5%EC%B1%A0</t>
+  </si>
+  <si>
+    <t>1329조 8329억 9591만</t>
   </si>
   <si>
     <t>아라사랑해</t>
@@ -1893,46 +1914,28 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%9D%BC%EC%82%AC%EB%9E%91%ED%95%B4</t>
   </si>
   <si>
-    <t>1310조 5224억 104만</t>
-  </si>
-  <si>
-    <t>융챠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%B5%EC%B1%A0</t>
-  </si>
-  <si>
-    <t>1301조 895억 4584만</t>
-  </si>
-  <si>
-    <t>유굥a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EA%B5%A5a</t>
+    <t>1315조 2134억 1586만</t>
+  </si>
+  <si>
+    <t>뮤내</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AE%A4%EB%82%B4</t>
+  </si>
+  <si>
+    <t>908조 4921억 2094만</t>
+  </si>
+  <si>
+    <t>도적레오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EB%A0%88%EC%98%A4</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>1264조 9606억 2514만</t>
-  </si>
-  <si>
-    <t>뮤내</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AE%A4%EB%82%B4</t>
-  </si>
-  <si>
-    <t>908조 2896억 3550만</t>
-  </si>
-  <si>
-    <t>도적레오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EB%A0%88%EC%98%A4</t>
-  </si>
-  <si>
-    <t>765조 8792억 6704만</t>
+    <t>778조 8819억 348만</t>
   </si>
   <si>
     <t>유이건</t>
@@ -1941,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%9D%B4%EA%B1%B4</t>
   </si>
   <si>
-    <t>682조 4287억 218만</t>
+    <t>702조 1965억 9515만</t>
   </si>
   <si>
     <t>다크홀리</t>
@@ -1950,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%81%AC%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>511조 1033억 2088만</t>
+    <t>530조 6969억 1370만</t>
   </si>
   <si>
     <t>룬보</t>
@@ -1959,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%AC%EB%B3%B4</t>
   </si>
   <si>
-    <t>449조 8547억 588만</t>
+    <t>486조 4330억 3942만</t>
   </si>
   <si>
     <t>우주경</t>
@@ -1971,7 +1974,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>405조 3255억 8022만</t>
+    <t>414조 5422억 9225만</t>
   </si>
   <si>
     <t>Libere</t>
@@ -1980,7 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=Libere</t>
   </si>
   <si>
-    <t>387조 940억 6316만</t>
+    <t>393조 8758억 1169만</t>
   </si>
   <si>
     <t>현수컷</t>
@@ -1989,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%88%98%EC%BB%B7</t>
   </si>
   <si>
-    <t>293조 5937억 2787만</t>
+    <t>313조 847억 5192만</t>
   </si>
   <si>
     <t>돈골대가</t>
@@ -2001,7 +2004,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>240조 9623억 1954만</t>
+    <t>251조 9335억 4895만</t>
   </si>
   <si>
     <t>손쨩1</t>
@@ -2013,7 +2016,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>219조 4263억 2812만</t>
+    <t>231조 7307억 6382만</t>
   </si>
   <si>
     <t>겨울파파</t>
@@ -2022,7 +2025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>206조 2978억 3222만</t>
+    <t>207조 8449억 3960만</t>
   </si>
   <si>
     <t>지니D</t>
@@ -2034,7 +2037,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>38조 9790억 4968만</t>
+    <t>41조 4178억 5590만</t>
   </si>
   <si>
     <t>종리츄</t>
@@ -2067,7 +2070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 499조 9492억 1534만</t>
+    <t>1경 762조 9596억 5662만</t>
   </si>
   <si>
     <t>친절한정육</t>
@@ -2085,7 +2088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>6048조 8679억 7558만</t>
+    <t>6063조 7111억 7030만</t>
   </si>
   <si>
     <t>딤츄</t>
@@ -2094,7 +2097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>2389조 1286억 2209만</t>
+    <t>2543조 1100억 8023만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -2103,7 +2106,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
   </si>
   <si>
-    <t>2369조 1990억 8629만</t>
+    <t>2410조 5237억 8213만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1706조 5042억 6230만</t>
   </si>
   <si>
     <t>유졍츄</t>
@@ -2112,16 +2124,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
   </si>
   <si>
-    <t>1636조 5757억 2044만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1611조 4400억 5242만</t>
+    <t>1660조 4582억 8500만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1418조 3994억 9351만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -2142,7 +2154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%82%B6</t>
   </si>
   <si>
-    <t>931조 5970억 7895만</t>
+    <t>1006조 9985억 2612만</t>
   </si>
   <si>
     <t>서전붕</t>
@@ -2160,7 +2172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>856조 372억 8227만</t>
+    <t>861조 5431억 9932만</t>
   </si>
   <si>
     <t>호야빵</t>
@@ -2172,22 +2184,22 @@
     <t>776조 4778억 6115만</t>
   </si>
   <si>
+    <t>현유수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
+  </si>
+  <si>
+    <t>680조 1186억 9588만</t>
+  </si>
+  <si>
     <t>푸들츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>652조 6644억 1930만</t>
-  </si>
-  <si>
-    <t>현유수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
-  </si>
-  <si>
-    <t>615조 6773억 7733만</t>
+    <t>668조 2040억 4833만</t>
   </si>
   <si>
     <t>루린츄</t>
@@ -2214,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>271조 6311억 6458만</t>
+    <t>302조 7184억 4243만</t>
   </si>
   <si>
     <t>하치츄</t>
@@ -2232,7 +2244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
   </si>
   <si>
-    <t>194조 789억 5974만</t>
+    <t>202조 890억 352만</t>
   </si>
   <si>
     <t>도리츄</t>
@@ -2241,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>174조 650억 2660만</t>
+    <t>176조 5756억 9029만</t>
   </si>
   <si>
     <t>주냥츄</t>
@@ -2250,7 +2262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
   </si>
   <si>
-    <t>158조 5928억 1904만</t>
+    <t>163조 9275억 2518만</t>
   </si>
   <si>
     <t>디나인</t>
@@ -2298,7 +2310,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%B4%EC%B8%84%EC%8B%AD%EB%B3%BC%ED%8A%B8</t>
   </si>
   <si>
-    <t>16조 9604억 8731만</t>
+    <t>16조 9704억 4542만</t>
   </si>
 </sst>
 </file>
@@ -2797,27 +2809,27 @@
         <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>18</v>
@@ -2829,13 +2841,13 @@
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2843,25 +2855,25 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>29</v>
@@ -2870,36 +2882,36 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>18</v>
@@ -2911,13 +2923,13 @@
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2925,22 +2937,22 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>18</v>
@@ -2949,16 +2961,16 @@
         <v>29</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>24</v>
@@ -2966,31 +2978,31 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>69</v>
@@ -3472,7 +3484,7 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>142</v>
@@ -3870,7 +3882,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>199</v>
@@ -3966,16 +3978,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -3987,7 +3999,7 @@
         <v>183</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3998,7 +4010,7 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>214</v>
@@ -4139,7 +4151,7 @@
         <v>220</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4171,7 +4183,7 @@
         <v>223</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4203,7 +4215,7 @@
         <v>226</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4235,7 +4247,7 @@
         <v>229</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4267,7 +4279,7 @@
         <v>232</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4299,7 +4311,7 @@
         <v>236</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4331,7 +4343,7 @@
         <v>239</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4363,7 +4375,7 @@
         <v>242</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4395,7 +4407,7 @@
         <v>245</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4427,7 +4439,7 @@
         <v>248</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4459,7 +4471,7 @@
         <v>251</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4491,7 +4503,7 @@
         <v>254</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4517,13 +4529,13 @@
         <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>257</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4555,7 +4567,7 @@
         <v>260</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4587,7 +4599,7 @@
         <v>263</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -4610,16 +4622,16 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -4630,28 +4642,28 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>270</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4674,7 +4686,7 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>146</v>
@@ -4683,7 +4695,7 @@
         <v>273</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4715,7 +4727,7 @@
         <v>276</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4738,7 +4750,7 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>156</v>
@@ -4747,7 +4759,7 @@
         <v>279</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4770,7 +4782,7 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>156</v>
@@ -4779,7 +4791,7 @@
         <v>282</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4811,7 +4823,7 @@
         <v>285</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4843,7 +4855,7 @@
         <v>288</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4875,7 +4887,7 @@
         <v>291</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4907,7 +4919,7 @@
         <v>294</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4915,7 +4927,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>295</v>
@@ -4939,7 +4951,7 @@
         <v>297</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4971,7 +4983,7 @@
         <v>300</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -5003,7 +5015,7 @@
         <v>303</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -5011,7 +5023,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>304</v>
@@ -5035,7 +5047,7 @@
         <v>306</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -5043,7 +5055,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>307</v>
@@ -5067,7 +5079,7 @@
         <v>309</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -5119,7 +5131,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5157,7 +5169,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
@@ -5189,7 +5201,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
@@ -5221,7 +5233,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>92</v>
@@ -5253,16 +5265,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>319</v>
@@ -5285,7 +5297,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>102</v>
@@ -5317,7 +5329,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>108</v>
@@ -5349,7 +5361,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>113</v>
@@ -5381,7 +5393,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>117</v>
@@ -5413,7 +5425,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>121</v>
@@ -5445,7 +5457,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>126</v>
@@ -5477,7 +5489,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>131</v>
@@ -5509,7 +5521,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>135</v>
@@ -5527,7 +5539,7 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>156</v>
@@ -5541,7 +5553,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>139</v>
@@ -5573,7 +5585,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>143</v>
@@ -5605,7 +5617,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>148</v>
@@ -5637,7 +5649,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>152</v>
@@ -5669,7 +5681,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
@@ -5701,7 +5713,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
@@ -5733,7 +5745,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
@@ -5765,7 +5777,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
@@ -5797,7 +5809,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>176</v>
@@ -5829,7 +5841,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>180</v>
@@ -5861,7 +5873,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
@@ -5893,7 +5905,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
@@ -5925,7 +5937,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>195</v>
@@ -5957,10 +5969,10 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>384</v>
@@ -5975,7 +5987,7 @@
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>183</v>
@@ -5989,7 +6001,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>202</v>
@@ -6021,7 +6033,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>206</v>
@@ -6053,10 +6065,10 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>393</v>
@@ -6085,10 +6097,10 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>396</v>
@@ -6202,7 +6214,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
@@ -6229,12 +6241,12 @@
         <v>402</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
@@ -6261,12 +6273,12 @@
         <v>405</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>92</v>
@@ -6293,12 +6305,12 @@
         <v>408</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
@@ -6325,12 +6337,12 @@
         <v>411</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>102</v>
@@ -6357,12 +6369,12 @@
         <v>414</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>108</v>
@@ -6389,12 +6401,12 @@
         <v>417</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>113</v>
@@ -6421,12 +6433,12 @@
         <v>420</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>117</v>
@@ -6453,12 +6465,12 @@
         <v>423</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>121</v>
@@ -6485,12 +6497,12 @@
         <v>426</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>126</v>
@@ -6517,76 +6529,76 @@
         <v>429</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>430</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>430</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>174</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>156</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>432</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>432</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>434</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>139</v>
@@ -6613,12 +6625,12 @@
         <v>437</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>143</v>
@@ -6645,12 +6657,12 @@
         <v>440</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>148</v>
@@ -6677,12 +6689,12 @@
         <v>443</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>152</v>
@@ -6709,12 +6721,12 @@
         <v>446</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
@@ -6741,12 +6753,12 @@
         <v>449</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
@@ -6773,12 +6785,12 @@
         <v>452</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
@@ -6805,12 +6817,12 @@
         <v>455</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
@@ -6837,12 +6849,12 @@
         <v>458</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>176</v>
@@ -6869,12 +6881,12 @@
         <v>461</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>180</v>
@@ -6901,12 +6913,12 @@
         <v>464</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
@@ -6933,12 +6945,12 @@
         <v>467</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
@@ -6965,12 +6977,12 @@
         <v>470</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>195</v>
@@ -6997,15 +7009,15 @@
         <v>473</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>474</v>
@@ -7029,12 +7041,12 @@
         <v>476</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>202</v>
@@ -7061,12 +7073,12 @@
         <v>479</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>206</v>
@@ -7093,15 +7105,15 @@
         <v>482</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>483</v>
@@ -7125,15 +7137,15 @@
         <v>486</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>487</v>
@@ -7157,7 +7169,7 @@
         <v>489</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -7247,7 +7259,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
@@ -7279,7 +7291,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
@@ -7311,7 +7323,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>92</v>
@@ -7343,16 +7355,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>499</v>
@@ -7364,7 +7376,7 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>500</v>
@@ -7375,7 +7387,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>102</v>
@@ -7407,7 +7419,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>108</v>
@@ -7439,7 +7451,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>113</v>
@@ -7471,7 +7483,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>117</v>
@@ -7503,7 +7515,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>121</v>
@@ -7535,7 +7547,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>126</v>
@@ -7567,7 +7579,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>131</v>
@@ -7585,10 +7597,10 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>521</v>
@@ -7599,7 +7611,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>135</v>
@@ -7617,10 +7629,10 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>524</v>
@@ -7631,7 +7643,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>139</v>
@@ -7663,7 +7675,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>143</v>
@@ -7695,7 +7707,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>148</v>
@@ -7727,7 +7739,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>152</v>
@@ -7759,7 +7771,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
@@ -7791,7 +7803,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
@@ -7809,10 +7821,10 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>542</v>
@@ -7823,7 +7835,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
@@ -7841,10 +7853,10 @@
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>545</v>
@@ -7855,7 +7867,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
@@ -7873,10 +7885,10 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>548</v>
@@ -7887,7 +7899,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>176</v>
@@ -7905,10 +7917,10 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>551</v>
@@ -7919,7 +7931,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>180</v>
@@ -7951,7 +7963,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
@@ -7983,7 +7995,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
@@ -8015,7 +8027,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>195</v>
@@ -8047,10 +8059,10 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>564</v>
@@ -8079,7 +8091,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>202</v>
@@ -8111,7 +8123,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>206</v>
@@ -8143,10 +8155,10 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>573</v>
@@ -8175,10 +8187,10 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>576</v>
@@ -8254,7 +8266,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8292,16 +8304,16 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>579</v>
@@ -8313,10 +8325,10 @@
         <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>219</v>
+        <v>580</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8324,19 +8336,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -8348,7 +8360,7 @@
         <v>146</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8356,19 +8368,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -8380,7 +8392,7 @@
         <v>165</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8388,19 +8400,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -8412,7 +8424,7 @@
         <v>299</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8420,19 +8432,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -8444,7 +8456,7 @@
         <v>299</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8452,19 +8464,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -8476,7 +8488,7 @@
         <v>299</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8484,19 +8496,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -8508,7 +8520,7 @@
         <v>299</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8516,19 +8528,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -8540,7 +8552,7 @@
         <v>299</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8548,19 +8560,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -8572,7 +8584,7 @@
         <v>485</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8580,19 +8592,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -8604,7 +8616,7 @@
         <v>398</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8612,19 +8624,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -8636,7 +8648,7 @@
         <v>398</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8644,28 +8656,28 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>613</v>
+        <v>398</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>614</v>
@@ -8676,7 +8688,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>139</v>
@@ -8694,13 +8706,13 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>398</v>
+        <v>617</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8708,31 +8720,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8740,19 +8752,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -8761,10 +8773,10 @@
         <v>235</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8772,28 +8784,28 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>627</v>
@@ -8804,7 +8816,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
@@ -8836,7 +8848,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
@@ -8857,10 +8869,10 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8868,19 +8880,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -8889,10 +8901,10 @@
         <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8900,19 +8912,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -8921,10 +8933,10 @@
         <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8932,19 +8944,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -8953,10 +8965,10 @@
         <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8964,19 +8976,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -8985,10 +8997,10 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8996,19 +9008,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -9017,10 +9029,10 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9028,19 +9040,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -9049,10 +9061,10 @@
         <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9060,19 +9072,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -9081,10 +9093,10 @@
         <v>129</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9092,19 +9104,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -9113,10 +9125,10 @@
         <v>129</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9124,19 +9136,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -9145,10 +9157,10 @@
         <v>129</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9156,19 +9168,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -9177,10 +9189,10 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9224,7 +9236,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -9271,19 +9283,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -9295,7 +9307,7 @@
         <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9303,7 +9315,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
@@ -9315,7 +9327,7 @@
         <v>70</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>164</v>
@@ -9327,7 +9339,7 @@
         <v>165</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9335,19 +9347,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -9356,10 +9368,10 @@
         <v>235</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>398</v>
+        <v>485</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9367,19 +9379,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -9391,7 +9403,7 @@
         <v>299</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9399,19 +9411,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -9420,10 +9432,10 @@
         <v>89</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9431,19 +9443,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -9455,7 +9467,7 @@
         <v>398</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9463,19 +9475,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -9484,10 +9496,10 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9495,19 +9507,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -9519,7 +9531,7 @@
         <v>485</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9527,19 +9539,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -9548,10 +9560,10 @@
         <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9559,19 +9571,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -9580,10 +9592,10 @@
         <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>626</v>
+        <v>398</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9591,28 +9603,28 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>699</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>700</v>
@@ -9623,7 +9635,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>135</v>
@@ -9641,13 +9653,13 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>703</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9655,31 +9667,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9687,31 +9699,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>266</v>
+        <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9719,31 +9731,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>124</v>
+        <v>269</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9751,19 +9763,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -9772,10 +9784,10 @@
         <v>124</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>659</v>
+        <v>633</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9783,19 +9795,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -9804,10 +9816,10 @@
         <v>193</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9815,19 +9827,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -9836,10 +9848,10 @@
         <v>124</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9847,31 +9859,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9879,31 +9891,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>235</v>
+        <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9911,31 +9923,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>89</v>
+        <v>235</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9943,19 +9955,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -9964,10 +9976,10 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9975,19 +9987,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -9996,10 +10008,10 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10007,31 +10019,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10039,19 +10051,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -10060,10 +10072,10 @@
         <v>124</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10071,19 +10083,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -10092,10 +10104,10 @@
         <v>124</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10103,28 +10115,28 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>749</v>
@@ -10135,7 +10147,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>206</v>
@@ -10156,10 +10168,10 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10167,19 +10179,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -10188,17 +10200,49 @@
         <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>666</v>
+        <v>752</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -10229,6 +10273,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -11,8 +11,8 @@
     <sheet name="설묘" sheetId="2" r:id="rId2"/>
     <sheet name="셀린느" sheetId="3" r:id="rId3"/>
     <sheet name="HERMES" sheetId="4" r:id="rId4"/>
-    <sheet name="유니크" sheetId="5" r:id="rId5"/>
-    <sheet name="빠따" sheetId="6" r:id="rId6"/>
+    <sheet name="빠따" sheetId="5" r:id="rId5"/>
+    <sheet name="유니크" sheetId="6" r:id="rId6"/>
     <sheet name="CRES" sheetId="7" r:id="rId7"/>
     <sheet name="TRIUMPH" sheetId="8" r:id="rId8"/>
   </sheets>
@@ -21,17 +21,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">HERMES!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">빠따!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">빠따!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">유니크!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">유니크!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="757">
   <si>
     <t>guild_name</t>
   </si>
@@ -156,6 +156,27 @@
     <t>명탐젓코난</t>
   </si>
   <si>
+    <t>빠따</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>541경 4853조 3239억 949만</t>
+  </si>
+  <si>
+    <t>매너친목아닌길드</t>
+  </si>
+  <si>
+    <t>o원기o</t>
+  </si>
+  <si>
     <t>유니크</t>
   </si>
   <si>
@@ -180,27 +201,6 @@
     <t>동땅이</t>
   </si>
   <si>
-    <t>빠따</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>541경 4853조 3239억 949만</t>
-  </si>
-  <si>
-    <t>매너친목아닌길드</t>
-  </si>
-  <si>
-    <t>o원기o</t>
-  </si>
-  <si>
     <t>CRES</t>
   </si>
   <si>
@@ -306,7 +306,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>127경 9398조 8573억 4847만</t>
+    <t>148경 7016조 6804억 294만</t>
   </si>
   <si>
     <t>3</t>
@@ -336,7 +336,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>40경 9302조 8286억 6262만</t>
+    <t>122</t>
+  </si>
+  <si>
+    <t>46경 9293조 376억 9117만</t>
   </si>
   <si>
     <t>5</t>
@@ -366,10 +369,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>34경 3801조 8477억 2219만</t>
+    <t>35경 8908조 6008억 7035만</t>
   </si>
   <si>
     <t>7</t>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>30경 3935조 631억 9583만</t>
+    <t>33경 7936조 9525억 5868만</t>
   </si>
   <si>
     <t>8</t>
@@ -393,7 +393,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
   </si>
   <si>
-    <t>27경 5354조 8887억 3874만</t>
+    <t>28경 2483조 7576억 982만</t>
   </si>
   <si>
     <t>9</t>
@@ -435,7 +435,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>13경 4975조 4851억 7583만</t>
+    <t>14경 1267조 3726억 2157만</t>
   </si>
   <si>
     <t>12</t>
@@ -459,7 +459,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>11경 2284조 7629억 3908만</t>
+    <t>11경 9957조 1699억 8930만</t>
   </si>
   <si>
     <t>14</t>
@@ -486,7 +486,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>6경 8149조 5923억 707만</t>
+    <t>7경 89조 7733억 1129만</t>
   </si>
   <si>
     <t>16</t>
@@ -516,7 +516,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
   </si>
   <si>
-    <t>5경 2230조 4268억 1822만</t>
+    <t>5경 4783조 8696억 6956만</t>
   </si>
   <si>
     <t>18</t>
@@ -543,7 +543,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>4경 3643조 5234억 1086만</t>
+    <t>4경 4375조 2811억 5421만</t>
   </si>
   <si>
     <t>20</t>
@@ -558,7 +558,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>3경 2534조 9024억 7216만</t>
+    <t>3경 6397조 2369억 447만</t>
   </si>
   <si>
     <t>21</t>
@@ -570,7 +570,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
   </si>
   <si>
-    <t>2경 903조 2186억 8410만</t>
+    <t>2경 2764조 5614억 4717만</t>
   </si>
   <si>
     <t>22</t>
@@ -582,52 +582,52 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
   </si>
   <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1경 9013조 8299억 3542만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>설앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>1경 5321조 4698억 3495만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>설치지마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EC%A7%80%EB%A7%88</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1경 4130조 1863억 7189만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>공룡박사원이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%A3%A1%EB%B0%95%EC%82%AC%EC%9B%90%EC%9D%B4</t>
+  </si>
+  <si>
     <t>115</t>
   </si>
   <si>
-    <t>1경 6169조 6284억 1304만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>설앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>1경 3569조 9243억 6675만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>설치지마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EC%A7%80%EB%A7%88</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1경 3284조 7758억 2759만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>공룡박사원이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%A3%A1%EB%B0%95%EC%82%AC%EC%9B%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1경 1008조 8977억 2613만</t>
+    <t>1경 1024조 8222억 2261만</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -660,7 +660,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>7510조 8126억 8889만</t>
+    <t>8078조 6502억 2066만</t>
   </si>
   <si>
     <t>양촌마을</t>
@@ -669,7 +669,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B4%8C%EB%A7%88%EC%9D%84</t>
   </si>
   <si>
-    <t>6095조 9324억 3963만</t>
+    <t>6571조 6510억 9833만</t>
   </si>
   <si>
     <t>30</t>
@@ -681,7 +681,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%97%A4%EB%B8%90%EC%9E%89</t>
   </si>
   <si>
-    <t>5060조 6323억 5555만</t>
+    <t>5567조 4268억 7808만</t>
   </si>
   <si>
     <t>빔냥이</t>
@@ -702,7 +702,7 @@
     <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
   </si>
   <si>
-    <t>58경 4001조 2779억 5325만</t>
+    <t>64경 4217조 575억 9009만</t>
   </si>
   <si>
     <t>진자이</t>
@@ -711,7 +711,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>53경 625조 5653억 3480만</t>
+    <t>55경 4363조 3706억 9167만</t>
   </si>
   <si>
     <t>돈스</t>
@@ -720,7 +720,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>48경 1083조 794억 4056만</t>
+    <t>55경 2525조 6218억 1334만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -729,7 +729,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>40경 4809조 4569억 7661만</t>
+    <t>41경 7711조 7799억 3444만</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>23경 6378조 9억 8238만</t>
+  </si>
+  <si>
+    <t>뽀리빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>23경 6194조 6186억 7365만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -744,31 +762,13 @@
     <t>23경 5452조 8627억 4888만</t>
   </si>
   <si>
-    <t>뽀리빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>22경 2897조 9622억 4868만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>22경 2364조 9461억 5527만</t>
-  </si>
-  <si>
     <t>부엉이형</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>12경 2879조 2905억 3861만</t>
+    <t>12경 4509조 2134억 7835만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -777,7 +777,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>9경 3208조 1900억 1331만</t>
+    <t>10경 280조 6073억 2728만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>9경 7717조 5279억 6925만</t>
   </si>
   <si>
     <t>국의</t>
@@ -786,16 +795,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>8경 6293조 6296억 417만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>8경 5425조 4820억 9586만</t>
+    <t>8경 6777조 8160억 7603만</t>
   </si>
   <si>
     <t>천천히걸어가</t>
@@ -804,7 +804,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
   </si>
   <si>
-    <t>7경 8521조 7245억 5404만</t>
+    <t>8경 32조 5919억 4407만</t>
+  </si>
+  <si>
+    <t>밉상b</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
+  </si>
+  <si>
+    <t>7경 6310조 4728억 1122만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -816,22 +825,13 @@
     <t>7경 3059조 933억 2511만</t>
   </si>
   <si>
-    <t>밉상b</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
-  </si>
-  <si>
-    <t>7경 145조 793억 7358만</t>
-  </si>
-  <si>
     <t>하후돈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>6경 7507조 6793억 8682만</t>
+    <t>7경 2264조 8746억 6831만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -843,7 +843,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>6경 5572조 9054억 2021만</t>
+    <t>6경 7680조 2331억 1997만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -861,7 +861,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>5경 6355조 5541억 4319만</t>
+    <t>5경 8342조 1557억 9929만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -879,7 +879,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
   </si>
   <si>
-    <t>4경 6208조 3978억 9628만</t>
+    <t>4경 7757조 7936억 9566만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -888,7 +888,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>1경 5432조 1524억 327만</t>
+    <t>1경 7102조 8495억 2595만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>1경 5351조 1664억 8613만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -900,22 +909,13 @@
     <t>1경 5275조 752억 3008만</t>
   </si>
   <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>1경 5042조 8838억 8041만</t>
-  </si>
-  <si>
     <t>프리프리</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>1경 2844조 9014억 2537만</t>
+    <t>1경 3944조 7727억 1715만</t>
   </si>
   <si>
     <t>익맹</t>
@@ -924,7 +924,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
   </si>
   <si>
-    <t>1경 84조 5679억 4324만</t>
+    <t>1경 2718조 2674억 5593만</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 14조 9938억 1255만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>9468조 2895억 2411만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
@@ -936,24 +954,6 @@
     <t>8944조 2540억 2789만</t>
   </si>
   <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>8488조 7335억 2631만</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>8263조 3641억 1604만</t>
-  </si>
-  <si>
     <t>제로슈가</t>
   </si>
   <si>
@@ -969,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%A5%EC%BB%A4</t>
   </si>
   <si>
-    <t>160경 368조 1168억 858만</t>
+    <t>164경 8200조 4244억 1892만</t>
   </si>
   <si>
     <t>적금묶인린풍</t>
@@ -978,7 +978,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EA%B8%88%EB%AC%B6%EC%9D%B8%EB%A6%B0%ED%92%8D</t>
   </si>
   <si>
-    <t>114경 187조 2032억 9841만</t>
+    <t>117경 1645조 8375억 9144만</t>
   </si>
   <si>
     <t>야느</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%83%90%EC%A0%93%EC%BD%94%EB%82%9C</t>
   </si>
   <si>
-    <t>53경 7558조 8546억 2362만</t>
+    <t>55경 5604조 3936억 7586만</t>
   </si>
   <si>
     <t>닐쿵</t>
@@ -1020,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%ED%8F%89%EA%B2%AC</t>
   </si>
   <si>
-    <t>33경 6845조 6962억 8158만</t>
+    <t>33경 8875조 6217억 640만</t>
   </si>
   <si>
     <t>돈슨환불하라</t>
@@ -1029,16 +1029,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A8%ED%99%98%EB%B6%88%ED%95%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>16경 5740조 1366억 190만</t>
-  </si>
-  <si>
-    <t>쁘헬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%81%98%ED%97%AC</t>
-  </si>
-  <si>
-    <t>9경 265조 4706억 783만</t>
+    <t>17경 2조 7391억 1560만</t>
+  </si>
+  <si>
+    <t>김취야호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B7%A8%EC%95%BC%ED%98%B8</t>
+  </si>
+  <si>
+    <t>10경 5657조 198억 2889만</t>
   </si>
   <si>
     <t>랍아</t>
@@ -1047,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8D%EC%95%84</t>
   </si>
   <si>
-    <t>8경 484조 5483억 3368만</t>
+    <t>8경 1324조 6362억 5088만</t>
   </si>
   <si>
     <t>월하의밤</t>
@@ -1065,7 +1065,7 @@
     <t>https://mgf.gg/contents/character.php?n=Tyrael</t>
   </si>
   <si>
-    <t>5경 6104조 766억 2522만</t>
+    <t>5경 7736조 9265억 3857만</t>
   </si>
   <si>
     <t>랏운</t>
@@ -1074,7 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%EC%9A%B4</t>
   </si>
   <si>
-    <t>4경 4379조 5496억 2571만</t>
+    <t>4경 9987조 4496억 4082만</t>
   </si>
   <si>
     <t>육퇴한아빠</t>
@@ -1083,7 +1083,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A1%ED%87%B4%ED%95%9C%EC%95%84%EB%B9%A0</t>
   </si>
   <si>
-    <t>4경 1367조 7381억 1866만</t>
+    <t>4경 1639조 2573억 4608만</t>
   </si>
   <si>
     <t>분평</t>
@@ -1092,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%84%ED%8F%89</t>
   </si>
   <si>
-    <t>3경 97조 803억 1885만</t>
+    <t>3경 1743조 1350억 8364만</t>
   </si>
   <si>
     <t>노건</t>
@@ -1101,7 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EA%B1%B4</t>
   </si>
   <si>
-    <t>2경 7356조 3612억 5503만</t>
+    <t>2경 8780조 3059억 5046만</t>
   </si>
   <si>
     <t>샤샤엘</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A8%EC%94%A8</t>
   </si>
   <si>
-    <t>2경 2620조 6420억 2041만</t>
+    <t>2경 3424조 1137억 7785만</t>
   </si>
   <si>
     <t>수냬</t>
@@ -1128,7 +1128,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%83%AC</t>
   </si>
   <si>
-    <t>1경 8073조 316억 2225만</t>
+    <t>1경 8838조 1918억 4815만</t>
   </si>
   <si>
     <t>일하</t>
@@ -1137,7 +1137,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%ED%95%98</t>
   </si>
   <si>
-    <t>1경 6666조 6912억 7835만</t>
+    <t>1경 7109조 1524억 5809만</t>
+  </si>
+  <si>
+    <t>새콤달콤해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EC%BD%A4%EB%8B%AC%EC%BD%A4%ED%95%B4</t>
+  </si>
+  <si>
+    <t>1경 2282조 9138억 1769만</t>
   </si>
   <si>
     <t>딸기껌</t>
@@ -1146,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EA%BB%8C</t>
   </si>
   <si>
-    <t>1경 1370조 8354억 5342만</t>
+    <t>1경 1705조 216억 2730만</t>
   </si>
   <si>
     <t>열도</t>
@@ -1155,16 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>1경 1152조 3255억 995만</t>
-  </si>
-  <si>
-    <t>새콤달콤해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EC%BD%A4%EB%8B%AC%EC%BD%A4%ED%95%B4</t>
-  </si>
-  <si>
-    <t>1경 501조 6231억 898만</t>
+    <t>1경 1198조 9025억 9658만</t>
   </si>
   <si>
     <t>장홍</t>
@@ -1173,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%99%8D</t>
   </si>
   <si>
-    <t>8915조 9516억 22만</t>
+    <t>8943조 7860억 9399만</t>
   </si>
   <si>
     <t>칸델</t>
@@ -1182,7 +1182,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%B8%EB%8D%B8</t>
   </si>
   <si>
-    <t>7854조 5403억 3321만</t>
+    <t>8013조 6168억 463만</t>
+  </si>
+  <si>
+    <t>주해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%B4</t>
+  </si>
+  <si>
+    <t>7836조 8193억 4414만</t>
   </si>
   <si>
     <t>고양이확대범</t>
@@ -1191,16 +1200,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%96%91%EC%9D%B4%ED%99%95%EB%8C%80%EB%B2%94</t>
   </si>
   <si>
-    <t>7181조 2079억 9766만</t>
-  </si>
-  <si>
-    <t>주해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%B4</t>
-  </si>
-  <si>
-    <t>6956조 3364억 2106만</t>
+    <t>7452조 3039억 2171만</t>
   </si>
   <si>
     <t>햄마요</t>
@@ -1227,636 +1227,627 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%B4%EB%A3%A8</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1793조 1252억 4947만</t>
+  </si>
+  <si>
+    <t>다씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%94%A8</t>
+  </si>
+  <si>
+    <t>228경 3744조 4229억 2046만</t>
+  </si>
+  <si>
+    <t>라온MS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
+  </si>
+  <si>
+    <t>178경 6628조 7559억 4369만</t>
+  </si>
+  <si>
+    <t>요르v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
+  </si>
+  <si>
+    <t>30경 6018조 6237억 3856만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
+  </si>
+  <si>
+    <t>23경 6880조 9868억 9798만</t>
+  </si>
+  <si>
+    <t>장짱맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A7%B1%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>21경 6693조 798억 5447만</t>
+  </si>
+  <si>
+    <t>쾌변한춘향</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EB%B3%80%ED%95%9C%EC%B6%98%ED%96%A5</t>
+  </si>
+  <si>
+    <t>16경 8983조 104억 677만</t>
+  </si>
+  <si>
+    <t>꽁칟뿡야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%9F%EB%BF%A1%EC%95%BC</t>
+  </si>
+  <si>
+    <t>11경 2345조 7006억 1544만</t>
+  </si>
+  <si>
+    <t>o엉댕o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
+  </si>
+  <si>
+    <t>7경 5552조 9553억 7210만</t>
+  </si>
+  <si>
+    <t>매쵸맛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%B5%B8%EB%A7%9B</t>
+  </si>
+  <si>
+    <t>5경 3053조 942억 4766만</t>
+  </si>
+  <si>
+    <t>설편</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%8E%B8</t>
+  </si>
+  <si>
+    <t>4경 5989조 8691억 6867만</t>
+  </si>
+  <si>
+    <t>여수로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%88%98%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>3경 544조 7051억 6224만</t>
+  </si>
+  <si>
+    <t>o후국o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
+  </si>
+  <si>
+    <t>2경 8526조 1391억 6769만</t>
+  </si>
+  <si>
+    <t>o진이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>2경 8284조 7504억 9727만</t>
+  </si>
+  <si>
+    <t>김규평</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B7%9C%ED%8F%89</t>
+  </si>
+  <si>
+    <t>2경 7089조 3601억 2658만</t>
+  </si>
+  <si>
+    <t>이원일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>2경 6911조 1474억 4475만</t>
+  </si>
+  <si>
+    <t>사단장님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%8B%A8%EC%9E%A5%EB%8B%98</t>
+  </si>
+  <si>
+    <t>2경 2683조 7644억 1125만</t>
+  </si>
+  <si>
+    <t>o볼륨o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B3%BC%EB%A5%A8o</t>
+  </si>
+  <si>
+    <t>2경 687조 4032억 7790만</t>
+  </si>
+  <si>
+    <t>후니와동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>1경 9273조 829억 522만</t>
+  </si>
+  <si>
+    <t>떠웅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EC%9B%85</t>
+  </si>
+  <si>
+    <t>1경 7859조 8721억 3862만</t>
+  </si>
+  <si>
+    <t>멩구v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%A9%EA%B5%ACv</t>
+  </si>
+  <si>
+    <t>1경 5406조 504억 5558만</t>
+  </si>
+  <si>
+    <t>화욤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
+  </si>
+  <si>
+    <t>1경 4875조 1822억 2534만</t>
+  </si>
+  <si>
+    <t>호이호이포이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1경 2295조 4757억 5582만</t>
+  </si>
+  <si>
+    <t>o아윤o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%95%84%EC%9C%A4o</t>
+  </si>
+  <si>
+    <t>9167조 2934억 5110만</t>
+  </si>
+  <si>
+    <t>뭥끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
+  </si>
+  <si>
+    <t>9073조 6965억 2569만</t>
+  </si>
+  <si>
+    <t>FFFK</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=FFFK</t>
+  </si>
+  <si>
+    <t>8656조 2699억 1299만</t>
+  </si>
+  <si>
+    <t>옹이잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%9D%B4%EC%9E%89</t>
+  </si>
+  <si>
+    <t>7861조 2137억 6072만</t>
+  </si>
+  <si>
+    <t>담훌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
+  </si>
+  <si>
+    <t>4722조 7330억 5332만</t>
+  </si>
+  <si>
+    <t>겨울난방</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
+  </si>
+  <si>
+    <t>4612조 813억 2711만</t>
+  </si>
+  <si>
+    <t>건들면혼남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%93%A4%EB%A9%B4%ED%98%BC%EB%82%A8</t>
+  </si>
+  <si>
+    <t>4379조 7993억 6587만</t>
+  </si>
+  <si>
+    <t>보마할래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>2961조 4012억 1670만</t>
+  </si>
+  <si>
+    <t>차김치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EA%B9%80%EC%B9%98</t>
+  </si>
+  <si>
+    <t>263경 1264조 6831억 1942만</t>
+  </si>
+  <si>
+    <t>낌완두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%8C%EC%99%84%EB%91%90</t>
+  </si>
+  <si>
+    <t>126경 8245조 877억 6439만</t>
+  </si>
+  <si>
+    <t>쌀만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>103경 3832조 4149억 326만</t>
+  </si>
+  <si>
+    <t>호호딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%ED%98%B8%EB%94%98</t>
+  </si>
+  <si>
+    <t>22경 6752조 4345억 3803만</t>
+  </si>
+  <si>
+    <t>우땨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%95%A8</t>
+  </si>
+  <si>
+    <t>13경 6065조 8576억 7344만</t>
+  </si>
+  <si>
+    <t>엘픽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%ED%94%BD</t>
+  </si>
+  <si>
+    <t>12경 2723조 780억 5934만</t>
+  </si>
+  <si>
+    <t>차수진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EC%88%98%EC%A7%84</t>
+  </si>
+  <si>
+    <t>11경 5243조 7484억 6548만</t>
+  </si>
+  <si>
+    <t>임씬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%94%AC</t>
+  </si>
+  <si>
+    <t>8경 540조 3712억 1485만</t>
+  </si>
+  <si>
+    <t>겐미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%90%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>6경 406조 9177억 7251만</t>
+  </si>
+  <si>
+    <t>텨숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%A8%EC%88%8D</t>
+  </si>
+  <si>
+    <t>5경 3091조 1746억 9095만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%95%85%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4경 3474조 3132억 749만</t>
+  </si>
+  <si>
+    <t>승질승</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%A7%88%EC%8A%B9</t>
+  </si>
+  <si>
+    <t>4경 586조 4035억 8300만</t>
+  </si>
+  <si>
+    <t>보레아스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A0%88%EC%95%84%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>2경 1485조 7176억 442만</t>
+  </si>
+  <si>
+    <t>뉴비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>2경 1078조 45억 8305만</t>
+  </si>
+  <si>
+    <t>서먕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%A8%95</t>
+  </si>
+  <si>
+    <t>2경 938조 9137억 4771만</t>
+  </si>
+  <si>
+    <t>향연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%A5%EC%97%B0</t>
+  </si>
+  <si>
+    <t>2경 602조 8417억 2281만</t>
+  </si>
+  <si>
+    <t>일등통신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EB%93%B1%ED%86%B5%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>2경 366조 909억 7624만</t>
+  </si>
+  <si>
+    <t>정령성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%A0%B9%EC%84%B1</t>
+  </si>
+  <si>
+    <t>1경 6333조 7647억 8373만</t>
+  </si>
+  <si>
+    <t>DAEBAK</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=DAEBAK</t>
+  </si>
+  <si>
+    <t>1경 4224조 883억 6307만</t>
+  </si>
+  <si>
+    <t>벞벞</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%9E%EB%B2%9E</t>
+  </si>
+  <si>
+    <t>1경 2189조 8683억 18만</t>
+  </si>
+  <si>
+    <t>쌉새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
+  </si>
+  <si>
+    <t>1경 513조 2367억 9292만</t>
+  </si>
+  <si>
+    <t>우탸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%B8</t>
+  </si>
+  <si>
+    <t>1경 64조 5452억 8788만</t>
+  </si>
+  <si>
+    <t>퍌라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%8C%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>6867조 1697억 3934만</t>
+  </si>
+  <si>
+    <t>띠디는띠디야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EB%94%94%EB%8A%94%EB%9D%A0%EB%94%94%EC%95%BC</t>
+  </si>
+  <si>
+    <t>6721조 4821억 5548만</t>
+  </si>
+  <si>
+    <t>마류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A5%98</t>
+  </si>
+  <si>
+    <t>6198조 287억 3288만</t>
+  </si>
+  <si>
+    <t>뚱뚱쉰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%EB%9A%B1%EC%89%B0</t>
+  </si>
+  <si>
+    <t>5112조 4521억 9686만</t>
+  </si>
+  <si>
+    <t>댤타냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%A4%ED%83%80%EB%83%A5</t>
+  </si>
+  <si>
+    <t>5080조 9923억 7302만</t>
+  </si>
+  <si>
+    <t>컈컈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%88%EC%BB%88</t>
+  </si>
+  <si>
+    <t>3960조 8132억 2490만</t>
+  </si>
+  <si>
+    <t>랜더스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9E%9C%EB%8D%94%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>3784조 5298억 7458만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A6%ACc</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>480경 8704조 1129억 8868만</t>
+  </si>
+  <si>
+    <t>김승관</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B9%EA%B4%80</t>
+  </si>
+  <si>
+    <t>20경 5291조 5659억 4363만</t>
+  </si>
+  <si>
+    <t>황서정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EC%84%9C%EC%A0%95</t>
+  </si>
+  <si>
+    <t>4경 3389조 6009억 739만</t>
+  </si>
+  <si>
+    <t>yullmu</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=yullmu</t>
+  </si>
+  <si>
+    <t>1경 1540조 8150억 8634만</t>
+  </si>
+  <si>
+    <t>황룹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EB%A3%B9</t>
+  </si>
+  <si>
+    <t>8990조 4799억 6435만</t>
+  </si>
+  <si>
+    <t>서공윤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EA%B3%B5%EC%9C%A4</t>
+  </si>
+  <si>
+    <t>6865조 6013억 4097만</t>
+  </si>
+  <si>
+    <t>마크오브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%81%AC%EC%98%A4%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>5429조 1955억 7548만</t>
+  </si>
+  <si>
+    <t>압러</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%95%EB%9F%AC</t>
+  </si>
+  <si>
+    <t>4744조 7928억 2300만</t>
+  </si>
+  <si>
+    <t>라리v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A6%ACv</t>
+  </si>
+  <si>
+    <t>4431조 313억 7999만</t>
+  </si>
+  <si>
+    <t>사랑보다깊은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%EB%B3%B4%EB%8B%A4%EA%B9%8A%EC%9D%80</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>1605조 8055억 3676만</t>
-  </si>
-  <si>
-    <t>차김치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EA%B9%80%EC%B9%98</t>
-  </si>
-  <si>
-    <t>263경 1264조 6831억 1942만</t>
-  </si>
-  <si>
-    <t>낌완두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%8C%EC%99%84%EB%91%90</t>
-  </si>
-  <si>
-    <t>120경 8312조 3819억 6875만</t>
-  </si>
-  <si>
-    <t>쌀만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>103경 3832조 4149억 326만</t>
-  </si>
-  <si>
-    <t>호호딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%ED%98%B8%EB%94%98</t>
-  </si>
-  <si>
-    <t>22경 1380조 1868억 2011만</t>
-  </si>
-  <si>
-    <t>우땨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%95%A8</t>
-  </si>
-  <si>
-    <t>12경 9231조 2918억 3891만</t>
-  </si>
-  <si>
-    <t>차수진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EC%88%98%EC%A7%84</t>
-  </si>
-  <si>
-    <t>11경 5243조 7484억 6548만</t>
-  </si>
-  <si>
-    <t>엘픽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%ED%94%BD</t>
-  </si>
-  <si>
-    <t>11경 831조 2626억 6651만</t>
-  </si>
-  <si>
-    <t>임씬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%94%AC</t>
-  </si>
-  <si>
-    <t>8경 540조 3712억 1485만</t>
-  </si>
-  <si>
-    <t>겐미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%90%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>5경 6895조 3874억 1493만</t>
-  </si>
-  <si>
-    <t>텨숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%A8%EC%88%8D</t>
-  </si>
-  <si>
-    <t>4경 9694조 9731억 8905만</t>
-  </si>
-  <si>
-    <t>승질승</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%A7%88%EC%8A%B9</t>
-  </si>
-  <si>
-    <t>4경 239조 7442억 1924만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%95%85%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3경 9265조 5752억 5679만</t>
-  </si>
-  <si>
-    <t>보레아스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A0%88%EC%95%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>2경 947조 9879억 613만</t>
-  </si>
-  <si>
-    <t>향연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%A5%EC%97%B0</t>
-  </si>
-  <si>
-    <t>2경 602조 8417억 2281만</t>
-  </si>
-  <si>
-    <t>서먕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%A8%95</t>
-  </si>
-  <si>
-    <t>2경 238조 7198억 1087만</t>
-  </si>
-  <si>
-    <t>일등통신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EB%93%B1%ED%86%B5%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>1경 9920조 9348억 5758만</t>
-  </si>
-  <si>
-    <t>뉴비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>1경 9730조 9484억 8556만</t>
-  </si>
-  <si>
-    <t>정령성</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%A0%B9%EC%84%B1</t>
-  </si>
-  <si>
-    <t>1경 6007조 4327억 1703만</t>
-  </si>
-  <si>
-    <t>DAEBAK</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=DAEBAK</t>
-  </si>
-  <si>
-    <t>1경 3538조 9525억 7635만</t>
-  </si>
-  <si>
-    <t>벞벞</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%9E%EB%B2%9E</t>
-  </si>
-  <si>
-    <t>1경 2189조 8683억 18만</t>
-  </si>
-  <si>
-    <t>쌉새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
-  </si>
-  <si>
-    <t>1경 170조 9338억 7233만</t>
-  </si>
-  <si>
-    <t>도운</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9A%B4</t>
-  </si>
-  <si>
-    <t>1경 28조 2632억 9477만</t>
-  </si>
-  <si>
-    <t>우탸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%B8</t>
-  </si>
-  <si>
-    <t>9631조 3747억 3263만</t>
-  </si>
-  <si>
-    <t>퍌라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%8C%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>6494조 3597억 6931만</t>
-  </si>
-  <si>
-    <t>띠디는띠디야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EB%94%94%EB%8A%94%EB%9D%A0%EB%94%94%EC%95%BC</t>
-  </si>
-  <si>
-    <t>6332조 9019억 6604만</t>
-  </si>
-  <si>
-    <t>마류</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A5%98</t>
-  </si>
-  <si>
-    <t>5488조 1815억 1778만</t>
-  </si>
-  <si>
-    <t>뚱뚱쉰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%EB%9A%B1%EC%89%B0</t>
-  </si>
-  <si>
-    <t>4760조 7160억 6436만</t>
-  </si>
-  <si>
-    <t>댤타냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%A4%ED%83%80%EB%83%A5</t>
-  </si>
-  <si>
-    <t>4711조 5145억 248만</t>
-  </si>
-  <si>
-    <t>컈컈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%88%EC%BB%88</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>3455조 2927억 560만</t>
-  </si>
-  <si>
-    <t>랜더스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9E%9C%EB%8D%94%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3360조 1688억 8677만</t>
-  </si>
-  <si>
-    <t>다씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%94%A8</t>
-  </si>
-  <si>
-    <t>227경 441조 4254억 7501만</t>
-  </si>
-  <si>
-    <t>라온MS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8MS</t>
-  </si>
-  <si>
-    <t>178경 6628조 7559억 4369만</t>
-  </si>
-  <si>
-    <t>요르v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
-  </si>
-  <si>
-    <t>28경 6838조 9885억 6059만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
-  </si>
-  <si>
-    <t>22경 4031조 5032억 9603만</t>
-  </si>
-  <si>
-    <t>장짱맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A7%B1%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>21경 6693조 798억 5447만</t>
-  </si>
-  <si>
-    <t>쾌변한춘향</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EB%B3%80%ED%95%9C%EC%B6%98%ED%96%A5</t>
-  </si>
-  <si>
-    <t>15경 3581조 2295억 3076만</t>
-  </si>
-  <si>
-    <t>꽁칟뿡야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%9F%EB%BF%A1%EC%95%BC</t>
-  </si>
-  <si>
-    <t>9경 9711조 7551억 1995만</t>
-  </si>
-  <si>
-    <t>o엉댕o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
-  </si>
-  <si>
-    <t>7경 2882조 1295억 9353만</t>
-  </si>
-  <si>
-    <t>매쵸맛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%B5%B8%EB%A7%9B</t>
-  </si>
-  <si>
-    <t>4경 7149조 6273억 3016만</t>
-  </si>
-  <si>
-    <t>설편</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%8E%B8</t>
-  </si>
-  <si>
-    <t>4경 5420조 9162억 9652만</t>
-  </si>
-  <si>
-    <t>여수로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%88%98%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>2경 8646조 1583억 1624만</t>
-  </si>
-  <si>
-    <t>o후국o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
-  </si>
-  <si>
-    <t>2경 8526조 1391억 6769만</t>
-  </si>
-  <si>
-    <t>o진이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>2경 6876조 2208억 1712만</t>
-  </si>
-  <si>
-    <t>김규평</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B7%9C%ED%8F%89</t>
-  </si>
-  <si>
-    <t>2경 6634조 386억 972만</t>
-  </si>
-  <si>
-    <t>이원일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>2경 5562조 4957억 8805만</t>
-  </si>
-  <si>
-    <t>o볼륨o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B3%BC%EB%A5%A8o</t>
-  </si>
-  <si>
-    <t>2경 687조 4032억 7790만</t>
-  </si>
-  <si>
-    <t>떠웅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EC%9B%85</t>
-  </si>
-  <si>
-    <t>1경 7465조 9577억 9299만</t>
-  </si>
-  <si>
-    <t>후니와동동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
-  </si>
-  <si>
-    <t>1경 5364조 8821억 4359만</t>
-  </si>
-  <si>
-    <t>사단장님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%8B%A8%EC%9E%A5%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1경 5073조 4203억 9618만</t>
-  </si>
-  <si>
-    <t>화욤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
-  </si>
-  <si>
-    <t>1경 4875조 1822억 2534만</t>
-  </si>
-  <si>
-    <t>멩구v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%A9%EA%B5%ACv</t>
-  </si>
-  <si>
-    <t>1경 4589조 2742억 1441만</t>
-  </si>
-  <si>
-    <t>호이호이포이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1경 2295조 4757억 5582만</t>
-  </si>
-  <si>
-    <t>뭥끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
-  </si>
-  <si>
-    <t>8662조 7378억 2262만</t>
-  </si>
-  <si>
-    <t>FFFK</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=FFFK</t>
-  </si>
-  <si>
-    <t>8477조 3763억 8738만</t>
-  </si>
-  <si>
-    <t>옹이잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%9D%B4%EC%9E%89</t>
-  </si>
-  <si>
-    <t>7861조 2137억 6072만</t>
-  </si>
-  <si>
-    <t>o아윤o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%95%84%EC%9C%A4o</t>
-  </si>
-  <si>
-    <t>7189조 9197억 1131만</t>
-  </si>
-  <si>
-    <t>겨울난방</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
-  </si>
-  <si>
-    <t>4571조 4731억 4344만</t>
-  </si>
-  <si>
-    <t>담훌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
-  </si>
-  <si>
-    <t>4284조 7797억 2852만</t>
-  </si>
-  <si>
-    <t>건들면혼남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%93%A4%EB%A9%B4%ED%98%BC%EB%82%A8</t>
-  </si>
-  <si>
-    <t>3536조 6744억 759만</t>
-  </si>
-  <si>
-    <t>보마할래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>2961조 4012억 1670만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A6%ACc</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>470경 553조 4118억 9856만</t>
-  </si>
-  <si>
-    <t>김승관</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B9%EA%B4%80</t>
-  </si>
-  <si>
-    <t>20경 5291조 5659억 4363만</t>
-  </si>
-  <si>
-    <t>황서정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EC%84%9C%EC%A0%95</t>
-  </si>
-  <si>
-    <t>3경 8661조 6767억 6273만</t>
-  </si>
-  <si>
-    <t>yullmu</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=yullmu</t>
-  </si>
-  <si>
-    <t>1경 1346조 1232억 3236만</t>
-  </si>
-  <si>
-    <t>황룹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EB%A3%B9</t>
-  </si>
-  <si>
-    <t>8306조 1218억 3388만</t>
-  </si>
-  <si>
-    <t>서공윤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EA%B3%B5%EC%9C%A4</t>
-  </si>
-  <si>
-    <t>6616조 8441억 7855만</t>
-  </si>
-  <si>
-    <t>마크오브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%81%AC%EC%98%A4%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>5057조 3629억 8668만</t>
-  </si>
-  <si>
-    <t>압러</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%95%EB%9F%AC</t>
-  </si>
-  <si>
-    <t>4384조 9103억 9361만</t>
-  </si>
-  <si>
-    <t>라리v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A6%ACv</t>
-  </si>
-  <si>
-    <t>3881조 8359억 5964만</t>
-  </si>
-  <si>
-    <t>사랑보다깊은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%EB%B3%B4%EB%8B%A4%EA%B9%8A%EC%9D%80</t>
-  </si>
-  <si>
     <t>3693조 5419억 5365만</t>
   </si>
   <si>
@@ -1875,7 +1866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8D%EC%86%94</t>
   </si>
   <si>
-    <t>2114조 6997억 5264만</t>
+    <t>2208조 5103억 8375만</t>
   </si>
   <si>
     <t>콜리콜리</t>
@@ -1896,7 +1887,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EA%B5%A5a</t>
   </si>
   <si>
-    <t>1338조 875억 1870만</t>
+    <t>1428조 376억 3031만</t>
   </si>
   <si>
     <t>융챠</t>
@@ -1905,7 +1896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%B5%EC%B1%A0</t>
   </si>
   <si>
-    <t>1329조 8329억 9591만</t>
+    <t>1362조 3842억 3352만</t>
   </si>
   <si>
     <t>아라사랑해</t>
@@ -1914,7 +1905,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%9D%BC%EC%82%AC%EB%9E%91%ED%95%B4</t>
   </si>
   <si>
-    <t>1315조 2134억 1586만</t>
+    <t>1337조 7416억 7529만</t>
   </si>
   <si>
     <t>뮤내</t>
@@ -1944,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%9D%B4%EA%B1%B4</t>
   </si>
   <si>
-    <t>702조 1965억 9515만</t>
+    <t>710조 7661억 6846만</t>
   </si>
   <si>
     <t>다크홀리</t>
@@ -1953,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%81%AC%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>530조 6969억 1370만</t>
+    <t>600조 4395억 6763만</t>
   </si>
   <si>
     <t>룬보</t>
@@ -1962,7 +1953,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%AC%EB%B3%B4</t>
   </si>
   <si>
-    <t>486조 4330억 3942만</t>
+    <t>574조 3828억 9290만</t>
+  </si>
+  <si>
+    <t>Libere</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Libere</t>
+  </si>
+  <si>
+    <t>425조 4683억 7933만</t>
   </si>
   <si>
     <t>우주경</t>
@@ -1977,15 +1977,6 @@
     <t>414조 5422억 9225만</t>
   </si>
   <si>
-    <t>Libere</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Libere</t>
-  </si>
-  <si>
-    <t>393조 8758억 1169만</t>
-  </si>
-  <si>
     <t>현수컷</t>
   </si>
   <si>
@@ -1995,6 +1986,18 @@
     <t>313조 847억 5192만</t>
   </si>
   <si>
+    <t>손쨩1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%A8%A91</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>265조 3015억 9343만</t>
+  </si>
+  <si>
     <t>돈골대가</t>
   </si>
   <si>
@@ -2007,25 +2010,13 @@
     <t>251조 9335억 4895만</t>
   </si>
   <si>
-    <t>손쨩1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EC%A8%A91</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>231조 7307억 6382만</t>
-  </si>
-  <si>
     <t>겨울파파</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>207조 8449억 3960만</t>
+    <t>225조 8419억 6680만</t>
   </si>
   <si>
     <t>지니D</t>
@@ -2037,7 +2028,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>41조 4178억 5590만</t>
+    <t>44조 1669억 79만</t>
   </si>
   <si>
     <t>종리츄</t>
@@ -2046,13 +2037,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>802경 4154조 4736억 8898만</t>
+    <t>813경 3160조 9953억 1431만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
   </si>
   <si>
-    <t>14경 7725조 8407억 2846만</t>
+    <t>22경 378조 1155억 8268만</t>
   </si>
   <si>
     <t>몰라츄</t>
@@ -2061,7 +2052,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 7036조 3241억 9832만</t>
+    <t>2경 78조 7679억 9826만</t>
+  </si>
+  <si>
+    <t>정육츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 4306조 1767억 1749만</t>
   </si>
   <si>
     <t>가푸츄</t>
@@ -2070,16 +2070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>1경 762조 9596억 5662만</t>
-  </si>
-  <si>
-    <t>친절한정육</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EC%A0%88%ED%95%9C%EC%A0%95%EC%9C%A1</t>
-  </si>
-  <si>
-    <t>7049조 2038억 8628만</t>
+    <t>1경 2389조 2억 1625만</t>
   </si>
   <si>
     <t>수달츄</t>
@@ -2088,7 +2079,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>6063조 7111억 7030만</t>
+    <t>6301조 4850억 7338만</t>
+  </si>
+  <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2698조 6805억 2581만</t>
   </si>
   <si>
     <t>딤츄</t>
@@ -2097,16 +2097,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>2543조 1100억 8023만</t>
-  </si>
-  <si>
-    <t>파숙츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2410조 5237억 8213만</t>
+    <t>2663조 1265억 72만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2119조 3696억 1726만</t>
   </si>
   <si>
     <t>천상츄</t>
@@ -2115,7 +2115,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
   </si>
   <si>
-    <t>1706조 5042억 6230만</t>
+    <t>1989조 1895억 3262만</t>
   </si>
   <si>
     <t>유졍츄</t>
@@ -2124,16 +2124,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
   </si>
   <si>
-    <t>1660조 4582억 8500만</t>
-  </si>
-  <si>
-    <t>조림츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1418조 3994억 9351만</t>
+    <t>1723조 433억 3057만</t>
+  </si>
+  <si>
+    <t>화정삶</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%82%B6</t>
+  </si>
+  <si>
+    <t>1173조 521억 246만</t>
   </si>
   <si>
     <t>Dollmeng2</t>
@@ -2145,16 +2145,16 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1070조 4663억 6787만</t>
-  </si>
-  <si>
-    <t>화정삶</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%82%B6</t>
-  </si>
-  <si>
-    <t>1006조 9985억 2612만</t>
+    <t>1161조 5682억 8531만</t>
+  </si>
+  <si>
+    <t>산과바다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1016조 320억 9190만</t>
   </si>
   <si>
     <t>서전붕</t>
@@ -2166,13 +2166,13 @@
     <t>878조 8276억 5928만</t>
   </si>
   <si>
-    <t>산과바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>861조 5431억 9932만</t>
+    <t>현유수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
+  </si>
+  <si>
+    <t>814조 5910억 50만</t>
   </si>
   <si>
     <t>호야빵</t>
@@ -2184,22 +2184,22 @@
     <t>776조 4778억 6115만</t>
   </si>
   <si>
-    <t>현유수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
-  </si>
-  <si>
-    <t>680조 1186억 9588만</t>
-  </si>
-  <si>
     <t>푸들츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>668조 2040억 4833만</t>
+    <t>766조 8747억 65만</t>
+  </si>
+  <si>
+    <t>묘피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%ED%94%BC</t>
+  </si>
+  <si>
+    <t>450조 2034억 4621만</t>
   </si>
   <si>
     <t>루린츄</t>
@@ -2211,22 +2211,13 @@
     <t>429조 3663억 1715만</t>
   </si>
   <si>
-    <t>묘피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%ED%94%BC</t>
-  </si>
-  <si>
-    <t>404조 6599억 8631만</t>
-  </si>
-  <si>
     <t>뽀야츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>302조 7184억 4243만</t>
+    <t>316조 9037억 2355만</t>
   </si>
   <si>
     <t>하치츄</t>
@@ -2235,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B9%98%EC%B8%84</t>
   </si>
   <si>
-    <t>212조 5209억 1094만</t>
+    <t>250조 4329억 1064만</t>
   </si>
   <si>
     <t>히히힣히힣</t>
@@ -2244,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
   </si>
   <si>
-    <t>202조 890억 352만</t>
+    <t>211조 4233억 228만</t>
   </si>
   <si>
     <t>도리츄</t>
@@ -2253,7 +2244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>176조 5756억 9029만</t>
+    <t>192조 6708억 238만</t>
   </si>
   <si>
     <t>주냥츄</t>
@@ -2262,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
   </si>
   <si>
-    <t>163조 9275억 2518만</t>
+    <t>167조 6859억 872만</t>
   </si>
   <si>
     <t>디나인</t>
@@ -2271,7 +2262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%82%98%EC%9D%B8</t>
   </si>
   <si>
-    <t>132조 6475억 1963만</t>
+    <t>154조 153억 4607만</t>
   </si>
   <si>
     <t>새벽츄</t>
@@ -2301,7 +2292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
   </si>
   <si>
-    <t>44조 6701억 901만</t>
+    <t>46조 8776억 8949만</t>
   </si>
   <si>
     <t>피카츄십볼트</t>
@@ -2310,7 +2301,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%B4%EC%B8%84%EC%8B%AD%EB%B3%BC%ED%8A%B8</t>
   </si>
   <si>
-    <t>16조 9704억 4542만</t>
+    <t>17조 3674억 9491만</t>
   </si>
 </sst>
 </file>
@@ -2873,7 +2864,7 @@
         <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>29</v>
@@ -2882,39 +2873,39 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="M5" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>29</v>
@@ -2932,7 +2923,7 @@
         <v>55</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3196,10 +3187,10 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3210,28 +3201,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3242,16 +3233,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -3260,7 +3251,7 @@
         <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>112</v>
@@ -3388,7 +3379,7 @@
         <v>129</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>130</v>
@@ -3420,7 +3411,7 @@
         <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>134</v>
@@ -3452,7 +3443,7 @@
         <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>138</v>
@@ -3609,7 +3600,7 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>156</v>
@@ -3708,7 +3699,7 @@
         <v>174</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>175</v>
@@ -3804,10 +3795,10 @@
         <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3818,28 +3809,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3850,16 +3841,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -3868,7 +3859,7 @@
         <v>155</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>198</v>
@@ -3900,7 +3891,7 @@
         <v>155</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>201</v>
@@ -3932,7 +3923,7 @@
         <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>205</v>
@@ -3964,7 +3955,7 @@
         <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>209</v>
@@ -4028,7 +4019,7 @@
         <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>216</v>
@@ -4177,7 +4168,7 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>223</v>
@@ -4209,7 +4200,7 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>226</v>
@@ -4241,7 +4232,7 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>229</v>
@@ -4255,7 +4246,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>230</v>
@@ -4273,7 +4264,7 @@
         <v>89</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>232</v>
@@ -4287,7 +4278,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>233</v>
@@ -4302,13 +4293,13 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>33</v>
@@ -4322,25 +4313,25 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>33</v>
@@ -4354,19 +4345,19 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>96</v>
@@ -4433,7 +4424,7 @@
         <v>129</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>248</v>
@@ -4462,10 +4453,10 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>251</v>
@@ -4494,10 +4485,10 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>254</v>
@@ -4558,7 +4549,7 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>193</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>156</v>
@@ -4590,7 +4581,7 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>156</v>
@@ -4686,7 +4677,7 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>146</v>
@@ -4721,7 +4712,7 @@
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>276</v>
@@ -4817,7 +4808,7 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>285</v>
@@ -4849,7 +4840,7 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>288</v>
@@ -4863,7 +4854,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>289</v>
@@ -4881,7 +4872,7 @@
         <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>291</v>
@@ -4895,7 +4886,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>292</v>
@@ -4913,7 +4904,7 @@
         <v>155</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>294</v>
@@ -4945,7 +4936,7 @@
         <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>297</v>
@@ -4962,22 +4953,22 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>32</v>
+        <v>298</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>32</v>
+        <v>298</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>299</v>
+        <v>197</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>300</v>
@@ -5009,7 +5000,7 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>303</v>
@@ -5026,22 +5017,22 @@
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>183</v>
+        <v>305</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>306</v>
@@ -5073,7 +5064,7 @@
         <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>309</v>
@@ -5131,7 +5122,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5190,7 +5181,7 @@
         <v>129</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>312</v>
@@ -5222,7 +5213,7 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>315</v>
@@ -5254,7 +5245,7 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>318</v>
@@ -5300,7 +5291,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>321</v>
@@ -5315,10 +5306,10 @@
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>323</v>
@@ -5332,7 +5323,7 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -5350,7 +5341,7 @@
         <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>326</v>
@@ -5414,7 +5405,7 @@
         <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>332</v>
@@ -5446,7 +5437,7 @@
         <v>155</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>335</v>
@@ -5606,7 +5597,7 @@
         <v>129</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>350</v>
@@ -5766,7 +5757,7 @@
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>365</v>
@@ -5798,7 +5789,7 @@
         <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>368</v>
@@ -5827,10 +5818,10 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>371</v>
@@ -5859,10 +5850,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>374</v>
@@ -5891,10 +5882,10 @@
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>183</v>
+        <v>305</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>377</v>
@@ -5908,7 +5899,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>378</v>
@@ -5926,7 +5917,7 @@
         <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>380</v>
@@ -5940,7 +5931,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>381</v>
@@ -5958,7 +5949,7 @@
         <v>155</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>383</v>
@@ -5987,10 +5978,10 @@
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>269</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>386</v>
@@ -6019,10 +6010,10 @@
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>269</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>389</v>
@@ -6051,10 +6042,10 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>392</v>
@@ -6083,10 +6074,10 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>395</v>
@@ -6232,7 +6223,7 @@
         <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>219</v>
@@ -6241,7 +6232,7 @@
         <v>402</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6264,7 +6255,7 @@
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>84</v>
@@ -6273,7 +6264,7 @@
         <v>405</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6299,13 +6290,13 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>408</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6316,28 +6307,28 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6345,16 +6336,16 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -6363,13 +6354,13 @@
         <v>155</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6377,31 +6368,31 @@
         <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6412,28 +6403,28 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>420</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6444,28 +6435,28 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6476,28 +6467,28 @@
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>426</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6508,28 +6499,28 @@
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>429</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6540,28 +6531,28 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>156</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6572,28 +6563,28 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>48</v>
+        <v>432</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>432</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>434</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6616,16 +6607,16 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>437</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6648,7 +6639,7 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>89</v>
+        <v>241</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>165</v>
@@ -6657,7 +6648,7 @@
         <v>440</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6680,16 +6671,16 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>443</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6712,7 +6703,7 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>183</v>
@@ -6721,7 +6712,7 @@
         <v>446</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6744,16 +6735,16 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>449</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6776,16 +6767,16 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>452</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6811,13 +6802,13 @@
         <v>129</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>455</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6840,16 +6831,16 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>458</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6872,16 +6863,16 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>461</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6904,16 +6895,16 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>299</v>
+        <v>197</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>464</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6936,16 +6927,16 @@
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>188</v>
+        <v>398</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>467</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6953,7 +6944,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>468</v>
@@ -6968,16 +6959,16 @@
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>241</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>183</v>
+        <v>305</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>470</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -6985,7 +6976,7 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>471</v>
@@ -7003,13 +6994,13 @@
         <v>129</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>473</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7032,16 +7023,16 @@
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>193</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>299</v>
+        <v>197</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>476</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7064,16 +7055,16 @@
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>183</v>
+        <v>398</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>479</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7096,16 +7087,16 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>482</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7128,16 +7119,16 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>486</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -7148,28 +7139,28 @@
         <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -7212,7 +7203,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7259,83 +7250,83 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>491</v>
-      </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>494</v>
-      </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -7344,53 +7335,53 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>498</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>498</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>499</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>500</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>501</v>
@@ -7408,21 +7399,21 @@
         <v>155</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>503</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>504</v>
@@ -7437,21 +7428,21 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>506</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>113</v>
@@ -7472,18 +7463,18 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>509</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>117</v>
@@ -7501,21 +7492,21 @@
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>512</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>121</v>
@@ -7533,21 +7524,21 @@
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>515</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>126</v>
@@ -7565,36 +7556,36 @@
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>518</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>520</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>89</v>
@@ -7603,411 +7594,411 @@
         <v>156</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>524</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>533</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>536</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>539</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>183</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>548</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>551</v>
-      </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>553</v>
-      </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>183</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -8016,126 +8007,126 @@
         <v>129</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>563</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>566</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>570</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>571</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -8144,81 +8135,49 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>485</v>
+        <v>398</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -8249,7 +8208,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8266,7 +8224,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8316,7 +8274,7 @@
         <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>164</v>
@@ -8325,10 +8283,10 @@
         <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8342,25 +8300,25 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>146</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8374,13 +8332,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -8392,7 +8350,7 @@
         <v>165</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8406,25 +8364,25 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8435,16 +8393,16 @@
         <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -8453,10 +8411,10 @@
         <v>129</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8467,28 +8425,28 @@
         <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8502,13 +8460,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -8517,10 +8475,10 @@
         <v>155</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>299</v>
+        <v>197</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8534,13 +8492,13 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -8549,10 +8507,10 @@
         <v>124</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8566,13 +8524,13 @@
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -8581,10 +8539,10 @@
         <v>124</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>485</v>
+        <v>398</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8598,13 +8556,13 @@
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -8613,10 +8571,10 @@
         <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>398</v>
+        <v>604</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8630,13 +8588,13 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -8648,7 +8606,7 @@
         <v>398</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8662,25 +8620,25 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>398</v>
+        <v>604</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8694,13 +8652,13 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -8709,10 +8667,10 @@
         <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8726,13 +8684,13 @@
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -8741,10 +8699,10 @@
         <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8758,25 +8716,25 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8790,13 +8748,13 @@
         <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -8805,10 +8763,10 @@
         <v>155</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8822,13 +8780,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -8837,10 +8795,10 @@
         <v>89</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>398</v>
+        <v>604</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8854,13 +8812,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -8869,10 +8827,10 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8886,13 +8844,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -8901,10 +8859,10 @@
         <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8918,13 +8876,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -8933,10 +8891,10 @@
         <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8950,13 +8908,13 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -8965,10 +8923,10 @@
         <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8982,13 +8940,13 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -8997,10 +8955,10 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9014,13 +8972,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -9029,10 +8987,10 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9043,16 +9001,16 @@
         <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -9064,7 +9022,7 @@
         <v>646</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9075,16 +9033,16 @@
         <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -9093,10 +9051,10 @@
         <v>129</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9110,13 +9068,13 @@
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -9125,10 +9083,10 @@
         <v>129</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9142,13 +9100,13 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -9157,10 +9115,10 @@
         <v>129</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9174,13 +9132,13 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -9189,10 +9147,10 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9289,13 +9247,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -9304,10 +9262,10 @@
         <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9327,7 +9285,7 @@
         <v>70</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>164</v>
@@ -9339,7 +9297,7 @@
         <v>165</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9353,25 +9311,25 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>485</v>
+        <v>398</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9385,13 +9343,13 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -9400,10 +9358,10 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>299</v>
+        <v>614</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9414,16 +9372,16 @@
         <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -9432,10 +9390,10 @@
         <v>89</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>617</v>
+        <v>197</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9446,16 +9404,16 @@
         <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -9467,7 +9425,7 @@
         <v>398</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9481,13 +9439,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -9496,10 +9454,10 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>617</v>
+        <v>398</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9513,13 +9471,13 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -9528,10 +9486,10 @@
         <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>485</v>
+        <v>614</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9545,13 +9503,13 @@
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -9560,10 +9518,10 @@
         <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>617</v>
+        <v>646</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9577,13 +9535,13 @@
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -9592,10 +9550,10 @@
         <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>398</v>
+        <v>614</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9609,13 +9567,13 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -9624,10 +9582,10 @@
         <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>646</v>
+        <v>604</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9641,25 +9599,25 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>703</v>
+        <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>646</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9673,25 +9631,25 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>89</v>
+        <v>703</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>646</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9705,25 +9663,25 @@
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>124</v>
+        <v>269</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9737,25 +9695,25 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>269</v>
+        <v>124</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9769,25 +9727,25 @@
         <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9801,25 +9759,25 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9833,13 +9791,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -9848,10 +9806,10 @@
         <v>124</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9865,25 +9823,25 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9897,25 +9855,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9929,25 +9887,25 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>646</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9961,13 +9919,13 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -9976,10 +9934,10 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9993,13 +9951,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -10008,10 +9966,10 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10022,16 +9980,16 @@
         <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -10040,10 +9998,10 @@
         <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10054,16 +10012,16 @@
         <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -10072,10 +10030,10 @@
         <v>124</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10089,13 +10047,13 @@
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -10104,10 +10062,10 @@
         <v>124</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10121,13 +10079,13 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -10136,10 +10094,10 @@
         <v>124</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10153,13 +10111,13 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -10168,10 +10126,10 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10185,13 +10143,13 @@
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -10200,10 +10158,10 @@
         <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10217,13 +10175,13 @@
         <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -10232,10 +10190,10 @@
         <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -17,7 +17,7 @@
     <sheet name="TRIUMPH" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">CRES!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">CRES!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">HERMES!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="760">
   <si>
     <t>guild_name</t>
   </si>
@@ -1764,7 +1764,7 @@
     <t>126</t>
   </si>
   <si>
-    <t>480경 8704조 1129억 8868만</t>
+    <t>480경 8936조 9577억 3954만</t>
   </si>
   <si>
     <t>김승관</t>
@@ -1782,7 +1782,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EC%84%9C%EC%A0%95</t>
   </si>
   <si>
-    <t>4경 3389조 6009억 739만</t>
+    <t>4경 3502조 20억 1620만</t>
+  </si>
+  <si>
+    <t>Birbx</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Birbx</t>
+  </si>
+  <si>
+    <t>1경 7303조 450억 4563만</t>
   </si>
   <si>
     <t>yullmu</t>
@@ -1791,7 +1800,7 @@
     <t>https://mgf.gg/contents/character.php?n=yullmu</t>
   </si>
   <si>
-    <t>1경 1540조 8150억 8634만</t>
+    <t>1경 1649조 3486억 7498만</t>
   </si>
   <si>
     <t>황룹</t>
@@ -1800,7 +1809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EB%A3%B9</t>
   </si>
   <si>
-    <t>8990조 4799억 6435만</t>
+    <t>8994조 5083억 6036만</t>
   </si>
   <si>
     <t>서공윤</t>
@@ -1809,7 +1818,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EA%B3%B5%EC%9C%A4</t>
   </si>
   <si>
-    <t>6865조 6013억 4097만</t>
+    <t>7438조 9088억 1698만</t>
   </si>
   <si>
     <t>마크오브</t>
@@ -1818,7 +1827,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%81%AC%EC%98%A4%EB%B8%8C</t>
   </si>
   <si>
-    <t>5429조 1955억 7548만</t>
+    <t>5430조 8782억 5772만</t>
   </si>
   <si>
     <t>압러</t>
@@ -1836,7 +1845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A6%ACv</t>
   </si>
   <si>
-    <t>4431조 313억 7999만</t>
+    <t>4581조 3752억 7163만</t>
   </si>
   <si>
     <t>사랑보다깊은</t>
@@ -1866,7 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8D%EC%86%94</t>
   </si>
   <si>
-    <t>2208조 5103억 8375만</t>
+    <t>2209조 3924억 1172만</t>
   </si>
   <si>
     <t>콜리콜리</t>
@@ -1881,31 +1890,31 @@
     <t>2094조 2516억 6756만</t>
   </si>
   <si>
+    <t>아라사랑해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%9D%BC%EC%82%AC%EB%9E%91%ED%95%B4</t>
+  </si>
+  <si>
+    <t>1560조 7099억 3585만</t>
+  </si>
+  <si>
+    <t>융챠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%B5%EC%B1%A0</t>
+  </si>
+  <si>
+    <t>1444조 2233억 5277만</t>
+  </si>
+  <si>
     <t>유굥a</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EA%B5%A5a</t>
   </si>
   <si>
-    <t>1428조 376억 3031만</t>
-  </si>
-  <si>
-    <t>융챠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%B5%EC%B1%A0</t>
-  </si>
-  <si>
-    <t>1362조 3842억 3352만</t>
-  </si>
-  <si>
-    <t>아라사랑해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%9D%BC%EC%82%AC%EB%9E%91%ED%95%B4</t>
-  </si>
-  <si>
-    <t>1337조 7416억 7529만</t>
+    <t>1429조 1005억 3285만</t>
   </si>
   <si>
     <t>뮤내</t>
@@ -1914,7 +1923,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%A4%EB%82%B4</t>
   </si>
   <si>
-    <t>908조 4921억 2094만</t>
+    <t>963조 5065억 3406만</t>
   </si>
   <si>
     <t>도적레오</t>
@@ -1926,7 +1935,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>778조 8819억 348만</t>
+    <t>859조 450억 1068만</t>
   </si>
   <si>
     <t>유이건</t>
@@ -1935,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%9D%B4%EA%B1%B4</t>
   </si>
   <si>
-    <t>710조 7661억 6846만</t>
+    <t>721조 9773억 3771만</t>
   </si>
   <si>
     <t>다크홀리</t>
@@ -1944,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%81%AC%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>600조 4395억 6763만</t>
+    <t>619조 7024억 3508만</t>
   </si>
   <si>
     <t>룬보</t>
@@ -1953,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%AC%EB%B3%B4</t>
   </si>
   <si>
-    <t>574조 3828억 9290만</t>
+    <t>612조 988억 4078만</t>
   </si>
   <si>
     <t>Libere</t>
@@ -1962,7 +1971,7 @@
     <t>https://mgf.gg/contents/character.php?n=Libere</t>
   </si>
   <si>
-    <t>425조 4683억 7933만</t>
+    <t>445조 9342억 7361만</t>
   </si>
   <si>
     <t>우주경</t>
@@ -1974,7 +1983,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>414조 5422억 9225만</t>
+    <t>427조 4531억 9513만</t>
   </si>
   <si>
     <t>현수컷</t>
@@ -1995,7 +2004,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>265조 3015억 9343만</t>
+    <t>268조 8367억 3878만</t>
   </si>
   <si>
     <t>돈골대가</t>
@@ -2004,226 +2013,226 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EA%B3%A8%EB%8C%80%EA%B0%80</t>
   </si>
   <si>
+    <t>251조 9335억 4895만</t>
+  </si>
+  <si>
+    <t>겨울파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>246조 1291억 5455만</t>
+  </si>
+  <si>
+    <t>지니D</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88D</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>44조 1669억 79만</t>
+  </si>
+  <si>
+    <t>종리츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>813경 3160조 9953억 1431만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>22경 378조 1155억 8268만</t>
+  </si>
+  <si>
+    <t>몰라츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2경 78조 7679억 9826만</t>
+  </si>
+  <si>
+    <t>정육츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 4306조 1767억 1749만</t>
+  </si>
+  <si>
+    <t>가푸츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1경 2389조 2억 1625만</t>
+  </si>
+  <si>
+    <t>수달츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>6301조 4850억 7338만</t>
+  </si>
+  <si>
+    <t>파숙츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2698조 6805억 2581만</t>
+  </si>
+  <si>
+    <t>딤츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2663조 1265억 72만</t>
+  </si>
+  <si>
+    <t>조림츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2119조 3696억 1726만</t>
+  </si>
+  <si>
+    <t>천상츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1989조 1895억 3262만</t>
+  </si>
+  <si>
+    <t>유졍츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1723조 433억 3057만</t>
+  </si>
+  <si>
+    <t>화정삶</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%82%B6</t>
+  </si>
+  <si>
+    <t>1173조 521억 246만</t>
+  </si>
+  <si>
+    <t>Dollmeng2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1161조 5682억 8531만</t>
+  </si>
+  <si>
+    <t>산과바다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1016조 320억 9190만</t>
+  </si>
+  <si>
+    <t>서전붕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%A0%84%EB%B6%95</t>
+  </si>
+  <si>
+    <t>878조 8276억 5928만</t>
+  </si>
+  <si>
+    <t>현유수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
+  </si>
+  <si>
+    <t>814조 5910억 50만</t>
+  </si>
+  <si>
+    <t>호야빵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%95%BC%EB%B9%B5</t>
+  </si>
+  <si>
+    <t>776조 4778억 6115만</t>
+  </si>
+  <si>
+    <t>푸들츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>766조 8747억 65만</t>
+  </si>
+  <si>
+    <t>묘피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%ED%94%BC</t>
+  </si>
+  <si>
+    <t>450조 2034억 4621만</t>
+  </si>
+  <si>
+    <t>루린츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A6%B0%EC%B8%84</t>
+  </si>
+  <si>
+    <t>429조 3663억 1715만</t>
+  </si>
+  <si>
+    <t>뽀야츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
+  </si>
+  <si>
+    <t>316조 9037억 2355만</t>
+  </si>
+  <si>
+    <t>하치츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B9%98%EC%B8%84</t>
+  </si>
+  <si>
     <t>107</t>
-  </si>
-  <si>
-    <t>251조 9335억 4895만</t>
-  </si>
-  <si>
-    <t>겨울파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>225조 8419억 6680만</t>
-  </si>
-  <si>
-    <t>지니D</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88D</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>44조 1669억 79만</t>
-  </si>
-  <si>
-    <t>종리츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>813경 3160조 9953억 1431만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>22경 378조 1155억 8268만</t>
-  </si>
-  <si>
-    <t>몰라츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2경 78조 7679억 9826만</t>
-  </si>
-  <si>
-    <t>정육츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%9C%A1%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1경 4306조 1767억 1749만</t>
-  </si>
-  <si>
-    <t>가푸츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%91%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1경 2389조 2억 1625만</t>
-  </si>
-  <si>
-    <t>수달츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>6301조 4850억 7338만</t>
-  </si>
-  <si>
-    <t>파숙츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%88%99%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2698조 6805억 2581만</t>
-  </si>
-  <si>
-    <t>딤츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2663조 1265억 72만</t>
-  </si>
-  <si>
-    <t>조림츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2119조 3696억 1726만</t>
-  </si>
-  <si>
-    <t>천상츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1989조 1895억 3262만</t>
-  </si>
-  <si>
-    <t>유졍츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1723조 433억 3057만</t>
-  </si>
-  <si>
-    <t>화정삶</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%82%B6</t>
-  </si>
-  <si>
-    <t>1173조 521억 246만</t>
-  </si>
-  <si>
-    <t>Dollmeng2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1161조 5682억 8531만</t>
-  </si>
-  <si>
-    <t>산과바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1016조 320억 9190만</t>
-  </si>
-  <si>
-    <t>서전붕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%A0%84%EB%B6%95</t>
-  </si>
-  <si>
-    <t>878조 8276억 5928만</t>
-  </si>
-  <si>
-    <t>현유수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%9C%A0%EC%88%98</t>
-  </si>
-  <si>
-    <t>814조 5910억 50만</t>
-  </si>
-  <si>
-    <t>호야빵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%95%BC%EB%B9%B5</t>
-  </si>
-  <si>
-    <t>776조 4778억 6115만</t>
-  </si>
-  <si>
-    <t>푸들츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>766조 8747억 65만</t>
-  </si>
-  <si>
-    <t>묘피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%ED%94%BC</t>
-  </si>
-  <si>
-    <t>450조 2034억 4621만</t>
-  </si>
-  <si>
-    <t>루린츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A6%B0%EC%B8%84</t>
-  </si>
-  <si>
-    <t>429조 3663억 1715만</t>
-  </si>
-  <si>
-    <t>뽀야츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>316조 9037억 2355만</t>
-  </si>
-  <si>
-    <t>하치츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%B9%98%EC%B8%84</t>
   </si>
   <si>
     <t>250조 4329억 1064만</t>
@@ -8215,7 +8224,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -8376,10 +8385,10 @@
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>305</v>
+        <v>398</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>586</v>
@@ -8408,7 +8417,7 @@
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>129</v>
+        <v>241</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>305</v>
@@ -8440,7 +8449,7 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>305</v>
@@ -8472,10 +8481,10 @@
         <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>595</v>
@@ -8504,10 +8513,10 @@
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>305</v>
+        <v>197</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>598</v>
@@ -8539,7 +8548,7 @@
         <v>124</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>398</v>
+        <v>305</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>601</v>
@@ -8568,13 +8577,13 @@
         <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8588,13 +8597,13 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -8603,7 +8612,7 @@
         <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>398</v>
+        <v>607</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>608</v>
@@ -8632,10 +8641,10 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>604</v>
+        <v>398</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>611</v>
@@ -8664,13 +8673,13 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>615</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8684,22 +8693,22 @@
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>614</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>618</v>
@@ -8728,10 +8737,10 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>621</v>
@@ -8760,10 +8769,10 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>624</v>
@@ -8795,7 +8804,7 @@
         <v>89</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>627</v>
@@ -8827,10 +8836,10 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8844,22 +8853,22 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>634</v>
@@ -8888,10 +8897,10 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>637</v>
@@ -8920,10 +8929,10 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>640</v>
@@ -8952,10 +8961,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>643</v>
@@ -8987,10 +8996,10 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9004,13 +9013,13 @@
         <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -9019,7 +9028,7 @@
         <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>650</v>
@@ -9048,13 +9057,13 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9068,13 +9077,13 @@
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -9083,10 +9092,10 @@
         <v>129</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9100,13 +9109,13 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -9115,10 +9124,10 @@
         <v>129</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9132,32 +9141,64 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="J29" s="2" t="s">
+      <c r="H30" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -9187,6 +9228,7 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9247,13 +9289,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -9265,7 +9307,7 @@
         <v>90</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9285,7 +9327,7 @@
         <v>70</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>164</v>
@@ -9297,7 +9339,7 @@
         <v>165</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9311,13 +9353,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -9329,7 +9371,7 @@
         <v>398</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9343,13 +9385,13 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -9358,10 +9400,10 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9375,13 +9417,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -9393,7 +9435,7 @@
         <v>197</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9407,13 +9449,13 @@
         <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -9425,7 +9467,7 @@
         <v>398</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9439,13 +9481,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -9457,7 +9499,7 @@
         <v>398</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9471,13 +9513,13 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -9486,10 +9528,10 @@
         <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9503,13 +9545,13 @@
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -9518,10 +9560,10 @@
         <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9535,13 +9577,13 @@
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -9550,10 +9592,10 @@
         <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9567,13 +9609,13 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -9582,10 +9624,10 @@
         <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9599,13 +9641,13 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -9614,10 +9656,10 @@
         <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9631,25 +9673,25 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9663,13 +9705,13 @@
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -9678,10 +9720,10 @@
         <v>269</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9695,13 +9737,13 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -9710,10 +9752,10 @@
         <v>124</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9727,13 +9769,13 @@
         <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -9742,10 +9784,10 @@
         <v>192</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9759,13 +9801,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -9774,10 +9816,10 @@
         <v>124</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9791,13 +9833,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -9806,10 +9848,10 @@
         <v>124</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9823,13 +9865,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -9838,10 +9880,10 @@
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9855,13 +9897,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -9870,10 +9912,10 @@
         <v>124</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9887,13 +9929,13 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -9902,10 +9944,10 @@
         <v>241</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9919,13 +9961,13 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -9934,10 +9976,10 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>657</v>
+        <v>733</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9951,13 +9993,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -9966,10 +10008,10 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9983,13 +10025,13 @@
         <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -9998,10 +10040,10 @@
         <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10015,13 +10057,13 @@
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -10030,10 +10072,10 @@
         <v>124</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10047,13 +10089,13 @@
         <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -10062,10 +10104,10 @@
         <v>124</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10079,13 +10121,13 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -10094,10 +10136,10 @@
         <v>124</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>657</v>
+        <v>733</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10111,13 +10153,13 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -10126,10 +10168,10 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10143,13 +10185,13 @@
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -10158,10 +10200,10 @@
         <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10175,13 +10217,13 @@
         <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -10190,10 +10232,10 @@
         <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">CRES!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">HERMES!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">HERMES!$A$1:$J$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">TRIUMPH!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">빠따!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="763">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,595 +84,595 @@
     <t>Scania 25</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>675경 8717조 9996억 6939만</t>
+  </si>
+  <si>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+  </si>
+  <si>
+    <t>설익은체리</t>
+  </si>
+  <si>
+    <t>2026.09.12</t>
+  </si>
+  <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>642경 7481조 8460억 1870만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN70위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.09.16</t>
+  </si>
+  <si>
+    <t>HERMES</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=HERMES</t>
+  </si>
+  <si>
+    <t>Scania 3</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>618경 1272조 9707억 7440만</t>
+  </si>
+  <si>
+    <t>No.1 HERMES</t>
+  </si>
+  <si>
+    <t>명탐젓코난</t>
+  </si>
+  <si>
+    <t>빠따</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>541경 4853조 3239억 949만</t>
+  </si>
+  <si>
+    <t>매너친목아닌길드</t>
+  </si>
+  <si>
+    <t>o원기o</t>
+  </si>
+  <si>
+    <t>유니크</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9C%A0%EB%8B%88%ED%81%AC</t>
+  </si>
+  <si>
+    <t>Scania 1</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>608경 2078조 7834억 2410만</t>
+  </si>
+  <si>
+    <t>똥!</t>
+  </si>
+  <si>
+    <t>동땅이</t>
+  </si>
+  <si>
+    <t>CRES</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=CRES</t>
+  </si>
+  <si>
+    <t>Scania 45</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>516경 83조 5432억 3820만</t>
+  </si>
+  <si>
+    <t>by invitation only</t>
+  </si>
+  <si>
+    <t>라리c</t>
+  </si>
+  <si>
+    <t>TRIUMPH</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
+  </si>
+  <si>
+    <t>Scania 63</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>852경 1476조 2154억 5750만</t>
+  </si>
+  <si>
+    <t>퐁이츄</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>187경 9039조 7170억 6795만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>캐일리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>148경 7368조 3536억 7158만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>킹규봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>62경 4188조 2543억 3793만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>48경 406조 1704억 4020만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>39경 540조 417억 1853만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>39경 253조 6696억 4859만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
+  </si>
+  <si>
+    <t>34경 9242조 31억 1393만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>28경 2483조 7576억 982만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>시드리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>23경 4505조 3815억 9635만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>셀렘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>21경 4753조 3765억 8338만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>졸귀탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>14경 7716조 6607억 7849만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>12경 9016조 1542억 5770만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>설딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
+  </si>
+  <si>
+    <t>12경 7975조 8170억 5111만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>경성2018</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>8경 1791조 1615억 2546만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>슐아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>7경 2382조 7642억 9212만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>설름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>7경 1664조 3246억 1746만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>5경 4783조 8696억 6956만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>4경 7730조 7682억 1650만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>4경 5345조 1275억 983만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>우열무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%97%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>3경 7349조 6182억 8236만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>수상구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>2경 4937조 7932억 1425만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>견아니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1경 9013조 8299억 3542만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>설앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>1경 5321조 4698억 3495만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>설치는정상인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1경 4257조 4743억 7156만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>공룡박사원이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%A3%A1%EB%B0%95%EC%82%AC%EC%9B%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 1117조 1799억 3663만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>9244조 8885억 1488만</t>
+  </si>
+  <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>8994조 5637억 24만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>8781조 4022억 5235만</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>675경 8717조 9996억 6939만</t>
-  </si>
-  <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
-  </si>
-  <si>
-    <t>설익은체리</t>
-  </si>
-  <si>
-    <t>2026.09.12</t>
-  </si>
-  <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>602경 2808조 3209억 1039만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN70위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.09.13</t>
-  </si>
-  <si>
-    <t>HERMES</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=HERMES</t>
-  </si>
-  <si>
-    <t>Scania 3</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>618경 1272조 9707억 7440만</t>
-  </si>
-  <si>
-    <t>No.1 HERMES</t>
-  </si>
-  <si>
-    <t>명탐젓코난</t>
-  </si>
-  <si>
-    <t>빠따</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>541경 4853조 3239억 949만</t>
-  </si>
-  <si>
-    <t>매너친목아닌길드</t>
-  </si>
-  <si>
-    <t>o원기o</t>
-  </si>
-  <si>
-    <t>유니크</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9C%A0%EB%8B%88%ED%81%AC</t>
-  </si>
-  <si>
-    <t>Scania 1</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>592경 4343조 4147억 6600만</t>
-  </si>
-  <si>
-    <t>똥!</t>
-  </si>
-  <si>
-    <t>동땅이</t>
-  </si>
-  <si>
-    <t>CRES</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=CRES</t>
-  </si>
-  <si>
-    <t>Scania 45</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>486경 6868조 2475억 4590만</t>
-  </si>
-  <si>
-    <t>by invitation only</t>
-  </si>
-  <si>
-    <t>라리c</t>
-  </si>
-  <si>
-    <t>TRIUMPH</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TRIUMPH</t>
-  </si>
-  <si>
-    <t>Scania 63</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>823경 131조 424억 1509만</t>
-  </si>
-  <si>
-    <t>퐁이츄</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>해물만두야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>187경 9039조 7170억 6795만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>캐일리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>148경 7016조 6804억 294만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>킹규봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>62경 4188조 2543억 3793만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>설함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>46경 9293조 376억 9117만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>38경 977조 8938억 5636만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>35경 8908조 6008억 7035만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>너굴얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
-  </si>
-  <si>
-    <t>33경 7936조 9525억 5868만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>루델밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>28경 2483조 7576억 982만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>시드리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>23경 4505조 3815억 9635만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>셀렘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>18경 4568조 198억 4901만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>졸귀탱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>14경 1267조 3726억 2157만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>설딩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
-  </si>
-  <si>
-    <t>12경 7975조 8170억 5111만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>11경 9957조 1699억 8930만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>슐아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>7경 2382조 7642억 9212만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>설름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
-  </si>
-  <si>
-    <t>7경 89조 7733억 1129만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>경성2018</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>6경 3038조 8711억 1572만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>5경 4783조 8696억 6956만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>4경 5345조 1275억 983만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>4경 4375조 2811억 5421만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>우열무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%97%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>3경 6397조 2369억 447만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>수상구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>2경 2764조 5614억 4717만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>견아니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>1경 9013조 8299억 3542만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>설앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>1경 5321조 4698억 3495만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>설치지마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EC%A7%80%EB%A7%88</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1경 4130조 1863억 7189만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>공룡박사원이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%A3%A1%EB%B0%95%EC%82%AC%EC%9B%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>1경 1024조 8222억 2261만</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>8896조 7359억 8277만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>8781조 4022억 5235만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>8078조 6502억 2066만</t>
-  </si>
-  <si>
     <t>양촌마을</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%B4%8C%EB%A7%88%EC%9D%84</t>
   </si>
   <si>
-    <t>6571조 6510억 9833만</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>7074조 1060억 8687만</t>
   </si>
   <si>
     <t>헤븐잉</t>
@@ -702,7 +702,16 @@
     <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
   </si>
   <si>
-    <t>64경 4217조 575억 9009만</t>
+    <t>67경 2705조 1001억 2336만</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>56경 7588조 8796억 205만</t>
   </si>
   <si>
     <t>진자이</t>
@@ -711,16 +720,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>55경 4363조 3706억 9167만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>55경 2525조 6218억 1334만</t>
+    <t>56경 4909조 216억 5226만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -729,7 +729,28 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>41경 7711조 7799억 3444만</t>
+    <t>43경 2523조 8528억 3452만</t>
+  </si>
+  <si>
+    <t>뽀리빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>26경 6603조 6785억 6620만</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>24경 6324조 2509억 4408만</t>
   </si>
   <si>
     <t>스타캐치</t>
@@ -741,34 +762,13 @@
     <t>23경 6378조 9억 8238만</t>
   </si>
   <si>
-    <t>뽀리빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>23경 6194조 6186억 7365만</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>23경 5452조 8627억 4888만</t>
-  </si>
-  <si>
     <t>부엉이형</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>12경 4509조 2134억 7835만</t>
+    <t>12경 5797조 5282억 3519만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -777,7 +777,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>10경 280조 6073억 2728만</t>
+    <t>10경 3790조 2974억 300만</t>
   </si>
   <si>
     <t>약어</t>
@@ -789,22 +789,22 @@
     <t>9경 7717조 5279억 6925만</t>
   </si>
   <si>
+    <t>천천히걸어가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
+  </si>
+  <si>
+    <t>9경 7134조 3747억 7858만</t>
+  </si>
+  <si>
     <t>국의</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>8경 6777조 8160억 7603만</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>8경 32조 5919억 4407만</t>
+    <t>8경 7873조 5334억 9992만</t>
   </si>
   <si>
     <t>밉상b</t>
@@ -813,7 +813,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%89%EC%83%81b</t>
   </si>
   <si>
-    <t>7경 6310조 4728억 1122만</t>
+    <t>8경 3399조 1839억 9474만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>7경 3342조 5921억 8584만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -825,15 +834,6 @@
     <t>7경 3059조 933억 2511만</t>
   </si>
   <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>7경 2264조 8746억 6831만</t>
-  </si>
-  <si>
     <t>잼포즈</t>
   </si>
   <si>
@@ -843,7 +843,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>6경 7680조 2331억 1997만</t>
+    <t>7경 1027조 7063억 5237만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -861,7 +861,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>5경 8342조 1557억 9929만</t>
+    <t>5경 8774조 7748억 8940만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -879,7 +879,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
   </si>
   <si>
-    <t>4경 7757조 7936억 9566만</t>
+    <t>5경 3594조 4156억 1520만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -888,7 +888,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>1경 7102조 8495억 2595만</t>
+    <t>1경 7878조 1123억 177만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -897,7 +897,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>1경 5351조 1664억 8613만</t>
+    <t>1경 6529조 5322억 4370만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -915,7 +915,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>1경 3944조 7727억 1715만</t>
+    <t>1경 4618조 2500억 6149만</t>
   </si>
   <si>
     <t>익맹</t>
@@ -924,7 +924,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9</t>
   </si>
   <si>
-    <t>1경 2718조 2674억 5593만</t>
+    <t>1경 2768조 6356억 4928만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -933,7 +933,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 14조 9938억 1255만</t>
+    <t>1경 1613조 6754억 1930만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -960,7 +960,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>6665조 3780억 1797만</t>
+    <t>7596조 3054억 8889만</t>
   </si>
   <si>
     <t>럥커</t>
@@ -969,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%A5%EC%BB%A4</t>
   </si>
   <si>
-    <t>164경 8200조 4244억 1892만</t>
+    <t>174경 3743조 2257억 9498만</t>
   </si>
   <si>
     <t>적금묶인린풍</t>
@@ -978,7 +978,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%EA%B8%88%EB%AC%B6%EC%9D%B8%EB%A6%B0%ED%92%8D</t>
   </si>
   <si>
-    <t>117경 1645조 8375억 9144만</t>
+    <t>127경 6830조 7192억 2385만</t>
   </si>
   <si>
     <t>야느</t>
@@ -1020,16 +1020,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%ED%8F%89%EA%B2%AC</t>
   </si>
   <si>
-    <t>33경 8875조 6217억 640만</t>
-  </si>
-  <si>
-    <t>돈슨환불하라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A8%ED%99%98%EB%B6%88%ED%95%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>17경 2조 7391억 1560만</t>
+    <t>34경 4710조 6367억 9998만</t>
+  </si>
+  <si>
+    <t>마그마GT</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B7%B8%EB%A7%88GT</t>
+  </si>
+  <si>
+    <t>17경 614조 875억 8014만</t>
   </si>
   <si>
     <t>김취야호</t>
@@ -1038,7 +1038,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B7%A8%EC%95%BC%ED%98%B8</t>
   </si>
   <si>
-    <t>10경 5657조 198억 2889만</t>
+    <t>12경 944조 3269억 2112만</t>
   </si>
   <si>
     <t>랍아</t>
@@ -1047,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8D%EC%95%84</t>
   </si>
   <si>
-    <t>8경 1324조 6362억 5088만</t>
+    <t>8경 4619조 2507억 1775만</t>
   </si>
   <si>
     <t>월하의밤</t>
@@ -1074,7 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%EC%9A%B4</t>
   </si>
   <si>
-    <t>4경 9987조 4496억 4082만</t>
+    <t>5경 1971조 1519억 6067만</t>
   </si>
   <si>
     <t>육퇴한아빠</t>
@@ -1083,7 +1083,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A1%ED%87%B4%ED%95%9C%EC%95%84%EB%B9%A0</t>
   </si>
   <si>
-    <t>4경 1639조 2573억 4608만</t>
+    <t>4경 3537조 8977억 8168만</t>
+  </si>
+  <si>
+    <t>노건</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EA%B1%B4</t>
+  </si>
+  <si>
+    <t>3경 2916조 7593억 1863만</t>
   </si>
   <si>
     <t>분평</t>
@@ -1092,16 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%84%ED%8F%89</t>
   </si>
   <si>
-    <t>3경 1743조 1350억 8364만</t>
-  </si>
-  <si>
-    <t>노건</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EA%B1%B4</t>
-  </si>
-  <si>
-    <t>2경 8780조 3059억 5046만</t>
+    <t>3경 2542조 300억 9212만</t>
   </si>
   <si>
     <t>샤샤엘</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A8%EC%94%A8</t>
   </si>
   <si>
-    <t>2경 3424조 1137억 7785만</t>
+    <t>2경 4548조 1177억 1999만</t>
   </si>
   <si>
     <t>수냬</t>
@@ -1128,7 +1128,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%83%AC</t>
   </si>
   <si>
-    <t>1경 8838조 1918억 4815만</t>
+    <t>2경 489조 8439억 9752만</t>
   </si>
   <si>
     <t>일하</t>
@@ -1137,7 +1137,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%ED%95%98</t>
   </si>
   <si>
-    <t>1경 7109조 1524억 5809만</t>
+    <t>1경 9225조 2062억 8608만</t>
   </si>
   <si>
     <t>새콤달콤해</t>
@@ -1155,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EA%BB%8C</t>
   </si>
   <si>
-    <t>1경 1705조 216억 2730만</t>
+    <t>1경 1823조 7616억 5742만</t>
   </si>
   <si>
     <t>열도</t>
@@ -1164,7 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>1경 1198조 9025억 9658만</t>
+    <t>1경 1204조 9086억 37만</t>
   </si>
   <si>
     <t>장홍</t>
@@ -1173,7 +1173,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%99%8D</t>
   </si>
   <si>
-    <t>8943조 7860억 9399만</t>
+    <t>9724조 7216억 9711만</t>
+  </si>
+  <si>
+    <t>주해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%B4</t>
+  </si>
+  <si>
+    <t>9119조 6076억 8548만</t>
   </si>
   <si>
     <t>칸델</t>
@@ -1182,16 +1191,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%B8%EB%8D%B8</t>
   </si>
   <si>
-    <t>8013조 6168억 463만</t>
-  </si>
-  <si>
-    <t>주해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%B4</t>
-  </si>
-  <si>
-    <t>7836조 8193억 4414만</t>
+    <t>8513조 3030억 9934만</t>
   </si>
   <si>
     <t>고양이확대범</t>
@@ -1203,6 +1203,15 @@
     <t>7452조 3039억 2171만</t>
   </si>
   <si>
+    <t>짬띡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%AC%EB%9D%A1</t>
+  </si>
+  <si>
+    <t>7070조 8022억 3183만</t>
+  </si>
+  <si>
     <t>햄마요</t>
   </si>
   <si>
@@ -1230,7 +1239,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>1793조 1252억 4947만</t>
+    <t>1849조 1055억 6219만</t>
   </si>
   <si>
     <t>다씨</t>
@@ -1239,7 +1248,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%94%A8</t>
   </si>
   <si>
-    <t>228경 3744조 4229억 2046만</t>
+    <t>229경 2838조 2167억 5155만</t>
   </si>
   <si>
     <t>라온MS</t>
@@ -1257,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
   </si>
   <si>
-    <t>30경 6018조 6237억 3856만</t>
+    <t>30경 7053조 1709억 24만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
@@ -1290,7 +1299,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%9F%EB%BF%A1%EC%95%BC</t>
   </si>
   <si>
-    <t>11경 2345조 7006억 1544만</t>
+    <t>12경 5481조 8764억 9180만</t>
   </si>
   <si>
     <t>o엉댕o</t>
@@ -1317,7 +1326,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%8E%B8</t>
   </si>
   <si>
-    <t>4경 5989조 8691억 6867만</t>
+    <t>4경 7116조 3534억 7673만</t>
+  </si>
+  <si>
+    <t>이원일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>3경 5599조 1905억 3722만</t>
   </si>
   <si>
     <t>여수로</t>
@@ -1329,6 +1347,15 @@
     <t>3경 544조 7051억 6224만</t>
   </si>
   <si>
+    <t>o진이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>3경 153조 1544억 84만</t>
+  </si>
+  <si>
     <t>o후국o</t>
   </si>
   <si>
@@ -1338,31 +1365,13 @@
     <t>2경 8526조 1391억 6769만</t>
   </si>
   <si>
-    <t>o진이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>2경 8284조 7504억 9727만</t>
-  </si>
-  <si>
     <t>김규평</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B7%9C%ED%8F%89</t>
   </si>
   <si>
-    <t>2경 7089조 3601억 2658만</t>
-  </si>
-  <si>
-    <t>이원일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>2경 6911조 1474억 4475만</t>
+    <t>2경 7258조 3559억 5683만</t>
   </si>
   <si>
     <t>사단장님</t>
@@ -1398,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EC%9B%85</t>
   </si>
   <si>
-    <t>1경 7859조 8721억 3862만</t>
+    <t>1경 8677조 6416억 2488만</t>
   </si>
   <si>
     <t>멩구v</t>
@@ -1407,7 +1416,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%A9%EA%B5%ACv</t>
   </si>
   <si>
-    <t>1경 5406조 504억 5558만</t>
+    <t>1경 7350조 7539억 5777만</t>
   </si>
   <si>
     <t>화욤</t>
@@ -1434,7 +1443,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%95%84%EC%9C%A4o</t>
   </si>
   <si>
-    <t>9167조 2934억 5110만</t>
+    <t>1경 1064조 7341억 107만</t>
   </si>
   <si>
     <t>뭥끼</t>
@@ -1443,7 +1452,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
   </si>
   <si>
-    <t>9073조 6965억 2569만</t>
+    <t>9262조 5337억 8267만</t>
   </si>
   <si>
     <t>FFFK</t>
@@ -1452,7 +1461,7 @@
     <t>https://mgf.gg/contents/character.php?n=FFFK</t>
   </si>
   <si>
-    <t>8656조 2699억 1299만</t>
+    <t>8786조 6534억 1694만</t>
   </si>
   <si>
     <t>옹이잉</t>
@@ -1461,7 +1470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%9D%B4%EC%9E%89</t>
   </si>
   <si>
-    <t>7861조 2137억 6072만</t>
+    <t>8093조 6976억 5808만</t>
   </si>
   <si>
     <t>담훌</t>
@@ -1470,7 +1479,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
   </si>
   <si>
-    <t>4722조 7330억 5332만</t>
+    <t>4903조 69억 8254만</t>
+  </si>
+  <si>
+    <t>건들면혼남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%93%A4%EB%A9%B4%ED%98%BC%EB%82%A8</t>
+  </si>
+  <si>
+    <t>4886조 4914억 6262만</t>
   </si>
   <si>
     <t>겨울난방</t>
@@ -1479,16 +1497,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
   </si>
   <si>
-    <t>4612조 813억 2711만</t>
-  </si>
-  <si>
-    <t>건들면혼남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%93%A4%EB%A9%B4%ED%98%BC%EB%82%A8</t>
-  </si>
-  <si>
-    <t>4379조 7993억 6587만</t>
+    <t>4786조 1595억 544만</t>
   </si>
   <si>
     <t>보마할래</t>
@@ -1497,7 +1506,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
   </si>
   <si>
-    <t>2961조 4012억 1670만</t>
+    <t>3095조 5192억 2263만</t>
   </si>
   <si>
     <t>차김치</t>
@@ -1515,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%8C%EC%99%84%EB%91%90</t>
   </si>
   <si>
-    <t>126경 8245조 877억 6439만</t>
+    <t>128경 9404조 2340억 6164만</t>
   </si>
   <si>
     <t>쌀만</t>
@@ -1533,7 +1542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%ED%98%B8%EB%94%98</t>
   </si>
   <si>
-    <t>22경 6752조 4345억 3803만</t>
+    <t>23경 3907조 3415억 7345만</t>
   </si>
   <si>
     <t>우땨</t>
@@ -1542,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%95%A8</t>
   </si>
   <si>
-    <t>13경 6065조 8576억 7344만</t>
+    <t>13경 7354조 8520억 6741만</t>
   </si>
   <si>
     <t>엘픽</t>
@@ -1551,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%ED%94%BD</t>
   </si>
   <si>
-    <t>12경 2723조 780억 5934만</t>
+    <t>12경 7314조 1039억 1634만</t>
   </si>
   <si>
     <t>차수진</t>
@@ -1569,7 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%94%AC</t>
   </si>
   <si>
-    <t>8경 540조 3712억 1485만</t>
+    <t>8경 2433조 5731억 896만</t>
   </si>
   <si>
     <t>겐미</t>
@@ -1578,7 +1587,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>6경 406조 9177억 7251만</t>
+    <t>7경 23조 6721억 946만</t>
   </si>
   <si>
     <t>텨숍</t>
@@ -1587,22 +1596,22 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%85%A8%EC%88%8D</t>
   </si>
   <si>
-    <t>5경 3091조 1746억 9095만</t>
+    <t>5경 9031조 4488억 167만</t>
+  </si>
+  <si>
+    <t>승질승</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%A7%88%EC%8A%B9</t>
+  </si>
+  <si>
+    <t>4경 3931조 2355억 3946만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%95%85%EC%9D%B4</t>
   </si>
   <si>
-    <t>4경 3474조 3132억 749만</t>
-  </si>
-  <si>
-    <t>승질승</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%A7%88%EC%8A%B9</t>
-  </si>
-  <si>
-    <t>4경 586조 4035억 8300만</t>
+    <t>4경 3494조 7561억 8013만</t>
   </si>
   <si>
     <t>보레아스</t>
@@ -1611,7 +1620,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A0%88%EC%95%84%EC%8A%A4</t>
   </si>
   <si>
-    <t>2경 1485조 7176억 442만</t>
+    <t>2경 1572조 3894억 3304만</t>
+  </si>
+  <si>
+    <t>향연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%A5%EC%97%B0</t>
+  </si>
+  <si>
+    <t>2경 1343조 8530억 3687만</t>
   </si>
   <si>
     <t>뉴비숍</t>
@@ -1620,7 +1638,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 1078조 45억 8305만</t>
+    <t>2경 1253조 999억 8390만</t>
+  </si>
+  <si>
+    <t>일등통신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EB%93%B1%ED%86%B5%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>2경 1234조 1052억 3014만</t>
   </si>
   <si>
     <t>서먕</t>
@@ -1632,31 +1659,13 @@
     <t>2경 938조 9137억 4771만</t>
   </si>
   <si>
-    <t>향연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%A5%EC%97%B0</t>
-  </si>
-  <si>
-    <t>2경 602조 8417억 2281만</t>
-  </si>
-  <si>
-    <t>일등통신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EB%93%B1%ED%86%B5%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>2경 366조 909억 7624만</t>
-  </si>
-  <si>
     <t>정령성</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%A0%B9%EC%84%B1</t>
   </si>
   <si>
-    <t>1경 6333조 7647억 8373만</t>
+    <t>1경 7955조 7456억 4643만</t>
   </si>
   <si>
     <t>DAEBAK</t>
@@ -1665,7 +1674,7 @@
     <t>https://mgf.gg/contents/character.php?n=DAEBAK</t>
   </si>
   <si>
-    <t>1경 4224조 883억 6307만</t>
+    <t>1경 7050조 5701억 4417만</t>
   </si>
   <si>
     <t>벞벞</t>
@@ -1677,22 +1686,22 @@
     <t>1경 2189조 8683억 18만</t>
   </si>
   <si>
+    <t>우탸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%B8</t>
+  </si>
+  <si>
+    <t>1경 1243조 1203억 396만</t>
+  </si>
+  <si>
     <t>쌉새</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>1경 513조 2367억 9292만</t>
-  </si>
-  <si>
-    <t>우탸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%B8</t>
-  </si>
-  <si>
-    <t>1경 64조 5452억 8788만</t>
+    <t>1경 561조 8786억 6516만</t>
   </si>
   <si>
     <t>퍌라딘</t>
@@ -1701,7 +1710,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%8C%EB%9D%BC%EB%94%98</t>
   </si>
   <si>
-    <t>6867조 1697억 3934만</t>
+    <t>7538조 4356억 9146만</t>
   </si>
   <si>
     <t>띠디는띠디야</t>
@@ -1710,7 +1719,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EB%94%94%EB%8A%94%EB%9D%A0%EB%94%94%EC%95%BC</t>
   </si>
   <si>
-    <t>6721조 4821억 5548만</t>
+    <t>7176조 9008억 574만</t>
   </si>
   <si>
     <t>마류</t>
@@ -1719,7 +1728,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%A5%98</t>
   </si>
   <si>
-    <t>6198조 287억 3288만</t>
+    <t>6629조 2352억 193만</t>
   </si>
   <si>
     <t>뚱뚱쉰</t>
@@ -1728,7 +1737,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%EB%9A%B1%EC%89%B0</t>
   </si>
   <si>
-    <t>5112조 4521억 9686만</t>
+    <t>5124조 5052억 5016만</t>
   </si>
   <si>
     <t>댤타냥</t>
@@ -1737,7 +1746,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%A4%ED%83%80%EB%83%A5</t>
   </si>
   <si>
-    <t>5080조 9923억 7302만</t>
+    <t>5086조 5349억 8587만</t>
+  </si>
+  <si>
+    <t>랜더스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9E%9C%EB%8D%94%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>3982조 7499억 2571만</t>
   </si>
   <si>
     <t>컈컈</t>
@@ -1749,22 +1767,13 @@
     <t>3960조 8132억 2490만</t>
   </si>
   <si>
-    <t>랜더스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9E%9C%EB%8D%94%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3784조 5298억 7458만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A6%ACc</t>
   </si>
   <si>
     <t>126</t>
   </si>
   <si>
-    <t>480경 8936조 9577억 3954만</t>
+    <t>480경 9285조 3223억 8456만</t>
   </si>
   <si>
     <t>김승관</t>
@@ -1773,7 +1782,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%8A%B9%EA%B4%80</t>
   </si>
   <si>
-    <t>20경 5291조 5659억 4363만</t>
+    <t>22경 5004조 9991억 4635만</t>
   </si>
   <si>
     <t>황서정</t>
@@ -1782,7 +1791,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EC%84%9C%EC%A0%95</t>
   </si>
   <si>
-    <t>4경 3502조 20억 1620만</t>
+    <t>4경 3513조 3183억 1342만</t>
   </si>
   <si>
     <t>Birbx</t>
@@ -1791,7 +1800,7 @@
     <t>https://mgf.gg/contents/character.php?n=Birbx</t>
   </si>
   <si>
-    <t>1경 7303조 450억 4563만</t>
+    <t>1경 7329조 6488억 1931만</t>
   </si>
   <si>
     <t>yullmu</t>
@@ -1800,7 +1809,7 @@
     <t>https://mgf.gg/contents/character.php?n=yullmu</t>
   </si>
   <si>
-    <t>1경 1649조 3486억 7498만</t>
+    <t>1경 2128조 3095억 2166만</t>
   </si>
   <si>
     <t>황룹</t>
@@ -1809,7 +1818,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EB%A3%B9</t>
   </si>
   <si>
-    <t>8994조 5083억 6036만</t>
+    <t>9119조 6373억 1685만</t>
   </si>
   <si>
     <t>서공윤</t>
@@ -1818,7 +1827,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EA%B3%B5%EC%9C%A4</t>
   </si>
   <si>
-    <t>7438조 9088억 1698만</t>
+    <t>8083조 704억 4806만</t>
   </si>
   <si>
     <t>마크오브</t>
@@ -1827,7 +1836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%81%AC%EC%98%A4%EB%B8%8C</t>
   </si>
   <si>
-    <t>5430조 8782억 5772만</t>
+    <t>5461조 8894억 7174만</t>
   </si>
   <si>
     <t>압러</t>
@@ -1860,6 +1869,18 @@
     <t>3693조 5419억 5365만</t>
   </si>
   <si>
+    <t>콜리콜리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%BD%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2342조 3163억 1098만</t>
+  </si>
+  <si>
     <t>노이도</t>
   </si>
   <si>
@@ -1875,19 +1896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8D%EC%86%94</t>
   </si>
   <si>
-    <t>2209조 3924억 1172만</t>
-  </si>
-  <si>
-    <t>콜리콜리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%A6%AC%EC%BD%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2094조 2516억 6756만</t>
+    <t>2210조 6323억 1187만</t>
   </si>
   <si>
     <t>아라사랑해</t>
@@ -1905,7 +1914,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%B5%EC%B1%A0</t>
   </si>
   <si>
-    <t>1444조 2233억 5277만</t>
+    <t>1505조 3252억 1274만</t>
   </si>
   <si>
     <t>유굥a</t>
@@ -1914,7 +1923,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EA%B5%A5a</t>
   </si>
   <si>
-    <t>1429조 1005억 3285만</t>
+    <t>1430조 1578억 2802만</t>
   </si>
   <si>
     <t>뮤내</t>
@@ -1935,7 +1944,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>859조 450억 1068만</t>
+    <t>861조 6058억 3689만</t>
   </si>
   <si>
     <t>유이건</t>
@@ -1953,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%81%AC%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>619조 7024억 3508만</t>
+    <t>620조 5117억 8401만</t>
   </si>
   <si>
     <t>룬보</t>
@@ -1962,7 +1971,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%AC%EB%B3%B4</t>
   </si>
   <si>
-    <t>612조 988억 4078만</t>
+    <t>612조 9953억 4590만</t>
   </si>
   <si>
     <t>Libere</t>
@@ -1971,7 +1980,7 @@
     <t>https://mgf.gg/contents/character.php?n=Libere</t>
   </si>
   <si>
-    <t>445조 9342억 7361만</t>
+    <t>457조 330억 5419만</t>
   </si>
   <si>
     <t>우주경</t>
@@ -1983,7 +1992,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>427조 4531억 9513만</t>
+    <t>437조 2278억 702만</t>
   </si>
   <si>
     <t>현수컷</t>
@@ -1992,7 +2001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%88%98%EC%BB%B7</t>
   </si>
   <si>
-    <t>313조 847억 5192만</t>
+    <t>375조 535억 5353만</t>
   </si>
   <si>
     <t>손쨩1</t>
@@ -2043,13 +2052,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>813경 3160조 9953억 1431만</t>
+    <t>813경 4437조 2338억 7109만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%90%81%EC%9D%B4%EC%B8%84</t>
   </si>
   <si>
-    <t>22경 378조 1155억 8268만</t>
+    <t>30경 6527조 5348억 3786만</t>
   </si>
   <si>
     <t>몰라츄</t>
@@ -2058,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9D%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>2경 78조 7679억 9826만</t>
+    <t>2경 5031조 3287억 1054만</t>
   </si>
   <si>
     <t>정육츄</t>
@@ -2085,7 +2094,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%8B%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>6301조 4850억 7338만</t>
+    <t>6459조 1165억 5053만</t>
+  </si>
+  <si>
+    <t>딤츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
+  </si>
+  <si>
+    <t>2716조 6342억 2252만</t>
   </si>
   <si>
     <t>파숙츄</t>
@@ -2097,22 +2115,13 @@
     <t>2698조 6805억 2581만</t>
   </si>
   <si>
-    <t>딤츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EC%B8%84</t>
-  </si>
-  <si>
-    <t>2663조 1265억 72만</t>
-  </si>
-  <si>
     <t>조림츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%A6%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>2119조 3696억 1726만</t>
+    <t>2482조 224억 5261만</t>
   </si>
   <si>
     <t>천상츄</t>
@@ -2121,7 +2130,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%B8%84</t>
   </si>
   <si>
-    <t>1989조 1895억 3262만</t>
+    <t>2050조 2413억 6522만</t>
+  </si>
+  <si>
+    <t>Dollmeng2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1952조 2005억 1307만</t>
   </si>
   <si>
     <t>유졍츄</t>
@@ -2130,28 +2151,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A1%8D%EC%B8%84</t>
   </si>
   <si>
-    <t>1723조 433억 3057만</t>
-  </si>
-  <si>
-    <t>화정삶</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%82%B6</t>
-  </si>
-  <si>
-    <t>1173조 521억 246만</t>
-  </si>
-  <si>
-    <t>Dollmeng2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Dollmeng2</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1161조 5682억 8531만</t>
+    <t>1832조 3620억 3679만</t>
+  </si>
+  <si>
+    <t>화정츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A0%95%EC%B8%84</t>
+  </si>
+  <si>
+    <t>1374조 9333억 4948만</t>
   </si>
   <si>
     <t>산과바다</t>
@@ -2160,7 +2169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EA%B3%BC%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>1016조 320억 9190만</t>
+    <t>1099조 4345억 6107만</t>
   </si>
   <si>
     <t>서전붕</t>
@@ -2169,7 +2178,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%A0%84%EB%B6%95</t>
   </si>
   <si>
-    <t>878조 8276억 5928만</t>
+    <t>1098조 7210억 19만</t>
+  </si>
+  <si>
+    <t>호야빵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%95%BC%EB%B9%B5</t>
+  </si>
+  <si>
+    <t>950조 1090억 6618만</t>
   </si>
   <si>
     <t>현유수</t>
@@ -2181,22 +2199,13 @@
     <t>814조 5910억 50만</t>
   </si>
   <si>
-    <t>호야빵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%95%BC%EB%B9%B5</t>
-  </si>
-  <si>
-    <t>776조 4778억 6115만</t>
-  </si>
-  <si>
     <t>푸들츄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%93%A4%EC%B8%84</t>
   </si>
   <si>
-    <t>766조 8747억 65만</t>
+    <t>768조 8152억 153만</t>
   </si>
   <si>
     <t>묘피</t>
@@ -2223,7 +2232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%95%BC%EC%B8%84</t>
   </si>
   <si>
-    <t>316조 9037억 2355만</t>
+    <t>325조 1003억 5014만</t>
   </si>
   <si>
     <t>하치츄</t>
@@ -2244,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%ED%9E%A3%ED%9E%88%ED%9E%A3</t>
   </si>
   <si>
-    <t>211조 4233억 228만</t>
+    <t>239조 8582억 3881만</t>
   </si>
   <si>
     <t>도리츄</t>
@@ -2253,7 +2262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%EC%B8%84</t>
   </si>
   <si>
-    <t>192조 6708억 238만</t>
+    <t>209조 7743억 1108만</t>
   </si>
   <si>
     <t>주냥츄</t>
@@ -2262,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%83%A5%EC%B8%84</t>
   </si>
   <si>
-    <t>167조 6859억 872만</t>
+    <t>172조 8382억 872만</t>
   </si>
   <si>
     <t>디나인</t>
@@ -2301,7 +2310,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%A8%80</t>
   </si>
   <si>
-    <t>46조 8776억 8949만</t>
+    <t>52조 9807억 6147만</t>
   </si>
   <si>
     <t>피카츄십볼트</t>
@@ -2310,7 +2319,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%B9%B4%EC%B8%84%EC%8B%AD%EB%B3%BC%ED%8A%B8</t>
   </si>
   <si>
-    <t>17조 3674억 9491만</t>
+    <t>19조 196억 3690만</t>
   </si>
 </sst>
 </file>
@@ -2920,16 +2929,16 @@
         <v>29</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>33</v>
@@ -2937,22 +2946,22 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>18</v>
@@ -2961,7 +2970,7 @@
         <v>29</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>61</v>
@@ -2973,7 +2982,7 @@
         <v>63</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3012,7 +3021,7 @@
         <v>70</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3225,13 +3234,13 @@
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3242,25 +3251,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>112</v>
@@ -3292,7 +3301,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>116</v>
@@ -3388,7 +3397,7 @@
         <v>129</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>130</v>
@@ -3420,7 +3429,7 @@
         <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>134</v>
@@ -3452,7 +3461,7 @@
         <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>138</v>
@@ -3484,7 +3493,7 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>142</v>
@@ -3513,13 +3522,13 @@
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3530,28 +3539,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3562,25 +3571,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>157</v>
@@ -3609,10 +3618,10 @@
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>161</v>
@@ -3629,25 +3638,25 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3658,25 +3667,25 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>170</v>
@@ -3708,7 +3717,7 @@
         <v>174</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>175</v>
@@ -3740,7 +3749,7 @@
         <v>95</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>179</v>
@@ -3804,7 +3813,7 @@
         <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>188</v>
@@ -3865,7 +3874,7 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>197</v>
@@ -3882,28 +3891,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3914,7 +3923,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>203</v>
@@ -3929,7 +3938,7 @@
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>197</v>
@@ -3961,7 +3970,7 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>197</v>
@@ -3978,16 +3987,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -3999,7 +4008,7 @@
         <v>183</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4010,7 +4019,7 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>214</v>
@@ -4177,7 +4186,7 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>223</v>
@@ -4209,7 +4218,7 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>226</v>
@@ -4241,7 +4250,7 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>229</v>
@@ -4287,7 +4296,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>233</v>
@@ -4302,7 +4311,7 @@
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>96</v>
@@ -4334,13 +4343,13 @@
         <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>33</v>
@@ -4354,19 +4363,19 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>96</v>
@@ -4398,10 +4407,10 @@
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>245</v>
@@ -4433,7 +4442,7 @@
         <v>129</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>248</v>
@@ -4465,7 +4474,7 @@
         <v>124</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>251</v>
@@ -4494,10 +4503,10 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>254</v>
@@ -4526,10 +4535,10 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>257</v>
@@ -4561,7 +4570,7 @@
         <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>260</v>
@@ -4575,7 +4584,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>261</v>
@@ -4590,10 +4599,10 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>263</v>
@@ -4607,7 +4616,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>264</v>
@@ -4622,10 +4631,10 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>266</v>
@@ -4657,7 +4666,7 @@
         <v>269</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>270</v>
@@ -4686,10 +4695,10 @@
         <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>273</v>
@@ -4703,7 +4712,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>274</v>
@@ -4753,7 +4762,7 @@
         <v>129</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>279</v>
@@ -4782,10 +4791,10 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>282</v>
@@ -4817,7 +4826,7 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>285</v>
@@ -4849,7 +4858,7 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>288</v>
@@ -4910,7 +4919,7 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>183</v>
@@ -4927,7 +4936,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>295</v>
@@ -4959,7 +4968,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>298</v>
@@ -4977,7 +4986,7 @@
         <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>300</v>
@@ -5023,7 +5032,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>32</v>
@@ -5035,7 +5044,7 @@
         <v>304</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>89</v>
@@ -5055,7 +5064,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>307</v>
@@ -5122,7 +5131,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5280,7 +5289,7 @@
         <v>319</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>95</v>
@@ -5315,7 +5324,7 @@
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>101</v>
@@ -5332,7 +5341,7 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -5350,7 +5359,7 @@
         <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>326</v>
@@ -5382,7 +5391,7 @@
         <v>124</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>329</v>
@@ -5414,7 +5423,7 @@
         <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>332</v>
@@ -5443,10 +5452,10 @@
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>335</v>
@@ -5478,7 +5487,7 @@
         <v>129</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>338</v>
@@ -5510,7 +5519,7 @@
         <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>341</v>
@@ -5542,7 +5551,7 @@
         <v>269</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>344</v>
@@ -5574,7 +5583,7 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>347</v>
@@ -5620,7 +5629,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>351</v>
@@ -5635,10 +5644,10 @@
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>353</v>
@@ -5652,7 +5661,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>354</v>
@@ -5667,10 +5676,10 @@
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>356</v>
@@ -5702,7 +5711,7 @@
         <v>89</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>359</v>
@@ -5734,7 +5743,7 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>362</v>
@@ -5748,7 +5757,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>363</v>
@@ -5859,7 +5868,7 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>183</v>
@@ -5955,10 +5964,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>305</v>
+        <v>197</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>383</v>
@@ -5972,7 +5981,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>384</v>
@@ -5987,10 +5996,10 @@
         <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>386</v>
@@ -6004,7 +6013,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>387</v>
@@ -6051,7 +6060,7 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>241</v>
+        <v>124</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>305</v>
@@ -6068,7 +6077,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>393</v>
@@ -6083,7 +6092,7 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>305</v>
@@ -6100,7 +6109,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>396</v>
@@ -6115,20 +6124,52 @@
         <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="H31" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J32"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6160,6 +6201,7 @@
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
     <hyperlink ref="E31" r:id="rId30"/>
+    <hyperlink ref="E32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6220,13 +6262,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -6238,7 +6280,7 @@
         <v>219</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6252,25 +6294,25 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6284,13 +6326,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -6302,7 +6344,7 @@
         <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6322,10 +6364,10 @@
         <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>89</v>
@@ -6334,7 +6376,7 @@
         <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6348,25 +6390,25 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>96</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6377,16 +6419,16 @@
         <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -6395,10 +6437,10 @@
         <v>124</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6412,13 +6454,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -6427,10 +6469,10 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6444,13 +6486,13 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -6459,10 +6501,10 @@
         <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6476,13 +6518,13 @@
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -6491,10 +6533,10 @@
         <v>124</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6508,13 +6550,13 @@
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -6523,10 +6565,10 @@
         <v>129</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6540,25 +6582,25 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6572,25 +6614,25 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6604,25 +6646,25 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>183</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6636,25 +6678,25 @@
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>241</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6665,28 +6707,28 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6697,16 +6739,16 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
@@ -6718,7 +6760,7 @@
         <v>183</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6732,25 +6774,25 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>183</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6764,13 +6806,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -6782,7 +6824,7 @@
         <v>197</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6793,16 +6835,16 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -6811,10 +6853,10 @@
         <v>129</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6828,25 +6870,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6860,13 +6902,13 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -6878,7 +6920,7 @@
         <v>183</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6892,25 +6934,25 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6924,13 +6966,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -6939,10 +6981,10 @@
         <v>192</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>398</v>
+        <v>305</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6956,25 +6998,25 @@
         <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>305</v>
+        <v>197</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6988,13 +7030,13 @@
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -7006,7 +7048,7 @@
         <v>197</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7017,16 +7059,16 @@
         <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -7038,7 +7080,7 @@
         <v>197</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7049,16 +7091,16 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -7067,10 +7109,10 @@
         <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>398</v>
+        <v>305</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7084,25 +7126,25 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>305</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7113,28 +7155,28 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>305</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7145,16 +7187,16 @@
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -7163,10 +7205,10 @@
         <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7265,25 +7307,25 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>33</v>
@@ -7297,13 +7339,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -7315,7 +7357,7 @@
         <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>33</v>
@@ -7329,13 +7371,13 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -7347,7 +7389,7 @@
         <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>33</v>
@@ -7361,13 +7403,13 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -7376,10 +7418,10 @@
         <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>33</v>
@@ -7393,25 +7435,25 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>33</v>
@@ -7422,28 +7464,28 @@
         <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>33</v>
@@ -7457,13 +7499,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -7472,10 +7514,10 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>33</v>
@@ -7489,25 +7531,25 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>33</v>
@@ -7521,25 +7563,25 @@
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>33</v>
@@ -7553,13 +7595,13 @@
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -7571,7 +7613,7 @@
         <v>183</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>33</v>
@@ -7585,25 +7627,25 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>522</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>522</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>174</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>33</v>
@@ -7617,25 +7659,25 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>521</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>521</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>33</v>
@@ -7649,13 +7691,13 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -7664,10 +7706,10 @@
         <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>33</v>
@@ -7681,13 +7723,13 @@
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -7696,10 +7738,10 @@
         <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>33</v>
@@ -7710,28 +7752,28 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>33</v>
@@ -7742,28 +7784,28 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>33</v>
@@ -7777,25 +7819,25 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>33</v>
@@ -7809,13 +7851,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -7824,10 +7866,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>33</v>
@@ -7838,16 +7880,16 @@
         <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -7856,10 +7898,10 @@
         <v>129</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>33</v>
@@ -7873,13 +7915,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -7891,7 +7933,7 @@
         <v>183</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>33</v>
@@ -7905,13 +7947,13 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -7920,10 +7962,10 @@
         <v>95</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>305</v>
+        <v>183</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>33</v>
@@ -7937,13 +7979,13 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -7952,10 +7994,10 @@
         <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>183</v>
+        <v>305</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>33</v>
@@ -7969,13 +8011,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -7984,10 +8026,10 @@
         <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>33</v>
@@ -8001,13 +8043,13 @@
         <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -8019,7 +8061,7 @@
         <v>197</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>33</v>
@@ -8033,13 +8075,13 @@
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -8051,7 +8093,7 @@
         <v>305</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>33</v>
@@ -8062,16 +8104,16 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -8083,7 +8125,7 @@
         <v>197</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>33</v>
@@ -8094,16 +8136,16 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -8115,7 +8157,7 @@
         <v>305</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>33</v>
@@ -8129,13 +8171,13 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -8144,10 +8186,10 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>398</v>
+        <v>197</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>33</v>
@@ -8158,16 +8200,16 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -8176,10 +8218,10 @@
         <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>197</v>
+        <v>401</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>33</v>
@@ -8271,7 +8313,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
@@ -8283,71 +8325,71 @@
         <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -8356,94 +8398,94 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>305</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -8452,94 +8494,94 @@
         <v>129</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>305</v>
+        <v>197</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>305</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -8551,27 +8593,27 @@
         <v>305</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -8580,30 +8622,30 @@
         <v>124</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -8612,190 +8654,190 @@
         <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>398</v>
+        <v>614</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>607</v>
+        <v>401</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -8804,30 +8846,30 @@
         <v>89</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -8836,30 +8878,30 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -8868,30 +8910,30 @@
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -8900,30 +8942,30 @@
         <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -8932,30 +8974,30 @@
         <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -8964,30 +9006,30 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -8996,30 +9038,30 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -9028,30 +9070,30 @@
         <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -9060,30 +9102,30 @@
         <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -9092,30 +9134,30 @@
         <v>129</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -9124,30 +9166,30 @@
         <v>129</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -9156,30 +9198,30 @@
         <v>129</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -9188,13 +9230,13 @@
         <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -9289,13 +9331,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -9307,10 +9349,10 @@
         <v>90</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -9327,22 +9369,22 @@
         <v>70</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>95</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -9353,28 +9395,28 @@
         <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -9385,13 +9427,13 @@
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -9400,13 +9442,13 @@
         <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -9417,13 +9459,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -9435,10 +9477,10 @@
         <v>197</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -9446,16 +9488,16 @@
         <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -9464,13 +9506,13 @@
         <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -9481,13 +9523,13 @@
         <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -9496,13 +9538,13 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>398</v>
+        <v>614</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -9513,13 +9555,13 @@
         <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -9528,13 +9570,13 @@
         <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>617</v>
+        <v>401</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -9545,13 +9587,13 @@
         <v>121</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -9560,13 +9602,13 @@
         <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -9577,13 +9619,13 @@
         <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -9592,13 +9634,13 @@
         <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -9609,28 +9651,28 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>702</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>607</v>
+        <v>636</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -9641,13 +9683,13 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -9656,13 +9698,13 @@
         <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>649</v>
+        <v>610</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -9673,28 +9715,28 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>705</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -9705,13 +9747,13 @@
         <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -9720,13 +9762,13 @@
         <v>269</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -9734,16 +9776,16 @@
         <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -9752,13 +9794,13 @@
         <v>124</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -9766,31 +9808,31 @@
         <v>64</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>649</v>
+        <v>614</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -9801,28 +9843,28 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>633</v>
+        <v>652</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -9833,13 +9875,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -9848,13 +9890,13 @@
         <v>124</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -9862,16 +9904,16 @@
         <v>64</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -9880,13 +9922,13 @@
         <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -9897,13 +9939,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -9912,13 +9954,13 @@
         <v>124</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -9929,28 +9971,28 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -9961,13 +10003,13 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -9976,13 +10018,13 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -9993,13 +10035,13 @@
         <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -10008,13 +10050,13 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -10025,13 +10067,13 @@
         <v>189</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -10040,13 +10082,13 @@
         <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -10057,13 +10099,13 @@
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -10072,13 +10114,13 @@
         <v>124</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -10086,16 +10128,16 @@
         <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -10104,13 +10146,13 @@
         <v>124</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -10118,16 +10160,16 @@
         <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -10136,13 +10178,13 @@
         <v>124</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -10153,13 +10195,13 @@
         <v>206</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -10168,13 +10210,13 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -10182,16 +10224,16 @@
         <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -10200,13 +10242,13 @@
         <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -10214,16 +10256,16 @@
         <v>64</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -10232,13 +10274,13 @@
         <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -12,18 +12,18 @@
     <sheet name="레플리카셋" sheetId="3" r:id="rId3"/>
     <sheet name="점프킹" sheetId="4" r:id="rId4"/>
     <sheet name="귀여미" sheetId="5" r:id="rId5"/>
-    <sheet name="리안" sheetId="6" r:id="rId6"/>
-    <sheet name="셀린느" sheetId="7" r:id="rId7"/>
+    <sheet name="셀린느" sheetId="6" r:id="rId6"/>
+    <sheet name="리안" sheetId="7" r:id="rId7"/>
     <sheet name="브리또" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">귀여미!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">레플리카셋!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">리안!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">리안!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">브리또!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">셀린느!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">점프킹!$A$1:$J$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>1073경 7739조 4056억 1700만</t>
+    <t>1089경 6103조 5933억 8200만</t>
   </si>
   <si>
     <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
@@ -105,7 +105,7 @@
     <t>설익은체리</t>
   </si>
   <si>
-    <t>2026.09.19</t>
+    <t>2026.09.20</t>
   </si>
   <si>
     <t>레플리카셋</t>
@@ -117,1341 +117,1341 @@
     <t>Scania 32</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>1200경 7284조 1008억 2700만</t>
+  </si>
+  <si>
+    <t>가입 문의: 코빨간돌프/깔지마오 &amp;lt;No.1 레플&amp;gt;</t>
+  </si>
+  <si>
+    <t>코빨간돌프</t>
+  </si>
+  <si>
+    <t>점프킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
+  </si>
+  <si>
+    <t>Scania 5</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>1113경 6549조 7565억 5899만</t>
+  </si>
+  <si>
+    <t>뛰어</t>
+  </si>
+  <si>
+    <t>아크메이딩동</t>
+  </si>
+  <si>
+    <t>귀여미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B7%80%EC%97%AC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>Scania 34</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>989경 8536조 5822억 5369만</t>
+  </si>
+  <si>
+    <t>가입 문의는 스탠딩메이지</t>
+  </si>
+  <si>
+    <t>슈랄</t>
+  </si>
+  <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>677경 9011조 3320억 5240만</t>
+  </si>
+  <si>
+    <t>문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>773경 3194조 5701억 330만</t>
+  </si>
+  <si>
+    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
+  </si>
+  <si>
+    <t>예습2</t>
+  </si>
+  <si>
+    <t>브리또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%8C%EB%A6%AC%EB%98%90</t>
+  </si>
+  <si>
+    <t>Scania 33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>627경 2089조 6861억 9290만</t>
+  </si>
+  <si>
+    <t>대항전 중점 길드, 컨텐츠 열심히 참여하실분! 같이 꾸준히 성장하실 분들 환영! 전투력 랭킹 100등 이상!</t>
+  </si>
+  <si>
+    <t>안데일2</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>마옥지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>239경 3650조 664억 5621만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>231경 7865조 5718억 420만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>캐일리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>151경 5004조 4630억 4973만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>킹규봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>62경 4188조 2543억 3793만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>52경 9932조 7914억 9061만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>45경 5109조 8480억 2031만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>39경 4856조 4335억 8984만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>39경 863조 8820억 7662만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
+  </si>
+  <si>
+    <t>35경 5866조 3798억 7180만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>시드리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>29경 7613조 5062억 2329만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
+  </si>
+  <si>
+    <t>22경 2622조 1388억 6246만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>셀렘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>21경 4753조 3765억 8338만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>마덕칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>18경 9870조 503억 9521만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>설딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
+  </si>
+  <si>
+    <t>18경 3564조 735억 3511만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>졸귀탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>15경 5795조 8588억 6810만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>13경 2105조 4816억 1933만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>경성2018</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>8경 1791조 1615억 2546만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>설름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>7경 4972조 6974억 1981만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>슐아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>7경 2382조 7642억 9212만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>5경 5478조 8492억 3032만</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>1200경 4158조 9063억 2800만</t>
-  </si>
-  <si>
-    <t>가입 문의: 코빨간돌프/깔지마오 &amp;lt;No.1 레플&amp;gt;</t>
-  </si>
-  <si>
-    <t>코빨간돌프</t>
-  </si>
-  <si>
-    <t>점프킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
-  </si>
-  <si>
-    <t>Scania 5</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>1106경 1096조 1412억 9499만</t>
-  </si>
-  <si>
-    <t>뛰어</t>
-  </si>
-  <si>
-    <t>아크메이딩동</t>
-  </si>
-  <si>
-    <t>귀여미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B7%80%EC%97%AC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>Scania 34</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>988경 8134조 9255억 8989만</t>
-  </si>
-  <si>
-    <t>가입 문의는 스탠딩메이지</t>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>5경 4783조 8696억 6956만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>5경 3005조 1147억 1318만</t>
+  </si>
+  <si>
+    <t>수상구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>2경 5422조 8458억 5094만</t>
+  </si>
+  <si>
+    <t>견아니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>2경 3101조 7046억 6202만</t>
+  </si>
+  <si>
+    <t>공대애봉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>2경 1802조 9715억 751만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>설앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>1경 7395조 9535억 4782만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>설치는정상인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1경 4405조 2903억 5532만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>9562조 1082억 7865만</t>
+  </si>
+  <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>9554조 6832억 9248만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>8781조 4022억 5235만</t>
+  </si>
+  <si>
+    <t>쉐도우그림자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%89%90%EB%8F%84%EC%9A%B0%EA%B7%B8%EB%A6%BC%EC%9E%90</t>
+  </si>
+  <si>
+    <t>476경 7507조 7774억 8537만</t>
+  </si>
+  <si>
+    <t>루졔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>286경 266조 995억 2968만</t>
+  </si>
+  <si>
+    <t>혀로꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EA%BD%83</t>
+  </si>
+  <si>
+    <t>106경 6285조 8850억 3516만</t>
+  </si>
+  <si>
+    <t>SlowDown</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=SlowDown</t>
+  </si>
+  <si>
+    <t>81경 5990조 9819억 6076만</t>
+  </si>
+  <si>
+    <t>뻥투기릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>65경 9932조 965억 1300만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%B9%A8%EA%B0%84%EB%8F%8C%ED%94%84</t>
+  </si>
+  <si>
+    <t>60경 5085조 4583억 8918만</t>
+  </si>
+  <si>
+    <t>기뚠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9A%A0</t>
+  </si>
+  <si>
+    <t>19경 4042조 5748억 8253만</t>
+  </si>
+  <si>
+    <t>쌰갈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%B0%EA%B0%88</t>
+  </si>
+  <si>
+    <t>17경 8782조 8938억 1126만</t>
+  </si>
+  <si>
+    <t>911TurboS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
+  </si>
+  <si>
+    <t>16경 1922조 7926억 2892만</t>
+  </si>
+  <si>
+    <t>하싱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
+  </si>
+  <si>
+    <t>12경 1991조 9300억 2209만</t>
+  </si>
+  <si>
+    <t>김라이트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>8경 6972조 5711억 9285만</t>
+  </si>
+  <si>
+    <t>어쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EC%93%B0</t>
+  </si>
+  <si>
+    <t>7경 7034조 5842억 5107만</t>
+  </si>
+  <si>
+    <t>최슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>5경 4251조 3619억 5465만</t>
+  </si>
+  <si>
+    <t>명품까칠공주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>5경 1012조 7398억 5095만</t>
+  </si>
+  <si>
+    <t>오이겐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
+  </si>
+  <si>
+    <t>4경 6228조 7401억 5505만</t>
+  </si>
+  <si>
+    <t>뿔피리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>4경 3971조 1941억 860만</t>
+  </si>
+  <si>
+    <t>깔지마오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EC%A7%80%EB%A7%88%EC%98%A4</t>
+  </si>
+  <si>
+    <t>2경 9330조 6252억 5962만</t>
+  </si>
+  <si>
+    <t>탄지로네즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2경 9296조 7213억 5282만</t>
+  </si>
+  <si>
+    <t>플더</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%8D%94</t>
+  </si>
+  <si>
+    <t>2경 8099조 9321억 3893만</t>
+  </si>
+  <si>
+    <t>이솔빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>2경 2709조 1532억 2189만</t>
+  </si>
+  <si>
+    <t>무명장수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%AA%85%EC%9E%A5%EC%88%98</t>
+  </si>
+  <si>
+    <t>2경 646조 1663억 9601만</t>
+  </si>
+  <si>
+    <t>멀해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%80%ED%95%B4</t>
+  </si>
+  <si>
+    <t>1경 6272조 175억 1648만</t>
+  </si>
+  <si>
+    <t>일단대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EB%8B%A8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1경 5136조 8361억 7335만</t>
+  </si>
+  <si>
+    <t>할끄야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%81%84%EC%95%BC</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>1경 2635조 4189억 4866만</t>
+  </si>
+  <si>
+    <t>루픠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%94%A0</t>
+  </si>
+  <si>
+    <t>1경 1892조 3515억 2521만</t>
+  </si>
+  <si>
+    <t>샹끄스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%B9%EB%81%84%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1경 979조 7090억 9802만</t>
+  </si>
+  <si>
+    <t>삼치회</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%B9%98%ED%9A%8C</t>
+  </si>
+  <si>
+    <t>8988조 1176억 7371만</t>
+  </si>
+  <si>
+    <t>어흫</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%AB</t>
+  </si>
+  <si>
+    <t>6882조 6419억 41만</t>
+  </si>
+  <si>
+    <t>멍쥐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EC%A5%90</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>3134조 7278억 5071만</t>
+  </si>
+  <si>
+    <t>라온XR</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8XR</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>432경 9223조 8741억 1396만</t>
+  </si>
+  <si>
+    <t>매스몬스터</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%AA%AC%EC%8A%A4%ED%84%B0</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>200경 8168조 6070억 3417만</t>
+  </si>
+  <si>
+    <t>하잉안파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>138경 1350조 7423억 259만</t>
+  </si>
+  <si>
+    <t>타이슨에어랩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
+  </si>
+  <si>
+    <t>49경 9381조 8066억 9716만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
+  </si>
+  <si>
+    <t>48경 9698조 8877억 6533만</t>
+  </si>
+  <si>
+    <t>미야고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%95%BC%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>47경 8006조 1800억 8094만</t>
+  </si>
+  <si>
+    <t>캔드릭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
+  </si>
+  <si>
+    <t>31경 3892조 796억 6625만</t>
+  </si>
+  <si>
+    <t>용보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>27경 4795조 8297억 625만</t>
+  </si>
+  <si>
+    <t>코코듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
+  </si>
+  <si>
+    <t>25경 4335조 5085억 901만</t>
+  </si>
+  <si>
+    <t>진압조</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
+  </si>
+  <si>
+    <t>21경 6353조 2736억 4672만</t>
+  </si>
+  <si>
+    <t>똥갈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
+  </si>
+  <si>
+    <t>14경 7872조 6408억 1802만</t>
+  </si>
+  <si>
+    <t>도적왕대현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EC%99%95%EB%8C%80%ED%98%84</t>
+  </si>
+  <si>
+    <t>10경 4325조 779억 3391만</t>
+  </si>
+  <si>
+    <t>도농롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%86%8D%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>10경 1936조 5029억 104만</t>
+  </si>
+  <si>
+    <t>힐옹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%98%B9</t>
+  </si>
+  <si>
+    <t>7경 3381조 1161억 5055만</t>
+  </si>
+  <si>
+    <t>반불</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
+  </si>
+  <si>
+    <t>5경 4711조 9552억 8177만</t>
+  </si>
+  <si>
+    <t>진쎅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%8E%85</t>
+  </si>
+  <si>
+    <t>5경 1642조 7677억 9914만</t>
+  </si>
+  <si>
+    <t>조명준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
+  </si>
+  <si>
+    <t>5경 720조 9496억 1123만</t>
+  </si>
+  <si>
+    <t>Redwine</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Redwine</t>
+  </si>
+  <si>
+    <t>4경 7803조 2952억 5856만</t>
+  </si>
+  <si>
+    <t>로생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
+  </si>
+  <si>
+    <t>4경 5141조 2898억 2799만</t>
+  </si>
+  <si>
+    <t>이다연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>4경 5048조 8438억 6980만</t>
+  </si>
+  <si>
+    <t>탤포</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%A4%ED%8F%AC</t>
+  </si>
+  <si>
+    <t>4경 1816조 4322억 9283만</t>
+  </si>
+  <si>
+    <t>그때그아이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2경 8964조 6795억 4359만</t>
+  </si>
+  <si>
+    <t>메키메렁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
+  </si>
+  <si>
+    <t>2경 7839조 9823억 8751만</t>
+  </si>
+  <si>
+    <t>서동구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8F%99%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>2경 2117조 4871억 3585만</t>
+  </si>
+  <si>
+    <t>꽁꽁얼었다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EC%96%BC%EC%97%88%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2경 415조 4230억 7944만</t>
+  </si>
+  <si>
+    <t>막또날드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
+  </si>
+  <si>
+    <t>1경 2868조 9507억 2068만</t>
+  </si>
+  <si>
+    <t>정희롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%9D%AC%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>8024조 4683억 4802만</t>
+  </si>
+  <si>
+    <t>안성대통령</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%84%B1%EB%8C%80%ED%86%B5%EB%A0%B9</t>
+  </si>
+  <si>
+    <t>6711조 1040억 7698만</t>
+  </si>
+  <si>
+    <t>라온JW</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8JW</t>
+  </si>
+  <si>
+    <t>480경 4353조 6531억 1401만</t>
+  </si>
+  <si>
+    <t>금은동S2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%EC%9D%80%EB%8F%99S2</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>361경 2344조 1033억 6930만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
+  </si>
+  <si>
+    <t>38경 6851조 2177억 7226만</t>
+  </si>
+  <si>
+    <t>아마날</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
+  </si>
+  <si>
+    <t>34경 8416조 6359억 8023만</t>
+  </si>
+  <si>
+    <t>쁘덍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%81%98%EB%8D%8D</t>
+  </si>
+  <si>
+    <t>10경 4233조 5280억 4183만</t>
+  </si>
+  <si>
+    <t>임홀리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>9경 4153조 805억 2573만</t>
+  </si>
+  <si>
+    <t>문신담배돼지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%8B%A0%EB%8B%B4%EB%B0%B0%EB%8F%BC%EC%A7%80</t>
+  </si>
+  <si>
+    <t>9경 2860조 5785억 5451만</t>
+  </si>
+  <si>
+    <t>제껴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
+  </si>
+  <si>
+    <t>8경 8259조 6479억 5030만</t>
+  </si>
+  <si>
+    <t>리브루므</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%B8%8C%EB%A3%A8%EB%AF%80</t>
+  </si>
+  <si>
+    <t>6경 1607조 2759억 2889만</t>
+  </si>
+  <si>
+    <t>우꼬쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>4경 928조 4628억 9427만</t>
+  </si>
+  <si>
+    <t>비밀키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
+  </si>
+  <si>
+    <t>3경 8363조 108억 1090만</t>
+  </si>
+  <si>
+    <t>누룽지룽누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EB%A3%BD%EC%A7%80%EB%A3%BD%EB%88%84</t>
+  </si>
+  <si>
+    <t>3경 8026조 9739억 7864만</t>
+  </si>
+  <si>
+    <t>어흥이다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>3경 5814조 8841억 8452만</t>
+  </si>
+  <si>
+    <t>지아라떼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%84%EB%9D%BC%EB%96%BC</t>
+  </si>
+  <si>
+    <t>2경 4160조 3615억 4238만</t>
+  </si>
+  <si>
+    <t>득츈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
+  </si>
+  <si>
+    <t>1경 9207조 5074억 5072만</t>
+  </si>
+  <si>
+    <t>붙잡아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
+  </si>
+  <si>
+    <t>1경 9163조 620억 1118만</t>
+  </si>
+  <si>
+    <t>슛맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>1경 8264조 7627억 870만</t>
+  </si>
+  <si>
+    <t>메론맛빵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
+  </si>
+  <si>
+    <t>1경 6582조 2316억 1444만</t>
+  </si>
+  <si>
+    <t>유깡깡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EA%B9%A1%EA%B9%A1</t>
+  </si>
+  <si>
+    <t>9304조 1012억 5646만</t>
+  </si>
+  <si>
+    <t>왕컹스맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%BB%B9%EC%8A%A4%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>9143조 6493억 6052만</t>
+  </si>
+  <si>
+    <t>출장괴물</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
+  </si>
+  <si>
+    <t>6634조 5766억 6072만</t>
+  </si>
+  <si>
+    <t>쏨열무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>6041조 2534억 6541만</t>
+  </si>
+  <si>
+    <t>이사통역</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%AC%ED%86%B5%EC%97%AD</t>
+  </si>
+  <si>
+    <t>5573조 4278억 8576만</t>
+  </si>
+  <si>
+    <t>원덍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%8D%8D</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>4192조 9713억 8802만</t>
+  </si>
+  <si>
+    <t>알테신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%ED%85%8C%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>3777조 3160억 2879만</t>
+  </si>
+  <si>
+    <t>갬두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AC%EB%91%90</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>3462조 2733억 2571만</t>
+  </si>
+  <si>
+    <t>뭉탕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AD%89%ED%83%95</t>
+  </si>
+  <si>
+    <t>2754조 9902억 925만</t>
   </si>
   <si>
     <t>스탠딩메이지</t>
   </si>
   <si>
-    <t>리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>772경 9666조 1583억 4720만</t>
-  </si>
-  <si>
-    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
-  </si>
-  <si>
-    <t>예습2</t>
-  </si>
-  <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>673경 5292조 3781억 1219만</t>
-  </si>
-  <si>
-    <t>문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>브리또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%8C%EB%A6%AC%EB%98%90</t>
-  </si>
-  <si>
-    <t>Scania 33</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>626경 3766조 7199억 5539만</t>
-  </si>
-  <si>
-    <t>대항전 중점 길드, 컨텐츠 열심히 참여하실분! 같이 꾸준히 성장하실 분들 환영! 전투력 랭킹 100등 이상!</t>
-  </si>
-  <si>
-    <t>안데일2</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>해물만두야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>231경 7865조 5718억 420만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>마옥지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
-  </si>
-  <si>
-    <t>229경 8495조 7258억 379만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>캐일리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>151경 4649조 5542억 9866만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>킹규봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>62경 4188조 2543억 3793만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>설함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>52경 9932조 7914억 9061만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>루델밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>45경 5109조 8480억 2031만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>39경 1509조 7156억 9977만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>39경 863조 8820억 7662만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>너굴얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
-  </si>
-  <si>
-    <t>35경 5866조 3798억 7180만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>시드리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>29경 7613조 5062억 2329만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>싲프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
-  </si>
-  <si>
-    <t>22경 2514조 1356억 9157만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>셀렘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>21경 4753조 3765억 8338만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>마덕칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>18경 9870조 503억 9521만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>졸귀탱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>15경 5172조 196억 122만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>13경 2105조 4816억 1933만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>설딩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
-  </si>
-  <si>
-    <t>12경 7975조 8170억 5111만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>경성2018</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>8경 1791조 1615억 2546만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>설름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>7경 4972조 6974억 1981만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>슐아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>7경 2382조 7642억 9212만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>5경 5478조 8492억 3032만</t>
-  </si>
-  <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>5경 4783조 8696억 6956만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>5경 90조 1569억 6839만</t>
-  </si>
-  <si>
-    <t>수상구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>2경 5422조 8458억 5094만</t>
-  </si>
-  <si>
-    <t>견아니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>2경 3101조 7046억 6202만</t>
-  </si>
-  <si>
-    <t>공대애봉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>2경 1802조 9715억 751만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>설앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>1경 7395조 9535억 4782만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>설치는정상인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>1경 4405조 2903억 5532만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>9554조 6832억 9248만</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>9288조 9444억 7420만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>8781조 4022억 5235만</t>
-  </si>
-  <si>
-    <t>쉐도우그림자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%89%90%EB%8F%84%EC%9A%B0%EA%B7%B8%EB%A6%BC%EC%9E%90</t>
-  </si>
-  <si>
-    <t>476경 7507조 7774억 8537만</t>
-  </si>
-  <si>
-    <t>루졔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>285경 9613조 2773억 571만</t>
-  </si>
-  <si>
-    <t>혀로꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EA%BD%83</t>
-  </si>
-  <si>
-    <t>106경 6285조 8850억 3516만</t>
-  </si>
-  <si>
-    <t>SlowDown</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=SlowDown</t>
-  </si>
-  <si>
-    <t>81경 5990조 9819억 6076만</t>
-  </si>
-  <si>
-    <t>뻥투기릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>65경 9443조 4067억 9882만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%B9%A8%EA%B0%84%EB%8F%8C%ED%94%84</t>
-  </si>
-  <si>
-    <t>60경 5085조 4583억 8918만</t>
-  </si>
-  <si>
-    <t>기뚠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9A%A0</t>
-  </si>
-  <si>
-    <t>19경 4042조 5748억 8253만</t>
-  </si>
-  <si>
-    <t>쌰갈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%B0%EA%B0%88</t>
-  </si>
-  <si>
-    <t>17경 8124조 852억 8670만</t>
-  </si>
-  <si>
-    <t>911TurboS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
-  </si>
-  <si>
-    <t>16경 1874조 9982억 7730만</t>
-  </si>
-  <si>
-    <t>하싱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
-  </si>
-  <si>
-    <t>12경 1825조 1889억 6675만</t>
-  </si>
-  <si>
-    <t>김라이트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>8경 6972조 5711억 9285만</t>
-  </si>
-  <si>
-    <t>어쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EC%93%B0</t>
-  </si>
-  <si>
-    <t>7경 7034조 5842억 5107만</t>
-  </si>
-  <si>
-    <t>최슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>5경 4251조 3619억 5465만</t>
-  </si>
-  <si>
-    <t>명품까칠공주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>5경 1012조 7398억 5095만</t>
-  </si>
-  <si>
-    <t>오이겐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
-  </si>
-  <si>
-    <t>4경 6210조 7269억 5635만</t>
-  </si>
-  <si>
-    <t>뿔피리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>4경 3949조 8811억 7277만</t>
-  </si>
-  <si>
-    <t>깔지마오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EC%A7%80%EB%A7%88%EC%98%A4</t>
-  </si>
-  <si>
-    <t>2경 9330조 6252억 5962만</t>
-  </si>
-  <si>
-    <t>탄지로네즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2경 8982조 6965억 9696만</t>
-  </si>
-  <si>
-    <t>플더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%8D%94</t>
-  </si>
-  <si>
-    <t>2경 8099조 9321억 3893만</t>
-  </si>
-  <si>
-    <t>이솔빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>2경 2693조 3447억 2714만</t>
-  </si>
-  <si>
-    <t>무명장수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%AA%85%EC%9E%A5%EC%88%98</t>
-  </si>
-  <si>
-    <t>2경 646조 1663억 9601만</t>
-  </si>
-  <si>
-    <t>멀해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%80%ED%95%B4</t>
-  </si>
-  <si>
-    <t>1경 6272조 175억 1648만</t>
-  </si>
-  <si>
-    <t>일단대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EB%8B%A8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1경 5136조 8361억 7335만</t>
-  </si>
-  <si>
-    <t>할끄야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%81%84%EC%95%BC</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>1경 2635조 4189억 4866만</t>
-  </si>
-  <si>
-    <t>루픠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%94%A0</t>
-  </si>
-  <si>
-    <t>1경 1892조 3515억 2521만</t>
-  </si>
-  <si>
-    <t>샹끄스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%B9%EB%81%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1경 251조 6317억 1486만</t>
-  </si>
-  <si>
-    <t>삼치회</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%B9%98%ED%9A%8C</t>
-  </si>
-  <si>
-    <t>8988조 1176억 7371만</t>
-  </si>
-  <si>
-    <t>어흫</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%AB</t>
-  </si>
-  <si>
-    <t>6869조 5400억 3918만</t>
-  </si>
-  <si>
-    <t>멍쥐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EC%A5%90</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>3134조 7278억 5071만</t>
-  </si>
-  <si>
-    <t>라온XR</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8XR</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>432경 9223조 8741억 1396만</t>
-  </si>
-  <si>
-    <t>매스몬스터</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%AA%AC%EC%8A%A4%ED%84%B0</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>200경 8168조 6070억 3417만</t>
-  </si>
-  <si>
-    <t>하잉안파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>132경 7317조 2771억 9115만</t>
-  </si>
-  <si>
-    <t>타이슨에어랩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
-  </si>
-  <si>
-    <t>49경 9381조 8066억 9716만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
-  </si>
-  <si>
-    <t>48경 9698조 8877억 6533만</t>
-  </si>
-  <si>
-    <t>미야고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%95%BC%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>47경 8006조 1800억 8094만</t>
-  </si>
-  <si>
-    <t>캔드릭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
-  </si>
-  <si>
-    <t>31경 3892조 796억 6625만</t>
-  </si>
-  <si>
-    <t>용보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>27경 4477조 3956억 8675만</t>
-  </si>
-  <si>
-    <t>코코듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
-  </si>
-  <si>
-    <t>25경 150조 7556억 4808만</t>
-  </si>
-  <si>
-    <t>진압조</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
-  </si>
-  <si>
-    <t>21경 5656조 8966억 4658만</t>
-  </si>
-  <si>
-    <t>똥갈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
-  </si>
-  <si>
-    <t>14경 7613조 116억 7536만</t>
-  </si>
-  <si>
-    <t>도농롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%86%8D%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>10경 1936조 5029억 104만</t>
-  </si>
-  <si>
-    <t>도적왕대현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EC%99%95%EB%8C%80%ED%98%84</t>
-  </si>
-  <si>
-    <t>8경 9754조 7736억 9961만</t>
-  </si>
-  <si>
-    <t>힐옹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%98%B9</t>
-  </si>
-  <si>
-    <t>7경 3381조 1161억 5055만</t>
-  </si>
-  <si>
-    <t>반불</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
-  </si>
-  <si>
-    <t>5경 4711조 9552억 8177만</t>
-  </si>
-  <si>
-    <t>진쎅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%8E%85</t>
-  </si>
-  <si>
-    <t>5경 1642조 7677억 9914만</t>
-  </si>
-  <si>
-    <t>조명준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
-  </si>
-  <si>
-    <t>5경 720조 9496억 1123만</t>
-  </si>
-  <si>
-    <t>Redwine</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Redwine</t>
-  </si>
-  <si>
-    <t>4경 7375조 9717억 7315만</t>
-  </si>
-  <si>
-    <t>로생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
-  </si>
-  <si>
-    <t>4경 5141조 2898억 2799만</t>
-  </si>
-  <si>
-    <t>이다연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>4경 4904조 616억 8594만</t>
-  </si>
-  <si>
-    <t>탤포</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%A4%ED%8F%AC</t>
-  </si>
-  <si>
-    <t>4경 1816조 4322억 9283만</t>
-  </si>
-  <si>
-    <t>그때그아이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2경 8457조 6517억 3028만</t>
-  </si>
-  <si>
-    <t>메키메렁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
-  </si>
-  <si>
-    <t>2경 7839조 9823억 8751만</t>
-  </si>
-  <si>
-    <t>서동구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8F%99%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>2경 2117조 4871억 3585만</t>
-  </si>
-  <si>
-    <t>꽁꽁얼었다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EC%96%BC%EC%97%88%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2경 415조 4230억 7944만</t>
-  </si>
-  <si>
-    <t>막또날드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
-  </si>
-  <si>
-    <t>1경 2557조 4313억 810만</t>
-  </si>
-  <si>
-    <t>정희롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%9D%AC%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>8024조 4683억 4802만</t>
-  </si>
-  <si>
-    <t>안성대통령</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%84%B1%EB%8C%80%ED%86%B5%EB%A0%B9</t>
-  </si>
-  <si>
-    <t>6711조 1040억 7698만</t>
-  </si>
-  <si>
-    <t>라온JW</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8JW</t>
-  </si>
-  <si>
-    <t>480경 4353조 6531억 1401만</t>
-  </si>
-  <si>
-    <t>금은동S2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%EC%9D%80%EB%8F%99S2</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>361경 2344조 1033억 6930만</t>
-  </si>
-  <si>
-    <t>슈랄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
-  </si>
-  <si>
-    <t>38경 6816조 3264억 5123만</t>
-  </si>
-  <si>
-    <t>아마날</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
-  </si>
-  <si>
-    <t>34경 8416조 6359억 8023만</t>
-  </si>
-  <si>
-    <t>쁘덍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%81%98%EB%8D%8D</t>
-  </si>
-  <si>
-    <t>10경 812조 4716억 8494만</t>
-  </si>
-  <si>
-    <t>임홀리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>9경 4153조 805억 2573만</t>
-  </si>
-  <si>
-    <t>문신담배돼지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%8B%A0%EB%8B%B4%EB%B0%B0%EB%8F%BC%EC%A7%80</t>
-  </si>
-  <si>
-    <t>9경 2860조 5785억 5451만</t>
-  </si>
-  <si>
-    <t>제껴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
-  </si>
-  <si>
-    <t>8경 3744조 2794억 2104만</t>
-  </si>
-  <si>
-    <t>리브루므</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%B8%8C%EB%A3%A8%EB%AF%80</t>
-  </si>
-  <si>
-    <t>6경 1607조 2759억 2889만</t>
-  </si>
-  <si>
-    <t>우꼬쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>4경 928조 4628억 9427만</t>
-  </si>
-  <si>
-    <t>비밀키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
-  </si>
-  <si>
-    <t>3경 8363조 108억 1090만</t>
-  </si>
-  <si>
-    <t>누룽지룽누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EB%A3%BD%EC%A7%80%EB%A3%BD%EB%88%84</t>
-  </si>
-  <si>
-    <t>3경 8026조 9739억 7864만</t>
-  </si>
-  <si>
-    <t>어흥이다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>3경 5772조 6477억 9262만</t>
-  </si>
-  <si>
-    <t>지아라떼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%84%EB%9D%BC%EB%96%BC</t>
-  </si>
-  <si>
-    <t>2경 3291조 2438억 5346만</t>
-  </si>
-  <si>
-    <t>득츈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
-  </si>
-  <si>
-    <t>1경 9207조 5074억 5072만</t>
-  </si>
-  <si>
-    <t>슛맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>1경 8260조 2785억 7588만</t>
-  </si>
-  <si>
-    <t>붙잡아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
-  </si>
-  <si>
-    <t>1경 7921조 7778억 5640만</t>
-  </si>
-  <si>
-    <t>메론맛빵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
-  </si>
-  <si>
-    <t>1경 6582조 2316억 1444만</t>
-  </si>
-  <si>
-    <t>유깡깡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EA%B9%A1%EA%B9%A1</t>
-  </si>
-  <si>
-    <t>9304조 1012억 5646만</t>
-  </si>
-  <si>
-    <t>왕컹스맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%BB%B9%EC%8A%A4%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>9080조 2446억 1887만</t>
-  </si>
-  <si>
-    <t>출장괴물</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
-  </si>
-  <si>
-    <t>6619조 4444억 129만</t>
-  </si>
-  <si>
-    <t>쏨열무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>6041조 2534억 6541만</t>
-  </si>
-  <si>
-    <t>이사통역</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%AC%ED%86%B5%EC%97%AD</t>
-  </si>
-  <si>
-    <t>5535조 9485억 6532만</t>
-  </si>
-  <si>
-    <t>원덍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%8D%8D</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>4185조 2539억 7196만</t>
-  </si>
-  <si>
-    <t>알테신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%ED%85%8C%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>3771조 7483억 8699만</t>
-  </si>
-  <si>
-    <t>갬두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%AC%EB%91%90</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>3375조 6764억 5027만</t>
-  </si>
-  <si>
-    <t>뭉탕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%89%ED%83%95</t>
-  </si>
-  <si>
-    <t>2698조 2551억 6544만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%A0%EB%94%A9%EB%A9%94%EC%9D%B4%EC%A7%80</t>
   </si>
   <si>
@@ -1476,7 +1476,274 @@
     <t>109</t>
   </si>
   <si>
-    <t>270조 3965억 358만</t>
+    <t>270조 9812억 9314만</t>
+  </si>
+  <si>
+    <t>빔냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>230경 375조 6847억 3301만</t>
+  </si>
+  <si>
+    <t>MNMMNMMNMMNM</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
+  </si>
+  <si>
+    <t>82경 6629조 1011억 3884만</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>59경 8932조 8415억 8249만</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>58경 2451조 9309억 7663만</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>45경 9931조 1583억 3973만</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>26경 7953조 6509억 6286만</t>
+  </si>
+  <si>
+    <t>뽀리빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>26경 7923조 9367억 2199만</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>25경 4823조 3360억 295만</t>
+  </si>
+  <si>
+    <t>부엉이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>15경 857조 7736억 9512만</t>
+  </si>
+  <si>
+    <t>걸음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>10경 4931조 5654억 7685만</t>
+  </si>
+  <si>
+    <t>천천히걸어가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
+  </si>
+  <si>
+    <t>10경 421조 9052억 6144만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>9경 7717조 5279억 6925만</t>
+  </si>
+  <si>
+    <t>국의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
+  </si>
+  <si>
+    <t>9경 7577조 4960억 8311만</t>
+  </si>
+  <si>
+    <t>익맹이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8경 5493조 5674억 6937만</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>7경 8676조 4971억 4482만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>7경 8132조 1663억 9724만</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>7경 3059조 933억 2511만</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>6경 4934조 151억 6468만</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>5경 8774조 7748억 8940만</t>
+  </si>
+  <si>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>5경 7132조 4680억 8461만</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>5경 5228조 9003억 4099만</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>1경 9039조 4842억 7168만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>1경 7944조 8437억 7238만</t>
+  </si>
+  <si>
+    <t>핫잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
+  </si>
+  <si>
+    <t>1경 5275조 752억 3008만</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1경 4618조 2500억 6149만</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 3784조 6932억 6395만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>1경 3172조 192억 1384만</t>
+  </si>
+  <si>
+    <t>아이스꾸임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
+  </si>
+  <si>
+    <t>1경 2961조 5558억 3160만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>1경 337조 3153억 1051만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>8232조 4493억 242만</t>
   </si>
   <si>
     <t>군보</t>
@@ -1494,7 +1761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%97%90%EB%B0%94%EB%9E%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>94경 6227조 2996억 4171만</t>
+    <t>94경 6651조 28억 1595만</t>
   </si>
   <si>
     <t>라온PB</t>
@@ -1509,7 +1776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
   </si>
   <si>
-    <t>63경 3086조 4893억 9267만</t>
+    <t>63경 3627조 945억 3403만</t>
   </si>
   <si>
     <t>Matter</t>
@@ -1518,7 +1785,7 @@
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>60경 339조 6350억 2632만</t>
+    <t>60경 2137조 6471억 89만</t>
   </si>
   <si>
     <t>혁수킹</t>
@@ -1563,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>28경 9236조 2434억 9997만</t>
+    <t>28경 9380조 1378억 8423만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -1581,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>10경 2139조 545억 6081만</t>
+    <t>10경 2294조 8734억 7967만</t>
   </si>
   <si>
     <t>악경</t>
@@ -1626,7 +1893,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%BA%90</t>
   </si>
   <si>
-    <t>3경 6071조 9160억 2452만</t>
+    <t>3경 6161조 8085억 1393만</t>
   </si>
   <si>
     <t>떠영아</t>
@@ -1671,7 +1938,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
   </si>
   <si>
-    <t>1경 5384조 8626억 1477만</t>
+    <t>1경 5752조 1911억 3914만</t>
   </si>
   <si>
     <t>표창빌런</t>
@@ -1698,7 +1965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%93%B0</t>
   </si>
   <si>
-    <t>7237조 9658억 4301만</t>
+    <t>7247조 66억 5048만</t>
   </si>
   <si>
     <t>미나별</t>
@@ -1728,274 +1995,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>44조 9295억 9035만</t>
-  </si>
-  <si>
-    <t>빔냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>228경 131조 6916억 361만</t>
-  </si>
-  <si>
-    <t>MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
-  </si>
-  <si>
-    <t>82경 5369조 9726억 1782만</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>59경 8932조 8415억 8249만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>57경 3507조 7593억 4456만</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>45경 8209조 1749억 7786만</t>
-  </si>
-  <si>
-    <t>뽀리빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>26경 7923조 9367억 2199만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>26경 4824조 3993억 8632만</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>24경 9930조 6612억 5723만</t>
-  </si>
-  <si>
-    <t>부엉이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>14경 9012조 3724억 7633만</t>
-  </si>
-  <si>
-    <t>걸음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>10경 4572조 1841억 4875만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>9경 7717조 5279억 6925만</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>9경 7134조 3747억 7858만</t>
-  </si>
-  <si>
-    <t>국의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
-  </si>
-  <si>
-    <t>9경 5359조 4682억 7643만</t>
-  </si>
-  <si>
-    <t>익맹이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8경 4785조 8773억 3366만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>7경 8016조 2969억 4906만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>7경 7727조 6633억 2044만</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>7경 3059조 933억 2511만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>6경 4885조 3111억 7395만</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>5경 8774조 7748억 8940만</t>
-  </si>
-  <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>5경 7118조 8624억 9362만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>5경 5228조 9003억 4099만</t>
-  </si>
-  <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>1경 9039조 4842억 7168만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>1경 7314조 2207억 4772만</t>
-  </si>
-  <si>
-    <t>핫잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
-  </si>
-  <si>
-    <t>1경 5275조 752억 3008만</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1경 4618조 2500억 6149만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>1경 3148조 1561억 8499만</t>
-  </si>
-  <si>
-    <t>아이스꾸임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
-  </si>
-  <si>
-    <t>1경 2802조 3487억 3746만</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1경 2301조 9332억 9820만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>1경 337조 3153억 1051만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>8232조 4493억 242만</t>
+    <t>45조 458억 3195만</t>
   </si>
   <si>
     <t>강서구도적</t>
@@ -2004,7 +2004,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
   </si>
   <si>
-    <t>345경 9914조 8396억 8840만</t>
+    <t>346경 3034조 6015억 351만</t>
   </si>
   <si>
     <t>계졍살사람귓</t>
@@ -2022,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EC%A1%8D%EC%82%AC%EC%8B%A4%EB%B6%84%EA%B7%93</t>
   </si>
   <si>
-    <t>74경 8431조 5194억 9420만</t>
+    <t>75경 818조 1584억 1999만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -2031,7 +2031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>23경 118조 6450억 1656만</t>
+    <t>23경 381조 8897억 1491만</t>
   </si>
   <si>
     <t>긴나라</t>
@@ -2076,7 +2076,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%A0%ED%91%B8%EB%8B%A5</t>
   </si>
   <si>
-    <t>6경 7270조 8857억 1492만</t>
+    <t>6경 7712조 9983억 4149만</t>
   </si>
   <si>
     <t>찹쌀2</t>
@@ -2085,7 +2085,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%B9%EC%8C%802</t>
   </si>
   <si>
-    <t>4경 3298조 2705억 6387만</t>
+    <t>4경 3421조 767억 7463만</t>
+  </si>
+  <si>
+    <t>하드웨어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
+  </si>
+  <si>
+    <t>3경 6476조 3126억 7435만</t>
   </si>
   <si>
     <t>원이유이</t>
@@ -2097,15 +2106,6 @@
     <t>3경 5872조 5602억 1798만</t>
   </si>
   <si>
-    <t>하드웨어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
-  </si>
-  <si>
-    <t>3경 5610조 1584억 2261만</t>
-  </si>
-  <si>
     <t>ShellyCake</t>
   </si>
   <si>
@@ -2163,7 +2163,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
   </si>
   <si>
-    <t>1경 1685조 8016억 1429만</t>
+    <t>1경 2013조 8085억 8346만</t>
+  </si>
+  <si>
+    <t>필림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%84%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>1경 400조 2190억 8029만</t>
   </si>
   <si>
     <t>예슬a</t>
@@ -2172,7 +2181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%ACa</t>
   </si>
   <si>
-    <t>1경 84조 6261억 3995만</t>
+    <t>1경 89조 1530억 2139만</t>
   </si>
   <si>
     <t>구미적</t>
@@ -2193,15 +2202,6 @@
     <t>9677조 4361억 8815만</t>
   </si>
   <si>
-    <t>필림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%84%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>9668조 1937억 9774만</t>
-  </si>
-  <si>
     <t>노지심이다</t>
   </si>
   <si>
@@ -2253,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EA%BC%AC</t>
   </si>
   <si>
-    <t>2425조 642억 3237만</t>
+    <t>2482조 7528억 844만</t>
   </si>
   <si>
     <t>삼촌용돈줘</t>
@@ -2869,22 +2869,22 @@
         <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2892,31 +2892,31 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>61</v>
@@ -2951,7 +2951,7 @@
         <v>67</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>29</v>
@@ -3409,7 +3409,7 @@
         <v>136</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>137</v>
@@ -3505,7 +3505,7 @@
         <v>93</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>149</v>
@@ -3537,7 +3537,7 @@
         <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>153</v>
@@ -3647,7 +3647,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>23</v>
@@ -3656,10 +3656,10 @@
         <v>23</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>93</v>
@@ -3668,7 +3668,7 @@
         <v>158</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3679,7 +3679,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>173</v>
@@ -3918,7 +3918,7 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>191</v>
@@ -3935,7 +3935,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>206</v>
@@ -3950,7 +3950,7 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>191</v>
@@ -4256,7 +4256,7 @@
         <v>229</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>126</v>
@@ -4646,7 +4646,7 @@
         <v>93</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>267</v>
@@ -4692,7 +4692,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>271</v>
@@ -4724,7 +4724,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>274</v>
@@ -4980,7 +4980,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>299</v>
@@ -5178,7 +5178,7 @@
         <v>98</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>313</v>
@@ -5236,7 +5236,7 @@
         <v>317</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>93</v>
@@ -5306,7 +5306,7 @@
         <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>324</v>
@@ -5370,7 +5370,7 @@
         <v>98</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>330</v>
@@ -5463,7 +5463,7 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>113</v>
@@ -5495,7 +5495,7 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>113</v>
@@ -5704,7 +5704,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>361</v>
@@ -5736,7 +5736,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>365</v>
@@ -6142,16 +6142,16 @@
         <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>397</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>136</v>
@@ -6160,7 +6160,7 @@
         <v>127</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6174,13 +6174,13 @@
         <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -6192,7 +6192,7 @@
         <v>127</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6206,13 +6206,13 @@
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -6224,7 +6224,7 @@
         <v>158</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6238,13 +6238,13 @@
         <v>105</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
@@ -6256,7 +6256,7 @@
         <v>158</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6270,13 +6270,13 @@
         <v>109</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
@@ -6288,7 +6288,7 @@
         <v>163</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6302,13 +6302,13 @@
         <v>115</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -6317,10 +6317,10 @@
         <v>136</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6334,13 +6334,13 @@
         <v>119</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -6352,7 +6352,7 @@
         <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6366,13 +6366,13 @@
         <v>123</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -6384,7 +6384,7 @@
         <v>182</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6398,13 +6398,13 @@
         <v>129</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
@@ -6416,7 +6416,7 @@
         <v>182</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6430,13 +6430,13 @@
         <v>133</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -6448,7 +6448,7 @@
         <v>158</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6462,13 +6462,13 @@
         <v>138</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -6480,7 +6480,7 @@
         <v>158</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6494,13 +6494,13 @@
         <v>142</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -6512,7 +6512,7 @@
         <v>158</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6526,13 +6526,13 @@
         <v>146</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
@@ -6541,10 +6541,10 @@
         <v>157</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6558,25 +6558,25 @@
         <v>150</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>436</v>
-      </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6590,25 +6590,25 @@
         <v>154</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>439</v>
-      </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6622,13 +6622,13 @@
         <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -6640,7 +6640,7 @@
         <v>186</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6654,13 +6654,13 @@
         <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -6672,7 +6672,7 @@
         <v>191</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6683,16 +6683,16 @@
         <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -6704,7 +6704,7 @@
         <v>191</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6715,16 +6715,16 @@
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -6736,7 +6736,7 @@
         <v>191</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6750,13 +6750,13 @@
         <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -6765,10 +6765,10 @@
         <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>285</v>
+        <v>191</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6782,13 +6782,13 @@
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -6800,7 +6800,7 @@
         <v>191</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6814,13 +6814,13 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -6829,10 +6829,10 @@
         <v>136</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6846,13 +6846,13 @@
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -6861,10 +6861,10 @@
         <v>136</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6878,13 +6878,13 @@
         <v>193</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>82</v>
@@ -6893,10 +6893,10 @@
         <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6910,13 +6910,13 @@
         <v>197</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>82</v>
@@ -6928,7 +6928,7 @@
         <v>285</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6942,22 +6942,22 @@
         <v>202</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>48</v>
+        <v>472</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>472</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>473</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>474</v>
@@ -6971,7 +6971,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>475</v>
@@ -6989,7 +6989,7 @@
         <v>136</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>477</v>
@@ -7070,985 +7070,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J29"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8096,19 +7117,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>566</v>
+        <v>482</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>566</v>
+        <v>482</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>567</v>
+        <v>483</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
@@ -8117,10 +7138,10 @@
         <v>309</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>394</v>
+        <v>305</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>568</v>
+        <v>484</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8128,19 +7149,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>569</v>
+        <v>485</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>569</v>
+        <v>485</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>570</v>
+        <v>486</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -8152,7 +7173,7 @@
         <v>218</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>571</v>
+        <v>487</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8160,19 +7181,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>572</v>
+        <v>488</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>572</v>
+        <v>488</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>573</v>
+        <v>489</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -8184,7 +7205,7 @@
         <v>218</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>574</v>
+        <v>490</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8192,19 +7213,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>575</v>
+        <v>491</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>575</v>
+        <v>491</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>576</v>
+        <v>492</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -8216,7 +7237,7 @@
         <v>84</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>577</v>
+        <v>493</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8224,19 +7245,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>578</v>
+        <v>494</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>578</v>
+        <v>494</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>579</v>
+        <v>495</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -8248,7 +7269,7 @@
         <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>580</v>
+        <v>496</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8256,31 +7277,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>581</v>
+        <v>497</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>581</v>
+        <v>497</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>582</v>
+        <v>498</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>583</v>
+        <v>499</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8288,31 +7309,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>584</v>
+        <v>500</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>584</v>
+        <v>500</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>585</v>
+        <v>501</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>127</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>586</v>
+        <v>502</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8320,19 +7341,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>587</v>
+        <v>503</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>587</v>
+        <v>503</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>588</v>
+        <v>504</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>82</v>
@@ -8344,7 +7365,7 @@
         <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>589</v>
+        <v>505</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8352,19 +7373,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>590</v>
+        <v>506</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>590</v>
+        <v>506</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>591</v>
+        <v>507</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>82</v>
@@ -8376,7 +7397,7 @@
         <v>113</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>592</v>
+        <v>508</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8384,19 +7405,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>593</v>
+        <v>509</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>593</v>
+        <v>509</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>594</v>
+        <v>510</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>82</v>
@@ -8408,7 +7429,7 @@
         <v>113</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>595</v>
+        <v>511</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8416,31 +7437,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>596</v>
+        <v>512</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>596</v>
+        <v>512</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>597</v>
+        <v>513</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>598</v>
+        <v>514</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8448,31 +7469,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>599</v>
+        <v>515</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>599</v>
+        <v>515</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>600</v>
+        <v>516</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>601</v>
+        <v>517</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8480,19 +7501,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>602</v>
+        <v>518</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>602</v>
+        <v>518</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>603</v>
+        <v>519</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>82</v>
@@ -8504,7 +7525,7 @@
         <v>113</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>604</v>
+        <v>520</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8512,19 +7533,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>605</v>
+        <v>521</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>605</v>
+        <v>521</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>606</v>
+        <v>522</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -8533,10 +7554,10 @@
         <v>93</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>607</v>
+        <v>523</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8544,31 +7565,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>608</v>
+        <v>524</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>608</v>
+        <v>524</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>609</v>
+        <v>525</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>163</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>610</v>
+        <v>526</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8576,31 +7597,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>611</v>
+        <v>527</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>611</v>
+        <v>527</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>612</v>
+        <v>528</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>613</v>
+        <v>529</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8608,19 +7629,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>614</v>
+        <v>530</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>614</v>
+        <v>530</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>615</v>
+        <v>531</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>82</v>
@@ -8632,7 +7653,7 @@
         <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>616</v>
+        <v>532</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8640,19 +7661,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>617</v>
+        <v>533</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>617</v>
+        <v>533</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>618</v>
+        <v>534</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>82</v>
@@ -8664,7 +7685,7 @@
         <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>619</v>
+        <v>535</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8672,19 +7693,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>620</v>
+        <v>536</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>620</v>
+        <v>536</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>621</v>
+        <v>537</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>82</v>
@@ -8696,7 +7717,7 @@
         <v>186</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>622</v>
+        <v>538</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8704,19 +7725,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>623</v>
+        <v>539</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>623</v>
+        <v>539</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>624</v>
+        <v>540</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>82</v>
@@ -8728,7 +7749,7 @@
         <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>625</v>
+        <v>541</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8736,19 +7757,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>626</v>
+        <v>542</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>626</v>
+        <v>542</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>627</v>
+        <v>543</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>82</v>
@@ -8760,7 +7781,7 @@
         <v>158</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>628</v>
+        <v>544</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8768,19 +7789,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>629</v>
+        <v>545</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>629</v>
+        <v>545</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>630</v>
+        <v>546</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>82</v>
@@ -8792,7 +7813,7 @@
         <v>182</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>631</v>
+        <v>547</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8800,19 +7821,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>632</v>
+        <v>548</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>632</v>
+        <v>548</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>633</v>
+        <v>549</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>82</v>
@@ -8824,7 +7845,7 @@
         <v>182</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>634</v>
+        <v>550</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8832,19 +7853,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>635</v>
+        <v>551</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>635</v>
+        <v>551</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>636</v>
+        <v>552</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>82</v>
@@ -8853,10 +7874,10 @@
         <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>637</v>
+        <v>553</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8864,19 +7885,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>638</v>
+        <v>554</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>638</v>
+        <v>554</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>639</v>
+        <v>555</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>82</v>
@@ -8888,7 +7909,7 @@
         <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>640</v>
+        <v>556</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8896,31 +7917,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>63</v>
+        <v>557</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>557</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>641</v>
+        <v>558</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>642</v>
+        <v>559</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8928,22 +7949,22 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>197</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>643</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>643</v>
+        <v>55</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>644</v>
+        <v>560</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>93</v>
@@ -8952,7 +7973,7 @@
         <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>645</v>
+        <v>561</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8960,19 +7981,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>646</v>
+        <v>562</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>646</v>
+        <v>562</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>647</v>
+        <v>563</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>82</v>
@@ -8981,10 +8002,10 @@
         <v>93</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>648</v>
+        <v>564</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8992,19 +8013,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>649</v>
+        <v>565</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>649</v>
+        <v>565</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>650</v>
+        <v>566</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>82</v>
@@ -9016,7 +8037,7 @@
         <v>186</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>651</v>
+        <v>567</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9024,19 +8045,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>652</v>
+        <v>568</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>652</v>
+        <v>568</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>653</v>
+        <v>569</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>82</v>
@@ -9048,7 +8069,7 @@
         <v>186</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>654</v>
+        <v>570</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -9092,9 +8113,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -9141,6 +8162,985 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J29"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -9479,10 +9479,10 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>687</v>
@@ -9511,10 +9511,10 @@
         <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>690</v>
@@ -9572,7 +9572,7 @@
         <v>694</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>200</v>
@@ -9752,7 +9752,7 @@
         <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>711</v>
@@ -9767,10 +9767,10 @@
         <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>461</v>
+        <v>285</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>713</v>
@@ -9784,7 +9784,7 @@
         <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>714</v>
@@ -9799,10 +9799,10 @@
         <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>285</v>
+        <v>460</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>716</v>
@@ -9831,10 +9831,10 @@
         <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>191</v>
+        <v>285</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>719</v>
@@ -9863,10 +9863,10 @@
         <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>285</v>
+        <v>191</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>722</v>
@@ -10040,7 +10040,7 @@
         <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>738</v>
@@ -10058,7 +10058,7 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>301</v>
+        <v>467</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>740</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">귀여미!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">레플리카셋!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">리안!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">리안!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">브리또!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">설묘!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">셀린느!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="743">
   <si>
     <t>guild_name</t>
   </si>
@@ -189,10 +189,10 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>677경 9011조 3320억 5240만</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>696경 7510조 7954억 5490만</t>
   </si>
   <si>
     <t>문의 [혜영]</t>
@@ -201,6 +201,9 @@
     <t>혜영</t>
   </si>
   <si>
+    <t>2026.09.21</t>
+  </si>
+  <si>
     <t>리안</t>
   </si>
   <si>
@@ -315,7 +318,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>151경 5004조 4630억 4973만</t>
+    <t>151경 5359조 252억 6874만</t>
   </si>
   <si>
     <t>4</t>
@@ -399,7 +402,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>35경 5866조 3798억 7180만</t>
+    <t>36경 6511조 8988억 7340만</t>
   </si>
   <si>
     <t>10</t>
@@ -429,7 +432,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>22경 2622조 1388억 6246만</t>
+    <t>23경 8604조 2602억 407만</t>
   </si>
   <si>
     <t>12</t>
@@ -444,7 +447,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>21경 4753조 3765억 8338만</t>
+    <t>22경 3669조 4484억 7448만</t>
   </si>
   <si>
     <t>13</t>
@@ -480,7 +483,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>15경 5795조 8588억 6810만</t>
+    <t>17경 4164조 9587억 8438만</t>
   </si>
   <si>
     <t>16</t>
@@ -492,7 +495,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>13경 2105조 4816억 1933만</t>
+    <t>13경 5108조 2316억 6087만</t>
   </si>
   <si>
     <t>17</t>
@@ -525,7 +528,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>7경 4972조 6974억 1981만</t>
+    <t>8경 1537조 6375억 7393만</t>
   </si>
   <si>
     <t>19</t>
@@ -540,6 +543,18 @@
     <t>7경 2382조 7642억 9212만</t>
   </si>
   <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>5경 6937조 649억 4869만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
@@ -549,18 +564,6 @@
     <t>5경 5478조 8492억 3032만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>5경 4783조 8696억 6956만</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -570,7 +573,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>5경 3005조 1147억 1318만</t>
+    <t>5경 3662조 5378억 2059만</t>
   </si>
   <si>
     <t>수상구</t>
@@ -579,49 +582,49 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%83%81%EA%B5%AC</t>
   </si>
   <si>
+    <t>2경 6159조 1196억 1911만</t>
+  </si>
+  <si>
+    <t>견아니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>2경 4542조 9763억 7625만</t>
+  </si>
+  <si>
+    <t>애봉얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>2경 2774조 3837억 9059만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>설앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
     <t>117</t>
   </si>
   <si>
-    <t>2경 5422조 8458억 5094만</t>
-  </si>
-  <si>
-    <t>견아니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%AC%EC%95%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>2경 3101조 7046억 6202만</t>
-  </si>
-  <si>
-    <t>공대애봉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>2경 1802조 9715억 751만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>설앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>1경 7395조 9535억 4782만</t>
+    <t>1경 7931조 5551억 2790만</t>
   </si>
   <si>
     <t>27</t>
@@ -642,22 +645,22 @@
     <t>28</t>
   </si>
   <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1경 298조 7664억 4784만</t>
+  </si>
+  <si>
     <t>설콩순</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>9562조 1082억 7865만</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>9554조 6832억 9248만</t>
+    <t>9845조 8620억 2111만</t>
   </si>
   <si>
     <t>30</t>
@@ -690,7 +693,7 @@
     <t>123</t>
   </si>
   <si>
-    <t>286경 266조 995억 2968만</t>
+    <t>295경 9785조 4697억 7288만</t>
   </si>
   <si>
     <t>혀로꽃</t>
@@ -699,16 +702,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EA%BD%83</t>
   </si>
   <si>
-    <t>106경 6285조 8850억 3516만</t>
-  </si>
-  <si>
-    <t>SlowDown</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=SlowDown</t>
-  </si>
-  <si>
-    <t>81경 5990조 9819억 6076만</t>
+    <t>109경 2412조 8739억 4794만</t>
+  </si>
+  <si>
+    <t>뽀로로남편</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
+  </si>
+  <si>
+    <t>81경 6149조 4470억 2779만</t>
   </si>
   <si>
     <t>뻥투기릿</t>
@@ -717,13 +720,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
   </si>
   <si>
-    <t>65경 9932조 965억 1300만</t>
+    <t>66경 703조 2354억 9701만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%B9%A8%EA%B0%84%EB%8F%8C%ED%94%84</t>
   </si>
   <si>
-    <t>60경 5085조 4583억 8918만</t>
+    <t>62경 1319조 3343억 3467만</t>
   </si>
   <si>
     <t>기뚠</t>
@@ -741,7 +744,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%B0%EA%B0%88</t>
   </si>
   <si>
-    <t>17경 8782조 8938억 1126만</t>
+    <t>18경 6352조 9350억 8951만</t>
   </si>
   <si>
     <t>911TurboS</t>
@@ -750,7 +753,7 @@
     <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
   </si>
   <si>
-    <t>16경 1922조 7926억 2892만</t>
+    <t>16경 2153조 6318억 3842만</t>
   </si>
   <si>
     <t>하싱</t>
@@ -759,7 +762,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
   </si>
   <si>
-    <t>12경 1991조 9300억 2209만</t>
+    <t>12경 8268조 1520억 1528만</t>
   </si>
   <si>
     <t>김라이트</t>
@@ -798,7 +801,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
   </si>
   <si>
-    <t>5경 1012조 7398억 5095만</t>
+    <t>5경 4122조 757억 5833만</t>
   </si>
   <si>
     <t>오이겐</t>
@@ -807,7 +810,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
   </si>
   <si>
-    <t>4경 6228조 7401억 5505만</t>
+    <t>4경 8600조 5220억 365만</t>
   </si>
   <si>
     <t>뿔피리</t>
@@ -816,7 +819,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>4경 3971조 1941억 860만</t>
+    <t>4경 6265조 6998억 9915만</t>
+  </si>
+  <si>
+    <t>탄지로네즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2경 9341조 7839억 336만</t>
   </si>
   <si>
     <t>깔지마오</t>
@@ -828,15 +840,6 @@
     <t>2경 9330조 6252억 5962만</t>
   </si>
   <si>
-    <t>탄지로네즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2경 9296조 7213억 5282만</t>
-  </si>
-  <si>
     <t>플더</t>
   </si>
   <si>
@@ -852,7 +855,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
   </si>
   <si>
-    <t>2경 2709조 1532억 2189만</t>
+    <t>2경 3903조 8365억 6256만</t>
   </si>
   <si>
     <t>무명장수</t>
@@ -864,6 +867,24 @@
     <t>2경 646조 1663억 9601만</t>
   </si>
   <si>
+    <t>루픠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%94%A0</t>
+  </si>
+  <si>
+    <t>2경 586조 1269억 7635만</t>
+  </si>
+  <si>
+    <t>샹끄스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%B9%EB%81%84%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1경 8414조 3886억 2003만</t>
+  </si>
+  <si>
     <t>멀해</t>
   </si>
   <si>
@@ -891,25 +912,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>1경 2635조 4189억 4866만</t>
-  </si>
-  <si>
-    <t>루픠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%ED%94%A0</t>
-  </si>
-  <si>
-    <t>1경 1892조 3515억 2521만</t>
-  </si>
-  <si>
-    <t>샹끄스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%B9%EB%81%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1경 979조 7090억 9802만</t>
+    <t>1경 2651조 6948억 1527만</t>
   </si>
   <si>
     <t>삼치회</t>
@@ -927,7 +930,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%AB</t>
   </si>
   <si>
-    <t>6882조 6419억 41만</t>
+    <t>6904조 6493억 1580만</t>
   </si>
   <si>
     <t>멍쥐</t>
@@ -939,7 +942,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>3134조 7278억 5071만</t>
+    <t>3327조 6353억 9750만</t>
   </si>
   <si>
     <t>라온XR</t>
@@ -963,7 +966,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>200경 8168조 6070억 3417만</t>
+    <t>204경 6012조 2750억 6450만</t>
   </si>
   <si>
     <t>하잉안파파</t>
@@ -972,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>138경 1350조 7423억 259만</t>
+    <t>138경 6520조 9234억 8499만</t>
   </si>
   <si>
     <t>타이슨에어랩</t>
@@ -999,6 +1002,15 @@
     <t>47경 8006조 1800억 8094만</t>
   </si>
   <si>
+    <t>코코듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
+  </si>
+  <si>
+    <t>38경 938조 2778억 2125만</t>
+  </si>
+  <si>
     <t>캔드릭</t>
   </si>
   <si>
@@ -1014,16 +1026,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>27경 4795조 8297억 625만</t>
-  </si>
-  <si>
-    <t>코코듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
-  </si>
-  <si>
-    <t>25경 4335조 5085억 901만</t>
+    <t>29경 6485조 5973억 9557만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -1032,7 +1035,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
   </si>
   <si>
-    <t>21경 6353조 2736억 4672만</t>
+    <t>21경 7131조 497억 9123만</t>
   </si>
   <si>
     <t>똥갈</t>
@@ -1041,7 +1044,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
   </si>
   <si>
-    <t>14경 7872조 6408억 1802만</t>
+    <t>14경 8014조 775억 1679만</t>
   </si>
   <si>
     <t>도적왕대현</t>
@@ -1077,7 +1080,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
   </si>
   <si>
-    <t>5경 4711조 9552억 8177만</t>
+    <t>5경 6513조 3812억 4647만</t>
   </si>
   <si>
     <t>진쎅</t>
@@ -1095,7 +1098,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
   </si>
   <si>
-    <t>5경 720조 9496억 1123만</t>
+    <t>5경 934조 4267억 976만</t>
   </si>
   <si>
     <t>Redwine</t>
@@ -1104,7 +1107,19 @@
     <t>https://mgf.gg/contents/character.php?n=Redwine</t>
   </si>
   <si>
-    <t>4경 7803조 2952억 5856만</t>
+    <t>4경 7985조 9079억 230만</t>
+  </si>
+  <si>
+    <t>이다연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>4경 5979조 5093억 8215만</t>
   </si>
   <si>
     <t>로생</t>
@@ -1116,18 +1131,6 @@
     <t>4경 5141조 2898억 2799만</t>
   </si>
   <si>
-    <t>이다연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>4경 5048조 8438억 6980만</t>
-  </si>
-  <si>
     <t>탤포</t>
   </si>
   <si>
@@ -1137,22 +1140,22 @@
     <t>4경 1816조 4322억 9283만</t>
   </si>
   <si>
+    <t>메키메렁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
+  </si>
+  <si>
+    <t>2경 9654조 9750억 3124만</t>
+  </si>
+  <si>
     <t>그때그아이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>2경 8964조 6795억 4359만</t>
-  </si>
-  <si>
-    <t>메키메렁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
-  </si>
-  <si>
-    <t>2경 7839조 9823억 8751만</t>
+    <t>2경 9218조 5549억 2127만</t>
   </si>
   <si>
     <t>서동구</t>
@@ -1161,7 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%8F%99%EA%B5%AC</t>
   </si>
   <si>
-    <t>2경 2117조 4871억 3585만</t>
+    <t>2경 2578조 7549억 3447만</t>
   </si>
   <si>
     <t>꽁꽁얼었다</t>
@@ -1179,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
   </si>
   <si>
-    <t>1경 2868조 9507억 2068만</t>
+    <t>1경 4749조 6308억 9577만</t>
   </si>
   <si>
     <t>정희롱</t>
@@ -1188,7 +1191,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%9D%AC%EB%A1%B1</t>
   </si>
   <si>
-    <t>8024조 4683억 4802만</t>
+    <t>8379조 7758억 1359만</t>
   </si>
   <si>
     <t>안성대통령</t>
@@ -1206,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8JW</t>
   </si>
   <si>
-    <t>480경 4353조 6531억 1401만</t>
+    <t>492경 3240조 3600억 5454만</t>
   </si>
   <si>
     <t>금은동S2</t>
@@ -1218,13 +1221,13 @@
     <t>125</t>
   </si>
   <si>
-    <t>361경 2344조 1033억 6930만</t>
+    <t>424경 2861조 6277억 6561만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
   </si>
   <si>
-    <t>38경 6851조 2177억 7226만</t>
+    <t>41경 7409조 2168억 7305만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -1251,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>9경 4153조 805억 2573만</t>
+    <t>9경 9981조 4998억 3250만</t>
   </si>
   <si>
     <t>문신담배돼지</t>
@@ -1269,7 +1272,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>8경 8259조 6479억 5030만</t>
+    <t>9경 1730조 8746억 8927만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -1281,13 +1284,22 @@
     <t>6경 1607조 2759억 2889만</t>
   </si>
   <si>
+    <t>누룽지룽누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EB%A3%BD%EC%A7%80%EB%A3%BD%EB%88%84</t>
+  </si>
+  <si>
+    <t>4경 2302조 9026억 9597만</t>
+  </si>
+  <si>
     <t>우꼬쨩</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
   </si>
   <si>
-    <t>4경 928조 4628억 9427만</t>
+    <t>4경 1007조 9406억 9448만</t>
   </si>
   <si>
     <t>비밀키</t>
@@ -1299,22 +1311,13 @@
     <t>3경 8363조 108억 1090만</t>
   </si>
   <si>
-    <t>누룽지룽누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EB%A3%BD%EC%A7%80%EB%A3%BD%EB%88%84</t>
-  </si>
-  <si>
-    <t>3경 8026조 9739억 7864만</t>
-  </si>
-  <si>
     <t>어흥이다</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>3경 5814조 8841억 8452만</t>
+    <t>3경 7569조 2749억 8895만</t>
   </si>
   <si>
     <t>지아라떼</t>
@@ -1332,7 +1335,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
   </si>
   <si>
-    <t>1경 9207조 5074억 5072만</t>
+    <t>2경 666조 3184억 2400만</t>
+  </si>
+  <si>
+    <t>슛맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>2경 17조 7849억 7482만</t>
   </si>
   <si>
     <t>붙잡아</t>
@@ -1341,16 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
   </si>
   <si>
-    <t>1경 9163조 620억 1118만</t>
-  </si>
-  <si>
-    <t>슛맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>1경 8264조 7627억 870만</t>
+    <t>1경 9853조 9172억 5674만</t>
   </si>
   <si>
     <t>메론맛빵</t>
@@ -1359,7 +1362,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
   </si>
   <si>
-    <t>1경 6582조 2316억 1444만</t>
+    <t>1경 7423조 4326억 4036만</t>
+  </si>
+  <si>
+    <t>왕컹스맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%BB%B9%EC%8A%A4%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>9567조 5612억 4828만</t>
   </si>
   <si>
     <t>유깡깡</t>
@@ -1368,16 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EA%B9%A1%EA%B9%A1</t>
   </si>
   <si>
-    <t>9304조 1012억 5646만</t>
-  </si>
-  <si>
-    <t>왕컹스맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%BB%B9%EC%8A%A4%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>9143조 6493억 6052만</t>
+    <t>9364조 3450억 5996만</t>
   </si>
   <si>
     <t>출장괴물</t>
@@ -1386,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>6634조 5766억 6072만</t>
+    <t>7060조 824억 635만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -1404,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%AC%ED%86%B5%EC%97%AD</t>
   </si>
   <si>
-    <t>5573조 4278억 8576만</t>
+    <t>5665조 3962억 4100만</t>
   </si>
   <si>
     <t>원덍</t>
@@ -1416,7 +1419,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>4192조 9713억 8802만</t>
+    <t>4219조 6797억 140만</t>
   </si>
   <si>
     <t>알테신</t>
@@ -1425,7 +1428,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%ED%85%8C%EC%8B%A0</t>
   </si>
   <si>
-    <t>3777조 3160억 2879만</t>
+    <t>3778조 7826억 8554만</t>
   </si>
   <si>
     <t>갬두</t>
@@ -1437,7 +1440,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>3462조 2733억 2571만</t>
+    <t>3521조 7715억 3819만</t>
   </si>
   <si>
     <t>뭉탕</t>
@@ -1446,7 +1449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AD%89%ED%83%95</t>
   </si>
   <si>
-    <t>2754조 9902억 925만</t>
+    <t>2803조 8987억 1924만</t>
   </si>
   <si>
     <t>스탠딩메이지</t>
@@ -1455,7 +1458,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%A0%EB%94%A9%EB%A9%94%EC%9D%B4%EC%A7%80</t>
   </si>
   <si>
-    <t>2058조 5213억 9805만</t>
+    <t>2116조 2700억 5081만</t>
   </si>
   <si>
     <t>물기둥</t>
@@ -1464,7 +1467,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%BC%EA%B8%B0%EB%91%A5</t>
   </si>
   <si>
-    <t>1731조 5415억 4887만</t>
+    <t>2087조 422억 3130만</t>
   </si>
   <si>
     <t>유유덍</t>
@@ -1476,7 +1479,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>270조 9812억 9314만</t>
+    <t>308조 6588억 4287만</t>
   </si>
   <si>
     <t>빔냥이</t>
@@ -1485,7 +1488,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%94%EB%83%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>230경 375조 6847억 3301만</t>
+    <t>237경 3832조 9827억 3587만</t>
   </si>
   <si>
     <t>MNMMNMMNMMNM</t>
@@ -1494,7 +1497,7 @@
     <t>https://mgf.gg/contents/character.php?n=MNMMNMMNMMNM</t>
   </si>
   <si>
-    <t>82경 6629조 1011억 3884만</t>
+    <t>84경 6922조 3647억 3514만</t>
   </si>
   <si>
     <t>진자이</t>
@@ -1503,7 +1506,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>59경 8932조 8415억 8249만</t>
+    <t>62경 1946조 3217억 3306만</t>
   </si>
   <si>
     <t>돈스</t>
@@ -1512,7 +1515,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>58경 2451조 9309억 7663만</t>
+    <t>58경 3504조 9661억 1085만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -1521,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>45경 9931조 1583억 3973만</t>
+    <t>46경 6681조 6977억 6438만</t>
   </si>
   <si>
     <t>스타캐치</t>
@@ -1530,7 +1533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
   </si>
   <si>
-    <t>26경 7953조 6509억 6286만</t>
+    <t>29경 3428조 9822억 7658만</t>
   </si>
   <si>
     <t>뽀리빠</t>
@@ -1539,7 +1542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A6%AC%EB%B9%A0</t>
   </si>
   <si>
-    <t>26경 7923조 9367억 2199만</t>
+    <t>26경 9454조 2047억 4223만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -1557,7 +1560,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>15경 857조 7736억 9512만</t>
+    <t>15경 918조 3225억 3682만</t>
+  </si>
+  <si>
+    <t>천천히걸어가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
+  </si>
+  <si>
+    <t>11경 307조 5408억 3327만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -1566,16 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>10경 4931조 5654억 7685만</t>
-  </si>
-  <si>
-    <t>천천히걸어가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B2%9C%ED%9E%88%EA%B1%B8%EC%96%B4%EA%B0%80</t>
-  </si>
-  <si>
-    <t>10경 421조 9052억 6144만</t>
+    <t>10경 8625조 1248억 9229만</t>
   </si>
   <si>
     <t>약어</t>
@@ -1584,7 +1587,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>9경 7717조 5279억 6925만</t>
+    <t>10경 4738조 815억 6221만</t>
   </si>
   <si>
     <t>국의</t>
@@ -1593,7 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>9경 7577조 4960억 8311만</t>
+    <t>9경 8834조 8762억 2038만</t>
   </si>
   <si>
     <t>익맹이</t>
@@ -1602,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B5%EB%A7%B9%EC%9D%B4</t>
   </si>
   <si>
-    <t>8경 5493조 5674억 6937만</t>
+    <t>8경 6680조 2850억 6904만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -1641,6 +1644,15 @@
     <t>6경 4934조 151억 6468만</t>
   </si>
   <si>
+    <t>김겨탱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
+  </si>
+  <si>
+    <t>6경 1668조 7392억 2259만</t>
+  </si>
+  <si>
     <t>킹몬</t>
   </si>
   <si>
@@ -1650,15 +1662,6 @@
     <t>5경 8774조 7748억 8940만</t>
   </si>
   <si>
-    <t>김겨탱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B2%A8%ED%83%B1</t>
-  </si>
-  <si>
-    <t>5경 7132조 4680억 8461만</t>
-  </si>
-  <si>
     <t>쾌감</t>
   </si>
   <si>
@@ -1668,22 +1671,22 @@
     <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>2경 1572조 3177억 5090만</t>
+  </si>
+  <si>
     <t>세아수호지호</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>1경 9039조 4842억 7168만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>1경 7944조 8437억 7238만</t>
+    <t>1경 9146조 5243억 1253만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -1692,7 +1695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>1경 5275조 752억 3008만</t>
+    <t>1경 7599조 1897억 5828만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -1710,13 +1713,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 3784조 6932억 6395만</t>
+    <t>1경 4546조 517억 3867만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 3172조 192억 1384만</t>
+    <t>1경 3471조 2104억 2832만</t>
   </si>
   <si>
     <t>아이스꾸임</t>
@@ -1725,7 +1728,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
   </si>
   <si>
-    <t>1경 2961조 5558억 3160만</t>
+    <t>1경 2975조 3166억 7368만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -1734,7 +1737,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 337조 3153억 1051만</t>
+    <t>1경 511조 753억 1132만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -1743,7 +1746,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>8232조 4493억 242만</t>
+    <t>8523조 7574억 722만</t>
   </si>
   <si>
     <t>군보</t>
@@ -1761,7 +1764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EC%97%90%EB%B0%94%EB%9E%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>94경 6651조 28억 1595만</t>
+    <t>94경 7286조 5764억 7023만</t>
   </si>
   <si>
     <t>라온PB</t>
@@ -1776,7 +1779,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
   </si>
   <si>
-    <t>63경 3627조 945억 3403만</t>
+    <t>63경 4296조 1762억 4733만</t>
   </si>
   <si>
     <t>Matter</t>
@@ -1785,7 +1788,7 @@
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>60경 2137조 6471억 89만</t>
+    <t>60경 2221조 4553억 19만</t>
   </si>
   <si>
     <t>혁수킹</t>
@@ -1794,7 +1797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
   </si>
   <si>
-    <t>55경 7881조 3223억 2425만</t>
+    <t>57경 9649조 21억 5625만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1806,15 +1809,6 @@
     <t>55경 5523조 6632억 6782만</t>
   </si>
   <si>
-    <t>셀문</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%AC%B8</t>
-  </si>
-  <si>
-    <t>52경 8262조 5847억 6743만</t>
-  </si>
-  <si>
     <t>총괄한석현</t>
   </si>
   <si>
@@ -1830,7 +1824,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>28경 9380조 1378억 8423만</t>
+    <t>29경 426조 4009억 7583만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -1848,7 +1842,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>10경 2294조 8734억 7967만</t>
+    <t>11경 2909조 1843억 2589만</t>
   </si>
   <si>
     <t>악경</t>
@@ -1875,7 +1869,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
   </si>
   <si>
-    <t>4경 2905조 1246억 2290만</t>
+    <t>4경 3856조 6186억 4463만</t>
+  </si>
+  <si>
+    <t>힐캐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%BA%90</t>
+  </si>
+  <si>
+    <t>3경 8119조 4978억 3022만</t>
   </si>
   <si>
     <t>히째히째</t>
@@ -1884,16 +1887,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
   </si>
   <si>
-    <t>3경 6705조 6123억 7632만</t>
-  </si>
-  <si>
-    <t>힐캐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%BA%90</t>
-  </si>
-  <si>
-    <t>3경 6161조 8085억 1393만</t>
+    <t>3경 7150조 4056억 6860만</t>
   </si>
   <si>
     <t>떠영아</t>
@@ -1938,7 +1932,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
   </si>
   <si>
-    <t>1경 5752조 1911억 3914만</t>
+    <t>1경 6586조 2859억 4313만</t>
   </si>
   <si>
     <t>표창빌런</t>
@@ -1995,7 +1989,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>45조 458억 3195만</t>
+    <t>46조 3143억 5091만</t>
   </si>
   <si>
     <t>강서구도적</t>
@@ -2004,7 +1998,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
   </si>
   <si>
-    <t>346경 3034조 6015억 351만</t>
+    <t>346경 5667조 9076억 8180만</t>
   </si>
   <si>
     <t>계졍살사람귓</t>
@@ -2022,7 +2016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EC%A1%8D%EC%82%AC%EC%8B%A4%EB%B6%84%EA%B7%93</t>
   </si>
   <si>
-    <t>75경 818조 1584억 1999만</t>
+    <t>76경 4258조 5804억 4075만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -2031,7 +2025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>23경 381조 8897억 1491만</t>
+    <t>23경 9355조 7296억 8094만</t>
   </si>
   <si>
     <t>긴나라</t>
@@ -2049,7 +2043,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
   </si>
   <si>
-    <t>14경 8774조 7966억 6678만</t>
+    <t>15경 9954조 6987억 6354만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -2076,7 +2070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%A0%ED%91%B8%EB%8B%A5</t>
   </si>
   <si>
-    <t>6경 7712조 9983억 4149만</t>
+    <t>7경 3955조 7922억 5811만</t>
   </si>
   <si>
     <t>찹쌀2</t>
@@ -2085,7 +2079,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%B9%EC%8C%802</t>
   </si>
   <si>
-    <t>4경 3421조 767억 7463만</t>
+    <t>4경 3622조 5815억 4102만</t>
+  </si>
+  <si>
+    <t>원이유이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%9D%B4%EC%9C%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3경 6662조 2604억 4374만</t>
   </si>
   <si>
     <t>하드웨어</t>
@@ -2094,16 +2097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>3경 6476조 3126억 7435만</t>
-  </si>
-  <si>
-    <t>원이유이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%9D%B4%EC%9C%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3경 5872조 5602억 1798만</t>
+    <t>3경 6585조 4672억 4682만</t>
   </si>
   <si>
     <t>ShellyCake</t>
@@ -2112,7 +2106,7 @@
     <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
   </si>
   <si>
-    <t>2경 5705조 4006억 8357만</t>
+    <t>2경 6044조 5063억 210만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
@@ -2127,7 +2121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>1경 8945조 7080억 9745만</t>
+    <t>1경 9391조 2286억 9277만</t>
   </si>
   <si>
     <t>양덕하늘채</t>
@@ -2136,7 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8D%95%ED%95%98%EB%8A%98%EC%B1%84</t>
   </si>
   <si>
-    <t>1경 3947조 5573억 8832만</t>
+    <t>1경 4281조 8034억 1050만</t>
   </si>
   <si>
     <t>주하사랑</t>
@@ -2145,7 +2139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
   </si>
   <si>
-    <t>1경 2514조 1464억 1212만</t>
+    <t>1경 2850조 6144억 3293만</t>
   </si>
   <si>
     <t>아포짓</t>
@@ -2163,7 +2157,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
   </si>
   <si>
-    <t>1경 2013조 8085억 8346만</t>
+    <t>1경 2022조 623억 7515만</t>
+  </si>
+  <si>
+    <t>검샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
+  </si>
+  <si>
+    <t>1경 956조 8485억 3097만</t>
+  </si>
+  <si>
+    <t>예슬a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%ACa</t>
+  </si>
+  <si>
+    <t>1경 888조 9755억 7502만</t>
   </si>
   <si>
     <t>필림</t>
@@ -2175,31 +2187,13 @@
     <t>1경 400조 2190억 8029만</t>
   </si>
   <si>
-    <t>예슬a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%ACa</t>
-  </si>
-  <si>
-    <t>1경 89조 1530억 2139만</t>
-  </si>
-  <si>
     <t>구미적</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
   </si>
   <si>
-    <t>1경 70조 9404억 2509만</t>
-  </si>
-  <si>
-    <t>검샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
-  </si>
-  <si>
-    <t>9677조 4361억 8815만</t>
+    <t>1경 328조 3273억 2159만</t>
   </si>
   <si>
     <t>노지심이다</t>
@@ -2208,7 +2202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EC%A7%80%EC%8B%AC%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>8899조 4114억 6397만</t>
+    <t>8938조 6010억 8598만</t>
   </si>
   <si>
     <t>꼬기갓</t>
@@ -2226,7 +2220,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
   </si>
   <si>
-    <t>5966조 4179억 8745만</t>
+    <t>6186조 4059억 7529만</t>
   </si>
   <si>
     <t>l빠다코코낫l</t>
@@ -2253,7 +2247,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EA%BC%AC</t>
   </si>
   <si>
-    <t>2482조 7528억 844만</t>
+    <t>2726조 5275억 1310만</t>
   </si>
   <si>
     <t>삼촌용돈줘</t>
@@ -2265,7 +2259,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>651조 4570억 7519만</t>
+    <t>653조 8415억 3406만</t>
   </si>
 </sst>
 </file>
@@ -2887,30 +2881,30 @@
         <v>55</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>
@@ -2919,13 +2913,13 @@
         <v>38</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>24</v>
@@ -2933,25 +2927,25 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>29</v>
@@ -2960,13 +2954,13 @@
         <v>20</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>24</v>
@@ -2998,7 +2992,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3007,28 +3001,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3039,28 +3033,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3071,28 +3065,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3103,28 +3097,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3135,28 +3129,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3167,28 +3161,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3199,28 +3193,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3231,28 +3225,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3263,28 +3257,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3295,28 +3289,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3327,28 +3321,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3359,28 +3353,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3391,28 +3385,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3423,28 +3417,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3455,28 +3449,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3487,28 +3481,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3519,28 +3513,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3551,28 +3545,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3583,28 +3577,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3615,28 +3609,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3650,25 +3644,25 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3679,28 +3673,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3711,28 +3705,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3746,22 +3740,22 @@
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>183</v>
@@ -3787,10 +3781,10 @@
         <v>185</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>186</v>
@@ -3819,7 +3813,7 @@
         <v>189</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>190</v>
@@ -3851,16 +3845,16 @@
         <v>195</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3871,28 +3865,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3903,28 +3897,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3935,28 +3929,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3967,28 +3961,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4052,28 +4046,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4084,28 +4078,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4116,28 +4110,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4148,28 +4142,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4180,28 +4174,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4212,28 +4206,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4244,7 +4238,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>33</v>
@@ -4253,19 +4247,19 @@
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4276,28 +4270,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4308,28 +4302,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4340,28 +4334,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4372,28 +4366,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4404,28 +4398,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4436,28 +4430,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4468,28 +4462,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4500,28 +4494,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4532,28 +4526,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4564,28 +4558,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4596,28 +4590,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4628,28 +4622,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4660,28 +4654,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4695,25 +4689,25 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4724,28 +4718,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4756,28 +4750,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4791,25 +4785,25 @@
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4823,22 +4817,22 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>285</v>
+        <v>191</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>286</v>
@@ -4864,10 +4858,10 @@
         <v>288</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>191</v>
@@ -4896,16 +4890,16 @@
         <v>291</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4916,28 +4910,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4948,28 +4942,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4980,28 +4974,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5064,28 +5058,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5096,28 +5090,28 @@
         <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>190</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5128,28 +5122,28 @@
         <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5160,28 +5154,28 @@
         <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5192,28 +5186,28 @@
         <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5224,7 +5218,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>41</v>
@@ -5233,19 +5227,19 @@
         <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5256,28 +5250,28 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5288,28 +5282,28 @@
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5320,28 +5314,28 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5352,28 +5346,28 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5384,28 +5378,28 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5416,28 +5410,28 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5448,28 +5442,28 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5480,28 +5474,28 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5512,28 +5506,28 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5544,28 +5538,28 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5576,28 +5570,28 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5608,28 +5602,28 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>190</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5640,28 +5634,28 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5672,28 +5666,28 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>157</v>
+        <v>361</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5707,25 +5701,25 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>363</v>
+        <v>158</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5736,28 +5730,28 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5768,28 +5762,28 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>310</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5803,25 +5797,25 @@
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>309</v>
+        <v>113</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5835,25 +5829,25 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5867,25 +5861,25 @@
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5899,25 +5893,25 @@
         <v>193</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5928,28 +5922,28 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5960,28 +5954,28 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6043,28 +6037,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6075,28 +6069,28 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6107,28 +6101,28 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6139,7 +6133,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>48</v>
@@ -6148,19 +6142,19 @@
         <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6171,28 +6165,28 @@
         <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6203,28 +6197,28 @@
         <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6235,28 +6229,28 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6267,28 +6261,28 @@
         <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6299,28 +6293,28 @@
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6331,28 +6325,28 @@
         <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6363,28 +6357,28 @@
         <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>363</v>
+        <v>84</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6395,28 +6389,28 @@
         <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>361</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6427,28 +6421,28 @@
         <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6459,28 +6453,28 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6491,28 +6485,28 @@
         <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6523,28 +6517,28 @@
         <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6555,28 +6549,28 @@
         <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6587,28 +6581,28 @@
         <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6619,28 +6613,28 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6651,28 +6645,28 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6686,25 +6680,25 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6715,28 +6709,28 @@
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6747,28 +6741,28 @@
         <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6782,25 +6776,25 @@
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6814,25 +6808,25 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6846,25 +6840,25 @@
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6878,25 +6872,25 @@
         <v>193</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6907,28 +6901,28 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6939,28 +6933,28 @@
         <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6971,28 +6965,28 @@
         <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7003,28 +6997,28 @@
         <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7079,7 +7073,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7088,28 +7082,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -7120,31 +7114,31 @@
         <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7152,31 +7146,31 @@
         <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7184,31 +7178,31 @@
         <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7216,31 +7210,31 @@
         <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7248,31 +7242,31 @@
         <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -7280,31 +7274,31 @@
         <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -7312,31 +7306,31 @@
         <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -7344,31 +7338,31 @@
         <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -7376,31 +7370,31 @@
         <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -7408,31 +7402,31 @@
         <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -7440,31 +7434,31 @@
         <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -7472,31 +7466,31 @@
         <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -7504,31 +7498,31 @@
         <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -7536,31 +7530,31 @@
         <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7568,31 +7562,31 @@
         <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>190</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7600,31 +7594,31 @@
         <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7632,31 +7626,31 @@
         <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7664,31 +7658,31 @@
         <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7696,31 +7690,31 @@
         <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7731,28 +7725,28 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7760,31 +7754,31 @@
         <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7792,31 +7786,31 @@
         <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7827,28 +7821,28 @@
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7859,28 +7853,28 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7891,28 +7885,28 @@
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7923,28 +7917,28 @@
         <v>193</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7952,7 +7946,7 @@
         <v>49</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>55</v>
@@ -7961,22 +7955,22 @@
         <v>55</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7984,31 +7978,31 @@
         <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -8016,31 +8010,31 @@
         <v>49</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -8048,31 +8042,31 @@
         <v>49</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -8115,7 +8109,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -8133,28 +8127,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -8162,31 +8156,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8194,31 +8188,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8226,31 +8220,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8258,31 +8252,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8290,31 +8284,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8322,31 +8316,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8354,31 +8348,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8386,31 +8380,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8418,31 +8412,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8450,31 +8444,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8482,31 +8476,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8514,31 +8508,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>112</v>
+        <v>246</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8546,31 +8540,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8578,31 +8572,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>309</v>
+        <v>361</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8610,31 +8604,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8642,31 +8636,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8674,31 +8668,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>93</v>
+        <v>246</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8706,31 +8700,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>245</v>
+        <v>137</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8738,31 +8732,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8770,31 +8764,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8802,31 +8796,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8834,31 +8828,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>182</v>
+        <v>292</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8866,31 +8860,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>285</v>
+        <v>186</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8898,31 +8892,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8930,31 +8924,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8962,31 +8956,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>285</v>
+        <v>461</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8994,70 +8988,38 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>460</v>
+        <v>651</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J28"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -9086,7 +9048,6 @@
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9103,7 +9064,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9112,28 +9073,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -9141,31 +9102,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9173,31 +9134,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9205,31 +9166,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9237,31 +9198,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9269,31 +9230,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9301,31 +9262,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9333,31 +9294,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9365,31 +9326,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>678</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9397,31 +9358,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9429,31 +9390,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9461,31 +9422,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9493,31 +9454,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>690</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9525,31 +9486,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9557,31 +9518,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9589,31 +9550,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9621,31 +9582,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>701</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9653,31 +9614,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>702</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9685,31 +9646,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9717,31 +9678,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9749,31 +9710,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9781,31 +9742,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9813,31 +9774,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9845,31 +9806,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>722</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9877,31 +9838,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9909,31 +9870,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9941,31 +9902,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9973,31 +9934,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10005,31 +9966,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>191</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10037,31 +9998,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>738</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10069,31 +10030,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -99,7 +99,7 @@
     <t>1200경 7284조 1008억 2700만</t>
   </si>
   <si>
-    <t>가입 문의:  코빨간돌프/깔지마오  &amp;lt;No.1 레플&amp;gt;</t>
+    <t>가입 문의: 코빨간돌프/깔지마오 &amp;lt;No.1 레플&amp;gt;</t>
   </si>
   <si>
     <t>코빨간돌프</t>
@@ -150,7 +150,7 @@
     <t>1089경 6103조 5933억 8200만</t>
   </si>
   <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중  문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
   </si>
   <si>
     <t>설익은체리</t>
@@ -303,7 +303,7 @@
     <t>129</t>
   </si>
   <si>
-    <t>3465경 3085조 8,290억 7,965만</t>
+    <t>3465경 3085조 8290억 7965만</t>
   </si>
   <si>
     <t>2</t>
@@ -321,7 +321,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>601경 6331조 4,412억 9,078만</t>
+    <t>601경 6331조 4412억 9078만</t>
   </si>
   <si>
     <t>3</t>
@@ -336,7 +336,7 @@
     <t>126</t>
   </si>
   <si>
-    <t>563경 6043조 9,088억 4,883만</t>
+    <t>563경 6043조 9088억 4883만</t>
   </si>
   <si>
     <t>4</t>
@@ -354,7 +354,7 @@
     <t>127</t>
   </si>
   <si>
-    <t>450경 8883조 2,276억 7,901만</t>
+    <t>450경 8883조 2276억 7901만</t>
   </si>
   <si>
     <t>5</t>
@@ -369,7 +369,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>420경 6269조 4,910억 8,038만</t>
+    <t>420경 6269조 4910억 8038만</t>
   </si>
   <si>
     <t>6</t>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
   </si>
   <si>
-    <t>315경 7931조 9,612억 2,036만</t>
+    <t>315경 7931조 9612억 2036만</t>
   </si>
   <si>
     <t>7</t>
@@ -396,7 +396,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>284경 2376조 9,293억 7,027만</t>
+    <t>284경 2376조 9293억 7027만</t>
   </si>
   <si>
     <t>8</t>
@@ -414,7 +414,7 @@
     <t>123</t>
   </si>
   <si>
-    <t>135경 6784조 206억 3,874만</t>
+    <t>135경 6784조 206억 3874만</t>
   </si>
   <si>
     <t>9</t>
@@ -426,7 +426,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
   </si>
   <si>
-    <t>78경 3119조 9,191억 2,348만</t>
+    <t>78경 3119조 9191억 2348만</t>
   </si>
   <si>
     <t>10</t>
@@ -441,7 +441,7 @@
     <t>122</t>
   </si>
   <si>
-    <t>74경 3470조 8,838억 859만</t>
+    <t>74경 3470조 8838억 859만</t>
   </si>
   <si>
     <t>11</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8J</t>
   </si>
   <si>
-    <t>38경 5764조 9,611억 6,669만</t>
+    <t>38경 5764조 9611억 6669만</t>
   </si>
   <si>
     <t>12</t>
@@ -471,7 +471,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>34경 1451조 9,714억 345만</t>
+    <t>34경 1451조 9714억 345만</t>
   </si>
   <si>
     <t>13</t>
@@ -483,7 +483,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EB%A5%B8</t>
   </si>
   <si>
-    <t>30경 7900조 3,282억 3,172만</t>
+    <t>30경 7900조 3282억 3172만</t>
   </si>
   <si>
     <t>14</t>
@@ -498,7 +498,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>22경 6456조 3,137억 8,236만</t>
+    <t>22경 6456조 3137억 8236만</t>
   </si>
   <si>
     <t>15</t>
@@ -513,7 +513,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>19경 3312조 5,233억 2,265만</t>
+    <t>19경 3312조 5233억 2265만</t>
   </si>
   <si>
     <t>16</t>
@@ -525,7 +525,7 @@
     <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
   </si>
   <si>
-    <t>17경 3946조 5,348억 1,517만</t>
+    <t>17경 3946조 5348억 1517만</t>
   </si>
   <si>
     <t>17</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
   </si>
   <si>
-    <t>15경 8565조 6,921억 1,543만</t>
+    <t>15경 8565조 6921억 1543만</t>
   </si>
   <si>
     <t>18</t>
@@ -552,7 +552,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>10경 9673조 4,839억 2,391만</t>
+    <t>10경 9673조 4839억 2391만</t>
   </si>
   <si>
     <t>19</t>
@@ -570,7 +570,7 @@
     <t>118</t>
   </si>
   <si>
-    <t>10경 9546조 4,143억 8,614만</t>
+    <t>10경 9546조 4143억 8614만</t>
   </si>
   <si>
     <t>20</t>
@@ -582,7 +582,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
   </si>
   <si>
-    <t>8경 6972조 5,711억 9,285만</t>
+    <t>8경 6972조 5711억 9285만</t>
   </si>
   <si>
     <t>21</t>
@@ -594,7 +594,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>6경 4795조 5,878억 5,573만</t>
+    <t>6경 4795조 5878억 5573만</t>
   </si>
   <si>
     <t>22</t>
@@ -609,7 +609,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>6경 4634조 4,428억 4,645만</t>
+    <t>6경 4634조 4428억 4645만</t>
   </si>
   <si>
     <t>23</t>
@@ -621,7 +621,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8A%AC</t>
   </si>
   <si>
-    <t>6경 4278조 6,791억 8,373만</t>
+    <t>6경 4278조 6791억 8373만</t>
   </si>
   <si>
     <t>24</t>
@@ -633,7 +633,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
   </si>
   <si>
-    <t>5경 7426조 2,445억 2,968만</t>
+    <t>5경 7426조 2445억 2968만</t>
   </si>
   <si>
     <t>25</t>
@@ -657,7 +657,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>4경 2653조 3,164억 10만</t>
+    <t>4경 2653조 3164억 10만</t>
   </si>
   <si>
     <t>27</t>
@@ -669,7 +669,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
   </si>
   <si>
-    <t>3경 471조 3,056억 2,823만</t>
+    <t>3경 471조 3056억 2823만</t>
   </si>
   <si>
     <t>28</t>
@@ -681,7 +681,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EC%A7%80%EB%A7%88%EC%98%A4</t>
   </si>
   <si>
-    <t>2경 9330조 6,252억 5,962만</t>
+    <t>2경 9330조 6252억 5962만</t>
   </si>
   <si>
     <t>29</t>
@@ -696,7 +696,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>1경 6272조 175억 1,648만</t>
+    <t>1경 6272조 175억 1648만</t>
   </si>
   <si>
     <t>30</t>
@@ -711,7 +711,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 5136조 8,361억 7,335만</t>
+    <t>1경 5136조 8361억 7335만</t>
   </si>
   <si>
     <t>금은동S2</t>
@@ -720,7 +720,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%EC%9D%80%EB%8F%99S2</t>
   </si>
   <si>
-    <t>926경 1868조 5,138억 6,982만</t>
+    <t>926경 1868조 5138억 6982만</t>
   </si>
   <si>
     <t>라온JW</t>
@@ -732,7 +732,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>564경 9054조 2,245억 2,703만</t>
+    <t>564경 9054조 2245억 2703만</t>
   </si>
   <si>
     <t>슨녀</t>
@@ -741,13 +741,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>83경 7316조 4,265억 7,115만</t>
+    <t>83경 7316조 4265억 7115만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
   </si>
   <si>
-    <t>43경 9111조 4,126억 228만</t>
+    <t>43경 9111조 4126억 228만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -756,7 +756,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
   </si>
   <si>
-    <t>39경 7201조 2,284억 1,187만</t>
+    <t>39경 7201조 2284억 1187만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -765,7 +765,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>33경 6195조 8,781억 3,849만</t>
+    <t>33경 6195조 8781억 3849만</t>
   </si>
   <si>
     <t>임홀리</t>
@@ -774,7 +774,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>12경 6271조 4,731억 4,064만</t>
+    <t>12경 6271조 4731억 4064만</t>
   </si>
   <si>
     <t>쁘덍</t>
@@ -783,7 +783,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%81%98%EB%8D%8D</t>
   </si>
   <si>
-    <t>12경 4823조 3,227억 7,538만</t>
+    <t>12경 4823조 3227억 7538만</t>
   </si>
   <si>
     <t>제껴</t>
@@ -792,7 +792,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>10경 3952조 5,796억 1,968만</t>
+    <t>10경 3952조 5796억 1968만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -804,7 +804,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>7경 5299조 1,666억 2,339만</t>
+    <t>7경 5299조 1666억 2339만</t>
   </si>
   <si>
     <t>엘리자베타</t>
@@ -813,7 +813,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A6%AC%EC%9E%90%EB%B2%A0%ED%83%80</t>
   </si>
   <si>
-    <t>5경 2625조 4,886억 9,728만</t>
+    <t>5경 2625조 4886억 9728만</t>
   </si>
   <si>
     <t>어흥이다</t>
@@ -822,7 +822,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>5경 2534조 3,569억 771만</t>
+    <t>5경 2534조 3569억 771만</t>
   </si>
   <si>
     <t>우꼬쨩</t>
@@ -831,7 +831,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
   </si>
   <si>
-    <t>4경 6715조 9,544억 8,339만</t>
+    <t>4경 6715조 9544억 8339만</t>
   </si>
   <si>
     <t>누룽지룽누</t>
@@ -840,7 +840,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EB%A3%BD%EC%A7%80%EB%A3%BD%EB%88%84</t>
   </si>
   <si>
-    <t>4경 6342조 5,950억 7,988만</t>
+    <t>4경 6342조 5950억 7988만</t>
   </si>
   <si>
     <t>비밀키</t>
@@ -849,7 +849,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
   </si>
   <si>
-    <t>3경 8363조 108억 1,090만</t>
+    <t>3경 8363조 108억 1090만</t>
   </si>
   <si>
     <t>홍시마로</t>
@@ -858,7 +858,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>3경 3663조 7,765억 3,019만</t>
+    <t>3경 3663조 7765억 3019만</t>
   </si>
   <si>
     <t>붙잡아</t>
@@ -867,7 +867,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
   </si>
   <si>
-    <t>3경 3402조 2,179억 6,058만</t>
+    <t>3경 3402조 2179억 6058만</t>
   </si>
   <si>
     <t>지아라떼</t>
@@ -876,7 +876,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%84%EB%9D%BC%EB%96%BC</t>
   </si>
   <si>
-    <t>3경 557조 9,334억 1,681만</t>
+    <t>3경 557조 9334억 1681만</t>
   </si>
   <si>
     <t>슛맨</t>
@@ -885,7 +885,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
   </si>
   <si>
-    <t>2경 8095조 7,314억 2,394만</t>
+    <t>2경 8095조 7314억 2394만</t>
   </si>
   <si>
     <t>o엔젤o</t>
@@ -894,7 +894,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
   </si>
   <si>
-    <t>2경 4819조 8,723억 7,152만</t>
+    <t>2경 4819조 8723억 7152만</t>
   </si>
   <si>
     <t>득츈</t>
@@ -903,7 +903,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
   </si>
   <si>
-    <t>2경 3813조 4,513억 3,727만</t>
+    <t>2경 3813조 4513억 3727만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -912,7 +912,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 2641조 6,242억 7,031만</t>
+    <t>2경 2641조 6242억 7031만</t>
   </si>
   <si>
     <t>메론맛빵</t>
@@ -921,7 +921,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
   </si>
   <si>
-    <t>1경 9736조 4,770억 2,575만</t>
+    <t>1경 9736조 4770억 2575만</t>
   </si>
   <si>
     <t>24년생정춘식</t>
@@ -930,7 +930,7 @@
     <t>https://mgf.gg/contents/character.php?n=24%EB%85%84%EC%83%9D%EC%A0%95%EC%B6%98%EC%8B%9D</t>
   </si>
   <si>
-    <t>1경 7516조 4,862억 2,994만</t>
+    <t>1경 7516조 4862억 2994만</t>
   </si>
   <si>
     <t>시프님</t>
@@ -939,7 +939,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
   </si>
   <si>
-    <t>1경 3725조 4,391억 3,830만</t>
+    <t>1경 3725조 4391억 3830만</t>
   </si>
   <si>
     <t>야옹이다</t>
@@ -948,7 +948,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>1경 633조 3,863억 8,751만</t>
+    <t>1경 633조 3863억 8751만</t>
   </si>
   <si>
     <t>출장괴물</t>
@@ -957,7 +957,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>9636조 9,388억 6,240만</t>
+    <t>9636조 9388억 6240만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -966,7 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>8547조 7,426억 824만</t>
+    <t>8547조 7426억 824만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -975,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>6791조 551억 5,027만</t>
+    <t>6791조 551억 5027만</t>
   </si>
   <si>
     <t>마옥지</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
   </si>
   <si>
-    <t>280경 3220조 6,404억 6,122만</t>
+    <t>280경 3220조 6404억 6122만</t>
   </si>
   <si>
     <t>해물만두야</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
   </si>
   <si>
-    <t>231경 7865조 5,718억 420만</t>
+    <t>231경 7865조 5718억 420만</t>
   </si>
   <si>
     <t>캐일리</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>186경 7071조 3,782억 8,079만</t>
+    <t>186경 7071조 3782억 8079만</t>
   </si>
   <si>
     <t>설익은앵숭</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
   </si>
   <si>
-    <t>105경 4731조 5,416억 8,730만</t>
+    <t>105경 4731조 5416억 8730만</t>
   </si>
   <si>
     <t>킹규봉</t>
@@ -1020,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
   </si>
   <si>
-    <t>85경 8894조 1,952억 8,378만</t>
+    <t>85경 8894조 1952억 8378만</t>
   </si>
   <si>
     <t>설함마</t>
@@ -1029,7 +1029,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>68경 6411조 7,432억 2,421만</t>
+    <t>68경 6411조 7432억 2421만</t>
   </si>
   <si>
     <t>설묘묘</t>
@@ -1038,7 +1038,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>46경 1721조 8,958억 6,847만</t>
+    <t>46경 1721조 8958억 6847만</t>
   </si>
   <si>
     <t>루델밍</t>
@@ -1047,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
   </si>
   <si>
-    <t>45경 5109조 8,480억 2,031만</t>
+    <t>45경 5109조 8480억 2031만</t>
   </si>
   <si>
     <t>설봄a</t>
@@ -1059,7 +1059,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>43경 847조 2,572억 7,170만</t>
+    <t>43경 847조 2572억 7170만</t>
   </si>
   <si>
     <t>너굴얌</t>
@@ -1068,7 +1068,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>42경 3138조 5,889억 4,039만</t>
+    <t>42경 3138조 5889억 4039만</t>
   </si>
   <si>
     <t>시드리안</t>
@@ -1077,7 +1077,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
   </si>
   <si>
-    <t>29경 7613조 5,062억 2,329만</t>
+    <t>29경 7613조 5062억 2329만</t>
   </si>
   <si>
     <t>싲프</t>
@@ -1086,7 +1086,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>29경 6216조 5,359억 3,679만</t>
+    <t>29경 6216조 5359억 3679만</t>
   </si>
   <si>
     <t>셀렘이</t>
@@ -1095,7 +1095,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>24경 3354조 9,527억 6,259만</t>
+    <t>24경 3354조 9527억 6259만</t>
   </si>
   <si>
     <t>졸귀탱이</t>
@@ -1104,7 +1104,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>20경 5428조 7,775억 656만</t>
+    <t>20경 5428조 7775억 656만</t>
   </si>
   <si>
     <t>설딩</t>
@@ -1113,7 +1113,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
   </si>
   <si>
-    <t>19경 7396조 2,622억 1,029만</t>
+    <t>19경 7396조 2622억 1029만</t>
   </si>
   <si>
     <t>마덕칠</t>
@@ -1122,7 +1122,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>18경 9870조 503억 9,521만</t>
+    <t>18경 9870조 503억 9521만</t>
   </si>
   <si>
     <t>선콜은차가워</t>
@@ -1131,7 +1131,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>18경 5875조 8,151억 3,649만</t>
+    <t>18경 5875조 8151억 3649만</t>
   </si>
   <si>
     <t>슐아</t>
@@ -1140,7 +1140,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
   </si>
   <si>
-    <t>11경 2907조 6억 1,960만</t>
+    <t>11경 2907조 6억 1960만</t>
   </si>
   <si>
     <t>경성2018</t>
@@ -1149,7 +1149,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
   </si>
   <si>
-    <t>9경 1574조 1,762억 1,736만</t>
+    <t>9경 1574조 1762억 1736만</t>
   </si>
   <si>
     <t>설름</t>
@@ -1167,7 +1167,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
   </si>
   <si>
-    <t>6경 5564조 1,888억 7,889만</t>
+    <t>6경 5564조 1888억 7889만</t>
   </si>
   <si>
     <t>다다익숍</t>
@@ -1176,13 +1176,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>6경 1783조 4,474억 1,098만</t>
+    <t>6경 1783조 4474억 1098만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>5경 5478조 8,492억 3,032만</t>
+    <t>5경 5478조 8492억 3032만</t>
   </si>
   <si>
     <t>애봉얌</t>
@@ -1194,7 +1194,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>3경 4312조 1,092억 5,647만</t>
+    <t>3경 4312조 1092억 5647만</t>
   </si>
   <si>
     <t>상구얌</t>
@@ -1203,7 +1203,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 944조 1,885억 5,352만</t>
+    <t>3경 944조 1885억 5352만</t>
   </si>
   <si>
     <t>설콩순</t>
@@ -1212,7 +1212,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 5307조 6,581억 7,894만</t>
+    <t>1경 5307조 6581억 7894만</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -1221,7 +1221,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 5301조 1,854억 5,754만</t>
+    <t>1경 5301조 1854억 5754만</t>
   </si>
   <si>
     <t>설치는정상인</t>
@@ -1230,7 +1230,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
   </si>
   <si>
-    <t>1경 4592조 3,595억 1,013만</t>
+    <t>1경 4592조 3595억 1013만</t>
   </si>
   <si>
     <t>네오메디</t>
@@ -1239,7 +1239,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
   </si>
   <si>
-    <t>1경 1050조 7,102억 6,148만</t>
+    <t>1경 1050조 7102억 6148만</t>
   </si>
   <si>
     <t>군보</t>
@@ -1248,7 +1248,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>203경 9556조 9,702억 3,150만</t>
+    <t>203경 9556조 9702억 3150만</t>
   </si>
   <si>
     <t>눙키</t>
@@ -1257,7 +1257,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
   </si>
   <si>
-    <t>128경 6382조 8,779억 8,244만</t>
+    <t>128경 6382조 8779억 8244만</t>
   </si>
   <si>
     <t>5형사</t>
@@ -1266,13 +1266,13 @@
     <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>104경 9897조 9,159억 7,613만</t>
+    <t>104경 9897조 9159억 7613만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
   </si>
   <si>
-    <t>75경 6411조 4,000억 426만</t>
+    <t>75경 6411조 4000억 426만</t>
   </si>
   <si>
     <t>심천</t>
@@ -1281,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>69경 9303조 5,433억 6,974만</t>
+    <t>69경 9303조 5433억 6974만</t>
   </si>
   <si>
     <t>혁수킹</t>
@@ -1290,7 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
   </si>
   <si>
-    <t>69경 6713조 8,769억 1,358만</t>
+    <t>69경 6713조 8769억 1358만</t>
   </si>
   <si>
     <t>Matter</t>
@@ -1299,7 +1299,7 @@
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>66경 8928조 7,109억 7,340만</t>
+    <t>66경 8928조 7109억 7340만</t>
   </si>
   <si>
     <t>또르뱅</t>
@@ -1308,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>64경 6281조 8,605억 3,325만</t>
+    <t>64경 6281조 8605억 3325만</t>
   </si>
   <si>
     <t>원중언니</t>
@@ -1317,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>58경 7502조 2,096억 8,571만</t>
+    <t>58경 7502조 2096억 8571만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1326,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%84%ED%98%B8%EB%96%A1</t>
   </si>
   <si>
-    <t>55경 5523조 6,632억 6,782만</t>
+    <t>55경 5523조 6632억 6782만</t>
   </si>
   <si>
     <t>총괄한석현</t>
@@ -1335,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%9D%EA%B4%84%ED%95%9C%EC%84%9D%ED%98%84</t>
   </si>
   <si>
-    <t>44경 4442조 9,717억 5,468만</t>
+    <t>44경 4442조 9717억 5468만</t>
   </si>
   <si>
     <t>냠규리</t>
@@ -1344,7 +1344,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>39경 129조 8,282억 7,515만</t>
+    <t>39경 129조 8282억 7515만</t>
   </si>
   <si>
     <t>파퍼</t>
@@ -1353,7 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>32경 7798조 7,344억 3,050만</t>
+    <t>32경 7798조 7344억 3050만</t>
   </si>
   <si>
     <t>김나뭉</t>
@@ -1362,7 +1362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
   </si>
   <si>
-    <t>30경 8735조 5,003억 7,097만</t>
+    <t>30경 8735조 5003억 7097만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1371,7 +1371,7 @@
     <t>https://mgf.gg/contents/character.php?n=Hoood</t>
   </si>
   <si>
-    <t>17경 8032조 1,522억 1,223만</t>
+    <t>17경 8032조 1522억 1223만</t>
   </si>
   <si>
     <t>찐맨듀</t>
@@ -1380,7 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
   </si>
   <si>
-    <t>14경 3225조 9,241억 6,322만</t>
+    <t>14경 3225조 9241억 6322만</t>
   </si>
   <si>
     <t>껌정색</t>
@@ -1389,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>14경 1580조 2,176억 6,617만</t>
+    <t>14경 1580조 2176억 6617만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1398,7 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>13경 5670조 5,033억 9,103만</t>
+    <t>13경 5670조 5033억 9103만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -1407,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
   </si>
   <si>
-    <t>13경 3744조 5,309억 977만</t>
+    <t>13경 3744조 5309억 977만</t>
   </si>
   <si>
     <t>악경</t>
@@ -1416,7 +1416,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
   </si>
   <si>
-    <t>10경 2388조 6,776억 2,691만</t>
+    <t>10경 2388조 6776억 2691만</t>
   </si>
   <si>
     <t>Rahee</t>
@@ -1425,7 +1425,7 @@
     <t>https://mgf.gg/contents/character.php?n=Rahee</t>
   </si>
   <si>
-    <t>7경 8782조 9,990억 6,632만</t>
+    <t>7경 8782조 9990억 6632만</t>
   </si>
   <si>
     <t>고먀츠나나</t>
@@ -1434,7 +1434,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
   </si>
   <si>
-    <t>7경 197조 6,667억 8,901만</t>
+    <t>7경 197조 6667억 8901만</t>
   </si>
   <si>
     <t>딤개</t>
@@ -1443,7 +1443,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
   </si>
   <si>
-    <t>5경 8018조 3,068억 3,402만</t>
+    <t>5경 8018조 3068억 3402만</t>
   </si>
   <si>
     <t>히째히째</t>
@@ -1452,7 +1452,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
   </si>
   <si>
-    <t>4경 6252조 5,336억 736만</t>
+    <t>4경 6252조 5336억 736만</t>
   </si>
   <si>
     <t>통뼈1</t>
@@ -1461,7 +1461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
   </si>
   <si>
-    <t>3경 9314조 1,653억 5,009만</t>
+    <t>3경 9314조 1653억 5009만</t>
   </si>
   <si>
     <t>돌로레스</t>
@@ -1470,7 +1470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EB%A1%9C%EB%A0%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>3경 8262조 6,756억 6,501만</t>
+    <t>3경 8262조 6756억 6501만</t>
   </si>
   <si>
     <t>바람의새벽</t>
@@ -1479,7 +1479,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
   </si>
   <si>
-    <t>2경 9221조 4,290억 1,767만</t>
+    <t>2경 9221조 4290억 1767만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1488,7 +1488,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 2518조 5,995억 7,371만</t>
+    <t>2경 2518조 5995억 7371만</t>
   </si>
   <si>
     <t>셀러문</t>
@@ -1500,7 +1500,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>4163조 60억 3,041만</t>
+    <t>4163조 60억 3041만</t>
   </si>
   <si>
     <t>라온XR</t>
@@ -1509,7 +1509,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8XR</t>
   </si>
   <si>
-    <t>453경 1832조 9,684억 178만</t>
+    <t>453경 1832조 9684억 178만</t>
   </si>
   <si>
     <t>매스몬스터</t>
@@ -1518,7 +1518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%AA%AC%EC%8A%A4%ED%84%B0</t>
   </si>
   <si>
-    <t>280경 1301조 4,537억 3,951만</t>
+    <t>280경 1301조 4537억 3951만</t>
   </si>
   <si>
     <t>하잉안파파</t>
@@ -1527,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>202경 5067조 3,570억 6,607만</t>
+    <t>202경 5067조 3570억 6607만</t>
   </si>
   <si>
     <t>코코듀</t>
@@ -1536,7 +1536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
   </si>
   <si>
-    <t>106경 8507조 3,404억 2,537만</t>
+    <t>106경 8507조 3404억 2537만</t>
   </si>
   <si>
     <t>타이슨에어랩</t>
@@ -1545,13 +1545,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
   </si>
   <si>
-    <t>62경 8614조 6,256억 7,372만</t>
+    <t>62경 8614조 6256억 7372만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
   </si>
   <si>
-    <t>55경 1587조 5,056억 2,487만</t>
+    <t>55경 1587조 5056억 2487만</t>
   </si>
   <si>
     <t>미야고</t>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%95%BC%EA%B3%A0</t>
   </si>
   <si>
-    <t>51경 2943조 3,453억 7,104만</t>
+    <t>51경 2943조 3453억 7104만</t>
   </si>
   <si>
     <t>캔드릭</t>
@@ -1569,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
   </si>
   <si>
-    <t>36경 7312조 8,666억 1,977만</t>
+    <t>36경 7312조 8666억 1977만</t>
   </si>
   <si>
     <t>용보이</t>
@@ -1578,7 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>36경 6925조 9,193억 5,914만</t>
+    <t>36경 6925조 9193억 5914만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -1587,7 +1587,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
   </si>
   <si>
-    <t>23경 5631조 1,681억 611만</t>
+    <t>23경 5631조 1681억 611만</t>
   </si>
   <si>
     <t>똥갈</t>
@@ -1596,7 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
   </si>
   <si>
-    <t>18경 9370조 4,942억 968만</t>
+    <t>18경 9370조 4942억 968만</t>
   </si>
   <si>
     <t>도적왕대현</t>
@@ -1605,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EC%99%95%EB%8C%80%ED%98%84</t>
   </si>
   <si>
-    <t>11경 2244조 3,229억 8,341만</t>
+    <t>11경 2244조 3229억 8341만</t>
   </si>
   <si>
     <t>도농롱</t>
@@ -1614,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%86%8D%EB%A1%B1</t>
   </si>
   <si>
-    <t>10경 7295조 4,564억 5,245만</t>
+    <t>10경 7295조 4564억 5245만</t>
   </si>
   <si>
     <t>힐옹</t>
@@ -1623,7 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%98%B9</t>
   </si>
   <si>
-    <t>8경 8501조 7,368억 9,660만</t>
+    <t>8경 8501조 7368억 9660만</t>
   </si>
   <si>
     <t>반불</t>
@@ -1632,7 +1632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
   </si>
   <si>
-    <t>7경 7130조 6,693억 9,364만</t>
+    <t>7경 7130조 6693억 9364만</t>
   </si>
   <si>
     <t>혜도로동</t>
@@ -1641,7 +1641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>7경 5608조 8,584억 2,657만</t>
+    <t>7경 5608조 8584억 2657만</t>
   </si>
   <si>
     <t>붕어줍</t>
@@ -1650,7 +1650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EC%96%B4%EC%A4%8D</t>
   </si>
   <si>
-    <t>7경 2005조 2,221억 3,118만</t>
+    <t>7경 2005조 2221억 3118만</t>
   </si>
   <si>
     <t>조명준</t>
@@ -1659,7 +1659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
   </si>
   <si>
-    <t>5경 8825조 2,726억 919만</t>
+    <t>5경 8825조 2726억 919만</t>
   </si>
   <si>
     <t>로생</t>
@@ -1668,7 +1668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
   </si>
   <si>
-    <t>5경 8284조 8,153억 7,505만</t>
+    <t>5경 8284조 8153억 7505만</t>
   </si>
   <si>
     <t>Redwine</t>
@@ -1686,7 +1686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
   </si>
   <si>
-    <t>5경 4338조 2,243억 5,938만</t>
+    <t>5경 4338조 2243억 5938만</t>
   </si>
   <si>
     <t>망치반죽</t>
@@ -1695,7 +1695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
   </si>
   <si>
-    <t>4경 8333조 414억 9,098만</t>
+    <t>4경 8333조 414억 9098만</t>
   </si>
   <si>
     <t>유도로동</t>
@@ -1704,7 +1704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>4경 3548조 1,193억 5,686만</t>
+    <t>4경 3548조 1193억 5686만</t>
   </si>
   <si>
     <t>그때그아이</t>
@@ -1713,7 +1713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>3경 1551조 4,991억 3,144만</t>
+    <t>3경 1551조 4991억 3144만</t>
   </si>
   <si>
     <t>메키메렁</t>
@@ -1722,7 +1722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
   </si>
   <si>
-    <t>3경 1254조 3,197억 3,591만</t>
+    <t>3경 1254조 3197억 3591만</t>
   </si>
   <si>
     <t>루빙</t>
@@ -1731,7 +1731,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
   </si>
   <si>
-    <t>2경 848조 8,453억 998만</t>
+    <t>2경 848조 8453억 998만</t>
   </si>
   <si>
     <t>꽁꽁얼었다</t>
@@ -1740,7 +1740,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EC%96%BC%EC%97%88%EB%8B%A4</t>
   </si>
   <si>
-    <t>2경 415조 4,230억 7,944만</t>
+    <t>2경 415조 4230억 7944만</t>
   </si>
   <si>
     <t>spemi</t>
@@ -1749,7 +1749,7 @@
     <t>https://mgf.gg/contents/character.php?n=spemi</t>
   </si>
   <si>
-    <t>1경 8496조 7,102억 7,539만</t>
+    <t>1경 8496조 7102억 7539만</t>
   </si>
   <si>
     <t>우솝이</t>
@@ -1758,7 +1758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
   </si>
   <si>
-    <t>1경 6505조 2,340억 1,882만</t>
+    <t>1경 6505조 2340억 1882만</t>
   </si>
   <si>
     <t>막또날드</t>
@@ -1767,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
   </si>
   <si>
-    <t>1경 5570조 6,988억 7,323만</t>
+    <t>1경 5570조 6988억 7323만</t>
   </si>
   <si>
     <t>강서구도적</t>
@@ -1776,7 +1776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
   </si>
   <si>
-    <t>561경 8770조 6,553억 4,335만</t>
+    <t>561경 8770조 6553억 4335만</t>
   </si>
   <si>
     <t>따코유</t>
@@ -1785,7 +1785,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EC%BD%94%EC%9C%A0</t>
   </si>
   <si>
-    <t>397경 9870조 1,742억 2,256만</t>
+    <t>397경 9870조 1742억 2256만</t>
   </si>
   <si>
     <t>뚱털</t>
@@ -1794,7 +1794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%ED%84%B8</t>
   </si>
   <si>
-    <t>139경 3957조 7,548억 7,251만</t>
+    <t>139경 3957조 7548억 7251만</t>
   </si>
   <si>
     <t>뽀로로남편</t>
@@ -1803,7 +1803,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
   </si>
   <si>
-    <t>109경 3197조 7,992억 7,558만</t>
+    <t>109경 3197조 7992억 7558만</t>
   </si>
   <si>
     <t>귤놈펜</t>
@@ -1812,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
   </si>
   <si>
-    <t>88경 1038조 2,454억 1,638만</t>
+    <t>88경 1038조 2454억 1638만</t>
   </si>
   <si>
     <t>꿀서은</t>
@@ -1821,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
   </si>
   <si>
-    <t>34경 695조 9,726억 7,064만</t>
+    <t>34경 695조 9726억 7064만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -1830,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>31경 6241조 1,543억 8,981만</t>
+    <t>31경 6241조 1543억 8981만</t>
   </si>
   <si>
     <t>게탕</t>
@@ -1839,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
   </si>
   <si>
-    <t>23경 7566조 8,246억 7,693만</t>
+    <t>23경 7566조 8246억 7693만</t>
   </si>
   <si>
     <t>긴나라</t>
@@ -1848,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>21경 6883조 2,459억 5,189만</t>
+    <t>21경 6883조 2459억 5189만</t>
   </si>
   <si>
     <t>쿨쥐돌</t>
@@ -1857,7 +1857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
   </si>
   <si>
-    <t>18경 9649조 7,630억 4,519만</t>
+    <t>18경 9649조 7630억 4519만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -1866,7 +1866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
   </si>
   <si>
-    <t>13경 5291조 6,646억 9,579만</t>
+    <t>13경 5291조 6646억 9579만</t>
   </si>
   <si>
     <t>류텐</t>
@@ -1875,7 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
   </si>
   <si>
-    <t>9경 3771조 2,580억 9,733만</t>
+    <t>9경 3771조 2580억 9733만</t>
   </si>
   <si>
     <t>철푸닥</t>
@@ -1884,7 +1884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%A0%ED%91%B8%EB%8B%A5</t>
   </si>
   <si>
-    <t>7경 7242조 4,697억 2,671만</t>
+    <t>7경 7242조 4697억 2671만</t>
   </si>
   <si>
     <t>원이유이</t>
@@ -1893,7 +1893,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%9D%B4%EC%9C%A0%EC%9D%B4</t>
   </si>
   <si>
-    <t>4경 2472조 8,316억 569만</t>
+    <t>4경 2472조 8316억 569만</t>
   </si>
   <si>
     <t>하드웨어</t>
@@ -1902,7 +1902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>3경 7289조 7,623억 1,803만</t>
+    <t>3경 7289조 7623억 1803만</t>
   </si>
   <si>
     <t>ShellyCake</t>
@@ -1911,13 +1911,13 @@
     <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
   </si>
   <si>
-    <t>2경 8542조 5,263억 2,188만</t>
+    <t>2경 8542조 5263억 2188만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
   </si>
   <si>
-    <t>2경 6547조 7,780억 2,631만</t>
+    <t>2경 6547조 7780억 2631만</t>
   </si>
   <si>
     <t>오정구불독</t>
@@ -1926,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>1경 9840조 8,606억 6,150만</t>
+    <t>1경 9840조 8606억 6150만</t>
   </si>
   <si>
     <t>양덕하늘채</t>
@@ -1935,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8D%95%ED%95%98%EB%8A%98%EC%B1%84</t>
   </si>
   <si>
-    <t>1경 7719조 5,512억 3,060만</t>
+    <t>1경 7719조 5512억 3060만</t>
   </si>
   <si>
     <t>레드플레이어</t>
@@ -1944,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
   </si>
   <si>
-    <t>1경 5246조 8,423억 953만</t>
+    <t>1경 5246조 8423억 953만</t>
   </si>
   <si>
     <t>주하사랑</t>
@@ -1953,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
   </si>
   <si>
-    <t>1경 4364조 8,262억 2,018만</t>
+    <t>1경 4364조 8262억 2018만</t>
   </si>
   <si>
     <t>구미적</t>
@@ -1962,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
   </si>
   <si>
-    <t>1경 3726조 7,395억 147만</t>
+    <t>1경 3726조 7395억 147만</t>
   </si>
   <si>
     <t>예슬a</t>
@@ -1974,7 +1974,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>1경 2932조 2,761억 2,173만</t>
+    <t>1경 2932조 2761억 2173만</t>
   </si>
   <si>
     <t>검샷</t>
@@ -1983,7 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
   </si>
   <si>
-    <t>1경 1615조 5,659억 493만</t>
+    <t>1경 1615조 5659억 493만</t>
   </si>
   <si>
     <t>브리또강철중</t>
@@ -1992,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A6%AC%EB%98%90%EA%B0%95%EC%B2%A0%EC%A4%91</t>
   </si>
   <si>
-    <t>1경 83조 3,899억 404만</t>
+    <t>1경 83조 3899억 404만</t>
   </si>
   <si>
     <t>꼬기갓</t>
@@ -2001,7 +2001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
   </si>
   <si>
-    <t>8285조 5,244억 911만</t>
+    <t>8285조 5244억 911만</t>
   </si>
   <si>
     <t>장아린</t>
@@ -2010,7 +2010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
   </si>
   <si>
-    <t>8133조 6,906억 9,372만</t>
+    <t>8133조 6906억 9372만</t>
   </si>
   <si>
     <t>l빠다코코낫l</t>
@@ -2019,7 +2019,7 @@
     <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
   </si>
   <si>
-    <t>7066조 4,815억 2,818만</t>
+    <t>7066조 4815억 2818만</t>
   </si>
   <si>
     <t>리광춘</t>
@@ -2028,7 +2028,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EA%B4%91%EC%B6%98</t>
   </si>
   <si>
-    <t>6098조 5,009억 8,907만</t>
+    <t>6098조 5009억 8907만</t>
   </si>
   <si>
     <t>어꼬</t>
@@ -2040,7 +2040,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>3751조 3,186억 2,243만</t>
+    <t>3751조 3186억 2243만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2049,7 +2049,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>25경 4823조 3,360억 295만</t>
+    <t>25경 4823조 3360억 295만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -2058,7 +2058,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>19경 8464조 5,082억 5,270만</t>
+    <t>19경 8464조 5082억 5270만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -2067,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>12경 4306조 3,052억 4,003만</t>
+    <t>12경 4306조 3052억 4003만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2076,7 +2076,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>11경 4105조 7,960억 279만</t>
+    <t>11경 4105조 7960억 279만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>10경 6154조 8799억 4676만</t>
   </si>
   <si>
     <t>약어</t>
@@ -2085,16 +2094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>10경 4738조 815억 6,221만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>10경 3451조 2,235억 7,402만</t>
+    <t>10경 4738조 815억 6221만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -2103,7 +2103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 3290조 8,758억 715만</t>
+    <t>9경 3423조 3510억 8891만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -2112,7 +2112,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>7경 6148조 2,651억 9,696만</t>
+    <t>7경 6148조 2651억 9696만</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>7경 3381조 2238억 1561만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -2121,16 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
   </si>
   <si>
-    <t>7경 3059조 933억 2,511만</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>6경 7083조 325억 1,634만</t>
+    <t>7경 3059조 933억 2511만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -2139,7 +2139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>5경 5228조 9,003억 4,099만</t>
+    <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -2148,7 +2148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 4504조 4,834억 827만</t>
+    <t>2경 4504조 4834억 827만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -2157,7 +2157,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 4130조 5,641억 7,043만</t>
+    <t>2경 4130조 5641억 7043만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -2166,7 +2166,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 3271조 2,021억 502만</t>
+    <t>2경 3271조 2021억 502만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -2175,7 +2175,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%94%88%ED%86%A1%EC%8C%80%EC%88%ADE</t>
   </si>
   <si>
-    <t>2경 2936조 4,015억 1,704만</t>
+    <t>2경 2936조 4015억 1704만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -2184,7 +2184,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>2경 1323조 7,490억 7,475만</t>
+    <t>2경 1323조 7490억 7475만</t>
   </si>
   <si>
     <t>반가성</t>
@@ -2193,13 +2193,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>1경 9258조 3,650억 1,564만</t>
+    <t>1경 9258조 3650억 1564만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 7139조 5,691억 7,924만</t>
+    <t>1경 7139조 5691억 7924만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -2208,7 +2208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 5876조 1,968억 392만</t>
+    <t>1경 5876조 1968억 392만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -2217,7 +2217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>1경 5688조 4,374억 8,127만</t>
+    <t>1경 5688조 4374억 8127만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2226,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 3148조 5,412억 6,446만</t>
+    <t>1경 3148조 5412억 6446만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -2235,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 2312조 9,961억 3,717만</t>
+    <t>1경 2819조 4851억 9770만</t>
   </si>
   <si>
     <t>라똥삐</t>
@@ -2244,7 +2244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
   </si>
   <si>
-    <t>1경 2085조 1,284억 3,396만</t>
+    <t>1경 2085조 1284억 3396만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -2253,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
   </si>
   <si>
-    <t>1경 1856조 4,618억 6,137만</t>
+    <t>1경 1856조 4618억 6137만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -2262,7 +2262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 2,945억 9,039만</t>
+    <t>1경 2945억 9039만</t>
   </si>
   <si>
     <t>러너</t>
@@ -2271,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>6443조 2,165억 2,470만</t>
+    <t>6443조 2165억 2470만</t>
   </si>
   <si>
     <t>해찬나래</t>
@@ -2280,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%B0%AC%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>5796조 3,675억 8,873만</t>
+    <t>5796조 3675억 8873만</t>
   </si>
   <si>
     <t>갓겜감별사</t>
@@ -2292,7 +2292,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>341조 6,408억 9,657만</t>
+    <t>341조 6408억 9657만</t>
   </si>
 </sst>
 </file>
@@ -3025,7 +3025,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="27.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4070,7 +4070,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5082,7 +5082,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6094,7 +6094,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7106,7 +7106,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8151,7 +8151,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9196,7 +9196,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9380,7 +9380,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>154</v>
@@ -9412,7 +9412,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>154</v>
@@ -9508,10 +9508,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>696</v>
@@ -9540,10 +9540,10 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>699</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -11,20 +11,20 @@
     <sheet name="레플리카셋" sheetId="2" r:id="rId2"/>
     <sheet name="귀여미" sheetId="3" r:id="rId3"/>
     <sheet name="설묘" sheetId="4" r:id="rId4"/>
-    <sheet name="리안" sheetId="5" r:id="rId5"/>
-    <sheet name="점프킹" sheetId="6" r:id="rId6"/>
-    <sheet name="브리또" sheetId="7" r:id="rId7"/>
+    <sheet name="브리또" sheetId="5" r:id="rId5"/>
+    <sheet name="리안" sheetId="6" r:id="rId6"/>
+    <sheet name="점프킹" sheetId="7" r:id="rId7"/>
     <sheet name="셀린느" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">귀여미!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">레플리카셋!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">리안!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">브리또!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">리안!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">브리또!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">설묘!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">셀린느!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">점프킹!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">점프킹!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,7 +141,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>44</t>
+    <t>45</t>
   </si>
   <si>
     <t>Lv.10</t>
@@ -156,6 +156,30 @@
     <t>설익은체리</t>
   </si>
   <si>
+    <t>브리또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%8C%EB%A6%AC%EB%98%90</t>
+  </si>
+  <si>
+    <t>Scania 33</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>627경 2089조 6861억 9290만</t>
+  </si>
+  <si>
+    <t>대항전 중점 길드, 컨텐츠 열심히 참여하실분! 같이 꾸준히 성장하실 분들 환영! 전투력 랭킹 100등 이상!</t>
+  </si>
+  <si>
+    <t>안데일2</t>
+  </si>
+  <si>
     <t>리안</t>
   </si>
   <si>
@@ -165,7 +189,7 @@
     <t>Scania 11</t>
   </si>
   <si>
-    <t>51</t>
+    <t>52</t>
   </si>
   <si>
     <t>4위</t>
@@ -213,30 +237,6 @@
     <t>2026.09.21</t>
   </si>
   <si>
-    <t>브리또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%8C%EB%A6%AC%EB%98%90</t>
-  </si>
-  <si>
-    <t>Scania 33</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>627경 2089조 6861억 9290만</t>
-  </si>
-  <si>
-    <t>대항전 중점 길드, 컨텐츠 열심히 참여하실분! 같이 꾸준히 성장하실 분들 환영! 전투력 랭킹 100등 이상!</t>
-  </si>
-  <si>
-    <t>안데일2</t>
-  </si>
-  <si>
     <t>셀린느</t>
   </si>
   <si>
@@ -246,7 +246,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>57</t>
+    <t>59</t>
   </si>
   <si>
     <t>3위</t>
@@ -354,7 +354,7 @@
     <t>127</t>
   </si>
   <si>
-    <t>450경 8883조 2276억 7901만</t>
+    <t>459경 5381조 4891억 6857만</t>
   </si>
   <si>
     <t>5</t>
@@ -369,7 +369,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>420경 6269조 4910억 8038만</t>
+    <t>422경 7012조 6194억 5243만</t>
   </si>
   <si>
     <t>6</t>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
   </si>
   <si>
-    <t>315경 7931조 9612억 2036만</t>
+    <t>315경 9802조 4873억 6925만</t>
   </si>
   <si>
     <t>7</t>
@@ -396,7 +396,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>284경 2376조 9293억 7027만</t>
+    <t>284경 5498조 1420억 2552만</t>
   </si>
   <si>
     <t>8</t>
@@ -426,7 +426,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
   </si>
   <si>
-    <t>78경 3119조 9191억 2348만</t>
+    <t>78경 3861조 395억 5887만</t>
   </si>
   <si>
     <t>10</t>
@@ -471,7 +471,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>34경 1451조 9714억 345만</t>
+    <t>34경 9320조 3247억 2674만</t>
   </si>
   <si>
     <t>13</t>
@@ -498,7 +498,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>22경 6456조 3137억 8236만</t>
+    <t>23경 597조 3649억 5340만</t>
   </si>
   <si>
     <t>15</t>
@@ -525,7 +525,7 @@
     <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
   </si>
   <si>
-    <t>17경 3946조 5348억 1517만</t>
+    <t>17경 4193조 2973억 5294만</t>
   </si>
   <si>
     <t>17</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
   </si>
   <si>
-    <t>15경 8565조 6921억 1543만</t>
+    <t>16경 526조 1329억 5295만</t>
   </si>
   <si>
     <t>18</t>
@@ -552,7 +552,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>10경 9673조 4839억 2391만</t>
+    <t>11경 8524조 2118억 7417만</t>
   </si>
   <si>
     <t>19</t>
@@ -570,7 +570,7 @@
     <t>118</t>
   </si>
   <si>
-    <t>10경 9546조 4143억 8614만</t>
+    <t>11경 3972조 3203억 2525만</t>
   </si>
   <si>
     <t>20</t>
@@ -588,28 +588,28 @@
     <t>21</t>
   </si>
   <si>
+    <t>명품까칠공주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>6경 5992조 5215억 2892만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>뿔피리</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>6경 4795조 5878억 5573만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>명품까칠공주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>6경 4634조 4428억 4645만</t>
+    <t>6경 5706조 711억 5620만</t>
   </si>
   <si>
     <t>23</t>
@@ -633,7 +633,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
   </si>
   <si>
-    <t>5경 7426조 2445억 2968만</t>
+    <t>5경 9313조 3254억 7200만</t>
   </si>
   <si>
     <t>25</t>
@@ -657,7 +657,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>4경 2653조 3164억 10만</t>
+    <t>4경 2718조 361억 6339만</t>
   </si>
   <si>
     <t>27</t>
@@ -669,7 +669,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
   </si>
   <si>
-    <t>3경 471조 3056억 2823만</t>
+    <t>3경 746조 2008억 30만</t>
   </si>
   <si>
     <t>28</t>
@@ -693,262 +693,265 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%80%ED%95%B4</t>
   </si>
   <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1경 6272조 175억 1648만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>일단대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EB%8B%A8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1경 5136조 8361억 7335만</t>
+  </si>
+  <si>
+    <t>금은동S2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%EC%9D%80%EB%8F%99S2</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>1041경 619조 5488억 4105만</t>
+  </si>
+  <si>
+    <t>라온JW</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8JW</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>564경 9054조 2245억 2703만</t>
+  </si>
+  <si>
+    <t>슨녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
+  </si>
+  <si>
+    <t>83경 7316조 4265억 7115만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
+  </si>
+  <si>
+    <t>44경 2858조 6272억 976만</t>
+  </si>
+  <si>
+    <t>아마날</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
+  </si>
+  <si>
+    <t>39경 7201조 2284억 1187만</t>
+  </si>
+  <si>
+    <t>김해님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
+  </si>
+  <si>
+    <t>33경 8171조 4987억 9934만</t>
+  </si>
+  <si>
+    <t>쁘덍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%81%98%EB%8D%8D</t>
+  </si>
+  <si>
+    <t>12경 8660조 3484억 6741만</t>
+  </si>
+  <si>
+    <t>임홀리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>12경 6294조 2538억 7075만</t>
+  </si>
+  <si>
+    <t>제껴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
+  </si>
+  <si>
+    <t>11경 251조 7199억 90만</t>
+  </si>
+  <si>
+    <t>리브루므</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%B8%8C%EB%A3%A8%EB%AF%80</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>7경 9921조 8943억 4152만</t>
+  </si>
+  <si>
+    <t>엘리자베타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A6%AC%EC%9E%90%EB%B2%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>6경 3230조 8249억 3567만</t>
+  </si>
+  <si>
+    <t>어흥이다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>5경 3048조 8458억 4104만</t>
+  </si>
+  <si>
+    <t>누룽지룽누</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EB%A3%BD%EC%A7%80%EB%A3%BD%EB%88%84</t>
+  </si>
+  <si>
+    <t>4경 8478조 2039억 38만</t>
+  </si>
+  <si>
+    <t>우꼬쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>4경 6838조 2248억 2671만</t>
+  </si>
+  <si>
+    <t>비밀키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
+  </si>
+  <si>
+    <t>3경 8363조 108억 1090만</t>
+  </si>
+  <si>
+    <t>홍시마로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>3경 5375조 3556억 7105만</t>
+  </si>
+  <si>
+    <t>붙잡아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
+  </si>
+  <si>
+    <t>3경 3402조 2179억 6058만</t>
+  </si>
+  <si>
+    <t>지아라떼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%84%EB%9D%BC%EB%96%BC</t>
+  </si>
+  <si>
+    <t>3경 557조 9334억 1681만</t>
+  </si>
+  <si>
+    <t>슛맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>2경 8454조 3204억 3418만</t>
+  </si>
+  <si>
+    <t>o엔젤o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
+  </si>
+  <si>
+    <t>2경 4819조 8723억 7152만</t>
+  </si>
+  <si>
+    <t>Bit숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
+  </si>
+  <si>
+    <t>2경 4515조 1344억 3452만</t>
+  </si>
+  <si>
+    <t>득츈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
+  </si>
+  <si>
+    <t>2경 3813조 4513억 3727만</t>
+  </si>
+  <si>
+    <t>메론맛빵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
+  </si>
+  <si>
+    <t>2경 969조 7803억 305만</t>
+  </si>
+  <si>
+    <t>24년생정춘식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=24%EB%85%84%EC%83%9D%EC%A0%95%EC%B6%98%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>1경 7793조 3082억 68만</t>
+  </si>
+  <si>
+    <t>시프님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1경 4343조 1675억 666만</t>
+  </si>
+  <si>
+    <t>야옹이다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EB%8B%A4</t>
+  </si>
+  <si>
     <t>115</t>
   </si>
   <si>
-    <t>1경 6272조 175억 1648만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>일단대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EB%8B%A8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>1경 5136조 8361억 7335만</t>
-  </si>
-  <si>
-    <t>금은동S2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%EC%9D%80%EB%8F%99S2</t>
-  </si>
-  <si>
-    <t>926경 1868조 5138억 6982만</t>
-  </si>
-  <si>
-    <t>라온JW</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8JW</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>564경 9054조 2245억 2703만</t>
-  </si>
-  <si>
-    <t>슨녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
-  </si>
-  <si>
-    <t>83경 7316조 4265억 7115만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
-  </si>
-  <si>
-    <t>43경 9111조 4126억 228만</t>
-  </si>
-  <si>
-    <t>아마날</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
-  </si>
-  <si>
-    <t>39경 7201조 2284억 1187만</t>
-  </si>
-  <si>
-    <t>김해님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
-  </si>
-  <si>
-    <t>33경 6195조 8781억 3849만</t>
-  </si>
-  <si>
-    <t>임홀리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>12경 6271조 4731억 4064만</t>
-  </si>
-  <si>
-    <t>쁘덍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%81%98%EB%8D%8D</t>
-  </si>
-  <si>
-    <t>12경 4823조 3227억 7538만</t>
-  </si>
-  <si>
-    <t>제껴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
-  </si>
-  <si>
-    <t>10경 3952조 5796억 1968만</t>
-  </si>
-  <si>
-    <t>리브루므</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%B8%8C%EB%A3%A8%EB%AF%80</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>7경 5299조 1666억 2339만</t>
-  </si>
-  <si>
-    <t>엘리자베타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A6%AC%EC%9E%90%EB%B2%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>5경 2625조 4886억 9728만</t>
-  </si>
-  <si>
-    <t>어흥이다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>5경 2534조 3569억 771만</t>
-  </si>
-  <si>
-    <t>우꼬쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>4경 6715조 9544억 8339만</t>
-  </si>
-  <si>
-    <t>누룽지룽누</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EB%A3%BD%EC%A7%80%EB%A3%BD%EB%88%84</t>
-  </si>
-  <si>
-    <t>4경 6342조 5950억 7988만</t>
-  </si>
-  <si>
-    <t>비밀키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
-  </si>
-  <si>
-    <t>3경 8363조 108억 1090만</t>
-  </si>
-  <si>
-    <t>홍시마로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>3경 3663조 7765억 3019만</t>
-  </si>
-  <si>
-    <t>붙잡아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
-  </si>
-  <si>
-    <t>3경 3402조 2179억 6058만</t>
-  </si>
-  <si>
-    <t>지아라떼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%84%EB%9D%BC%EB%96%BC</t>
-  </si>
-  <si>
-    <t>3경 557조 9334억 1681만</t>
-  </si>
-  <si>
-    <t>슛맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>2경 8095조 7314억 2394만</t>
-  </si>
-  <si>
-    <t>o엔젤o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
-  </si>
-  <si>
-    <t>2경 4819조 8723억 7152만</t>
-  </si>
-  <si>
-    <t>득츈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
-  </si>
-  <si>
-    <t>2경 3813조 4513억 3727만</t>
-  </si>
-  <si>
-    <t>Bit숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
-  </si>
-  <si>
-    <t>2경 2641조 6242억 7031만</t>
-  </si>
-  <si>
-    <t>메론맛빵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
-  </si>
-  <si>
-    <t>1경 9736조 4770억 2575만</t>
-  </si>
-  <si>
-    <t>24년생정춘식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=24%EB%85%84%EC%83%9D%EC%A0%95%EC%B6%98%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>1경 7516조 4862억 2994만</t>
-  </si>
-  <si>
-    <t>시프님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1경 3725조 4391억 3830만</t>
-  </si>
-  <si>
-    <t>야옹이다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1경 633조 3863억 8751만</t>
+    <t>1경 1465조 5448억 942만</t>
   </si>
   <si>
     <t>출장괴물</t>
@@ -957,7 +960,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>9636조 9388억 6240만</t>
+    <t>9694조 9027억 8135만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -966,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>8547조 7426억 824만</t>
+    <t>8553조 2085억 2976만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -975,7 +978,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>6791조 551억 5027만</t>
+    <t>7124조 6145억 132만</t>
   </si>
   <si>
     <t>마옥지</t>
@@ -1002,7 +1005,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>186경 7071조 3782억 8079만</t>
+    <t>186경 7791조 7180억 8576만</t>
   </si>
   <si>
     <t>설익은앵숭</t>
@@ -1029,7 +1032,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>68경 6411조 7432억 2421만</t>
+    <t>70경 3411조 543억 9761만</t>
   </si>
   <si>
     <t>설묘묘</t>
@@ -1038,7 +1041,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>46경 1721조 8958억 6847만</t>
+    <t>46경 5893조 4558억 8082만</t>
   </si>
   <si>
     <t>루델밍</t>
@@ -1068,7 +1071,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>42경 3138조 5889억 4039만</t>
+    <t>42경 3171조 6570억 2266만</t>
   </si>
   <si>
     <t>시드리안</t>
@@ -1086,7 +1089,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>29경 6216조 5359억 3679만</t>
+    <t>29경 6457조 7252억 8350만</t>
   </si>
   <si>
     <t>셀렘이</t>
@@ -1095,7 +1098,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>24경 3354조 9527억 6259만</t>
+    <t>26경 304조 7942억 7478만</t>
   </si>
   <si>
     <t>졸귀탱이</t>
@@ -1104,7 +1107,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>20경 5428조 7775억 656만</t>
+    <t>20경 5726조 4261억 8056만</t>
   </si>
   <si>
     <t>설딩</t>
@@ -1131,7 +1134,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>18경 5875조 8151억 3649만</t>
+    <t>18경 9155조 2333억 8429만</t>
   </si>
   <si>
     <t>슐아</t>
@@ -1158,7 +1161,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>8경 5991조 208억 856만</t>
+    <t>8경 6856조 4210억 2441만</t>
   </si>
   <si>
     <t>폰병</t>
@@ -1176,7 +1179,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>6경 1783조 4474억 1098만</t>
+    <t>6경 1816조 4690억 8482만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
@@ -1191,9 +1194,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
     <t>3경 4312조 1092억 5647만</t>
   </si>
   <si>
@@ -1203,7 +1203,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 944조 1885억 5352만</t>
+    <t>3경 954조 4911억 7546만</t>
+  </si>
+  <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1경 5656조 4416억 3248만</t>
   </si>
   <si>
     <t>설콩순</t>
@@ -1212,16 +1221,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 5307조 6581억 7894만</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>1경 5301조 1854억 5754만</t>
+    <t>1경 5368조 6516억 4049만</t>
   </si>
   <si>
     <t>설치는정상인</t>
@@ -1242,13 +1242,286 @@
     <t>1경 1050조 7102억 6148만</t>
   </si>
   <si>
+    <t>강서구도적</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
+  </si>
+  <si>
+    <t>582경 5633조 3434억 1209만</t>
+  </si>
+  <si>
+    <t>따코유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EC%BD%94%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>397경 9870조 1742억 2256만</t>
+  </si>
+  <si>
+    <t>뚱털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%ED%84%B8</t>
+  </si>
+  <si>
+    <t>139경 3957조 7548억 7251만</t>
+  </si>
+  <si>
+    <t>뽀로로남편</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
+  </si>
+  <si>
+    <t>109경 4347조 146억 4375만</t>
+  </si>
+  <si>
+    <t>귤놈펜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
+  </si>
+  <si>
+    <t>89경 7539조 3952억 3270만</t>
+  </si>
+  <si>
+    <t>꿀서은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
+  </si>
+  <si>
+    <t>34경 3390조 7130억 781만</t>
+  </si>
+  <si>
+    <t>퀸더쪼이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>32경 1778조 427억 3343만</t>
+  </si>
+  <si>
+    <t>게탕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
+  </si>
+  <si>
+    <t>23경 7633조 3478억 4374만</t>
+  </si>
+  <si>
+    <t>긴나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>21경 7704조 3013억 5974만</t>
+  </si>
+  <si>
+    <t>쿨쥐돌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
+  </si>
+  <si>
+    <t>18경 9649조 7630억 4519만</t>
+  </si>
+  <si>
+    <t>우둉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
+  </si>
+  <si>
+    <t>13경 6304조 935억 110만</t>
+  </si>
+  <si>
+    <t>류텐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
+  </si>
+  <si>
+    <t>9경 3771조 2580억 9733만</t>
+  </si>
+  <si>
+    <t>철푸닥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%A0%ED%91%B8%EB%8B%A5</t>
+  </si>
+  <si>
+    <t>7경 7242조 4697억 2671만</t>
+  </si>
+  <si>
+    <t>원이유이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%9D%B4%EC%9C%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4경 2472조 8316억 569만</t>
+  </si>
+  <si>
+    <t>하드웨어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
+  </si>
+  <si>
+    <t>3경 7420조 2128억 5293만</t>
+  </si>
+  <si>
+    <t>ShellyCake</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
+  </si>
+  <si>
+    <t>2경 9098조 3578억 5360만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
+  </si>
+  <si>
+    <t>2경 7284조 797억 1001만</t>
+  </si>
+  <si>
+    <t>오정구불독</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
+  </si>
+  <si>
+    <t>2경 4043조 5902억 7249만</t>
+  </si>
+  <si>
+    <t>양덕하늘채</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8D%95%ED%95%98%EB%8A%98%EC%B1%84</t>
+  </si>
+  <si>
+    <t>1경 7734조 9676억 2191만</t>
+  </si>
+  <si>
+    <t>레드플레이어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
+  </si>
+  <si>
+    <t>1경 5264조 3402억 5185만</t>
+  </si>
+  <si>
+    <t>구미적</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
+  </si>
+  <si>
+    <t>1경 4979조 4621억 2512만</t>
+  </si>
+  <si>
+    <t>주하사랑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
+  </si>
+  <si>
+    <t>1경 4364조 8262억 2018만</t>
+  </si>
+  <si>
+    <t>검샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
+  </si>
+  <si>
+    <t>1경 3318조 2871억 4594만</t>
+  </si>
+  <si>
+    <t>예슬a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%ACa</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>1경 2932조 2761억 2173만</t>
+  </si>
+  <si>
+    <t>브리또강철중</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A6%AC%EB%98%90%EA%B0%95%EC%B2%A0%EC%A4%91</t>
+  </si>
+  <si>
+    <t>1경 177조 670억 8640만</t>
+  </si>
+  <si>
+    <t>장아린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>9779조 7293억 9893만</t>
+  </si>
+  <si>
+    <t>꼬기갓</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
+  </si>
+  <si>
+    <t>8285조 5244억 911만</t>
+  </si>
+  <si>
+    <t>l빠다코코낫l</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
+  </si>
+  <si>
+    <t>7579조 1977억 8625만</t>
+  </si>
+  <si>
+    <t>리광춘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EA%B4%91%EC%B6%98</t>
+  </si>
+  <si>
+    <t>6213조 297억 1292만</t>
+  </si>
+  <si>
+    <t>어꼬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EA%BC%AC</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>3852조 7462억 8910만</t>
+  </si>
+  <si>
     <t>군보</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>203경 9556조 9702억 3150만</t>
+    <t>204경 8248조 734억 8566만</t>
   </si>
   <si>
     <t>눙키</t>
@@ -1257,7 +1530,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
   </si>
   <si>
-    <t>128경 6382조 8779억 8244만</t>
+    <t>132경 1834조 3761억 3417만</t>
   </si>
   <si>
     <t>5형사</t>
@@ -1266,7 +1539,7 @@
     <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>104경 9897조 9159억 7613만</t>
+    <t>105경 2061조 4279억 9876만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
@@ -1275,22 +1548,22 @@
     <t>75경 6411조 4000억 426만</t>
   </si>
   <si>
+    <t>혁수킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
+  </si>
+  <si>
+    <t>71경 2535조 1115억 3507만</t>
+  </si>
+  <si>
     <t>심천</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>69경 9303조 5433억 6974만</t>
-  </si>
-  <si>
-    <t>혁수킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
-  </si>
-  <si>
-    <t>69경 6713조 8769억 1358만</t>
+    <t>70경 694조 6094억 7367만</t>
   </si>
   <si>
     <t>Matter</t>
@@ -1299,7 +1572,7 @@
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>66경 8928조 7109억 7340만</t>
+    <t>67경 1112조 5296억 2467만</t>
   </si>
   <si>
     <t>또르뱅</t>
@@ -1308,7 +1581,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>64경 6281조 8605억 3325만</t>
+    <t>64경 9359조 5186억 5220만</t>
   </si>
   <si>
     <t>원중언니</t>
@@ -1317,7 +1590,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>58경 7502조 2096억 8571만</t>
+    <t>59경 3375조 8867억 8762만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1353,7 +1626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>32경 7798조 7344억 3050만</t>
+    <t>33경 807조 14억 2513만</t>
   </si>
   <si>
     <t>김나뭉</t>
@@ -1362,7 +1635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
   </si>
   <si>
-    <t>30경 8735조 5003억 7097만</t>
+    <t>32경 1529조 9226억 8356만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1371,7 +1644,16 @@
     <t>https://mgf.gg/contents/character.php?n=Hoood</t>
   </si>
   <si>
-    <t>17경 8032조 1522억 1223만</t>
+    <t>17경 8223조 8720억 3869만</t>
+  </si>
+  <si>
+    <t>껌정색</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
+  </si>
+  <si>
+    <t>15경 4423조 9677억 1789만</t>
   </si>
   <si>
     <t>찐맨듀</t>
@@ -1380,16 +1662,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
   </si>
   <si>
-    <t>14경 3225조 9241억 6322만</t>
-  </si>
-  <si>
-    <t>껌정색</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
-  </si>
-  <si>
-    <t>14경 1580조 2176억 6617만</t>
+    <t>15경 1501조 8621억 7551만</t>
+  </si>
+  <si>
+    <t>이삼2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
+  </si>
+  <si>
+    <t>14경 1983조 8733억 8411만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1398,16 +1680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>13경 5670조 5033억 9103만</t>
-  </si>
-  <si>
-    <t>이삼2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
-  </si>
-  <si>
-    <t>13경 3744조 5309억 977만</t>
+    <t>13경 5742조 4781억 9281만</t>
   </si>
   <si>
     <t>악경</t>
@@ -1425,7 +1698,7 @@
     <t>https://mgf.gg/contents/character.php?n=Rahee</t>
   </si>
   <si>
-    <t>7경 8782조 9990억 6632만</t>
+    <t>7경 9114조 6045억 826만</t>
   </si>
   <si>
     <t>고먀츠나나</t>
@@ -1434,7 +1707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
   </si>
   <si>
-    <t>7경 197조 6667억 8901만</t>
+    <t>7경 7681조 4092억 2482만</t>
   </si>
   <si>
     <t>딤개</t>
@@ -1443,7 +1716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
   </si>
   <si>
-    <t>5경 8018조 3068억 3402만</t>
+    <t>6경 102조 1325억 1418만</t>
   </si>
   <si>
     <t>히째히째</t>
@@ -1452,7 +1725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
   </si>
   <si>
-    <t>4경 6252조 5336억 736만</t>
+    <t>4경 6413조 9292억 4906만</t>
   </si>
   <si>
     <t>통뼈1</t>
@@ -1461,7 +1734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
   </si>
   <si>
-    <t>3경 9314조 1653억 5009만</t>
+    <t>4경 3909조 8818억 4974만</t>
   </si>
   <si>
     <t>돌로레스</t>
@@ -1488,7 +1761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 2518조 5995억 7371만</t>
+    <t>2경 2811조 8130억 7852만</t>
   </si>
   <si>
     <t>셀러문</t>
@@ -1500,7 +1773,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>4163조 60억 3041만</t>
+    <t>4171조 588억 426만</t>
   </si>
   <si>
     <t>라온XR</t>
@@ -1527,7 +1800,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>202경 5067조 3570억 6607만</t>
+    <t>202경 5213조 3573억 6099만</t>
   </si>
   <si>
     <t>코코듀</t>
@@ -1536,7 +1809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
   </si>
   <si>
-    <t>106경 8507조 3404억 2537만</t>
+    <t>107경 50조 3372억 7613만</t>
   </si>
   <si>
     <t>타이슨에어랩</t>
@@ -1545,13 +1818,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
   </si>
   <si>
-    <t>62경 8614조 6256억 7372만</t>
+    <t>62경 9145조 4295억 6367만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
   </si>
   <si>
-    <t>55경 1587조 5056억 2487만</t>
+    <t>55경 2187조 5827억 5986만</t>
   </si>
   <si>
     <t>미야고</t>
@@ -1563,22 +1836,22 @@
     <t>51경 2943조 3453억 7104만</t>
   </si>
   <si>
+    <t>용보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>37경 6569조 638억 2355만</t>
+  </si>
+  <si>
     <t>캔드릭</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
   </si>
   <si>
-    <t>36경 7312조 8666억 1977만</t>
-  </si>
-  <si>
-    <t>용보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>36경 6925조 9193억 5914만</t>
+    <t>37경 220조 9594억 6486만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -1596,7 +1869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
   </si>
   <si>
-    <t>18경 9370조 4942억 968만</t>
+    <t>18경 9416조 6626억 7901만</t>
   </si>
   <si>
     <t>도적왕대현</t>
@@ -1605,7 +1878,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EC%99%95%EB%8C%80%ED%98%84</t>
   </si>
   <si>
-    <t>11경 2244조 3229억 8341만</t>
+    <t>11경 2643조 4220억 6938만</t>
   </si>
   <si>
     <t>도농롱</t>
@@ -1632,7 +1905,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
   </si>
   <si>
-    <t>7경 7130조 6693억 9364만</t>
+    <t>7경 8531조 6587억 2143만</t>
   </si>
   <si>
     <t>혜도로동</t>
@@ -1641,7 +1914,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>7경 5608조 8584억 2657만</t>
+    <t>7경 7856조 6156억 2930만</t>
   </si>
   <si>
     <t>붕어줍</t>
@@ -1659,7 +1932,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
   </si>
   <si>
-    <t>5경 8825조 2726억 919만</t>
+    <t>6경 2900조 1923억 1410만</t>
   </si>
   <si>
     <t>로생</t>
@@ -1668,7 +1941,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
   </si>
   <si>
-    <t>5경 8284조 8153억 7505만</t>
+    <t>6경 2081조 7415억 8986만</t>
   </si>
   <si>
     <t>Redwine</t>
@@ -1677,7 +1950,7 @@
     <t>https://mgf.gg/contents/character.php?n=Redwine</t>
   </si>
   <si>
-    <t>5경 6201조 817억 991만</t>
+    <t>5경 8673조 7807억 379만</t>
   </si>
   <si>
     <t>이다연</t>
@@ -1686,7 +1959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
   </si>
   <si>
-    <t>5경 4338조 2243억 5938만</t>
+    <t>5경 4405조 7832억 8310만</t>
   </si>
   <si>
     <t>망치반죽</t>
@@ -1695,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
   </si>
   <si>
-    <t>4경 8333조 414억 9098만</t>
+    <t>5경 298조 6467억 3963만</t>
   </si>
   <si>
     <t>유도로동</t>
@@ -1704,7 +1977,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>4경 3548조 1193억 5686만</t>
+    <t>4경 3674조 8359억 9725만</t>
   </si>
   <si>
     <t>그때그아이</t>
@@ -1722,7 +1995,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
   </si>
   <si>
-    <t>3경 1254조 3197억 3591만</t>
+    <t>3경 1432조 3768억 3422만</t>
   </si>
   <si>
     <t>루빙</t>
@@ -1731,7 +2004,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
   </si>
   <si>
-    <t>2경 848조 8453억 998만</t>
+    <t>2경 1709조 395억 4256만</t>
   </si>
   <si>
     <t>꽁꽁얼었다</t>
@@ -1749,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=spemi</t>
   </si>
   <si>
-    <t>1경 8496조 7102억 7539만</t>
+    <t>1경 9184조 7426억 6819만</t>
   </si>
   <si>
     <t>우솝이</t>
@@ -1758,7 +2031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
   </si>
   <si>
-    <t>1경 6505조 2340억 1882만</t>
+    <t>1경 7474조 253억 6627만</t>
   </si>
   <si>
     <t>막또날드</t>
@@ -1767,280 +2040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
   </si>
   <si>
-    <t>1경 5570조 6988억 7323만</t>
-  </si>
-  <si>
-    <t>강서구도적</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
-  </si>
-  <si>
-    <t>561경 8770조 6553억 4335만</t>
-  </si>
-  <si>
-    <t>따코유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EC%BD%94%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>397경 9870조 1742억 2256만</t>
-  </si>
-  <si>
-    <t>뚱털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%ED%84%B8</t>
-  </si>
-  <si>
-    <t>139경 3957조 7548억 7251만</t>
-  </si>
-  <si>
-    <t>뽀로로남편</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
-  </si>
-  <si>
-    <t>109경 3197조 7992억 7558만</t>
-  </si>
-  <si>
-    <t>귤놈펜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
-  </si>
-  <si>
-    <t>88경 1038조 2454억 1638만</t>
-  </si>
-  <si>
-    <t>꿀서은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
-  </si>
-  <si>
-    <t>34경 695조 9726억 7064만</t>
-  </si>
-  <si>
-    <t>퀸더쪼이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>31경 6241조 1543억 8981만</t>
-  </si>
-  <si>
-    <t>게탕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
-  </si>
-  <si>
-    <t>23경 7566조 8246억 7693만</t>
-  </si>
-  <si>
-    <t>긴나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>21경 6883조 2459억 5189만</t>
-  </si>
-  <si>
-    <t>쿨쥐돌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
-  </si>
-  <si>
-    <t>18경 9649조 7630억 4519만</t>
-  </si>
-  <si>
-    <t>우둉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
-  </si>
-  <si>
-    <t>13경 5291조 6646억 9579만</t>
-  </si>
-  <si>
-    <t>류텐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
-  </si>
-  <si>
-    <t>9경 3771조 2580억 9733만</t>
-  </si>
-  <si>
-    <t>철푸닥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%A0%ED%91%B8%EB%8B%A5</t>
-  </si>
-  <si>
-    <t>7경 7242조 4697억 2671만</t>
-  </si>
-  <si>
-    <t>원이유이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%9D%B4%EC%9C%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4경 2472조 8316억 569만</t>
-  </si>
-  <si>
-    <t>하드웨어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
-  </si>
-  <si>
-    <t>3경 7289조 7623억 1803만</t>
-  </si>
-  <si>
-    <t>ShellyCake</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
-  </si>
-  <si>
-    <t>2경 8542조 5263억 2188만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
-  </si>
-  <si>
-    <t>2경 6547조 7780억 2631만</t>
-  </si>
-  <si>
-    <t>오정구불독</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
-  </si>
-  <si>
-    <t>1경 9840조 8606억 6150만</t>
-  </si>
-  <si>
-    <t>양덕하늘채</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8D%95%ED%95%98%EB%8A%98%EC%B1%84</t>
-  </si>
-  <si>
-    <t>1경 7719조 5512억 3060만</t>
-  </si>
-  <si>
-    <t>레드플레이어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
-  </si>
-  <si>
-    <t>1경 5246조 8423억 953만</t>
-  </si>
-  <si>
-    <t>주하사랑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
-  </si>
-  <si>
-    <t>1경 4364조 8262억 2018만</t>
-  </si>
-  <si>
-    <t>구미적</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
-  </si>
-  <si>
-    <t>1경 3726조 7395억 147만</t>
-  </si>
-  <si>
-    <t>예슬a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%ACa</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>1경 2932조 2761억 2173만</t>
-  </si>
-  <si>
-    <t>검샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
-  </si>
-  <si>
-    <t>1경 1615조 5659억 493만</t>
-  </si>
-  <si>
-    <t>브리또강철중</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A6%AC%EB%98%90%EA%B0%95%EC%B2%A0%EC%A4%91</t>
-  </si>
-  <si>
-    <t>1경 83조 3899억 404만</t>
-  </si>
-  <si>
-    <t>꼬기갓</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
-  </si>
-  <si>
-    <t>8285조 5244억 911만</t>
-  </si>
-  <si>
-    <t>장아린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>8133조 6906억 9372만</t>
-  </si>
-  <si>
-    <t>l빠다코코낫l</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
-  </si>
-  <si>
-    <t>7066조 4815억 2818만</t>
-  </si>
-  <si>
-    <t>리광춘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EA%B4%91%EC%B6%98</t>
-  </si>
-  <si>
-    <t>6098조 5009억 8907만</t>
-  </si>
-  <si>
-    <t>어꼬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EA%BC%AC</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>3751조 3186억 2243만</t>
+    <t>1경 5575조 7834억 2052만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2058,7 +2058,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>19경 8464조 5082억 5270만</t>
+    <t>21경 913조 6729억 9538만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -2067,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>12경 4306조 3052억 4003만</t>
+    <t>12경 6297조 3934억 1589만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2076,7 +2076,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>11경 4105조 7960억 279만</t>
+    <t>12경 3858조 1172억 6063만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -2085,7 +2085,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>10경 6154조 8799억 4676만</t>
+    <t>10경 6184조 3457억 7322만</t>
   </si>
   <si>
     <t>약어</t>
@@ -2103,7 +2103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 3423조 3510억 8891만</t>
+    <t>9경 3479조 369억 3638만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -2112,7 +2112,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>7경 6148조 2651억 9696만</t>
+    <t>8경 2706조 3135억 2808만</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>7경 5292조 4238억 2660만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -2124,15 +2133,6 @@
     <t>7경 3381조 2238억 1561만</t>
   </si>
   <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>7경 3059조 933억 2511만</t>
-  </si>
-  <si>
     <t>쾌감</t>
   </si>
   <si>
@@ -2142,22 +2142,22 @@
     <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>2경 5374조 9474억 3745만</t>
+  </si>
+  <si>
     <t>핫잇</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 4504조 4834억 827만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>2경 4130조 5641억 7043만</t>
+    <t>2경 5181조 6388억 1979만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -2193,7 +2193,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>1경 9258조 3650억 1564만</t>
+    <t>2경 616조 9601억 9592만</t>
+  </si>
+  <si>
+    <t>쌉새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
+  </si>
+  <si>
+    <t>1경 7942조 150억 6859만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
@@ -2208,16 +2217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 5876조 1968억 392만</t>
-  </si>
-  <si>
-    <t>쌉새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
-  </si>
-  <si>
-    <t>1경 5688조 4374억 8127만</t>
+    <t>1경 6180조 1094억 5337만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2226,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 3148조 5412억 6446만</t>
+    <t>1경 3352조 5107억 6670만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -2238,6 +2238,15 @@
     <t>1경 2819조 4851억 9770만</t>
   </si>
   <si>
+    <t>오곤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
+  </si>
+  <si>
+    <t>1경 2644조 7980억 538만</t>
+  </si>
+  <si>
     <t>라똥삐</t>
   </si>
   <si>
@@ -2247,22 +2256,13 @@
     <t>1경 2085조 1284억 3396만</t>
   </si>
   <si>
-    <t>오곤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
-  </si>
-  <si>
-    <t>1경 1856조 4618억 6137만</t>
-  </si>
-  <si>
     <t>제로슈가</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 2945억 9039만</t>
+    <t>1경 75조 3638억 2592만</t>
   </si>
   <si>
     <t>러너</t>
@@ -2280,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%B0%AC%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>5796조 3675억 8873만</t>
+    <t>5822조 9050억 2851만</t>
   </si>
   <si>
     <t>갓겜감별사</t>
@@ -2292,7 +2292,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>341조 6408억 9657만</t>
+    <t>355조 4686억 5920만</t>
   </si>
 </sst>
 </file>
@@ -2858,104 +2858,104 @@
         <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="M5" s="2" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2996,7 +2996,7 @@
         <v>75</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3276,7 +3276,7 @@
         <v>120</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>121</v>
@@ -3721,13 +3721,13 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3738,25 +3738,25 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>192</v>
@@ -3820,7 +3820,7 @@
         <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>200</v>
@@ -3884,7 +3884,7 @@
         <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>208</v>
@@ -3916,7 +3916,7 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>212</v>
@@ -3948,7 +3948,7 @@
         <v>125</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>216</v>
@@ -4012,10 +4012,10 @@
         <v>105</v>
       </c>
       <c r="H31" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4114,22 +4114,22 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>229</v>
@@ -4510,10 +4510,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>266</v>
@@ -4542,10 +4542,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>269</v>
@@ -4577,7 +4577,7 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>272</v>
@@ -4609,7 +4609,7 @@
         <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>275</v>
@@ -4641,7 +4641,7 @@
         <v>256</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>278</v>
@@ -4705,7 +4705,7 @@
         <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>284</v>
@@ -4737,7 +4737,7 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>287</v>
@@ -4766,10 +4766,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>290</v>
@@ -4783,7 +4783,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>291</v>
@@ -4798,10 +4798,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>293</v>
@@ -4833,7 +4833,7 @@
         <v>144</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>296</v>
@@ -4865,7 +4865,7 @@
         <v>232</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>299</v>
@@ -4929,10 +4929,10 @@
         <v>172</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4946,13 +4946,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -4961,10 +4961,10 @@
         <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4978,13 +4978,13 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -4993,10 +4993,10 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5010,13 +5010,13 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
@@ -5025,10 +5025,10 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5126,13 +5126,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
@@ -5144,7 +5144,7 @@
         <v>111</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5158,13 +5158,13 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
@@ -5173,10 +5173,10 @@
         <v>256</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5190,13 +5190,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -5208,7 +5208,7 @@
         <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5222,13 +5222,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -5240,7 +5240,7 @@
         <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5254,25 +5254,25 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5286,13 +5286,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -5304,7 +5304,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5318,13 +5318,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -5336,7 +5336,7 @@
         <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5350,13 +5350,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
@@ -5368,7 +5368,7 @@
         <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5382,25 +5382,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5414,13 +5414,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -5432,7 +5432,7 @@
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5446,13 +5446,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
@@ -5461,10 +5461,10 @@
         <v>125</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5478,13 +5478,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
@@ -5496,7 +5496,7 @@
         <v>145</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5510,13 +5510,13 @@
         <v>147</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -5528,7 +5528,7 @@
         <v>145</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5542,13 +5542,13 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -5560,7 +5560,7 @@
         <v>154</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5574,13 +5574,13 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -5592,7 +5592,7 @@
         <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5606,13 +5606,13 @@
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -5624,7 +5624,7 @@
         <v>145</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5638,13 +5638,13 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
@@ -5656,7 +5656,7 @@
         <v>145</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5670,13 +5670,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
@@ -5688,7 +5688,7 @@
         <v>159</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5702,13 +5702,13 @@
         <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -5720,7 +5720,7 @@
         <v>159</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5734,13 +5734,13 @@
         <v>180</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -5752,7 +5752,7 @@
         <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5766,25 +5766,25 @@
         <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5795,16 +5795,16 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -5816,7 +5816,7 @@
         <v>159</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5836,7 +5836,7 @@
         <v>40</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>134</v>
@@ -5848,7 +5848,7 @@
         <v>178</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5862,22 +5862,22 @@
         <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>386</v>
+        <v>228</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>387</v>
@@ -5938,10 +5938,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>256</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>393</v>
@@ -5970,10 +5970,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>396</v>
@@ -6005,7 +6005,7 @@
         <v>177</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>399</v>
@@ -6037,7 +6037,7 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>402</v>
@@ -6085,1018 +6085,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7144,147 +6132,147 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>490</v>
+        <v>403</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>490</v>
+        <v>403</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>491</v>
+        <v>404</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>386</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>492</v>
+        <v>405</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>493</v>
+        <v>406</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>493</v>
+        <v>406</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>494</v>
+        <v>407</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>495</v>
+        <v>408</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>496</v>
+        <v>409</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>496</v>
+        <v>409</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>497</v>
+        <v>410</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
+        <v>256</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>498</v>
+        <v>411</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>499</v>
+        <v>412</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>499</v>
+        <v>412</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>500</v>
+        <v>413</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>501</v>
+        <v>414</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>502</v>
+        <v>415</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>502</v>
+        <v>415</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>503</v>
+        <v>416</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -7293,62 +6281,62 @@
         <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>504</v>
+        <v>417</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>418</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>58</v>
+        <v>418</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>505</v>
+        <v>419</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>506</v>
+        <v>420</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>507</v>
+        <v>421</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>507</v>
+        <v>421</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -7360,91 +6348,91 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>509</v>
+        <v>423</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>510</v>
+        <v>424</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>510</v>
+        <v>424</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>511</v>
+        <v>425</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>256</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>512</v>
+        <v>426</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>513</v>
+        <v>427</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>513</v>
+        <v>427</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>514</v>
+        <v>428</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>386</v>
+        <v>177</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>515</v>
+        <v>429</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>516</v>
+        <v>430</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>516</v>
+        <v>430</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>517</v>
+        <v>431</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -7453,94 +6441,94 @@
         <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>518</v>
+        <v>432</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>519</v>
+        <v>433</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>519</v>
+        <v>433</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>520</v>
+        <v>434</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>521</v>
+        <v>435</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>522</v>
+        <v>436</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>522</v>
+        <v>436</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>523</v>
+        <v>437</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>524</v>
+        <v>438</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>525</v>
+        <v>439</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>525</v>
+        <v>439</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>526</v>
+        <v>440</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -7552,91 +6540,91 @@
         <v>154</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>527</v>
+        <v>441</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>528</v>
+        <v>442</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>528</v>
+        <v>442</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>529</v>
+        <v>443</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>530</v>
+        <v>444</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>531</v>
+        <v>445</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>531</v>
+        <v>445</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>532</v>
+        <v>446</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>533</v>
+        <v>447</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>534</v>
+        <v>448</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>534</v>
+        <v>448</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>535</v>
+        <v>449</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -7645,126 +6633,126 @@
         <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>536</v>
+        <v>450</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>537</v>
+        <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>537</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>539</v>
+        <v>452</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>540</v>
+        <v>453</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>540</v>
+        <v>453</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>541</v>
+        <v>454</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>386</v>
+        <v>232</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>542</v>
+        <v>455</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>543</v>
+        <v>456</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>543</v>
+        <v>456</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>544</v>
+        <v>457</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>545</v>
+        <v>458</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>546</v>
+        <v>459</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>546</v>
+        <v>459</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>547</v>
+        <v>460</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -7773,62 +6761,62 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>548</v>
+        <v>461</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>549</v>
+        <v>462</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>549</v>
+        <v>462</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>550</v>
+        <v>463</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>232</v>
+        <v>144</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>305</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>551</v>
+        <v>464</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>552</v>
+        <v>465</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>552</v>
+        <v>465</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>553</v>
+        <v>466</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -7837,269 +6825,269 @@
         <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>554</v>
+        <v>467</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>555</v>
+        <v>468</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>555</v>
+        <v>468</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>556</v>
+        <v>469</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>557</v>
+        <v>470</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>558</v>
+        <v>471</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>558</v>
+        <v>471</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>559</v>
+        <v>472</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>341</v>
+        <v>256</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>191</v>
+        <v>473</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>560</v>
+        <v>474</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>561</v>
+        <v>475</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>561</v>
+        <v>475</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>562</v>
+        <v>476</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>191</v>
+        <v>473</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>563</v>
+        <v>477</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>564</v>
+        <v>478</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>564</v>
+        <v>478</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>565</v>
+        <v>479</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>566</v>
+        <v>480</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>567</v>
+        <v>481</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>567</v>
+        <v>481</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>568</v>
+        <v>482</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>569</v>
+        <v>483</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>570</v>
+        <v>484</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>570</v>
+        <v>484</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>571</v>
+        <v>485</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>232</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>572</v>
+        <v>486</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>573</v>
+        <v>487</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>573</v>
+        <v>487</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>574</v>
+        <v>488</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>225</v>
+        <v>305</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>575</v>
+        <v>489</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>222</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>576</v>
+        <v>490</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>576</v>
+        <v>490</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>577</v>
+        <v>491</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>94</v>
+        <v>228</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>225</v>
+        <v>492</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>578</v>
+        <v>493</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -8140,6 +7128,1018 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -8189,147 +8189,147 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>228</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>256</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -8338,62 +8338,62 @@
         <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>594</v>
+        <v>66</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>594</v>
+        <v>66</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -8402,94 +8402,94 @@
         <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -8498,94 +8498,94 @@
         <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -8597,91 +8597,91 @@
         <v>154</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -8690,126 +8690,126 @@
         <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -8818,222 +8818,222 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>232</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>256</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>646</v>
+        <v>159</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>125</v>
+        <v>342</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>646</v>
+        <v>178</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -9042,109 +9042,109 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>222</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>386</v>
+        <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>668</v>
+        <v>220</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>669</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -9261,7 +9261,7 @@
         <v>672</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -9293,7 +9293,7 @@
         <v>675</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -9325,7 +9325,7 @@
         <v>678</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -9357,7 +9357,7 @@
         <v>681</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -9389,7 +9389,7 @@
         <v>684</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -9421,7 +9421,7 @@
         <v>687</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -9444,7 +9444,7 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>386</v>
+        <v>228</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>159</v>
@@ -9453,7 +9453,7 @@
         <v>690</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -9485,7 +9485,7 @@
         <v>693</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -9508,16 +9508,16 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>696</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -9540,16 +9540,16 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>699</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -9581,7 +9581,7 @@
         <v>702</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -9607,13 +9607,13 @@
         <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>705</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -9639,13 +9639,13 @@
         <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>708</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -9671,13 +9671,13 @@
         <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>711</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -9703,13 +9703,13 @@
         <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>714</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -9735,13 +9735,13 @@
         <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>717</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -9767,13 +9767,13 @@
         <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>720</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -9784,28 +9784,28 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>75</v>
+        <v>721</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>75</v>
+        <v>721</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -9816,28 +9816,28 @@
         <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>723</v>
+        <v>75</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>723</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>724</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>225</v>
+        <v>305</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>725</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -9860,7 +9860,7 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>220</v>
@@ -9869,7 +9869,7 @@
         <v>728</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -9895,13 +9895,13 @@
         <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>731</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -9909,7 +9909,7 @@
         <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>732</v>
@@ -9927,13 +9927,13 @@
         <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>734</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -9956,7 +9956,7 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>220</v>
@@ -9965,7 +9965,7 @@
         <v>737</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -9988,16 +9988,16 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>225</v>
+        <v>305</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>740</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -10023,13 +10023,13 @@
         <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>743</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -10055,13 +10055,13 @@
         <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>746</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -10087,13 +10087,13 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>488</v>
+        <v>579</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>749</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -10125,7 +10125,7 @@
         <v>753</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -189,7 +189,7 @@
     <t>Scania 11</t>
   </si>
   <si>
-    <t>52</t>
+    <t>53</t>
   </si>
   <si>
     <t>4위</t>
@@ -219,7 +219,7 @@
     <t>Scania 5</t>
   </si>
   <si>
-    <t>43</t>
+    <t>44</t>
   </si>
   <si>
     <t>28명</t>
@@ -246,7 +246,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>59</t>
+    <t>62</t>
   </si>
   <si>
     <t>3위</t>
@@ -303,7 +303,7 @@
     <t>129</t>
   </si>
   <si>
-    <t>3465경 3085조 8290억 7965만</t>
+    <t>3467경 4256조 3283억 7780만</t>
   </si>
   <si>
     <t>2</t>
@@ -336,7 +336,7 @@
     <t>126</t>
   </si>
   <si>
-    <t>563경 6043조 9088억 4883만</t>
+    <t>569경 286조 8309억 6135만</t>
   </si>
   <si>
     <t>4</t>
@@ -354,7 +354,7 @@
     <t>127</t>
   </si>
   <si>
-    <t>459경 5381조 4891억 6857만</t>
+    <t>461경 9750조 8492억 670만</t>
   </si>
   <si>
     <t>5</t>
@@ -369,7 +369,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>422경 7012조 6194억 5243만</t>
+    <t>423경 3889조 6308억 3139만</t>
   </si>
   <si>
     <t>6</t>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
   </si>
   <si>
-    <t>315경 9802조 4873억 6925만</t>
+    <t>319경 1172조 9821억 4103만</t>
   </si>
   <si>
     <t>7</t>
@@ -426,7 +426,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
   </si>
   <si>
-    <t>78경 3861조 395억 5887만</t>
+    <t>78경 4929조 1448억 3618만</t>
   </si>
   <si>
     <t>10</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8J</t>
   </si>
   <si>
-    <t>38경 5764조 9611억 6669만</t>
+    <t>38경 9204조 7304억 5367만</t>
   </si>
   <si>
     <t>12</t>
@@ -471,7 +471,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>34경 9320조 3247억 2674만</t>
+    <t>34경 9682조 4625억 7498만</t>
   </si>
   <si>
     <t>13</t>
@@ -483,7 +483,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EB%A5%B8</t>
   </si>
   <si>
-    <t>30경 7900조 3282억 3172만</t>
+    <t>30경 9626조 1014억 2408만</t>
   </si>
   <si>
     <t>14</t>
@@ -513,7 +513,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>19경 3312조 5233억 2265만</t>
+    <t>21경 8165조 4122억 941만</t>
   </si>
   <si>
     <t>16</t>
@@ -525,7 +525,7 @@
     <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
   </si>
   <si>
-    <t>17경 4193조 2973억 5294만</t>
+    <t>17경 8560조 7818억 3751만</t>
   </si>
   <si>
     <t>17</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
   </si>
   <si>
-    <t>16경 526조 1329억 5295만</t>
+    <t>16경 1008조 4764억 9680만</t>
   </si>
   <si>
     <t>18</t>
@@ -552,7 +552,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>11경 8524조 2118억 7417만</t>
+    <t>12경 467조 436억 6657만</t>
   </si>
   <si>
     <t>19</t>
@@ -588,6 +588,18 @@
     <t>21</t>
   </si>
   <si>
+    <t>최슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>6경 6287조 6681억 6245만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>명품까칠공주</t>
   </si>
   <si>
@@ -600,7 +612,7 @@
     <t>6경 5992조 5215억 2892만</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>뿔피리</t>
@@ -609,19 +621,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>6경 5706조 711억 5620만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>최슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>6경 4278조 6791억 8373만</t>
+    <t>6경 5760조 1530억 8575만</t>
   </si>
   <si>
     <t>24</t>
@@ -633,7 +633,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
   </si>
   <si>
-    <t>5경 9313조 3254억 7200만</t>
+    <t>6경 1456조 6829억 3896만</t>
   </si>
   <si>
     <t>25</t>
@@ -645,7 +645,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
   </si>
   <si>
-    <t>5경 7174조 730억 723만</t>
+    <t>5경 7594조 5870억 5368만</t>
   </si>
   <si>
     <t>26</t>
@@ -657,7 +657,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>4경 2718조 361억 6339만</t>
+    <t>4경 4360조 5840억 4025만</t>
   </si>
   <si>
     <t>27</t>
@@ -669,7 +669,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
   </si>
   <si>
-    <t>3경 746조 2008억 30만</t>
+    <t>3경 1156조 3380억 4689만</t>
   </si>
   <si>
     <t>28</t>
@@ -720,7 +720,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>1041경 619조 5488억 4105만</t>
+    <t>1054경 9858조 9855억 4247만</t>
   </si>
   <si>
     <t>라온JW</t>
@@ -741,13 +741,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>83경 7316조 4265억 7115만</t>
+    <t>85경 3381조 3531억 4631만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
   </si>
   <si>
-    <t>44경 2858조 6272억 976만</t>
+    <t>46경 2168조 6492억 8596만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -756,7 +756,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
   </si>
   <si>
-    <t>39경 7201조 2284억 1187만</t>
+    <t>39경 9517조 2523억 8938만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -765,7 +765,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>33경 8171조 4987억 9934만</t>
+    <t>33경 8232조 9760억 4390만</t>
+  </si>
+  <si>
+    <t>임홀리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>13경 1056조 2031억 6452만</t>
   </si>
   <si>
     <t>쁘덍</t>
@@ -774,16 +783,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%81%98%EB%8D%8D</t>
   </si>
   <si>
-    <t>12경 8660조 3484억 6741만</t>
-  </si>
-  <si>
-    <t>임홀리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>12경 6294조 2538억 7075만</t>
+    <t>13경 571조 4329억 3235만</t>
   </si>
   <si>
     <t>제껴</t>
@@ -792,7 +792,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>11경 251조 7199억 90만</t>
+    <t>12경 2297조 5767억 8466만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -804,7 +804,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>7경 9921조 8943억 4152만</t>
+    <t>8경 5350조 1987억 502만</t>
   </si>
   <si>
     <t>엘리자베타</t>
@@ -822,7 +822,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>5경 3048조 8458억 4104만</t>
+    <t>5경 5018조 7346억 5388만</t>
   </si>
   <si>
     <t>누룽지룽누</t>
@@ -831,7 +831,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EB%A3%BD%EC%A7%80%EB%A3%BD%EB%88%84</t>
   </si>
   <si>
-    <t>4경 8478조 2039억 38만</t>
+    <t>5경 1079조 7644억 7227만</t>
   </si>
   <si>
     <t>우꼬쨩</t>
@@ -840,7 +840,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
   </si>
   <si>
-    <t>4경 6838조 2248억 2671만</t>
+    <t>4경 7452조 4287억 952만</t>
+  </si>
+  <si>
+    <t>붙잡아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
+  </si>
+  <si>
+    <t>4경 782조 1505억 9630만</t>
+  </si>
+  <si>
+    <t>홍시마로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>3경 9169조 9159억 1083만</t>
   </si>
   <si>
     <t>비밀키</t>
@@ -852,24 +870,6 @@
     <t>3경 8363조 108억 1090만</t>
   </si>
   <si>
-    <t>홍시마로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>3경 5375조 3556억 7105만</t>
-  </si>
-  <si>
-    <t>붙잡아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
-  </si>
-  <si>
-    <t>3경 3402조 2179억 6058만</t>
-  </si>
-  <si>
     <t>지아라떼</t>
   </si>
   <si>
@@ -885,7 +885,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
   </si>
   <si>
-    <t>2경 8454조 3204억 3418만</t>
+    <t>2경 8928조 5852억 6249만</t>
   </si>
   <si>
     <t>o엔젤o</t>
@@ -894,7 +894,16 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
   </si>
   <si>
-    <t>2경 4819조 8723억 7152만</t>
+    <t>2경 7492조 7270억 4205만</t>
+  </si>
+  <si>
+    <t>득츈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
+  </si>
+  <si>
+    <t>2경 6799조 832억 6782만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -903,16 +912,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 4515조 1344억 3452만</t>
-  </si>
-  <si>
-    <t>득츈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
-  </si>
-  <si>
-    <t>2경 3813조 4513억 3727만</t>
+    <t>2경 5072조 2965억 8076만</t>
   </si>
   <si>
     <t>메론맛빵</t>
@@ -921,7 +921,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
   </si>
   <si>
-    <t>2경 969조 7803억 305만</t>
+    <t>2경 2584조 5728억 6543만</t>
   </si>
   <si>
     <t>24년생정춘식</t>
@@ -930,7 +930,7 @@
     <t>https://mgf.gg/contents/character.php?n=24%EB%85%84%EC%83%9D%EC%A0%95%EC%B6%98%EC%8B%9D</t>
   </si>
   <si>
-    <t>1경 7793조 3082억 68만</t>
+    <t>1경 8607조 5196억 216만</t>
   </si>
   <si>
     <t>시프님</t>
@@ -948,19 +948,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
+    <t>1경 2396조 2579억 5715만</t>
+  </si>
+  <si>
+    <t>출장괴물</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
+  </si>
+  <si>
     <t>115</t>
   </si>
   <si>
-    <t>1경 1465조 5448억 942만</t>
-  </si>
-  <si>
-    <t>출장괴물</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
-  </si>
-  <si>
-    <t>9694조 9027억 8135만</t>
+    <t>9784조 7490억 6642만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -969,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>8553조 2085억 2976만</t>
+    <t>8559조 719억 6317만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -1032,7 +1032,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>70경 3411조 543억 9761만</t>
+    <t>70경 5202조 5289억 6005만</t>
   </si>
   <si>
     <t>설묘묘</t>
@@ -1041,7 +1041,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
   </si>
   <si>
-    <t>46경 5893조 4558억 8082만</t>
+    <t>47경 490조 6765억 9738만</t>
   </si>
   <si>
     <t>루델밍</t>
@@ -1074,6 +1074,15 @@
     <t>42경 3171조 6570억 2266만</t>
   </si>
   <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
+  </si>
+  <si>
+    <t>31경 3120조 4090억 8744만</t>
+  </si>
+  <si>
     <t>시드리안</t>
   </si>
   <si>
@@ -1083,22 +1092,13 @@
     <t>29경 7613조 5062억 2329만</t>
   </si>
   <si>
-    <t>싲프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
-  </si>
-  <si>
-    <t>29경 6457조 7252억 8350만</t>
-  </si>
-  <si>
     <t>셀렘이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>26경 304조 7942억 7478만</t>
+    <t>26경 3393조 6831억 3749만</t>
   </si>
   <si>
     <t>졸귀탱이</t>
@@ -1107,7 +1107,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>20경 5726조 4261억 8056만</t>
+    <t>21경 4601조 3855억 149만</t>
   </si>
   <si>
     <t>설딩</t>
@@ -1125,7 +1125,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>18경 9870조 503억 9521만</t>
+    <t>19경 4410조 4980억 5909만</t>
   </si>
   <si>
     <t>선콜은차가워</t>
@@ -1134,7 +1134,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>18경 9155조 2333억 8429만</t>
+    <t>19경 1787조 3571억 1968만</t>
   </si>
   <si>
     <t>슐아</t>
@@ -1161,7 +1161,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>8경 6856조 4210억 2441만</t>
+    <t>9경 420조 3518억 4554만</t>
   </si>
   <si>
     <t>폰병</t>
@@ -1179,7 +1179,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>6경 1816조 4690억 8482만</t>
+    <t>6경 3605조 1616억 212만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
@@ -1203,7 +1203,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
   </si>
   <si>
-    <t>3경 954조 4911억 7546만</t>
+    <t>3경 2981조 5907억 6449만</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -1212,7 +1212,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 5656조 4416억 3248만</t>
+    <t>1경 5849조 5535억 3532만</t>
   </si>
   <si>
     <t>설콩순</t>
@@ -1221,7 +1221,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 5368조 6516억 4049만</t>
+    <t>1경 5485조 9970억 1336만</t>
   </si>
   <si>
     <t>설치는정상인</t>
@@ -1239,7 +1239,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
   </si>
   <si>
-    <t>1경 1050조 7102억 6148만</t>
+    <t>1경 4431조 7171억 1764만</t>
   </si>
   <si>
     <t>강서구도적</t>
@@ -1248,7 +1248,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
   </si>
   <si>
-    <t>582경 5633조 3434억 1209만</t>
+    <t>584경 4182조 4009억 8197만</t>
   </si>
   <si>
     <t>따코유</t>
@@ -1257,7 +1257,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EC%BD%94%EC%9C%A0</t>
   </si>
   <si>
-    <t>397경 9870조 1742억 2256만</t>
+    <t>398경 2928조 4091억 7162만</t>
   </si>
   <si>
     <t>뚱털</t>
@@ -1266,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%ED%84%B8</t>
   </si>
   <si>
-    <t>139경 3957조 7548억 7251만</t>
+    <t>179경 6295조 7467억 9574만</t>
   </si>
   <si>
     <t>뽀로로남편</t>
@@ -1275,7 +1275,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
   </si>
   <si>
-    <t>109경 4347조 146억 4375만</t>
+    <t>109경 6317조 3860억 1636만</t>
   </si>
   <si>
     <t>귤놈펜</t>
@@ -1284,7 +1284,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
   </si>
   <si>
-    <t>89경 7539조 3952억 3270만</t>
+    <t>90경 2837조 1837억 811만</t>
   </si>
   <si>
     <t>꿀서은</t>
@@ -1293,7 +1293,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
   </si>
   <si>
-    <t>34경 3390조 7130억 781만</t>
+    <t>35경 1670조 5392억 5360만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -1302,7 +1302,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>32경 1778조 427억 3343만</t>
+    <t>33경 3161조 5149억 9342만</t>
   </si>
   <si>
     <t>게탕</t>
@@ -1311,7 +1311,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
   </si>
   <si>
-    <t>23경 7633조 3478억 4374만</t>
+    <t>24경 764조 8050억 6052만</t>
   </si>
   <si>
     <t>긴나라</t>
@@ -1329,7 +1329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
   </si>
   <si>
-    <t>18경 9649조 7630억 4519만</t>
+    <t>21경 1966조 9552억 8025만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -1356,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%A0%ED%91%B8%EB%8B%A5</t>
   </si>
   <si>
-    <t>7경 7242조 4697억 2671만</t>
+    <t>7경 9177조 9508억 9347만</t>
   </si>
   <si>
     <t>원이유이</t>
@@ -1365,7 +1365,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%9D%B4%EC%9C%A0%EC%9D%B4</t>
   </si>
   <si>
-    <t>4경 2472조 8316억 569만</t>
+    <t>4경 2694조 7769억 7457만</t>
   </si>
   <si>
     <t>하드웨어</t>
@@ -1374,7 +1374,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>3경 7420조 2128억 5293만</t>
+    <t>3경 7485조 2563억 5299만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
+  </si>
+  <si>
+    <t>3경 1464조 7934억 743만</t>
   </si>
   <si>
     <t>ShellyCake</t>
@@ -1386,19 +1392,13 @@
     <t>2경 9098조 3578억 5360만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
-  </si>
-  <si>
-    <t>2경 7284조 797억 1001만</t>
-  </si>
-  <si>
     <t>오정구불독</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>2경 4043조 5902억 7249만</t>
+    <t>2경 4378조 708억 4495만</t>
   </si>
   <si>
     <t>양덕하늘채</t>
@@ -1407,7 +1407,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8D%95%ED%95%98%EB%8A%98%EC%B1%84</t>
   </si>
   <si>
-    <t>1경 7734조 9676억 2191만</t>
+    <t>2경 842조 77억 7410만</t>
+  </si>
+  <si>
+    <t>구미적</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
+  </si>
+  <si>
+    <t>1경 5541조 5808억 6362만</t>
   </si>
   <si>
     <t>레드플레이어</t>
@@ -1416,16 +1425,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
   </si>
   <si>
-    <t>1경 5264조 3402억 5185만</t>
-  </si>
-  <si>
-    <t>구미적</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
-  </si>
-  <si>
-    <t>1경 4979조 4621억 2512만</t>
+    <t>1경 5297조 169억 3027만</t>
+  </si>
+  <si>
+    <t>검샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
+  </si>
+  <si>
+    <t>1경 4840조 5856억 4141만</t>
   </si>
   <si>
     <t>주하사랑</t>
@@ -1434,16 +1443,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
   </si>
   <si>
-    <t>1경 4364조 8262억 2018만</t>
-  </si>
-  <si>
-    <t>검샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
-  </si>
-  <si>
-    <t>1경 3318조 2871억 4594만</t>
+    <t>1경 4796조 6856억 4386만</t>
   </si>
   <si>
     <t>예슬a</t>
@@ -1458,6 +1458,15 @@
     <t>1경 2932조 2761억 2173만</t>
   </si>
   <si>
+    <t>장아린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>1경 1524조 6705억 1313만</t>
+  </si>
+  <si>
     <t>브리또강철중</t>
   </si>
   <si>
@@ -1467,22 +1476,13 @@
     <t>1경 177조 670억 8640만</t>
   </si>
   <si>
-    <t>장아린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>9779조 7293억 9893만</t>
-  </si>
-  <si>
     <t>꼬기갓</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
   </si>
   <si>
-    <t>8285조 5244억 911만</t>
+    <t>8429조 8652억 331만</t>
   </si>
   <si>
     <t>l빠다코코낫l</t>
@@ -1500,7 +1500,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EA%B4%91%EC%B6%98</t>
   </si>
   <si>
-    <t>6213조 297억 1292만</t>
+    <t>6245조 8404억 7741만</t>
   </si>
   <si>
     <t>어꼬</t>
@@ -1512,7 +1512,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>3852조 7462억 8910만</t>
+    <t>3973조 6123억 4128만</t>
   </si>
   <si>
     <t>군보</t>
@@ -1521,7 +1521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>204경 8248조 734억 8566만</t>
+    <t>210경 3206조 7370억 9169만</t>
   </si>
   <si>
     <t>눙키</t>
@@ -1530,7 +1530,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
   </si>
   <si>
-    <t>132경 1834조 3761억 3417만</t>
+    <t>133경 3501조 2330억 9710만</t>
   </si>
   <si>
     <t>5형사</t>
@@ -1539,13 +1539,22 @@
     <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>105경 2061조 4279억 9876만</t>
+    <t>107경 8322조 6519억 4570만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
   </si>
   <si>
-    <t>75경 6411조 4000억 426만</t>
+    <t>75경 7956조 1553억 5478만</t>
+  </si>
+  <si>
+    <t>심천</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
+  </si>
+  <si>
+    <t>71경 6093조 5551억 1204만</t>
   </si>
   <si>
     <t>혁수킹</t>
@@ -1554,16 +1563,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
   </si>
   <si>
-    <t>71경 2535조 1115억 3507만</t>
-  </si>
-  <si>
-    <t>심천</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
-  </si>
-  <si>
-    <t>70경 694조 6094억 7367만</t>
+    <t>71경 2832조 7567억 198만</t>
   </si>
   <si>
     <t>Matter</t>
@@ -1572,7 +1572,7 @@
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>67경 1112조 5296억 2467만</t>
+    <t>67경 1286조 4798억 6476만</t>
   </si>
   <si>
     <t>또르뱅</t>
@@ -1581,7 +1581,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>64경 9359조 5186억 5220만</t>
+    <t>64경 9435조 4122억 760만</t>
   </si>
   <si>
     <t>원중언니</t>
@@ -1626,7 +1626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>33경 807조 14억 2513만</t>
+    <t>34경 1559조 6259억 9502만</t>
   </si>
   <si>
     <t>김나뭉</t>
@@ -1635,7 +1635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
   </si>
   <si>
-    <t>32경 1529조 9226억 8356만</t>
+    <t>32경 4946조 4552억 5241만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1644,7 +1644,16 @@
     <t>https://mgf.gg/contents/character.php?n=Hoood</t>
   </si>
   <si>
-    <t>17경 8223조 8720억 3869만</t>
+    <t>17경 9927조 5833억 5670만</t>
+  </si>
+  <si>
+    <t>찐맨듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
+  </si>
+  <si>
+    <t>16경 5241조 2114억 2698만</t>
   </si>
   <si>
     <t>껌정색</t>
@@ -1653,16 +1662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>15경 4423조 9677억 1789만</t>
-  </si>
-  <si>
-    <t>찐맨듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
-  </si>
-  <si>
-    <t>15경 1501조 8621억 7551만</t>
+    <t>15경 8062조 1522억 1141만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -1671,7 +1671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
   </si>
   <si>
-    <t>14경 1983조 8733억 8411만</t>
+    <t>14경 2140조 2961억 6634만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1698,7 +1698,7 @@
     <t>https://mgf.gg/contents/character.php?n=Rahee</t>
   </si>
   <si>
-    <t>7경 9114조 6045억 826만</t>
+    <t>7경 9130조 4991억 1078만</t>
   </si>
   <si>
     <t>고먀츠나나</t>
@@ -1716,7 +1716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
   </si>
   <si>
-    <t>6경 102조 1325억 1418만</t>
+    <t>6경 2630조 7320억 1623만</t>
   </si>
   <si>
     <t>히째히째</t>
@@ -1725,7 +1725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
   </si>
   <si>
-    <t>4경 6413조 9292억 4906만</t>
+    <t>4경 6502조 4984억 6129만</t>
   </si>
   <si>
     <t>통뼈1</t>
@@ -1761,7 +1761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 2811조 8130억 7852만</t>
+    <t>2경 2821조 2788억 4255만</t>
   </si>
   <si>
     <t>셀러문</t>
@@ -1773,7 +1773,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>4171조 588억 426만</t>
+    <t>5043조 4538억 803만</t>
   </si>
   <si>
     <t>라온XR</t>
@@ -1782,7 +1782,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8XR</t>
   </si>
   <si>
-    <t>453경 1832조 9684억 178만</t>
+    <t>454경 1026조 4435억 4176만</t>
   </si>
   <si>
     <t>매스몬스터</t>
@@ -1809,7 +1809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
   </si>
   <si>
-    <t>107경 50조 3372억 7613만</t>
+    <t>107경 8963조 5279억 4017만</t>
   </si>
   <si>
     <t>타이슨에어랩</t>
@@ -1818,13 +1818,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
   </si>
   <si>
-    <t>62경 9145조 4295억 6367만</t>
+    <t>64경 9301조 8216억 4418만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
   </si>
   <si>
-    <t>55경 2187조 5827억 5986만</t>
+    <t>55경 3172조 6580억 9280만</t>
   </si>
   <si>
     <t>미야고</t>
@@ -1836,22 +1836,22 @@
     <t>51경 2943조 3453억 7104만</t>
   </si>
   <si>
+    <t>캔드릭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
+  </si>
+  <si>
+    <t>41경 6726조 9287억 7400만</t>
+  </si>
+  <si>
     <t>용보이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>37경 6569조 638억 2355만</t>
-  </si>
-  <si>
-    <t>캔드릭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
-  </si>
-  <si>
-    <t>37경 220조 9594억 6486만</t>
+    <t>38경 2586조 8944억 5397만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -1869,7 +1869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
   </si>
   <si>
-    <t>18경 9416조 6626억 7901만</t>
+    <t>19경 1276조 3734억 6455만</t>
   </si>
   <si>
     <t>도적왕대현</t>
@@ -1878,7 +1878,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EC%99%95%EB%8C%80%ED%98%84</t>
   </si>
   <si>
-    <t>11경 2643조 4220억 6938만</t>
+    <t>11경 6944조 1963억 7415만</t>
   </si>
   <si>
     <t>도농롱</t>
@@ -1899,6 +1899,15 @@
     <t>8경 8501조 7368억 9660만</t>
   </si>
   <si>
+    <t>혜도로동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
+  </si>
+  <si>
+    <t>8경 220조 6234억 6616만</t>
+  </si>
+  <si>
     <t>반불</t>
   </si>
   <si>
@@ -1908,15 +1917,6 @@
     <t>7경 8531조 6587억 2143만</t>
   </si>
   <si>
-    <t>혜도로동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
-  </si>
-  <si>
-    <t>7경 7856조 6156억 2930만</t>
-  </si>
-  <si>
     <t>붕어줍</t>
   </si>
   <si>
@@ -1932,7 +1932,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
   </si>
   <si>
-    <t>6경 2900조 1923억 1410만</t>
+    <t>6경 2939조 9723억 8197만</t>
   </si>
   <si>
     <t>로생</t>
@@ -1950,7 +1950,7 @@
     <t>https://mgf.gg/contents/character.php?n=Redwine</t>
   </si>
   <si>
-    <t>5경 8673조 7807억 379만</t>
+    <t>5경 8890조 2641억 9762만</t>
   </si>
   <si>
     <t>이다연</t>
@@ -1959,7 +1959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
   </si>
   <si>
-    <t>5경 4405조 7832억 8310만</t>
+    <t>5경 6833조 5925억 8941만</t>
   </si>
   <si>
     <t>망치반죽</t>
@@ -1968,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
   </si>
   <si>
-    <t>5경 298조 6467억 3963만</t>
+    <t>5경 832조 3054억 7661만</t>
   </si>
   <si>
     <t>유도로동</t>
@@ -1977,7 +1977,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>4경 3674조 8359억 9725만</t>
+    <t>4경 4708조 3034억 16만</t>
+  </si>
+  <si>
+    <t>메키메렁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
+  </si>
+  <si>
+    <t>3경 7051조 1682억 7439만</t>
   </si>
   <si>
     <t>그때그아이</t>
@@ -1989,22 +1998,13 @@
     <t>3경 1551조 4991억 3144만</t>
   </si>
   <si>
-    <t>메키메렁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
-  </si>
-  <si>
-    <t>3경 1432조 3768억 3422만</t>
-  </si>
-  <si>
     <t>루빙</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
   </si>
   <si>
-    <t>2경 1709조 395억 4256만</t>
+    <t>2경 3340조 8610억 3608만</t>
   </si>
   <si>
     <t>꽁꽁얼었다</t>
@@ -2022,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=spemi</t>
   </si>
   <si>
-    <t>1경 9184조 7426억 6819만</t>
+    <t>1경 9251조 1500억 5785만</t>
   </si>
   <si>
     <t>우솝이</t>
@@ -2031,7 +2031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
   </si>
   <si>
-    <t>1경 7474조 253억 6627만</t>
+    <t>1경 7586조 2544억 7904만</t>
   </si>
   <si>
     <t>막또날드</t>
@@ -2040,7 +2040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
   </si>
   <si>
-    <t>1경 5575조 7834억 2052만</t>
+    <t>1경 6542조 9992억 2302만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2061,6 +2061,24 @@
     <t>21경 913조 6729억 9538만</t>
   </si>
   <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>12경 7805조 791억 5905만</t>
+  </si>
+  <si>
+    <t>국의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
+  </si>
+  <si>
+    <t>12경 7170조 9223억 583만</t>
+  </si>
+  <si>
     <t>걸음</t>
   </si>
   <si>
@@ -2070,13 +2088,13 @@
     <t>12경 6297조 3934억 1589만</t>
   </si>
   <si>
-    <t>국의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
-  </si>
-  <si>
-    <t>12경 3858조 1172억 6063만</t>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>10경 7475조 5883억 7689만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -2085,7 +2103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>10경 6184조 3457억 7322만</t>
+    <t>10경 6741조 2066억 6237만</t>
   </si>
   <si>
     <t>약어</t>
@@ -2103,25 +2121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>9경 3479조 369억 3638만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>8경 2706조 3135억 2808만</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>7경 5292조 4238억 2660만</t>
+    <t>9경 8900조 2461억 1026만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -2130,7 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>7경 3381조 2238억 1561만</t>
+    <t>8경 889조 8820억 3333만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -2142,22 +2142,22 @@
     <t>5경 5228조 9003억 4099만</t>
   </si>
   <si>
+    <t>핫잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
+  </si>
+  <si>
+    <t>2경 5674조 8497억 6042만</t>
+  </si>
+  <si>
     <t>할룽</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 5374조 9474억 3745만</t>
-  </si>
-  <si>
-    <t>핫잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
-  </si>
-  <si>
-    <t>2경 5181조 6388억 1979만</t>
+    <t>2경 5389조 5126억 3656만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -2166,7 +2166,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 3271조 2021억 502만</t>
+    <t>2경 3490조 8557억 971만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -2193,7 +2193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>2경 616조 9601억 9592만</t>
+    <t>2경 1051조 6678억 8223만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -2202,22 +2202,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>1경 7942조 150억 6859만</t>
+    <t>1경 8946조 4328억 6990만</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1경 7975조 2343억 1795만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 7139조 5691억 7924만</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1경 6180조 1094억 5337만</t>
+    <t>1경 7967조 8531억 1276만</t>
+  </si>
+  <si>
+    <t>니뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>1경 3466조 9661억 2553만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2229,13 +2238,13 @@
     <t>1경 3352조 5107억 6670만</t>
   </si>
   <si>
-    <t>니뚜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
-  </si>
-  <si>
-    <t>1경 2819조 4851억 9770만</t>
+    <t>라똥삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
+  </si>
+  <si>
+    <t>1경 3335조 5943억 5779만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -2247,22 +2256,13 @@
     <t>1경 2644조 7980억 538만</t>
   </si>
   <si>
-    <t>라똥삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%98%A5%EC%82%90</t>
-  </si>
-  <si>
-    <t>1경 2085조 1284억 3396만</t>
-  </si>
-  <si>
     <t>제로슈가</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 75조 3638억 2592만</t>
+    <t>1경 81조 8065억 59만</t>
   </si>
   <si>
     <t>러너</t>
@@ -2271,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>6443조 2165억 2470만</t>
+    <t>6503조 8983억 4302만</t>
   </si>
   <si>
     <t>해찬나래</t>
@@ -3721,13 +3721,13 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3738,25 +3738,25 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>192</v>
@@ -3785,7 +3785,7 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>178</v>
@@ -3820,7 +3820,7 @@
         <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>200</v>
@@ -3884,7 +3884,7 @@
         <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>208</v>
@@ -3916,7 +3916,7 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>212</v>
@@ -3948,7 +3948,7 @@
         <v>125</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>216</v>
@@ -4070,7 +4070,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4417,7 +4417,7 @@
         <v>256</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>257</v>
@@ -4545,7 +4545,7 @@
         <v>232</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>269</v>
@@ -4574,10 +4574,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>256</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>272</v>
@@ -4609,7 +4609,7 @@
         <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>275</v>
@@ -4638,10 +4638,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>256</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>278</v>
@@ -4705,7 +4705,7 @@
         <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>284</v>
@@ -4737,7 +4737,7 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>287</v>
@@ -4766,10 +4766,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>290</v>
@@ -4783,7 +4783,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>291</v>
@@ -4798,10 +4798,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>293</v>
@@ -4929,10 +4929,10 @@
         <v>172</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4946,13 +4946,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -4961,7 +4961,7 @@
         <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>309</v>
@@ -4993,7 +4993,7 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>312</v>
@@ -5025,7 +5025,7 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>315</v>
@@ -5458,10 +5458,10 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>349</v>
@@ -5490,10 +5490,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>352</v>
@@ -5557,7 +5557,7 @@
         <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>358</v>
@@ -5589,7 +5589,7 @@
         <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>361</v>
@@ -5781,7 +5781,7 @@
         <v>342</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>379</v>
@@ -5795,7 +5795,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>380</v>
@@ -6409,7 +6409,7 @@
         <v>177</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>429</v>
@@ -6505,7 +6505,7 @@
         <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>438</v>
@@ -6618,25 +6618,25 @@
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6650,22 +6650,22 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>450</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>450</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>451</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>452</v>
@@ -6697,7 +6697,7 @@
         <v>232</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>455</v>
@@ -6758,10 +6758,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>461</v>
@@ -6790,10 +6790,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>305</v>
+        <v>220</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>464</v>
@@ -6807,7 +6807,7 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>465</v>
@@ -6822,10 +6822,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>467</v>
@@ -6854,10 +6854,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>470</v>
@@ -6921,7 +6921,7 @@
         <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>473</v>
+        <v>308</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>477</v>
@@ -6953,7 +6953,7 @@
         <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>305</v>
+        <v>473</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>480</v>
@@ -6985,7 +6985,7 @@
         <v>172</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>483</v>
@@ -7017,7 +7017,7 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>486</v>
@@ -7049,7 +7049,7 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>489</v>
@@ -7323,7 +7323,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>172</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>126</v>
@@ -7355,7 +7355,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>126</v>
@@ -7675,7 +7675,7 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>342</v>
+        <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>154</v>
@@ -7707,7 +7707,7 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>342</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>154</v>
@@ -7852,7 +7852,7 @@
         <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>556</v>
@@ -8030,7 +8030,7 @@
         <v>144</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>573</v>
@@ -8306,7 +8306,7 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>592</v>
@@ -8431,10 +8431,10 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>603</v>
@@ -8463,10 +8463,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>606</v>
@@ -8655,10 +8655,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>624</v>
@@ -8687,10 +8687,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>627</v>
@@ -8864,7 +8864,7 @@
         <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>643</v>
@@ -8943,10 +8943,10 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>342</v>
+        <v>120</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>651</v>
@@ -8975,10 +8975,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>342</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>654</v>
@@ -9010,7 +9010,7 @@
         <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>657</v>
@@ -9042,7 +9042,7 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>660</v>
@@ -9074,7 +9074,7 @@
         <v>232</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>663</v>
@@ -9316,10 +9316,10 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>678</v>
@@ -9380,7 +9380,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>154</v>
@@ -9412,7 +9412,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>154</v>
@@ -9444,10 +9444,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>690</v>
@@ -9476,7 +9476,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>154</v>
@@ -9508,7 +9508,7 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>159</v>
@@ -9543,7 +9543,7 @@
         <v>105</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>699</v>
@@ -9607,7 +9607,7 @@
         <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>705</v>
@@ -9639,7 +9639,7 @@
         <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>708</v>
@@ -9671,7 +9671,7 @@
         <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>711</v>
@@ -9799,7 +9799,7 @@
         <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>723</v>
@@ -9816,25 +9816,25 @@
         <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>724</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>75</v>
+        <v>724</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>305</v>
+        <v>220</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>67</v>
@@ -9848,22 +9848,22 @@
         <v>180</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>726</v>
+        <v>75</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>726</v>
+        <v>75</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>727</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>728</v>
@@ -9892,7 +9892,7 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>220</v>
@@ -9909,7 +9909,7 @@
         <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>732</v>
@@ -9924,10 +9924,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>734</v>
@@ -9956,10 +9956,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>737</v>
@@ -9988,10 +9988,10 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>305</v>
+        <v>220</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>740</v>
@@ -10055,7 +10055,7 @@
         <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>746</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -11,19 +11,19 @@
     <sheet name="레플리카셋" sheetId="2" r:id="rId2"/>
     <sheet name="귀여미" sheetId="3" r:id="rId3"/>
     <sheet name="브리또" sheetId="4" r:id="rId4"/>
-    <sheet name="설묘" sheetId="5" r:id="rId5"/>
-    <sheet name="리안" sheetId="6" r:id="rId6"/>
+    <sheet name="리안" sheetId="5" r:id="rId5"/>
+    <sheet name="설묘" sheetId="6" r:id="rId6"/>
     <sheet name="점프킹" sheetId="7" r:id="rId7"/>
     <sheet name="셀린느" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">귀여미!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">귀여미!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">레플리카셋!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">리안!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">리안!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">브리또!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">설묘!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">셀린느!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">설묘!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">점프킹!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="762">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 32</t>
   </si>
   <si>
-    <t>42</t>
+    <t>43</t>
   </si>
   <si>
     <t>1위</t>
@@ -117,7 +117,7 @@
     <t>Scania 34</t>
   </si>
   <si>
-    <t>48</t>
+    <t>49</t>
   </si>
   <si>
     <t>30명</t>
@@ -141,7 +141,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>67</t>
+    <t>68</t>
   </si>
   <si>
     <t>2위</t>
@@ -156,6 +156,39 @@
     <t>안데일2</t>
   </si>
   <si>
+    <t>리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>5위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>26명</t>
+  </si>
+  <si>
+    <t>815경 6691조 2701억 4039만</t>
+  </si>
+  <si>
+    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
+  </si>
+  <si>
+    <t>예습2</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
     <t>설묘</t>
   </si>
   <si>
@@ -165,63 +198,30 @@
     <t>Scania 25</t>
   </si>
   <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>1089경 6103조 5933억 8200만</t>
+  </si>
+  <si>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+  </si>
+  <si>
+    <t>설익은체리</t>
+  </si>
+  <si>
+    <t>점프킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
+  </si>
+  <si>
+    <t>Scania 5</t>
+  </si>
+  <si>
     <t>46</t>
   </si>
   <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>1089경 6103조 5933억 8200만</t>
-  </si>
-  <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
-  </si>
-  <si>
-    <t>설익은체리</t>
-  </si>
-  <si>
-    <t>리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>4위</t>
-  </si>
-  <si>
-    <t>26명</t>
-  </si>
-  <si>
-    <t>815경 6691조 2701억 4039만</t>
-  </si>
-  <si>
-    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
-  </si>
-  <si>
-    <t>예습2</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
-    <t>점프킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
-  </si>
-  <si>
-    <t>Scania 5</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
     <t>28명</t>
   </si>
   <si>
@@ -246,7 +246,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>64</t>
+    <t>65</t>
   </si>
   <si>
     <t>3위</t>
@@ -297,112 +297,124 @@
     <t>N</t>
   </si>
   <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>4155경 9968조 5861억 5343만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>쉐도우그림자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%89%90%EB%8F%84%EC%9A%B0%EA%B7%B8%EB%A6%BC%EC%9E%90</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>751경 3081조 8777억 5514만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>유이파더</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%9D%B4%ED%8C%8C%EB%8D%94</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>633경 2278조 2171억 6001만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>라온A</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8A</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>462경 1350조 5798억 5105만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>루졔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>444경 6314조 8526억 2319만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>꾱환</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
+  </si>
+  <si>
+    <t>419경 745조 2321억 2687만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>씬큥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%94%AC%ED%81%A5</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>302경 2653조 7345억 9944만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>배멀미캡틴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%A9%80%EB%AF%B8%EC%BA%A1%ED%8B%B4</t>
+  </si>
+  <si>
     <t>바이퍼</t>
   </si>
   <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>3595경 1781조 4055억 2766만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>쉐도우그림자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%89%90%EB%8F%84%EC%9A%B0%EA%B7%B8%EB%A6%BC%EC%9E%90</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>690경 596조 456억 2675만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>유이파더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%9D%B4%ED%8C%8C%EB%8D%94</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>632경 9114조 565억 5060만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>라온A</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8A</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>461경 9750조 8492억 670만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>루졔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>442경 5680조 89억 7761만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>꾱환</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
-  </si>
-  <si>
-    <t>371경 9193조 1660억 5464만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>씬큥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%94%AC%ED%81%A5</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>284경 5498조 1420억 2552만</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>230경 8416조 5905억 5061만</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>혀로꽃</t>
@@ -411,52 +423,52 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EA%BD%83</t>
   </si>
   <si>
+    <t>147경 5173조 6026억 6674만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>뻥투기릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>89경 9862조 1727억 1627만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%B9%A8%EA%B0%84%EB%8F%8C%ED%94%84</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>135경 6784조 206억 3874만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>뻥투기릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>89경 9862조 1727억 1627만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%B9%A8%EA%B0%84%EB%8F%8C%ED%94%84</t>
-  </si>
-  <si>
-    <t>Y</t>
+    <t>74경 3470조 8838억 859만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>라온J</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8J</t>
   </si>
   <si>
     <t>122</t>
   </si>
   <si>
-    <t>74경 3470조 8838억 859만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>라온J</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8J</t>
-  </si>
-  <si>
-    <t>38경 9204조 7304억 5367만</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>38경 9298조 5739억 2595만</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>데브쫑</t>
@@ -471,10 +483,10 @@
     <t>121</t>
   </si>
   <si>
-    <t>34경 9682조 4625억 7498만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>35경 202조 6817억 6084만</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>다다른</t>
@@ -483,10 +495,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EB%A5%B8</t>
   </si>
   <si>
-    <t>34경 5306조 5802억 337만</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>34경 7227조 6576억 9472만</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>기뚠</t>
@@ -498,10 +510,10 @@
     <t>120</t>
   </si>
   <si>
-    <t>24경 9119조 9639억 9948만</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>25경 3316조 9144억 3489만</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>쌰갈</t>
@@ -513,10 +525,10 @@
     <t>119</t>
   </si>
   <si>
-    <t>21경 8165조 4122억 941만</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>22경 4392조 8883억 4703만</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>911TurboS</t>
@@ -525,10 +537,10 @@
     <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
   </si>
   <si>
-    <t>19경 1685조 4273억 7300만</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>19경 6218조 4556억 7817만</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>하싱</t>
@@ -537,10 +549,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
   </si>
   <si>
-    <t>16경 1332조 1691억 753만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>16경 3990조 6719억 51만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>라온U</t>
@@ -552,10 +564,10 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>12경 467조 436억 6657만</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>12경 507조 2384억 2548만</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>어쓰</t>
@@ -570,10 +582,10 @@
     <t>118</t>
   </si>
   <si>
-    <t>11경 3972조 3203억 2525만</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>11경 6880조 8854억 1127만</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>김라이트</t>
@@ -582,10 +594,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
   </si>
   <si>
-    <t>8경 6972조 5711억 9285만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>10경 6729조 1013억 4895만</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>명품까칠공주</t>
@@ -600,7 +612,19 @@
     <t>7경 2851조 9198억 3933만</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
+  </si>
+  <si>
+    <t>원탱구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>7경 1980조 9591억 8016만</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>뿔피리</t>
@@ -609,22 +633,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>6경 8910조 654억 8704만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>원탱구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>6경 6671조 753억 8802만</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>7경 1885조 5862억 3242만</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>최슬</t>
@@ -636,7 +648,7 @@
     <t>6경 6287조 6681억 6245만</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>오이겐</t>
@@ -645,10 +657,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
   </si>
   <si>
-    <t>5경 7594조 5870억 5368만</t>
-  </si>
-  <si>
-    <t>26</t>
+    <t>5경 9039조 7523억 8314만</t>
+  </si>
+  <si>
+    <t>27</t>
   </si>
   <si>
     <t>탄지로네즈</t>
@@ -657,10 +669,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>4경 4402조 9615억 138만</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>4경 5526조 7637억 7168만</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>이솔빠</t>
@@ -672,7 +684,7 @@
     <t>3경 1156조 3380억 4689만</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>깔지마오</t>
@@ -684,7 +696,7 @@
     <t>2경 9330조 6252억 5962만</t>
   </si>
   <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>멀해</t>
@@ -696,19 +708,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 6272조 175억 1648만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>일단대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EB%8B%A8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1경 5136조 8361억 7335만</t>
+    <t>1경 6422조 6374억 5721만</t>
   </si>
   <si>
     <t>금은동S2</t>
@@ -717,7 +717,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%EC%9D%80%EB%8F%99S2</t>
   </si>
   <si>
-    <t>1122경 5767조 194억 7158만</t>
+    <t>1159경 4178조 2780억 3366만</t>
   </si>
   <si>
     <t>라온JW</t>
@@ -744,7 +744,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
   </si>
   <si>
-    <t>47경 1992조 6678억 224만</t>
+    <t>47경 2519조 948억 9725만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -762,7 +762,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>33경 8817조 6945억 7563만</t>
+    <t>35경 4629조 5145억 676만</t>
+  </si>
+  <si>
+    <t>꿈넴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%88%EB%84%B4</t>
+  </si>
+  <si>
+    <t>17경 743조 9428억 5319만</t>
   </si>
   <si>
     <t>쁘덍</t>
@@ -780,7 +789,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>13경 6457조 6420억 4968만</t>
+    <t>13경 8786조 2832억 2611만</t>
   </si>
   <si>
     <t>제껴</t>
@@ -789,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>12경 2297조 5767억 8466만</t>
+    <t>13경 1736조 7234억 9549만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -801,7 +810,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>8경 9338조 1880억 7443만</t>
+    <t>10경 1365조 1930억 8622만</t>
   </si>
   <si>
     <t>엘리자베타</t>
@@ -810,7 +819,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A6%AC%EC%9E%90%EB%B2%A0%ED%83%80</t>
   </si>
   <si>
-    <t>6경 3230조 8249억 3567만</t>
+    <t>6경 8617조 3478억 9957만</t>
   </si>
   <si>
     <t>어흥이다</t>
@@ -819,7 +828,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>5경 6253조 7342억 2328만</t>
+    <t>5경 6520조 555억 1030만</t>
   </si>
   <si>
     <t>우꼬쨩</t>
@@ -840,22 +849,22 @@
     <t>5경 1934조 9124억 872만</t>
   </si>
   <si>
+    <t>붙잡아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
+  </si>
+  <si>
+    <t>4경 9986조 2289억 7035만</t>
+  </si>
+  <si>
     <t>홍시마로</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>4경 5405조 1742억 3714만</t>
-  </si>
-  <si>
-    <t>붙잡아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%99%EC%9E%A1%EC%95%84</t>
-  </si>
-  <si>
-    <t>4경 782조 1505억 9630만</t>
+    <t>4경 7368조 9807억 1240만</t>
   </si>
   <si>
     <t>비밀키</t>
@@ -864,7 +873,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
   </si>
   <si>
-    <t>3경 8363조 108억 1090만</t>
+    <t>4경 6485조 1235억 1735만</t>
+  </si>
+  <si>
+    <t>슛맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>3경 4296조 6719억 5656만</t>
   </si>
   <si>
     <t>지아라떼</t>
@@ -876,22 +894,13 @@
     <t>3경 2561조 2843억 5580만</t>
   </si>
   <si>
-    <t>슛맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>3경 320조 3479억 8653만</t>
-  </si>
-  <si>
     <t>o엔젤o</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
   </si>
   <si>
-    <t>2경 7595조 8076억 9409만</t>
+    <t>2경 9247조 2806억 238만</t>
   </si>
   <si>
     <t>득츈</t>
@@ -900,7 +909,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
   </si>
   <si>
-    <t>2경 7355조 2238억 3371만</t>
+    <t>2경 7989조 9330억 7146만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -909,7 +918,16 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 6264조 7613억 2916만</t>
+    <t>2경 6281조 6067억 4914만</t>
+  </si>
+  <si>
+    <t>24년생정춘식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=24%EB%85%84%EC%83%9D%EC%A0%95%EC%B6%98%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>2경 4335조 2640억 3242만</t>
   </si>
   <si>
     <t>메론맛빵</t>
@@ -921,22 +939,13 @@
     <t>2경 2830조 9768억 724만</t>
   </si>
   <si>
-    <t>24년생정춘식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=24%EB%85%84%EC%83%9D%EC%A0%95%EC%B6%98%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>2경 2448조 6657억 7816만</t>
-  </si>
-  <si>
     <t>시프님</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
   </si>
   <si>
-    <t>1경 6612조 3097억 734만</t>
+    <t>1경 7014조 4769억 8334만</t>
   </si>
   <si>
     <t>야옹이다</t>
@@ -945,7 +954,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>1경 2402조 8821억 8442만</t>
+    <t>1경 3779조 5162억 8939만</t>
   </si>
   <si>
     <t>출장괴물</t>
@@ -954,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>1경 347조 280억 8124만</t>
+    <t>1경 702조 7667억 7739만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -966,7 +975,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>9172조 4957억 4646만</t>
+    <t>9486조 8381억 910만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -975,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>8910조 1683억 253만</t>
+    <t>9235조 2239억 9662만</t>
   </si>
   <si>
     <t>강서구도적</t>
@@ -984,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
   </si>
   <si>
-    <t>661경 5215조 7685억 4670만</t>
+    <t>671경 6240조 2914억 3585만</t>
   </si>
   <si>
     <t>따코유</t>
@@ -993,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EC%BD%94%EC%9C%A0</t>
   </si>
   <si>
-    <t>460경 2925조 7118억 1048만</t>
+    <t>493경 4454조 9046억 4956만</t>
   </si>
   <si>
     <t>뚱털</t>
@@ -1011,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
   </si>
   <si>
-    <t>110경 1585조 7196억 155만</t>
+    <t>110경 8096조 6017억 7967만</t>
   </si>
   <si>
     <t>귤놈펜</t>
@@ -1020,7 +1029,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
   </si>
   <si>
-    <t>90경 3645조 5541억 1474만</t>
+    <t>91경 7305조 6984억 8016만</t>
   </si>
   <si>
     <t>꿀서은</t>
@@ -1029,7 +1038,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
   </si>
   <si>
-    <t>35경 7037조 4373억 6009만</t>
+    <t>36경 4147조 5777억 9639만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -1038,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>35경 691조 7098억 7927만</t>
+    <t>36경 1912조 8926억 1964만</t>
   </si>
   <si>
     <t>게탕</t>
@@ -1047,7 +1056,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
   </si>
   <si>
-    <t>24경 1067조 8255억 5192만</t>
+    <t>24경 1135조 926억 7989만</t>
   </si>
   <si>
     <t>쿨쥐돌</t>
@@ -1065,7 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>22경 5983조 2810억 2777만</t>
+    <t>22경 8426조 8244억 8301만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -1074,7 +1083,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
   </si>
   <si>
-    <t>13경 8496조 6554억 9733만</t>
+    <t>13경 9741조 2678억 5328만</t>
   </si>
   <si>
     <t>류텐</t>
@@ -1083,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
   </si>
   <si>
-    <t>9경 3771조 2580억 9733만</t>
+    <t>10경 101조 9956억 9608만</t>
   </si>
   <si>
     <t>철푸닥</t>
@@ -1092,7 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%A0%ED%91%B8%EB%8B%A5</t>
   </si>
   <si>
-    <t>7경 9799조 7012억 3193만</t>
+    <t>8경 4548조 3618억 9707만</t>
   </si>
   <si>
     <t>원이유이</t>
@@ -1101,7 +1110,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%9D%B4%EC%9C%A0%EC%9D%B4</t>
   </si>
   <si>
-    <t>5경 2161조 6549억 9969만</t>
+    <t>5경 7654조 8032억 4582만</t>
   </si>
   <si>
     <t>하드웨어</t>
@@ -1110,13 +1119,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>3경 8546조 1885억 8551만</t>
+    <t>4경 518조 6712억 6491만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
   </si>
   <si>
-    <t>3경 1952조 6417억 5034만</t>
+    <t>3경 2140조 5447억 6348만</t>
   </si>
   <si>
     <t>ShellyCake</t>
@@ -1125,7 +1134,7 @@
     <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
   </si>
   <si>
-    <t>2경 9299조 8100억 8089만</t>
+    <t>3경 488조 6677억 1566만</t>
   </si>
   <si>
     <t>오정구불독</t>
@@ -1152,7 +1161,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
   </si>
   <si>
-    <t>1경 7802조 322억 7104만</t>
+    <t>1경 8912조 9957억 2621만</t>
   </si>
   <si>
     <t>레드플레이어</t>
@@ -1161,7 +1170,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
   </si>
   <si>
-    <t>1경 5297조 169억 3027만</t>
+    <t>1경 5493조 9021억 1126만</t>
+  </si>
+  <si>
+    <t>검샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
+  </si>
+  <si>
+    <t>1경 5390조 9404억 6035만</t>
   </si>
   <si>
     <t>주하사랑</t>
@@ -1173,42 +1191,33 @@
     <t>1경 5163조 9079억 2710만</t>
   </si>
   <si>
-    <t>검샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
-  </si>
-  <si>
-    <t>1경 5005조 3473억 3531만</t>
-  </si>
-  <si>
     <t>예슬a</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%ACa</t>
   </si>
   <si>
+    <t>1경 3288조 2411억 4294만</t>
+  </si>
+  <si>
+    <t>장아린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>1경 3180조 7052억 299만</t>
+  </si>
+  <si>
+    <t>브리또강철중</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A6%AC%EB%98%90%EA%B0%95%EC%B2%A0%EC%A4%91</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>1경 2932조 2761억 2173만</t>
-  </si>
-  <si>
-    <t>장아린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>1경 2632조 8455억 113만</t>
-  </si>
-  <si>
-    <t>브리또강철중</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A6%AC%EB%98%90%EA%B0%95%EC%B2%A0%EC%A4%91</t>
-  </si>
-  <si>
     <t>1경 177조 670억 8640만</t>
   </si>
   <si>
@@ -1218,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
   </si>
   <si>
-    <t>8429조 8652억 331만</t>
+    <t>8746조 8499억 1434만</t>
   </si>
   <si>
     <t>l빠다코코낫l</t>
@@ -1227,7 +1236,7 @@
     <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
   </si>
   <si>
-    <t>8050조 8071억 8699만</t>
+    <t>8491조 2943억 8606만</t>
   </si>
   <si>
     <t>리광춘</t>
@@ -1236,7 +1245,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EA%B4%91%EC%B6%98</t>
   </si>
   <si>
-    <t>6245조 8404억 7741만</t>
+    <t>6546조 9192억 3489만</t>
   </si>
   <si>
     <t>어꼬</t>
@@ -1251,7 +1260,277 @@
     <t>112</t>
   </si>
   <si>
-    <t>3973조 6123억 4128만</t>
+    <t>4228조 7124억 6092만</t>
+  </si>
+  <si>
+    <t>군보</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
+  </si>
+  <si>
+    <t>220경 4372조 9701억 1514만</t>
+  </si>
+  <si>
+    <t>눙키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
+  </si>
+  <si>
+    <t>139경 8515조 2898억 1653만</t>
+  </si>
+  <si>
+    <t>5형사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
+  </si>
+  <si>
+    <t>109경 3383조 7982억 841만</t>
+  </si>
+  <si>
+    <t>총괄한석현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%9D%EA%B4%84%ED%95%9C%EC%84%9D%ED%98%84</t>
+  </si>
+  <si>
+    <t>88경 97조 324억 8358만</t>
+  </si>
+  <si>
+    <t>심천</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
+  </si>
+  <si>
+    <t>85경 962조 2392억 5904만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
+  </si>
+  <si>
+    <t>84경 9973조 5244억 6861만</t>
+  </si>
+  <si>
+    <t>혁수킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
+  </si>
+  <si>
+    <t>77경 7775조 9712억 658만</t>
+  </si>
+  <si>
+    <t>Matter</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Matter</t>
+  </si>
+  <si>
+    <t>67경 3530조 7017억 5712만</t>
+  </si>
+  <si>
+    <t>또르뱅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
+  </si>
+  <si>
+    <t>65경 6587조 5523억 357만</t>
+  </si>
+  <si>
+    <t>원중언니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
+  </si>
+  <si>
+    <t>61경 4596조 3831억 1373만</t>
+  </si>
+  <si>
+    <t>가을호떡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%84%ED%98%B8%EB%96%A1</t>
+  </si>
+  <si>
+    <t>55경 5523조 6632억 6782만</t>
+  </si>
+  <si>
+    <t>냠규리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>41경 6888조 5378억 9600만</t>
+  </si>
+  <si>
+    <t>파퍼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
+  </si>
+  <si>
+    <t>34경 3415조 7933억 865만</t>
+  </si>
+  <si>
+    <t>김나뭉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
+  </si>
+  <si>
+    <t>33경 4686조 8087억 3508만</t>
+  </si>
+  <si>
+    <t>Hoood</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Hoood</t>
+  </si>
+  <si>
+    <t>30경 6712억 4376만</t>
+  </si>
+  <si>
+    <t>껌정색</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>19경 6910조 1924억 4865만</t>
+  </si>
+  <si>
+    <t>찐맨듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
+  </si>
+  <si>
+    <t>17경 4273조 517억 842만</t>
+  </si>
+  <si>
+    <t>다끝남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
+  </si>
+  <si>
+    <t>15경 2060조 4908억 8640만</t>
+  </si>
+  <si>
+    <t>이삼2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
+  </si>
+  <si>
+    <t>14경 2203조 8270억 7007만</t>
+  </si>
+  <si>
+    <t>악경</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
+  </si>
+  <si>
+    <t>10경 2388조 6776억 2691만</t>
+  </si>
+  <si>
+    <t>Rahee</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
+  </si>
+  <si>
+    <t>8경 4278조 2698억 8627만</t>
+  </si>
+  <si>
+    <t>고먀츠나나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>7경 7681조 4092억 2482만</t>
+  </si>
+  <si>
+    <t>딤개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>6경 4311조 1275억 7769만</t>
+  </si>
+  <si>
+    <t>히째히째</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
+  </si>
+  <si>
+    <t>5경 1038조 7726억 1822만</t>
+  </si>
+  <si>
+    <t>통뼈1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
+  </si>
+  <si>
+    <t>4경 3909조 8818억 4974만</t>
+  </si>
+  <si>
+    <t>돌로레스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EB%A1%9C%EB%A0%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>3경 8262조 6756억 6501만</t>
+  </si>
+  <si>
+    <t>바람의새벽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
+  </si>
+  <si>
+    <t>2경 9221조 4290억 1767만</t>
+  </si>
+  <si>
+    <t>김도유니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2경 3501조 4842억 4044만</t>
+  </si>
+  <si>
+    <t>셀러문</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%9F%AC%EB%AC%B8</t>
+  </si>
+  <si>
+    <t>5150조 9465억 5638만</t>
+  </si>
+  <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>297경 2867조 5488억 4785만</t>
   </si>
   <si>
     <t>마옥지</t>
@@ -1260,16 +1539,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
   </si>
   <si>
-    <t>280경 3220조 6404억 6122만</t>
-  </si>
-  <si>
-    <t>해물만두야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
-  </si>
-  <si>
-    <t>270경 7618조 922억 2211만</t>
+    <t>289경 6454조 4742억 1360만</t>
   </si>
   <si>
     <t>캐일리</t>
@@ -1278,7 +1548,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>191경 2058조 3901억 1862만</t>
+    <t>206경 7530조 1038억 2497만</t>
   </si>
   <si>
     <t>설익은앵숭</t>
@@ -1305,7 +1575,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>74경 3866조 7469억 4439만</t>
+    <t>76경 7872조 6949억 9142만</t>
   </si>
   <si>
     <t>설묘묘</t>
@@ -1332,9 +1602,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
   </si>
   <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
     <t>45경 1339조 4074억 6761만</t>
   </si>
   <si>
@@ -1353,7 +1620,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>36경 9418조 7315억 5162만</t>
+    <t>37경 8186조 166억 18만</t>
   </si>
   <si>
     <t>시드리안</t>
@@ -1371,7 +1638,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>26경 3393조 6831억 3749만</t>
+    <t>28경 2514조 7004억 9852만</t>
   </si>
   <si>
     <t>졸귀탱이</t>
@@ -1380,7 +1647,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>24경 1488조 7361억 7301만</t>
+    <t>24경 6036조 6491억 3235만</t>
   </si>
   <si>
     <t>마덕칠</t>
@@ -1389,7 +1656,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>20경 2140조 5598억 6840만</t>
+    <t>21경 127조 2151억 9086만</t>
+  </si>
+  <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>20경 5514조 8976억 7519만</t>
   </si>
   <si>
     <t>설딩</t>
@@ -1401,15 +1677,6 @@
     <t>19경 7396조 2622억 1029만</t>
   </si>
   <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>19경 2997조 2320억 2150만</t>
-  </si>
-  <si>
     <t>슐아</t>
   </si>
   <si>
@@ -1425,7 +1692,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>10경 1397조 804억 329만</t>
+    <t>10경 5928조 6370억 6895만</t>
   </si>
   <si>
     <t>경성2018</t>
@@ -1434,7 +1701,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
   </si>
   <si>
-    <t>9경 1574조 1762억 1736만</t>
+    <t>10경 491조 6226억 4381만</t>
   </si>
   <si>
     <t>다다익숍</t>
@@ -1443,7 +1710,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>6경 8871조 9348억 2549만</t>
+    <t>7경 4318조 3235억 2661만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>7경 2830조 3342억 6906만</t>
   </si>
   <si>
     <t>폰병</t>
@@ -1455,10 +1728,13 @@
     <t>6경 5564조 1888억 7889만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>5경 5478조 8492억 3032만</t>
+    <t>상구얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
+  </si>
+  <si>
+    <t>5경 4800조 2727억 5361만</t>
   </si>
   <si>
     <t>애봉얌</t>
@@ -1470,13 +1746,13 @@
     <t>4경 3134조 5060억 9315만</t>
   </si>
   <si>
-    <t>상구얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
-  </si>
-  <si>
-    <t>3경 6630조 3879억 9954만</t>
+    <t>설치는정상인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>2경 420조 1374억 5167만</t>
   </si>
   <si>
     <t>설콩순</t>
@@ -1485,7 +1761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 6721조 8484억 2590만</t>
+    <t>1경 8428조 4809억 2430만</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -1494,16 +1770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 6320조 3647억 4463만</t>
-  </si>
-  <si>
-    <t>설치는정상인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>1경 4592조 3595억 1013만</t>
+    <t>1경 6393조 9171억 9294만</t>
   </si>
   <si>
     <t>네오메디</t>
@@ -1515,264 +1782,6 @@
     <t>1경 4431조 7171억 1764만</t>
   </si>
   <si>
-    <t>군보</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
-  </si>
-  <si>
-    <t>210경 9278조 4438억 6681만</t>
-  </si>
-  <si>
-    <t>눙키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
-  </si>
-  <si>
-    <t>133경 3501조 2330억 9710만</t>
-  </si>
-  <si>
-    <t>5형사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
-  </si>
-  <si>
-    <t>107경 8794조 8113억 3771만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
-  </si>
-  <si>
-    <t>84경 2032조 2935억 6722만</t>
-  </si>
-  <si>
-    <t>심천</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
-  </si>
-  <si>
-    <t>71경 6205조 2065억 5354만</t>
-  </si>
-  <si>
-    <t>혁수킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
-  </si>
-  <si>
-    <t>71경 2925조 7273억 3032만</t>
-  </si>
-  <si>
-    <t>Matter</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Matter</t>
-  </si>
-  <si>
-    <t>67경 1286조 4798억 6476만</t>
-  </si>
-  <si>
-    <t>또르뱅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
-  </si>
-  <si>
-    <t>65경 1367조 1600억 3749만</t>
-  </si>
-  <si>
-    <t>원중언니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
-  </si>
-  <si>
-    <t>61경 1903조 3852억 328만</t>
-  </si>
-  <si>
-    <t>가을호떡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%84%ED%98%B8%EB%96%A1</t>
-  </si>
-  <si>
-    <t>55경 5523조 6632억 6782만</t>
-  </si>
-  <si>
-    <t>총괄한석현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%9D%EA%B4%84%ED%95%9C%EC%84%9D%ED%98%84</t>
-  </si>
-  <si>
-    <t>44경 4442조 9717억 5468만</t>
-  </si>
-  <si>
-    <t>냠규리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>40경 4955조 8370억 5290만</t>
-  </si>
-  <si>
-    <t>파퍼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
-  </si>
-  <si>
-    <t>34경 1559조 6259억 9502만</t>
-  </si>
-  <si>
-    <t>김나뭉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
-  </si>
-  <si>
-    <t>33경 1767조 6467억 7693만</t>
-  </si>
-  <si>
-    <t>Hoood</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Hoood</t>
-  </si>
-  <si>
-    <t>19경 8552조 985억 5605만</t>
-  </si>
-  <si>
-    <t>껌정색</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
-  </si>
-  <si>
-    <t>18경 2023조 8915억 2003만</t>
-  </si>
-  <si>
-    <t>찐맨듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
-  </si>
-  <si>
-    <t>17경 1896조 9147억 3572만</t>
-  </si>
-  <si>
-    <t>다끝남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
-  </si>
-  <si>
-    <t>14경 4855조 588억 6506만</t>
-  </si>
-  <si>
-    <t>이삼2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
-  </si>
-  <si>
-    <t>14경 2203조 8270억 7007만</t>
-  </si>
-  <si>
-    <t>악경</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
-  </si>
-  <si>
-    <t>10경 2388조 6776억 2691만</t>
-  </si>
-  <si>
-    <t>Rahee</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
-  </si>
-  <si>
-    <t>7경 9130조 4991억 1078만</t>
-  </si>
-  <si>
-    <t>고먀츠나나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>7경 7681조 4092억 2482만</t>
-  </si>
-  <si>
-    <t>딤개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>6경 4311조 1275억 7769만</t>
-  </si>
-  <si>
-    <t>히째히째</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
-  </si>
-  <si>
-    <t>4경 6519조 6216억 5112만</t>
-  </si>
-  <si>
-    <t>통뼈1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
-  </si>
-  <si>
-    <t>4경 3909조 8818억 4974만</t>
-  </si>
-  <si>
-    <t>돌로레스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EB%A1%9C%EB%A0%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3경 8262조 6756억 6501만</t>
-  </si>
-  <si>
-    <t>바람의새벽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
-  </si>
-  <si>
-    <t>2경 9221조 4290억 1767만</t>
-  </si>
-  <si>
-    <t>김도유니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2경 2860조 2991억 2314만</t>
-  </si>
-  <si>
-    <t>셀러문</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%9F%AC%EB%AC%B8</t>
-  </si>
-  <si>
-    <t>5150조 9465억 5638만</t>
-  </si>
-  <si>
     <t>라온XR</t>
   </si>
   <si>
@@ -1788,7 +1797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%AA%AC%EC%8A%A4%ED%84%B0</t>
   </si>
   <si>
-    <t>286경 6131조 9215억 6713만</t>
+    <t>296경 3289조 3297억 8201만</t>
   </si>
   <si>
     <t>하잉안파파</t>
@@ -1797,7 +1806,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>203경 7745조 365억 3502만</t>
+    <t>208경 3919조 8798억 5760만</t>
   </si>
   <si>
     <t>코코듀</t>
@@ -1806,7 +1815,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
   </si>
   <si>
-    <t>126경 5282조 4478억 7631만</t>
+    <t>158경 6217조 6777억 9683만</t>
   </si>
   <si>
     <t>타이슨에어랩</t>
@@ -1821,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
   </si>
   <si>
-    <t>59경 5595조 4953억 488만</t>
+    <t>59경 9155조 6081억 4696만</t>
   </si>
   <si>
     <t>미야고</t>
@@ -1839,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
   </si>
   <si>
-    <t>41경 7274조 5523억 4280만</t>
+    <t>42경 6518조 3397억 6778만</t>
   </si>
   <si>
     <t>용보이</t>
@@ -1866,7 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
   </si>
   <si>
-    <t>20경 4395조 1344억 2620만</t>
+    <t>21경 7735조 1571억 7387만</t>
   </si>
   <si>
     <t>도농롱</t>
@@ -1875,7 +1884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%86%8D%EB%A1%B1</t>
   </si>
   <si>
-    <t>12경 4876조 6487억 3656만</t>
+    <t>12경 7181조 2474억 1301만</t>
   </si>
   <si>
     <t>도적왕대현</t>
@@ -1893,7 +1902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%98%B9</t>
   </si>
   <si>
-    <t>9경 977조 6709억 8992만</t>
+    <t>9경 3146조 6570억 6418만</t>
   </si>
   <si>
     <t>반불</t>
@@ -1902,7 +1911,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
   </si>
   <si>
-    <t>8경 3472조 5026억 612만</t>
+    <t>8경 5986조 4420억 3952만</t>
   </si>
   <si>
     <t>혜도로동</t>
@@ -1929,7 +1938,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
   </si>
   <si>
-    <t>6경 7816조 2012억 3122만</t>
+    <t>6경 8299조 1636억 3935만</t>
   </si>
   <si>
     <t>로생</t>
@@ -1938,7 +1947,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
   </si>
   <si>
-    <t>6경 3374조 2748억 8562만</t>
+    <t>6경 4217조 1676억 9573만</t>
+  </si>
+  <si>
+    <t>망치반죽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
+  </si>
+  <si>
+    <t>6경 3149조 8324억 7709만</t>
+  </si>
+  <si>
+    <t>이다연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
+  </si>
+  <si>
+    <t>6경 1188조 6325억 3790만</t>
   </si>
   <si>
     <t>Redwine</t>
@@ -1947,25 +1974,7 @@
     <t>https://mgf.gg/contents/character.php?n=Redwine</t>
   </si>
   <si>
-    <t>6경 356조 6772억 7538만</t>
-  </si>
-  <si>
-    <t>이다연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
-  </si>
-  <si>
-    <t>5경 6854조 4469억 9024만</t>
-  </si>
-  <si>
-    <t>망치반죽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
-  </si>
-  <si>
-    <t>5경 2400조 1176억 6608만</t>
+    <t>6경 934조 9506억 3188만</t>
   </si>
   <si>
     <t>유도로동</t>
@@ -1974,7 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>4경 6465조 8004억 1521만</t>
+    <t>4경 6494조 3848억 5019만</t>
   </si>
   <si>
     <t>메키메렁</t>
@@ -1983,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
   </si>
   <si>
-    <t>3경 7065조 1635억 6998만</t>
+    <t>3경 7844조 1246억 30만</t>
   </si>
   <si>
     <t>그때그아이</t>
@@ -2001,7 +2010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
   </si>
   <si>
-    <t>2경 3340조 8610억 3608만</t>
+    <t>2경 4411조 7473억 3316만</t>
   </si>
   <si>
     <t>꽁꽁얼었다</t>
@@ -2019,7 +2028,7 @@
     <t>https://mgf.gg/contents/character.php?n=spemi</t>
   </si>
   <si>
-    <t>1경 9595조 6640억 3374만</t>
+    <t>2경 286조 4550억 7089만</t>
   </si>
   <si>
     <t>우솝이</t>
@@ -2028,7 +2037,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
   </si>
   <si>
-    <t>1경 8527조 7103억 1989만</t>
+    <t>2경 157조 6090억 3322만</t>
   </si>
   <si>
     <t>막또날드</t>
@@ -2037,7 +2046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
   </si>
   <si>
-    <t>1경 7941조 7388억 2096만</t>
+    <t>1경 8003조 4168억 1713만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2046,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>25경 5968조 5279억 8792만</t>
+    <t>26경 4852조 2614억 1968만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -2055,7 +2064,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>21경 3830조 9069억 3101만</t>
+    <t>21경 4363조 7782억 2245만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2073,7 +2082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>12경 9636조 105억 4675만</t>
+    <t>13경 1932조 6330억 1482만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -2091,7 +2100,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>11경 4318조 9260억 2021만</t>
+    <t>11경 4765조 3141억 9866만</t>
   </si>
   <si>
     <t>약어</t>
@@ -2118,7 +2127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>10경 4273조 612억 9717만</t>
+    <t>10경 5815조 2768억 8824만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -2127,7 +2136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>8경 3545조 3307억 6722만</t>
+    <t>8경 8180조 3418억 7758만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -2136,7 +2145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>5경 5228조 9003억 4099만</t>
+    <t>6경 9105조 2843억 3125만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -2145,7 +2154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 7925조 8043억 3035만</t>
+    <t>2경 8241조 5079억 1888만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -2154,7 +2163,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 7756조 2579억 7515만</t>
+    <t>2경 7759조 6503억 7144만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -2172,7 +2181,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 3490조 8557억 971만</t>
+    <t>2경 5490조 5466억 3494만</t>
+  </si>
+  <si>
+    <t>관리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B4%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2경 5040조 3923억 9599만</t>
   </si>
   <si>
     <t>반가성</t>
@@ -2199,7 +2217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%89%EC%83%88</t>
   </si>
   <si>
-    <t>2경 679조 9420억 5073만</t>
+    <t>2경 1101조 5163억 3714만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -2208,13 +2226,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 9568조 5677억 2556만</t>
+    <t>1경 9583조 9296억 6627만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 8123조 8491억 9227만</t>
+    <t>1경 9206조 5759억 431만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>1경 3924조 4290억 8656만</t>
+  </si>
+  <si>
+    <t>오곤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
+  </si>
+  <si>
+    <t>1경 3778조 4071억 622만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -2223,16 +2259,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 3466조 9661억 2553만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>1경 3352조 5107억 6670만</t>
+    <t>1경 3657조 3032억 2557만</t>
   </si>
   <si>
     <t>라똥이</t>
@@ -2244,22 +2271,22 @@
     <t>1경 3335조 5943억 5779만</t>
   </si>
   <si>
-    <t>오곤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
-  </si>
-  <si>
-    <t>1경 2805조 1072억 4398만</t>
-  </si>
-  <si>
     <t>제로슈가</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 501조 4529억 6137만</t>
+    <t>1경 863조 343억 2047만</t>
+  </si>
+  <si>
+    <t>초식왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%8B%9D%EC%99%95</t>
+  </si>
+  <si>
+    <t>8154조 2007억 5516만</t>
   </si>
   <si>
     <t>러너</t>
@@ -2289,19 +2316,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>1887조 978억 6719만</t>
-  </si>
-  <si>
-    <t>갓겜감별사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>412조 3890억 3560만</t>
+    <t>2209조 1036억 14만</t>
   </si>
 </sst>
 </file>
@@ -2864,66 +2879,66 @@
         <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3154,13 +3169,13 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3171,28 +3186,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3203,16 +3218,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -3221,10 +3236,10 @@
         <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3235,28 +3250,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3267,28 +3282,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3299,28 +3314,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="H9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3331,28 +3346,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3363,28 +3378,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>133</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3395,28 +3410,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3427,28 +3442,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3459,25 +3474,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>150</v>
@@ -3506,13 +3521,13 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3523,28 +3538,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3555,25 +3570,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>164</v>
@@ -3602,10 +3617,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>168</v>
@@ -3634,13 +3649,13 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3651,28 +3666,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3683,25 +3698,25 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>183</v>
@@ -3730,13 +3745,13 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3747,25 +3762,25 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>192</v>
@@ -3794,10 +3809,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>196</v>
@@ -3826,10 +3841,10 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>200</v>
@@ -3858,10 +3873,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>204</v>
@@ -3890,10 +3905,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>208</v>
@@ -3922,10 +3937,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>212</v>
@@ -3954,10 +3969,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>216</v>
@@ -3986,13 +4001,13 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4003,25 +4018,25 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>225</v>
@@ -4070,7 +4085,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4079,7 +4094,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4135,10 +4150,10 @@
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>228</v>
@@ -4170,7 +4185,7 @@
         <v>231</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>232</v>
@@ -4199,10 +4214,10 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>235</v>
@@ -4216,7 +4231,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>32</v>
@@ -4228,13 +4243,13 @@
         <v>236</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>237</v>
@@ -4248,7 +4263,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>238</v>
@@ -4263,10 +4278,10 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>240</v>
@@ -4280,7 +4295,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>241</v>
@@ -4295,10 +4310,10 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>243</v>
@@ -4312,7 +4327,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>244</v>
@@ -4327,10 +4342,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>246</v>
@@ -4344,7 +4359,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>247</v>
@@ -4359,10 +4374,10 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>249</v>
@@ -4376,7 +4391,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>250</v>
@@ -4391,10 +4406,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>252</v>
@@ -4408,7 +4423,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>253</v>
@@ -4423,13 +4438,13 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4440,25 +4455,25 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>259</v>
@@ -4472,7 +4487,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>260</v>
@@ -4487,10 +4502,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>262</v>
@@ -4504,7 +4519,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>263</v>
@@ -4519,10 +4534,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>231</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>265</v>
@@ -4551,10 +4566,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>268</v>
@@ -4568,7 +4583,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>269</v>
@@ -4583,10 +4598,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>258</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>271</v>
@@ -4600,7 +4615,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>272</v>
@@ -4615,10 +4630,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>274</v>
@@ -4647,10 +4662,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>277</v>
@@ -4679,10 +4694,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>280</v>
@@ -4696,7 +4711,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>281</v>
@@ -4711,10 +4726,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>283</v>
@@ -4728,7 +4743,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>284</v>
@@ -4743,10 +4758,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>286</v>
@@ -4775,10 +4790,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>289</v>
@@ -4792,7 +4807,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>290</v>
@@ -4807,10 +4822,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>292</v>
@@ -4839,10 +4854,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>295</v>
@@ -4874,7 +4889,7 @@
         <v>231</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>298</v>
@@ -4903,10 +4918,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>301</v>
@@ -4935,10 +4950,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>304</v>
@@ -4967,10 +4982,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>307</v>
@@ -4999,13 +5014,13 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5019,22 +5034,22 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>314</v>
@@ -5043,8 +5058,40 @@
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5075,6 +5122,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5135,13 +5183,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
@@ -5150,10 +5198,10 @@
         <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5167,25 +5215,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5199,25 +5247,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>255</v>
+        <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5228,28 +5276,28 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5260,28 +5308,28 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5292,28 +5340,28 @@
         <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5324,28 +5372,28 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5356,28 +5404,28 @@
         <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5388,28 +5436,28 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5420,28 +5468,28 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5452,28 +5500,28 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5484,16 +5532,16 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
@@ -5502,10 +5550,10 @@
         <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5516,28 +5564,28 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5551,25 +5599,25 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5580,28 +5628,28 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5612,7 +5660,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>40</v>
@@ -5621,19 +5669,19 @@
         <v>40</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5647,25 +5695,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5679,13 +5727,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
@@ -5694,10 +5742,10 @@
         <v>231</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5708,28 +5756,28 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5740,28 +5788,28 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5775,25 +5823,25 @@
         <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5804,28 +5852,28 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5839,13 +5887,13 @@
         <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -5854,10 +5902,10 @@
         <v>88</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5871,25 +5919,25 @@
         <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>385</v>
+        <v>313</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5903,25 +5951,25 @@
         <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5935,25 +5983,25 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5967,25 +6015,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5999,25 +6047,25 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6031,25 +6079,25 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6060,28 +6108,28 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6180,28 +6228,28 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>255</v>
+        <v>105</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6212,28 +6260,28 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>255</v>
+        <v>176</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6244,28 +6292,28 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6273,31 +6321,31 @@
         <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6305,31 +6353,31 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6337,31 +6385,31 @@
         <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>422</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>422</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>100</v>
+        <v>181</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6369,31 +6417,31 @@
         <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6401,31 +6449,31 @@
         <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6433,31 +6481,31 @@
         <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>433</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6465,31 +6513,31 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6497,31 +6545,31 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6529,31 +6577,31 @@
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>258</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6561,31 +6609,31 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6596,28 +6644,28 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6625,31 +6673,31 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6657,31 +6705,31 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6692,28 +6740,28 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6724,28 +6772,28 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6753,31 +6801,31 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6785,31 +6833,31 @@
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6820,28 +6868,28 @@
         <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6849,31 +6897,31 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>433</v>
+        <v>120</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6884,28 +6932,28 @@
         <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>48</v>
+        <v>476</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>476</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6916,28 +6964,28 @@
         <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>404</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -6948,28 +6996,28 @@
         <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6980,28 +7028,28 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>255</v>
+        <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7012,28 +7060,28 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7044,28 +7092,28 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>177</v>
+        <v>407</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7076,28 +7124,28 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>220</v>
+        <v>394</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -7186,930 +7234,930 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>258</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>172</v>
+        <v>258</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>506</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>506</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>456</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>255</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>231</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>433</v>
+        <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>172</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>556</v>
+        <v>58</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>556</v>
+        <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>231</v>
+        <v>456</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>172</v>
+        <v>407</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>144</v>
+        <v>258</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>404</v>
+        <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>385</v>
+        <v>224</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -8204,25 +8252,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>67</v>
@@ -8236,25 +8284,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>67</v>
@@ -8268,25 +8316,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>67</v>
@@ -8297,28 +8345,28 @@
         <v>59</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>67</v>
@@ -8329,28 +8377,28 @@
         <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>67</v>
@@ -8361,7 +8409,7 @@
         <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>66</v>
@@ -8370,19 +8418,19 @@
         <v>66</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>67</v>
@@ -8393,28 +8441,28 @@
         <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>67</v>
@@ -8425,28 +8473,28 @@
         <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>67</v>
@@ -8457,28 +8505,28 @@
         <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>67</v>
@@ -8489,28 +8537,28 @@
         <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>67</v>
@@ -8521,28 +8569,28 @@
         <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>67</v>
@@ -8553,28 +8601,28 @@
         <v>59</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>67</v>
@@ -8585,28 +8633,28 @@
         <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>67</v>
@@ -8620,25 +8668,25 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>67</v>
@@ -8649,16 +8697,16 @@
         <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -8667,10 +8715,10 @@
         <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>67</v>
@@ -8681,28 +8729,28 @@
         <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>67</v>
@@ -8716,25 +8764,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>67</v>
@@ -8748,25 +8796,25 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>67</v>
@@ -8777,16 +8825,16 @@
         <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -8795,10 +8843,10 @@
         <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>67</v>
@@ -8809,28 +8857,28 @@
         <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>67</v>
@@ -8844,13 +8892,13 @@
         <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -8859,10 +8907,10 @@
         <v>231</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>67</v>
@@ -8873,28 +8921,28 @@
         <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>67</v>
@@ -8908,25 +8956,25 @@
         <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>67</v>
@@ -8940,25 +8988,25 @@
         <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>67</v>
@@ -8972,25 +9020,25 @@
         <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>67</v>
@@ -9004,25 +9052,25 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>67</v>
@@ -9036,25 +9084,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>67</v>
@@ -9068,13 +9116,13 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -9083,10 +9131,10 @@
         <v>231</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>67</v>
@@ -9100,25 +9148,25 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>67</v>
@@ -9129,16 +9177,16 @@
         <v>59</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
@@ -9147,10 +9195,10 @@
         <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>67</v>
@@ -9196,7 +9244,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -9249,25 +9297,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>67</v>
@@ -9281,13 +9329,13 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
@@ -9296,10 +9344,10 @@
         <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>67</v>
@@ -9313,25 +9361,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>67</v>
@@ -9342,28 +9390,28 @@
         <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>67</v>
@@ -9374,28 +9422,28 @@
         <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>67</v>
@@ -9406,16 +9454,16 @@
         <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -9424,10 +9472,10 @@
         <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>67</v>
@@ -9438,28 +9486,28 @@
         <v>68</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>67</v>
@@ -9470,28 +9518,28 @@
         <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>67</v>
@@ -9502,28 +9550,28 @@
         <v>68</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>67</v>
@@ -9534,28 +9582,28 @@
         <v>68</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>67</v>
@@ -9566,28 +9614,28 @@
         <v>68</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>67</v>
@@ -9598,28 +9646,28 @@
         <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>67</v>
@@ -9630,28 +9678,28 @@
         <v>68</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>67</v>
@@ -9665,25 +9713,25 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>67</v>
@@ -9694,28 +9742,28 @@
         <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>67</v>
@@ -9726,28 +9774,28 @@
         <v>68</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>67</v>
@@ -9761,25 +9809,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>67</v>
@@ -9793,25 +9841,25 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>310</v>
+        <v>191</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>67</v>
@@ -9822,28 +9870,28 @@
         <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>220</v>
+        <v>313</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>67</v>
@@ -9854,28 +9902,28 @@
         <v>68</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>729</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>75</v>
+        <v>729</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>310</v>
+        <v>224</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>67</v>
@@ -9889,25 +9937,25 @@
         <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>728</v>
+        <v>75</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>728</v>
+        <v>75</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>220</v>
+        <v>313</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>67</v>
@@ -9918,28 +9966,28 @@
         <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>67</v>
@@ -9953,25 +10001,25 @@
         <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>310</v>
+        <v>224</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>67</v>
@@ -9985,13 +10033,13 @@
         <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -10000,10 +10048,10 @@
         <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>67</v>
@@ -10017,25 +10065,25 @@
         <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>220</v>
+        <v>313</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>67</v>
@@ -10049,25 +10097,25 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>310</v>
+        <v>224</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>67</v>
@@ -10081,25 +10129,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>385</v>
+        <v>313</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>67</v>
@@ -10113,25 +10161,25 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>751</v>
+        <v>313</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>67</v>
@@ -10145,32 +10193,64 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>255</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>755</v>
+        <v>394</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>67</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -10201,6 +10281,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="763">
   <si>
     <t>guild_name</t>
   </si>
@@ -303,7 +303,7 @@
     <t>129</t>
   </si>
   <si>
-    <t>4155경 9968조 5861억 5343만</t>
+    <t>4625경 1520조 1019억 5521만</t>
   </si>
   <si>
     <t>2</t>
@@ -336,7 +336,7 @@
     <t>126</t>
   </si>
   <si>
-    <t>633경 2278조 2171억 6001만</t>
+    <t>645경 7929조 909억 9912만</t>
   </si>
   <si>
     <t>4</t>
@@ -369,7 +369,7 @@
     <t>124</t>
   </si>
   <si>
-    <t>444경 6314조 8526억 2319만</t>
+    <t>449경 6135조 8337억 9287만</t>
   </si>
   <si>
     <t>6</t>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
   </si>
   <si>
-    <t>419경 745조 2321억 2687만</t>
+    <t>447경 3453조 4556억 5806만</t>
   </si>
   <si>
     <t>7</t>
@@ -396,7 +396,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>302경 2653조 7345억 9944만</t>
+    <t>302경 6482조 5589억 696만</t>
   </si>
   <si>
     <t>8</t>
@@ -423,7 +423,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EA%BD%83</t>
   </si>
   <si>
-    <t>147경 5173조 6026억 6674만</t>
+    <t>147경 7115조 8291억 8074만</t>
   </si>
   <si>
     <t>10</t>
@@ -483,7 +483,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>35경 202조 6817억 6084만</t>
+    <t>35경 4110조 1263억 241만</t>
   </si>
   <si>
     <t>14</t>
@@ -522,121 +522,133 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%B0%EA%B0%88</t>
   </si>
   <si>
+    <t>22경 6918조 2458억 857만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>911TurboS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
+  </si>
+  <si>
+    <t>19경 6218조 4556억 7817만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>하싱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
+  </si>
+  <si>
+    <t>17경 823조 8543억 4673만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>권도권</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B6%8C%EB%8F%84%EA%B6%8C</t>
+  </si>
+  <si>
+    <t>14경 9677조 1439억 1944만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>라온U</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8U</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>12경 507조 2384억 2548만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>어쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EC%93%B0</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>11경 9770조 3590억 9667만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>김라이트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>10경 6729조 1013억 4895만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>원탱구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>7경 7001조 5487억 8967만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>명품까칠공주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>7경 4995조 8583억 5181만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>뿔피리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
+  </si>
+  <si>
     <t>119</t>
   </si>
   <si>
-    <t>22경 4392조 8883억 4703만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>911TurboS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
-  </si>
-  <si>
-    <t>19경 6218조 4556억 7817만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>하싱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
-  </si>
-  <si>
-    <t>16경 3990조 6719억 51만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>라온U</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8U</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>12경 507조 2384억 2548만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>어쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EC%93%B0</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>11경 6880조 8854억 1127만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>김라이트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>10경 6729조 1013억 4895만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>명품까칠공주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>7경 2851조 9198억 3933만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>원탱구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>7경 1980조 9591억 8016만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>뿔피리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>7경 1885조 5862억 3242만</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>7경 1952조 9318억 1794만</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
   <si>
     <t>최슬</t>
@@ -648,7 +660,7 @@
     <t>6경 6287조 6681억 6245만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>오이겐</t>
@@ -657,10 +669,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
   </si>
   <si>
-    <t>5경 9039조 7523억 8314만</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>6경 37조 7197억 2873만</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>탄지로네즈</t>
@@ -672,7 +684,7 @@
     <t>4경 5526조 7637억 7168만</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>이솔빠</t>
@@ -681,19 +693,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
   </si>
   <si>
-    <t>3경 1156조 3380억 4689만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>깔지마오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EC%A7%80%EB%A7%88%EC%98%A4</t>
-  </si>
-  <si>
-    <t>2경 9330조 6252억 5962만</t>
+    <t>3경 1615조 7046억 2560만</t>
   </si>
   <si>
     <t>30</t>
@@ -708,7 +708,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 6422조 6374억 5721만</t>
+    <t>1경 7626조 1890억 9733만</t>
   </si>
   <si>
     <t>금은동S2</t>
@@ -717,7 +717,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%EC%9D%80%EB%8F%99S2</t>
   </si>
   <si>
-    <t>1159경 4178조 2780억 3366만</t>
+    <t>128</t>
+  </si>
+  <si>
+    <t>1231경 5075조 7802억 8113만</t>
   </si>
   <si>
     <t>라온JW</t>
@@ -744,7 +747,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
   </si>
   <si>
-    <t>47경 2519조 948억 9725만</t>
+    <t>53경 2077조 911억 9467만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -753,7 +756,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
   </si>
   <si>
-    <t>40경 4265조 2635억 2581만</t>
+    <t>41경 1695조 5797억 61만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -762,7 +765,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>35경 4629조 5145억 676만</t>
+    <t>35경 4648조 3687억 9997만</t>
   </si>
   <si>
     <t>꿈넴</t>
@@ -771,34 +774,34 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%88%EB%84%B4</t>
   </si>
   <si>
-    <t>17경 743조 9428억 5319만</t>
-  </si>
-  <si>
-    <t>쁘덍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%81%98%EB%8D%8D</t>
+    <t>18경 1932조 174억 7133만</t>
+  </si>
+  <si>
+    <t>임홀리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>14경 6329조 6072억 4143만</t>
+  </si>
+  <si>
+    <t>쵸힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%ED%9E%9D</t>
   </si>
   <si>
     <t>13경 9735조 5019억 1699만</t>
   </si>
   <si>
-    <t>임홀리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>13경 8786조 2832억 2611만</t>
-  </si>
-  <si>
     <t>제껴</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>13경 1736조 7234억 9549만</t>
+    <t>13경 2621조 9840억 9730만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -810,7 +813,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>10경 1365조 1930억 8622만</t>
+    <t>10경 7247조 7705억 7370만</t>
   </si>
   <si>
     <t>엘리자베타</t>
@@ -849,6 +852,15 @@
     <t>5경 1934조 9124억 872만</t>
   </si>
   <si>
+    <t>비밀키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
+  </si>
+  <si>
+    <t>5경 1246조 2137억 2761만</t>
+  </si>
+  <si>
     <t>붙잡아</t>
   </si>
   <si>
@@ -864,22 +876,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>4경 7368조 9807억 1240만</t>
-  </si>
-  <si>
-    <t>비밀키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
-  </si>
-  <si>
-    <t>4경 6485조 1235억 1735만</t>
-  </si>
-  <si>
-    <t>슛맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9B%EB%A7%A8</t>
+    <t>4경 7396조 718억 5844만</t>
+  </si>
+  <si>
+    <t>저요S2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EC%9A%94S2</t>
   </si>
   <si>
     <t>3경 4296조 6719억 5656만</t>
@@ -918,7 +921,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 6281조 6067억 4914만</t>
+    <t>2경 6291조 6489억 5095만</t>
   </si>
   <si>
     <t>24년생정춘식</t>
@@ -927,7 +930,7 @@
     <t>https://mgf.gg/contents/character.php?n=24%EB%85%84%EC%83%9D%EC%A0%95%EC%B6%98%EC%8B%9D</t>
   </si>
   <si>
-    <t>2경 4335조 2640억 3242만</t>
+    <t>2경 4378조 5712억 3689만</t>
   </si>
   <si>
     <t>메론맛빵</t>
@@ -945,7 +948,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
   </si>
   <si>
-    <t>1경 7014조 4769억 8334만</t>
+    <t>1경 9561조 2569억 6775만</t>
   </si>
   <si>
     <t>야옹이다</t>
@@ -954,7 +957,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>1경 3779조 5162억 8939만</t>
+    <t>1경 4460조 4049억 9777만</t>
   </si>
   <si>
     <t>출장괴물</t>
@@ -963,7 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>1경 702조 7667억 7739만</t>
+    <t>1경 1354조 1851억 3930만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -975,7 +978,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>9486조 8381억 910만</t>
+    <t>9536조 3266억 700만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -1002,7 +1005,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EC%BD%94%EC%9C%A0</t>
   </si>
   <si>
-    <t>493경 4454조 9046억 4956만</t>
+    <t>495경 3932조 7937억 9195만</t>
   </si>
   <si>
     <t>뚱털</t>
@@ -1020,7 +1023,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
   </si>
   <si>
-    <t>110경 8096조 6017억 7967만</t>
+    <t>122경 7097조 8314억 2190만</t>
   </si>
   <si>
     <t>귤놈펜</t>
@@ -1047,7 +1050,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>36경 1912조 8926억 1964만</t>
+    <t>36경 1943조 204억 9997만</t>
   </si>
   <si>
     <t>게탕</t>
@@ -1056,7 +1059,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
   </si>
   <si>
-    <t>24경 1135조 926억 7989만</t>
+    <t>24경 1695조 5618억 140만</t>
   </si>
   <si>
     <t>쿨쥐돌</t>
@@ -1074,7 +1077,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>22경 8426조 8244억 8301만</t>
+    <t>22경 9311조 6012억 1817만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -1083,7 +1086,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
   </si>
   <si>
-    <t>13경 9741조 2678억 5328만</t>
+    <t>14경 5804조 2953억 5049만</t>
   </si>
   <si>
     <t>류텐</t>
@@ -1092,7 +1095,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
   </si>
   <si>
-    <t>10경 101조 9956억 9608만</t>
+    <t>10경 2996조 1657억 2930만</t>
   </si>
   <si>
     <t>철푸닥</t>
@@ -1101,7 +1104,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%A0%ED%91%B8%EB%8B%A5</t>
   </si>
   <si>
-    <t>8경 4548조 3618억 9707만</t>
+    <t>9경 4267조 2192억 7520만</t>
   </si>
   <si>
     <t>원이유이</t>
@@ -1119,13 +1122,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>4경 518조 6712억 6491만</t>
+    <t>4경 1201조 3066억 5002만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
   </si>
   <si>
-    <t>3경 2140조 5447억 6348만</t>
+    <t>3경 2150조 2700억 8513만</t>
   </si>
   <si>
     <t>ShellyCake</t>
@@ -1134,7 +1137,7 @@
     <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
   </si>
   <si>
-    <t>3경 488조 6677억 1566만</t>
+    <t>3경 514조 7210억 6633만</t>
   </si>
   <si>
     <t>오정구불독</t>
@@ -1161,7 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
   </si>
   <si>
-    <t>1경 8912조 9957억 2621만</t>
+    <t>1경 9461조 7096억 4569만</t>
   </si>
   <si>
     <t>레드플레이어</t>
@@ -1170,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
   </si>
   <si>
-    <t>1경 5493조 9021억 1126만</t>
+    <t>1경 5766조 5005억 5398만</t>
   </si>
   <si>
     <t>검샷</t>
@@ -1206,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
   </si>
   <si>
-    <t>1경 3180조 7052억 299만</t>
+    <t>1경 3187조 9844억 4180만</t>
   </si>
   <si>
     <t>브리또강철중</t>
@@ -1227,7 +1230,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
   </si>
   <si>
-    <t>8746조 8499억 1434만</t>
+    <t>9351조 5589억 7637만</t>
   </si>
   <si>
     <t>l빠다코코낫l</t>
@@ -1260,7 +1263,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>4228조 7124억 6092만</t>
+    <t>4262조 7358억 503만</t>
   </si>
   <si>
     <t>군보</t>
@@ -1269,7 +1272,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>220경 4372조 9701억 1514만</t>
+    <t>222경 2234조 3054억 4455만</t>
   </si>
   <si>
     <t>눙키</t>
@@ -1278,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
   </si>
   <si>
-    <t>139경 8515조 2898억 1653만</t>
+    <t>140경 2941조 5143억 5110만</t>
   </si>
   <si>
     <t>5형사</t>
@@ -1287,7 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>109경 3383조 7982억 841만</t>
+    <t>117경 6144조 2178억 876만</t>
   </si>
   <si>
     <t>총괄한석현</t>
@@ -1305,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>85경 962조 2392억 5904만</t>
+    <t>85경 2892조 1073억 3908만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
@@ -1323,22 +1326,22 @@
     <t>77경 7775조 9712억 658만</t>
   </si>
   <si>
+    <t>또르뱅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
+  </si>
+  <si>
+    <t>71경 5890조 2599억 6913만</t>
+  </si>
+  <si>
     <t>Matter</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>67경 3530조 7017억 5712만</t>
-  </si>
-  <si>
-    <t>또르뱅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
-  </si>
-  <si>
-    <t>65경 6587조 5523억 357만</t>
+    <t>67경 9875조 9509억 8032만</t>
   </si>
   <si>
     <t>원중언니</t>
@@ -1347,7 +1350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>61경 4596조 3831억 1373만</t>
+    <t>61경 5771조 5817억 9562만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1365,7 +1368,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>41경 6888조 5378억 9600만</t>
+    <t>42경 4392조 5503억 576만</t>
   </si>
   <si>
     <t>파퍼</t>
@@ -1374,7 +1377,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>34경 3415조 7933억 865만</t>
+    <t>34경 5435조 770억 172만</t>
   </si>
   <si>
     <t>김나뭉</t>
@@ -1383,7 +1386,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
   </si>
   <si>
-    <t>33경 4686조 8087억 3508만</t>
+    <t>34경 4082조 8383억 6627만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1404,7 +1407,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>19경 6910조 1924억 4865만</t>
+    <t>19경 7043조 4739억 7546만</t>
   </si>
   <si>
     <t>찐맨듀</t>
@@ -1413,7 +1416,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
   </si>
   <si>
-    <t>17경 4273조 517억 842만</t>
+    <t>17경 4851조 7404억 9596만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1431,7 +1434,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
   </si>
   <si>
-    <t>14경 2203조 8270억 7007만</t>
+    <t>15경 1396조 8929억 8493만</t>
   </si>
   <si>
     <t>악경</t>
@@ -1476,7 +1479,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
   </si>
   <si>
-    <t>5경 1038조 7726억 1822만</t>
+    <t>5경 1608조 6947억 4605만</t>
+  </si>
+  <si>
+    <t>돌로레스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EB%A1%9C%EB%A0%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>4경 9014조 2749억 544만</t>
   </si>
   <si>
     <t>통뼈1</t>
@@ -1488,15 +1500,6 @@
     <t>4경 3909조 8818억 4974만</t>
   </si>
   <si>
-    <t>돌로레스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EB%A1%9C%EB%A0%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3경 8262조 6756억 6501만</t>
-  </si>
-  <si>
     <t>바람의새벽</t>
   </si>
   <si>
@@ -1512,7 +1515,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 3501조 4842억 4044만</t>
+    <t>2경 3538조 6291억 9020만</t>
   </si>
   <si>
     <t>셀러문</t>
@@ -1521,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%9F%AC%EB%AC%B8</t>
   </si>
   <si>
-    <t>5150조 9465억 5638만</t>
+    <t>5165조 9513억 7715만</t>
   </si>
   <si>
     <t>해물만두야</t>
@@ -1530,7 +1533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
   </si>
   <si>
-    <t>297경 2867조 5488억 4785만</t>
+    <t>308경 5775조 8635억 934만</t>
   </si>
   <si>
     <t>마옥지</t>
@@ -1539,7 +1542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
   </si>
   <si>
-    <t>289경 6454조 4742억 1360만</t>
+    <t>296경 225조 5202억 8461만</t>
   </si>
   <si>
     <t>캐일리</t>
@@ -1548,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>206경 7530조 1038억 2497만</t>
+    <t>210경 3232조 1464억 2197만</t>
   </si>
   <si>
     <t>설익은앵숭</t>
@@ -1575,7 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>76경 7872조 6949억 9142만</t>
+    <t>78경 3943조 4780억 2568만</t>
   </si>
   <si>
     <t>설묘묘</t>
@@ -1587,6 +1590,15 @@
     <t>48경 834조 2237억 8543만</t>
   </si>
   <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>46경 2528조 6129억 7820만</t>
+  </si>
+  <si>
     <t>루델밍</t>
   </si>
   <si>
@@ -1596,22 +1608,13 @@
     <t>45경 5109조 8480억 2031만</t>
   </si>
   <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>45경 1339조 4074억 6761만</t>
-  </si>
-  <si>
     <t>너굴얌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>43경 1581조 3006억 376만</t>
+    <t>44경 6683조 9426억 1397만</t>
   </si>
   <si>
     <t>싲프</t>
@@ -1620,7 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>37경 8186조 166억 18만</t>
+    <t>37경 8729조 5286억 2732만</t>
   </si>
   <si>
     <t>시드리안</t>
@@ -1647,7 +1650,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>24경 6036조 6491억 3235만</t>
+    <t>24경 9067조 3518억 5만</t>
+  </si>
+  <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>21경 148조 2647억 9744만</t>
   </si>
   <si>
     <t>마덕칠</t>
@@ -1659,15 +1671,6 @@
     <t>21경 127조 2151억 9086만</t>
   </si>
   <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>20경 5514조 8976억 7519만</t>
-  </si>
-  <si>
     <t>설딩</t>
   </si>
   <si>
@@ -1692,7 +1695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
   </si>
   <si>
-    <t>10경 5928조 6370억 6895만</t>
+    <t>10경 6016조 364억 6115만</t>
   </si>
   <si>
     <t>경성2018</t>
@@ -1704,6 +1707,15 @@
     <t>10경 491조 6226억 4381만</t>
   </si>
   <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>7경 4772조 1310억 7065만</t>
+  </si>
+  <si>
     <t>다다익숍</t>
   </si>
   <si>
@@ -1719,15 +1731,6 @@
     <t>7경 2830조 3342억 6906만</t>
   </si>
   <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>6경 5564조 1888억 7889만</t>
-  </si>
-  <si>
     <t>상구얌</t>
   </si>
   <si>
@@ -1761,7 +1764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 8428조 4809억 2430만</t>
+    <t>1경 8768조 6008억 6927만</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -1770,7 +1773,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 6393조 9171억 9294만</t>
+    <t>1경 6685조 4095억 6058만</t>
   </si>
   <si>
     <t>네오메디</t>
@@ -1806,7 +1809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>208경 3919조 8798억 5760만</t>
+    <t>208경 9202조 9405억 3035만</t>
   </si>
   <si>
     <t>코코듀</t>
@@ -1830,7 +1833,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
   </si>
   <si>
-    <t>59경 9155조 6081억 4696만</t>
+    <t>60경 1652조 3816억 8428만</t>
   </si>
   <si>
     <t>미야고</t>
@@ -1848,7 +1851,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
   </si>
   <si>
-    <t>42경 6518조 3397억 6778만</t>
+    <t>45경 4692조 1850억 8339만</t>
   </si>
   <si>
     <t>용보이</t>
@@ -1857,7 +1860,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>38경 2586조 8944억 5397만</t>
+    <t>38경 5125조 8611억 6597만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -1866,7 +1869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
   </si>
   <si>
-    <t>23경 5631조 1681억 611만</t>
+    <t>25경 8669조 8756억 3928만</t>
   </si>
   <si>
     <t>똥갈</t>
@@ -1875,7 +1878,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
   </si>
   <si>
-    <t>21경 7735조 1571억 7387만</t>
+    <t>21경 7863조 2862억 3987만</t>
   </si>
   <si>
     <t>도농롱</t>
@@ -1911,7 +1914,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
   </si>
   <si>
-    <t>8경 5986조 4420억 3952만</t>
+    <t>9경 409조 3130억 3만</t>
   </si>
   <si>
     <t>혜도로동</t>
@@ -1938,7 +1941,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
   </si>
   <si>
-    <t>6경 8299조 1636억 3935만</t>
+    <t>6경 8390조 5281억 8939만</t>
   </si>
   <si>
     <t>로생</t>
@@ -1956,7 +1959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
   </si>
   <si>
-    <t>6경 3149조 8324억 7709만</t>
+    <t>6경 4020조 38억 5737만</t>
   </si>
   <si>
     <t>이다연</t>
@@ -1965,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
   </si>
   <si>
-    <t>6경 1188조 6325억 3790만</t>
+    <t>6경 1530조 3811억 4552만</t>
   </si>
   <si>
     <t>Redwine</t>
@@ -1974,7 +1977,7 @@
     <t>https://mgf.gg/contents/character.php?n=Redwine</t>
   </si>
   <si>
-    <t>6경 934조 9506억 3188만</t>
+    <t>6경 986조 5392억 5124만</t>
   </si>
   <si>
     <t>유도로동</t>
@@ -1983,7 +1986,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>4경 6494조 3848억 5019만</t>
+    <t>4경 6574조 7370억 7426만</t>
   </si>
   <si>
     <t>메키메렁</t>
@@ -1992,7 +1995,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
   </si>
   <si>
-    <t>3경 7844조 1246억 30만</t>
+    <t>3경 7892조 7070억 342만</t>
   </si>
   <si>
     <t>그때그아이</t>
@@ -2010,7 +2013,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
   </si>
   <si>
-    <t>2경 4411조 7473억 3316만</t>
+    <t>2경 4488조 6921억 634만</t>
   </si>
   <si>
     <t>꽁꽁얼었다</t>
@@ -2022,6 +2025,15 @@
     <t>2경 415조 4230억 7944만</t>
   </si>
   <si>
+    <t>우솝이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2경 391조 6561억 765만</t>
+  </si>
+  <si>
     <t>spemi</t>
   </si>
   <si>
@@ -2031,22 +2043,13 @@
     <t>2경 286조 4550억 7089만</t>
   </si>
   <si>
-    <t>우솝이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2경 157조 6090억 3322만</t>
-  </si>
-  <si>
     <t>막또날드</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
   </si>
   <si>
-    <t>1경 8003조 4168억 1713만</t>
+    <t>1경 8603조 1535억 9902만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2064,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>21경 4363조 7782억 2245만</t>
+    <t>21경 4602조 2880억 4838만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2082,7 +2085,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>13경 1932조 6330억 1482만</t>
+    <t>13경 7587조 3965억 6582만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -2100,7 +2103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>11경 4765조 3141억 9866만</t>
+    <t>11경 4888조 1019억 6279만</t>
   </si>
   <si>
     <t>약어</t>
@@ -2127,7 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>10경 5815조 2768억 8824만</t>
+    <t>10경 7242조 7937억 8721만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -2136,7 +2139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>8경 8180조 3418억 7758만</t>
+    <t>9경 3317조 4001억 9160만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -2154,7 +2157,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>2경 8241조 5079억 1888만</t>
+    <t>2경 9699조 1981억 6015만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -2163,7 +2166,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 7759조 6503억 7144만</t>
+    <t>2경 7903조 5183억 9816만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -2181,7 +2184,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 5490조 5466억 3494만</t>
+    <t>2경 5712조 7806억 9494만</t>
   </si>
   <si>
     <t>관리</t>
@@ -2199,7 +2202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>2경 3019조 5691억 5455만</t>
+    <t>2경 3508조 3251억 6396만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -2226,13 +2229,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 9583조 9296억 6627만</t>
+    <t>1경 9797조 8732억 636만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>1경 9206조 5759억 431만</t>
+    <t>1경 9793조 2926억 2205만</t>
+  </si>
+  <si>
+    <t>니뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>1경 4316조 7438억 6414만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2241,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 3924조 4290억 8656만</t>
+    <t>1경 4044조 2010억 4291만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -2253,15 +2265,6 @@
     <t>1경 3778조 4071억 622만</t>
   </si>
   <si>
-    <t>니뚜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
-  </si>
-  <si>
-    <t>1경 3657조 3032억 2557만</t>
-  </si>
-  <si>
     <t>라똥이</t>
   </si>
   <si>
@@ -2277,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 863조 343억 2047만</t>
+    <t>1경 1347조 2778억 8822만</t>
   </si>
   <si>
     <t>초식왕</t>
@@ -2316,7 +2319,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>2209조 1036억 14만</t>
+    <t>2291조 6804억 2795만</t>
   </si>
 </sst>
 </file>
@@ -3588,10 +3591,10 @@
         <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3602,16 +3605,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
@@ -3623,7 +3626,7 @@
         <v>158</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3634,16 +3637,16 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
@@ -3655,7 +3658,7 @@
         <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3666,28 +3669,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3698,28 +3701,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="H21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3730,28 +3733,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3762,28 +3765,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3794,16 +3797,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -3812,10 +3815,10 @@
         <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3826,28 +3829,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3858,25 +3861,25 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>204</v>
@@ -3908,7 +3911,7 @@
         <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>208</v>
@@ -3940,7 +3943,7 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>212</v>
@@ -3972,7 +3975,7 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>216</v>
@@ -4001,10 +4004,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>220</v>
@@ -4153,10 +4156,10 @@
         <v>105</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>106</v>
+        <v>228</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4170,25 +4173,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4202,13 +4205,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -4220,7 +4223,7 @@
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4240,7 +4243,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>137</v>
@@ -4252,7 +4255,7 @@
         <v>143</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4266,13 +4269,13 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -4284,7 +4287,7 @@
         <v>143</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4298,13 +4301,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -4316,7 +4319,7 @@
         <v>149</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4330,13 +4333,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -4348,7 +4351,7 @@
         <v>158</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4362,13 +4365,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
@@ -4377,10 +4380,10 @@
         <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4394,13 +4397,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
@@ -4409,10 +4412,10 @@
         <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4426,13 +4429,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -4444,7 +4447,7 @@
         <v>158</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4458,25 +4461,25 @@
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4490,13 +4493,13 @@
         <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
@@ -4505,10 +4508,10 @@
         <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4522,13 +4525,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -4537,10 +4540,10 @@
         <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4554,25 +4557,25 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4586,25 +4589,25 @@
         <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4618,25 +4621,25 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>258</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4647,28 +4650,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4679,28 +4682,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4711,16 +4714,16 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -4729,10 +4732,10 @@
         <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4743,16 +4746,16 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -4761,10 +4764,10 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4775,16 +4778,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -4793,10 +4796,10 @@
         <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4807,16 +4810,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -4828,7 +4831,7 @@
         <v>224</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4839,16 +4842,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -4857,10 +4860,10 @@
         <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4871,28 +4874,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4903,16 +4906,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -4924,7 +4927,7 @@
         <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4938,13 +4941,13 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
@@ -4956,7 +4959,7 @@
         <v>224</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4970,25 +4973,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>224</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5002,13 +5005,13 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -5020,7 +5023,7 @@
         <v>224</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5034,13 +5037,13 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
@@ -5049,10 +5052,10 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5066,13 +5069,13 @@
         <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
@@ -5081,10 +5084,10 @@
         <v>105</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5183,13 +5186,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
@@ -5201,7 +5204,7 @@
         <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5215,25 +5218,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5247,13 +5250,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -5265,7 +5268,7 @@
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5279,13 +5282,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -5297,7 +5300,7 @@
         <v>138</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5311,13 +5314,13 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -5329,7 +5332,7 @@
         <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5343,13 +5346,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -5361,7 +5364,7 @@
         <v>143</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5375,13 +5378,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -5393,7 +5396,7 @@
         <v>143</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5407,13 +5410,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
@@ -5425,7 +5428,7 @@
         <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5439,13 +5442,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
@@ -5457,7 +5460,7 @@
         <v>158</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5471,25 +5474,25 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5503,25 +5506,25 @@
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5535,13 +5538,13 @@
         <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
@@ -5553,7 +5556,7 @@
         <v>158</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5567,13 +5570,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -5585,7 +5588,7 @@
         <v>158</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5599,13 +5602,13 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -5614,10 +5617,10 @@
         <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5631,13 +5634,13 @@
         <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -5646,10 +5649,10 @@
         <v>148</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5669,19 +5672,19 @@
         <v>40</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>137</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5692,16 +5695,16 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
@@ -5710,10 +5713,10 @@
         <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5724,28 +5727,28 @@
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5756,16 +5759,16 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -5774,10 +5777,10 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5788,16 +5791,16 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -5806,10 +5809,10 @@
         <v>148</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5820,16 +5823,16 @@
         <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -5841,7 +5844,7 @@
         <v>224</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5852,16 +5855,16 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -5873,7 +5876,7 @@
         <v>224</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5884,16 +5887,16 @@
         <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -5902,10 +5905,10 @@
         <v>88</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5916,28 +5919,28 @@
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5948,16 +5951,16 @@
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -5966,10 +5969,10 @@
         <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5983,13 +5986,13 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
@@ -5998,10 +6001,10 @@
         <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6015,25 +6018,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6047,13 +6050,13 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -6062,10 +6065,10 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6079,13 +6082,13 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
@@ -6094,10 +6097,10 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6111,25 +6114,25 @@
         <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6228,13 +6231,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
@@ -6246,7 +6249,7 @@
         <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>51</v>
@@ -6260,25 +6263,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>51</v>
@@ -6292,13 +6295,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -6307,10 +6310,10 @@
         <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>51</v>
@@ -6324,13 +6327,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -6342,7 +6345,7 @@
         <v>143</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>51</v>
@@ -6356,13 +6359,13 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -6374,7 +6377,7 @@
         <v>138</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>51</v>
@@ -6394,19 +6397,19 @@
         <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>137</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>51</v>
@@ -6420,25 +6423,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>51</v>
@@ -6452,25 +6455,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>51</v>
@@ -6484,25 +6487,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>51</v>
@@ -6516,13 +6519,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -6534,7 +6537,7 @@
         <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>51</v>
@@ -6548,13 +6551,13 @@
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
@@ -6566,7 +6569,7 @@
         <v>143</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>51</v>
@@ -6580,25 +6583,25 @@
         <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>149</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>51</v>
@@ -6612,13 +6615,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -6630,7 +6633,7 @@
         <v>143</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>51</v>
@@ -6644,13 +6647,13 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -6662,7 +6665,7 @@
         <v>149</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>51</v>
@@ -6676,25 +6679,25 @@
         <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>149</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>51</v>
@@ -6708,25 +6711,25 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>51</v>
@@ -6737,16 +6740,16 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
@@ -6758,7 +6761,7 @@
         <v>158</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>51</v>
@@ -6769,16 +6772,16 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
@@ -6790,7 +6793,7 @@
         <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>51</v>
@@ -6801,16 +6804,16 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -6822,7 +6825,7 @@
         <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>51</v>
@@ -6833,28 +6836,28 @@
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>51</v>
@@ -6865,16 +6868,16 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -6883,10 +6886,10 @@
         <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>51</v>
@@ -6897,16 +6900,16 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -6915,10 +6918,10 @@
         <v>120</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>51</v>
@@ -6929,28 +6932,28 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>51</v>
@@ -6961,16 +6964,16 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -6979,10 +6982,10 @@
         <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>51</v>
@@ -6993,28 +6996,28 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>51</v>
@@ -7028,25 +7031,25 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>51</v>
@@ -7060,13 +7063,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -7075,10 +7078,10 @@
         <v>148</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>51</v>
@@ -7092,25 +7095,25 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>51</v>
@@ -7124,25 +7127,25 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>51</v>
@@ -7240,25 +7243,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7272,25 +7275,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7304,13 +7307,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -7322,7 +7325,7 @@
         <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7336,13 +7339,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -7354,7 +7357,7 @@
         <v>138</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7368,13 +7371,13 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -7386,7 +7389,7 @@
         <v>143</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7400,13 +7403,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -7418,7 +7421,7 @@
         <v>138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7432,13 +7435,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -7450,7 +7453,7 @@
         <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7464,25 +7467,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>105</v>
+        <v>457</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7496,25 +7499,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>456</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7528,13 +7531,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -7546,7 +7549,7 @@
         <v>143</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7560,13 +7563,13 @@
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
@@ -7578,7 +7581,7 @@
         <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7592,13 +7595,13 @@
         <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
@@ -7610,7 +7613,7 @@
         <v>143</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7624,13 +7627,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -7642,7 +7645,7 @@
         <v>149</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7656,13 +7659,13 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -7674,7 +7677,7 @@
         <v>149</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7688,25 +7691,25 @@
         <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7720,25 +7723,25 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7749,16 +7752,16 @@
         <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
@@ -7770,7 +7773,7 @@
         <v>149</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7781,16 +7784,16 @@
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
@@ -7802,7 +7805,7 @@
         <v>158</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7813,16 +7816,16 @@
         <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -7834,7 +7837,7 @@
         <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7845,16 +7848,16 @@
         <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -7863,10 +7866,10 @@
         <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7877,28 +7880,28 @@
         <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>457</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7909,28 +7912,28 @@
         <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>58</v>
+        <v>561</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>561</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7941,28 +7944,28 @@
         <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>562</v>
+        <v>58</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>562</v>
+        <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>456</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7973,16 +7976,16 @@
         <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -7991,10 +7994,10 @@
         <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8005,28 +8008,28 @@
         <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8040,25 +8043,25 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8072,25 +8075,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>224</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8104,13 +8107,13 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -8122,7 +8125,7 @@
         <v>224</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8136,13 +8139,13 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
@@ -8154,7 +8157,7 @@
         <v>224</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8252,25 +8255,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>67</v>
@@ -8284,13 +8287,13 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
@@ -8302,7 +8305,7 @@
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>67</v>
@@ -8316,13 +8319,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -8334,7 +8337,7 @@
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>67</v>
@@ -8348,13 +8351,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -8366,7 +8369,7 @@
         <v>149</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>67</v>
@@ -8380,13 +8383,13 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -8398,7 +8401,7 @@
         <v>143</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>67</v>
@@ -8418,7 +8421,7 @@
         <v>66</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>137</v>
@@ -8430,7 +8433,7 @@
         <v>138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>67</v>
@@ -8444,13 +8447,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -8462,7 +8465,7 @@
         <v>143</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>67</v>
@@ -8476,25 +8479,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>143</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>67</v>
@@ -8508,25 +8511,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>143</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>67</v>
@@ -8540,13 +8543,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -8558,7 +8561,7 @@
         <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>67</v>
@@ -8572,13 +8575,13 @@
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
@@ -8590,7 +8593,7 @@
         <v>158</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>67</v>
@@ -8604,13 +8607,13 @@
         <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
@@ -8622,7 +8625,7 @@
         <v>158</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>67</v>
@@ -8636,13 +8639,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -8654,7 +8657,7 @@
         <v>158</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>67</v>
@@ -8668,13 +8671,13 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -8686,7 +8689,7 @@
         <v>158</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>67</v>
@@ -8700,13 +8703,13 @@
         <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -8715,10 +8718,10 @@
         <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>67</v>
@@ -8732,13 +8735,13 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -8750,7 +8753,7 @@
         <v>158</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>67</v>
@@ -8761,16 +8764,16 @@
         <v>59</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
@@ -8779,10 +8782,10 @@
         <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>67</v>
@@ -8793,28 +8796,28 @@
         <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>67</v>
@@ -8825,16 +8828,16 @@
         <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -8846,7 +8849,7 @@
         <v>158</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>67</v>
@@ -8857,16 +8860,16 @@
         <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -8875,10 +8878,10 @@
         <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>67</v>
@@ -8889,28 +8892,28 @@
         <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>67</v>
@@ -8921,16 +8924,16 @@
         <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -8939,10 +8942,10 @@
         <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>67</v>
@@ -8953,16 +8956,16 @@
         <v>59</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -8971,10 +8974,10 @@
         <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>67</v>
@@ -8985,16 +8988,16 @@
         <v>59</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -9003,10 +9006,10 @@
         <v>120</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>67</v>
@@ -9017,28 +9020,28 @@
         <v>59</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>67</v>
@@ -9052,13 +9055,13 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
@@ -9067,10 +9070,10 @@
         <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>67</v>
@@ -9084,13 +9087,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -9099,10 +9102,10 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>67</v>
@@ -9116,25 +9119,25 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>67</v>
@@ -9148,25 +9151,25 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>67</v>
@@ -9180,13 +9183,13 @@
         <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
@@ -9198,7 +9201,7 @@
         <v>224</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>67</v>
@@ -9297,25 +9300,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>143</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>67</v>
@@ -9329,13 +9332,13 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
@@ -9347,7 +9350,7 @@
         <v>158</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>67</v>
@@ -9361,13 +9364,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -9379,7 +9382,7 @@
         <v>149</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>67</v>
@@ -9393,13 +9396,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -9411,7 +9414,7 @@
         <v>149</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>67</v>
@@ -9425,25 +9428,25 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>67</v>
@@ -9457,13 +9460,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -9475,7 +9478,7 @@
         <v>158</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>67</v>
@@ -9489,13 +9492,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -9507,7 +9510,7 @@
         <v>158</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>67</v>
@@ -9521,25 +9524,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>158</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>67</v>
@@ -9553,25 +9556,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>67</v>
@@ -9585,13 +9588,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -9600,10 +9603,10 @@
         <v>105</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>67</v>
@@ -9617,13 +9620,13 @@
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
@@ -9632,10 +9635,10 @@
         <v>148</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>67</v>
@@ -9649,13 +9652,13 @@
         <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
@@ -9664,10 +9667,10 @@
         <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>67</v>
@@ -9681,13 +9684,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -9696,10 +9699,10 @@
         <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>67</v>
@@ -9713,13 +9716,13 @@
         <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -9728,10 +9731,10 @@
         <v>105</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>67</v>
@@ -9745,13 +9748,13 @@
         <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -9760,10 +9763,10 @@
         <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>67</v>
@@ -9777,13 +9780,13 @@
         <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -9792,10 +9795,10 @@
         <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>67</v>
@@ -9806,16 +9809,16 @@
         <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
@@ -9827,7 +9830,7 @@
         <v>224</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>67</v>
@@ -9838,16 +9841,16 @@
         <v>68</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
@@ -9856,10 +9859,10 @@
         <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>67</v>
@@ -9870,16 +9873,16 @@
         <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -9888,10 +9891,10 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>67</v>
@@ -9902,16 +9905,16 @@
         <v>68</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -9920,10 +9923,10 @@
         <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>67</v>
@@ -9934,7 +9937,7 @@
         <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>75</v>
@@ -9943,7 +9946,7 @@
         <v>75</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>137</v>
@@ -9952,10 +9955,10 @@
         <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>67</v>
@@ -9966,28 +9969,28 @@
         <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>67</v>
@@ -9998,28 +10001,28 @@
         <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>67</v>
@@ -10030,28 +10033,28 @@
         <v>68</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>224</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>67</v>
@@ -10062,28 +10065,28 @@
         <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>313</v>
+        <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>67</v>
@@ -10097,13 +10100,13 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
@@ -10115,7 +10118,7 @@
         <v>224</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>67</v>
@@ -10129,13 +10132,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -10144,10 +10147,10 @@
         <v>105</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>67</v>
@@ -10161,13 +10164,13 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
@@ -10176,10 +10179,10 @@
         <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>67</v>
@@ -10193,13 +10196,13 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
@@ -10208,10 +10211,10 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>67</v>
@@ -10225,13 +10228,13 @@
         <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
@@ -10240,10 +10243,10 @@
         <v>88</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>67</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="레플리카셋" sheetId="2" r:id="rId2"/>
-    <sheet name="브리또" sheetId="3" r:id="rId3"/>
+    <sheet name="설묘" sheetId="3" r:id="rId3"/>
     <sheet name="리안" sheetId="4" r:id="rId4"/>
-    <sheet name="설묘" sheetId="5" r:id="rId5"/>
+    <sheet name="브리또" sheetId="5" r:id="rId5"/>
     <sheet name="점프킹" sheetId="6" r:id="rId6"/>
     <sheet name="귀여미" sheetId="7" r:id="rId7"/>
     <sheet name="셀린느" sheetId="8" r:id="rId8"/>
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">귀여미!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">레플리카셋!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">리안!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">브리또!$A$1:$J$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">설묘!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">브리또!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">설묘!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">점프킹!$A$1:$J$31</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="760">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 32</t>
   </si>
   <si>
-    <t>43</t>
+    <t>45</t>
   </si>
   <si>
     <t>1위</t>
@@ -108,6 +108,63 @@
     <t>2026.09.20</t>
   </si>
   <si>
+    <t>설묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%84%A4%EB%AC%98</t>
+  </si>
+  <si>
+    <t>Scania 25</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>1089경 6103조 5933억 8200만</t>
+  </si>
+  <si>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+  </si>
+  <si>
+    <t>설익은체리</t>
+  </si>
+  <si>
+    <t>리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>7위</t>
+  </si>
+  <si>
+    <t>26명</t>
+  </si>
+  <si>
+    <t>815경 6691조 2701억 4039만</t>
+  </si>
+  <si>
+    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
+  </si>
+  <si>
+    <t>예습2</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
     <t>브리또</t>
   </si>
   <si>
@@ -117,138 +174,81 @@
     <t>Scania 33</t>
   </si>
   <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>627경 2089조 6861억 9290만</t>
+  </si>
+  <si>
+    <t>대항전 중점 길드, 컨텐츠 열심히 참여하실분! 같이 꾸준히 성장하실 분들 환영! 전투력 랭킹 100등 이상!</t>
+  </si>
+  <si>
+    <t>안데일2</t>
+  </si>
+  <si>
+    <t>점프킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
+  </si>
+  <si>
+    <t>Scania 5</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>1134경 3201조 9049억 7099만</t>
+  </si>
+  <si>
+    <t>뛰어</t>
+  </si>
+  <si>
+    <t>아크메이딩동</t>
+  </si>
+  <si>
+    <t>2026.09.21</t>
+  </si>
+  <si>
+    <t>귀여미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B7%80%EC%97%AC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>Scania 34</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>989경 8536조 5822억 5369만</t>
+  </si>
+  <si>
+    <t>가입 문의는 슈랄</t>
+  </si>
+  <si>
+    <t>슈랄</t>
+  </si>
+  <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
     <t>68</t>
   </si>
   <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>627경 2089조 6861억 9290만</t>
-  </si>
-  <si>
-    <t>대항전 중점 길드, 컨텐츠 열심히 참여하실분! 같이 꾸준히 성장하실 분들 환영! 전투력 랭킹 100등 이상!</t>
-  </si>
-  <si>
-    <t>안데일2</t>
-  </si>
-  <si>
-    <t>리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>5위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>26명</t>
-  </si>
-  <si>
-    <t>815경 6691조 2701억 4039만</t>
-  </si>
-  <si>
-    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
-  </si>
-  <si>
-    <t>예습2</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
-    <t>설묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%84%A4%EB%AC%98</t>
-  </si>
-  <si>
-    <t>Scania 25</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>1089경 6103조 5933억 8200만</t>
-  </si>
-  <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
-  </si>
-  <si>
-    <t>설익은체리</t>
-  </si>
-  <si>
-    <t>점프킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
-  </si>
-  <si>
-    <t>Scania 5</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>1134경 3201조 9049억 7099만</t>
-  </si>
-  <si>
-    <t>뛰어</t>
-  </si>
-  <si>
-    <t>아크메이딩동</t>
-  </si>
-  <si>
-    <t>2026.09.21</t>
-  </si>
-  <si>
-    <t>귀여미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B7%80%EC%97%AC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>Scania 34</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>989경 8536조 5822억 5369만</t>
-  </si>
-  <si>
-    <t>가입 문의는 슈랄</t>
-  </si>
-  <si>
-    <t>슈랄</t>
-  </si>
-  <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>3위</t>
   </si>
   <si>
@@ -303,7 +303,7 @@
     <t>129</t>
   </si>
   <si>
-    <t>4625경 1520조 1019억 5521만</t>
+    <t>4648경 5323조 2659억 1890만</t>
   </si>
   <si>
     <t>2</t>
@@ -339,12 +339,24 @@
     <t>126</t>
   </si>
   <si>
-    <t>645경 7929조 909억 9912만</t>
+    <t>645경 9997조 3244억 1619만</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>꾱환</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
+  </si>
+  <si>
+    <t>473경 1188조 5302억 7047만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>라온A</t>
   </si>
   <si>
@@ -360,7 +372,7 @@
     <t>462경 1350조 5798억 5105만</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>루졔</t>
@@ -369,19 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
   </si>
   <si>
-    <t>453경 5416조 8726억 8324만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>꾱환</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
-  </si>
-  <si>
-    <t>448경 9877조 7513억 5426만</t>
+    <t>453경 8852조 9934억 8203만</t>
   </si>
   <si>
     <t>7</t>
@@ -396,7 +396,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>303경 1310조 1262억 628만</t>
+    <t>303경 2069조 2268억 5242만</t>
   </si>
   <si>
     <t>8</t>
@@ -468,7 +468,7 @@
     <t>122</t>
   </si>
   <si>
-    <t>38경 9298조 5739억 2595만</t>
+    <t>39경 5201조 5822억 3551만</t>
   </si>
   <si>
     <t>13</t>
@@ -525,7 +525,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%B0%EA%B0%88</t>
   </si>
   <si>
-    <t>23경 1243조 7572억 7383만</t>
+    <t>23경 3828조 3785억 7962만</t>
   </si>
   <si>
     <t>17</t>
@@ -567,6 +567,18 @@
     <t>20</t>
   </si>
   <si>
+    <t>라온U</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8U</t>
+  </si>
+  <si>
+    <t>12경 4526조 6909억 8242만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>어쓰</t>
   </si>
   <si>
@@ -582,18 +594,6 @@
     <t>12경 2006조 7135억 837만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>라온U</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8U</t>
-  </si>
-  <si>
-    <t>12경 507조 2384억 2548만</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -630,7 +630,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
   </si>
   <si>
-    <t>7경 7581조 4478억 4108만</t>
+    <t>7경 8121조 8129억 4732만</t>
   </si>
   <si>
     <t>25</t>
@@ -708,7 +708,538 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 7627조 8098억 1162만</t>
+    <t>1경 8543조 1612억 6160만</t>
+  </si>
+  <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>311경 3611조 3158억 5220만</t>
+  </si>
+  <si>
+    <t>마옥지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
+  </si>
+  <si>
+    <t>302경 3995조 3295억 7935만</t>
+  </si>
+  <si>
+    <t>캐일리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>210경 4058조 3294억 9261만</t>
+  </si>
+  <si>
+    <t>설익은앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>105경 4731조 5416억 8730만</t>
+  </si>
+  <si>
+    <t>킹규봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+  </si>
+  <si>
+    <t>85경 8894조 1952억 8378만</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>81경 1380조 9531억 7826만</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>48경 834조 2237억 8543만</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>47경 6048조 4947억 5487만</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>47경 3154조 386억 1171만</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
+  </si>
+  <si>
+    <t>44경 9169조 3146억 906만</t>
+  </si>
+  <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
+  </si>
+  <si>
+    <t>42경 752조 5877억 8211만</t>
+  </si>
+  <si>
+    <t>시드리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>29경 7613조 5062억 2329만</t>
+  </si>
+  <si>
+    <t>셀렘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>29경 4933조 8598억 7698만</t>
+  </si>
+  <si>
+    <t>졸귀탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>25경 4104조 2759억 1048만</t>
+  </si>
+  <si>
+    <t>선콜은차가워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>21경 2055조 3477억 5841만</t>
+  </si>
+  <si>
+    <t>마덕칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>21경 127조 2151억 9086만</t>
+  </si>
+  <si>
+    <t>설딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
+  </si>
+  <si>
+    <t>19경 7396조 2622억 1029만</t>
+  </si>
+  <si>
+    <t>슐아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>13경 5408조 677억 8062만</t>
+  </si>
+  <si>
+    <t>설름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>11경 597조 4783억 2861만</t>
+  </si>
+  <si>
+    <t>경성2018</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
+  </si>
+  <si>
+    <t>10경 491조 6226억 4381만</t>
+  </si>
+  <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>7경 8552조 1769억 220만</t>
+  </si>
+  <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>7경 4772조 1310억 7065만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>7경 2830조 3342억 6906만</t>
+  </si>
+  <si>
+    <t>상구얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
+  </si>
+  <si>
+    <t>5경 4800조 2727억 5361만</t>
+  </si>
+  <si>
+    <t>애봉얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>4경 3134조 5060억 9315만</t>
+  </si>
+  <si>
+    <t>설치는정상인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>2경 420조 1374억 5167만</t>
+  </si>
+  <si>
+    <t>설콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>1경 8903조 4165억 5232만</t>
+  </si>
+  <si>
+    <t>읏코츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1경 7082조 8310억 4105만</t>
+  </si>
+  <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>1경 4431조 7171억 1764만</t>
+  </si>
+  <si>
+    <t>군보</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
+  </si>
+  <si>
+    <t>226경 3624조 9900억 8707만</t>
+  </si>
+  <si>
+    <t>눙키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
+  </si>
+  <si>
+    <t>153경 8340조 6596억 4671만</t>
+  </si>
+  <si>
+    <t>5형사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
+  </si>
+  <si>
+    <t>122경 2058조 9957억 4528만</t>
+  </si>
+  <si>
+    <t>심천</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
+  </si>
+  <si>
+    <t>96경 1288조 1360억 5581만</t>
+  </si>
+  <si>
+    <t>총괄한석현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%9D%EA%B4%84%ED%95%9C%EC%84%9D%ED%98%84</t>
+  </si>
+  <si>
+    <t>88경 97조 324억 8358만</t>
+  </si>
+  <si>
+    <t>또르뱅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
+  </si>
+  <si>
+    <t>87경 7235조 1631억 5842만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
+  </si>
+  <si>
+    <t>86경 50조 568억 3960만</t>
+  </si>
+  <si>
+    <t>혁수킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
+  </si>
+  <si>
+    <t>77경 7775조 9712억 658만</t>
+  </si>
+  <si>
+    <t>Matter</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Matter</t>
+  </si>
+  <si>
+    <t>76경 1803조 128억 83만</t>
+  </si>
+  <si>
+    <t>원중언니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
+  </si>
+  <si>
+    <t>63경 2623조 7103억 8416만</t>
+  </si>
+  <si>
+    <t>가을호떡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%84%ED%98%B8%EB%96%A1</t>
+  </si>
+  <si>
+    <t>55경 5523조 6632억 6782만</t>
+  </si>
+  <si>
+    <t>냠규리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>42경 4596조 4295억 7642만</t>
+  </si>
+  <si>
+    <t>김나뭉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
+  </si>
+  <si>
+    <t>38경 2353조 9516억 8252만</t>
+  </si>
+  <si>
+    <t>파퍼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
+  </si>
+  <si>
+    <t>34경 7977조 2499억 5197만</t>
+  </si>
+  <si>
+    <t>Hoood</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Hoood</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>30경 6712억 4376만</t>
+  </si>
+  <si>
+    <t>껌정색</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
+  </si>
+  <si>
+    <t>20경 6481조 3192억 6128만</t>
+  </si>
+  <si>
+    <t>찐맨듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
+  </si>
+  <si>
+    <t>19경 3852조 9498억 8492만</t>
+  </si>
+  <si>
+    <t>다끝남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
+  </si>
+  <si>
+    <t>15경 6963조 5144억 170만</t>
+  </si>
+  <si>
+    <t>이삼2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
+  </si>
+  <si>
+    <t>15경 1396조 8929억 8493만</t>
+  </si>
+  <si>
+    <t>악경</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
+  </si>
+  <si>
+    <t>10경 2388조 6776억 2691만</t>
+  </si>
+  <si>
+    <t>Rahee</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
+  </si>
+  <si>
+    <t>8경 4278조 2698억 8627만</t>
+  </si>
+  <si>
+    <t>고먀츠나나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
+  </si>
+  <si>
+    <t>7경 7681조 4092억 2482만</t>
+  </si>
+  <si>
+    <t>딤개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>6경 8742조 2511억 982만</t>
+  </si>
+  <si>
+    <t>히째히째</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
+  </si>
+  <si>
+    <t>5경 4655조 9844억 8425만</t>
+  </si>
+  <si>
+    <t>돌로레스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EB%A1%9C%EB%A0%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>4경 9014조 2749억 544만</t>
+  </si>
+  <si>
+    <t>통뼈1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
+  </si>
+  <si>
+    <t>4경 5564조 7041억 204만</t>
+  </si>
+  <si>
+    <t>바람의새벽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
+  </si>
+  <si>
+    <t>3경 655조 4594억 5626만</t>
+  </si>
+  <si>
+    <t>김도유니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2경 4606조 8331억 956만</t>
+  </si>
+  <si>
+    <t>셀러문</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%9F%AC%EB%AC%B8</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>5329조 7290억 7632만</t>
   </si>
   <si>
     <t>강서구도적</t>
@@ -744,7 +1275,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
   </si>
   <si>
-    <t>126경 563조 4862억 9383만</t>
+    <t>128경 8366조 7732억 1557만</t>
   </si>
   <si>
     <t>귤놈펜</t>
@@ -762,7 +1293,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
   </si>
   <si>
-    <t>36경 6780조 1538억 5267만</t>
+    <t>36경 6947조 8154억 6849만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -780,7 +1311,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
   </si>
   <si>
-    <t>26경 7921조 9695억 7666만</t>
+    <t>26경 7930조 4439억 3182만</t>
   </si>
   <si>
     <t>쿨쥐돌</t>
@@ -789,7 +1320,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
   </si>
   <si>
-    <t>25경 3856조 2804억 3225만</t>
+    <t>25경 7681조 8225억 532만</t>
   </si>
   <si>
     <t>긴나라</t>
@@ -798,7 +1329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>22경 9311조 6012억 1817만</t>
+    <t>25경 1558조 8648억 7196만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -807,7 +1338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
   </si>
   <si>
-    <t>15경 549조 4091억 4581만</t>
+    <t>15경 3242조 2461억 2069만</t>
   </si>
   <si>
     <t>류텐</t>
@@ -843,7 +1374,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>4경 1267조 6936억 8414만</t>
+    <t>4경 1280조 7306억 4782만</t>
   </si>
   <si>
     <t>무명장수</t>
@@ -858,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
   </si>
   <si>
-    <t>3경 7480조 113억 7919만</t>
+    <t>3경 7517조 5238억 1395만</t>
   </si>
   <si>
     <t>ShellyCake</t>
@@ -876,9 +1407,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
     <t>2경 5391조 9478억 8415만</t>
   </si>
   <si>
@@ -897,45 +1425,45 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
   </si>
   <si>
+    <t>2경 517조 7707억 1039만</t>
+  </si>
+  <si>
+    <t>검샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
+  </si>
+  <si>
+    <t>1경 6350조 814억 826만</t>
+  </si>
+  <si>
+    <t>레드플레이어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
+  </si>
+  <si>
+    <t>1경 6041조 8436억 8150만</t>
+  </si>
+  <si>
+    <t>주하사랑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
+  </si>
+  <si>
+    <t>1경 5163조 9079억 2710만</t>
+  </si>
+  <si>
+    <t>장아린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
+  </si>
+  <si>
     <t>115</t>
   </si>
   <si>
-    <t>2경 211조 6113억 773만</t>
-  </si>
-  <si>
-    <t>레드플레이어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
-  </si>
-  <si>
-    <t>1경 5766조 5005억 5398만</t>
-  </si>
-  <si>
-    <t>검샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
-  </si>
-  <si>
-    <t>1경 5390조 9404억 6035만</t>
-  </si>
-  <si>
-    <t>주하사랑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
-  </si>
-  <si>
-    <t>1경 5163조 9079억 2710만</t>
-  </si>
-  <si>
-    <t>장아린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%95%84%EB%A6%B0</t>
-  </si>
-  <si>
     <t>1경 3399조 7861억 7097만</t>
   </si>
   <si>
@@ -945,9 +1473,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%ACa</t>
   </si>
   <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
     <t>1경 3288조 2411억 4294만</t>
   </si>
   <si>
@@ -957,10 +1482,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A6%AC%EB%98%90%EA%B0%95%EC%B2%A0%EC%A4%91</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>1경 177조 670억 8640만</t>
+    <t>1경 2238조 8084억 982만</t>
   </si>
   <si>
     <t>꼬기갓</t>
@@ -969,7 +1491,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
   </si>
   <si>
-    <t>9704조 8434억 6879만</t>
+    <t>9832조 2838억 3594만</t>
   </si>
   <si>
     <t>l빠다코코낫l</t>
@@ -978,19 +1500,7 @@
     <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
   </si>
   <si>
-    <t>8491조 2943억 8606만</t>
-  </si>
-  <si>
-    <t>리광춘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EA%B4%91%EC%B6%98</t>
-  </si>
-  <si>
-    <t>6546조 9192억 3489만</t>
-  </si>
-  <si>
-    <t>31</t>
+    <t>8736조 7457억 7565만</t>
   </si>
   <si>
     <t>어꼬</t>
@@ -999,534 +1509,12 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EA%BC%AC</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
     <t>4262조 7358억 503만</t>
   </si>
   <si>
-    <t>군보</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
-  </si>
-  <si>
-    <t>226경 3624조 9900억 8707만</t>
-  </si>
-  <si>
-    <t>눙키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
-  </si>
-  <si>
-    <t>153경 8340조 6596억 4671만</t>
-  </si>
-  <si>
-    <t>5형사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
-  </si>
-  <si>
-    <t>119경 8810조 3780억 2099만</t>
-  </si>
-  <si>
-    <t>총괄한석현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%9D%EA%B4%84%ED%95%9C%EC%84%9D%ED%98%84</t>
-  </si>
-  <si>
-    <t>88경 97조 324억 8358만</t>
-  </si>
-  <si>
-    <t>심천</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
-  </si>
-  <si>
-    <t>87경 7682조 6574억 1443만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
-  </si>
-  <si>
-    <t>86경 50조 568억 3960만</t>
-  </si>
-  <si>
-    <t>혁수킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
-  </si>
-  <si>
-    <t>77경 7775조 9712억 658만</t>
-  </si>
-  <si>
-    <t>Matter</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Matter</t>
-  </si>
-  <si>
-    <t>76경 1606조 8983억 5176만</t>
-  </si>
-  <si>
-    <t>또르뱅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
-  </si>
-  <si>
-    <t>75경 3464조 514억 1481만</t>
-  </si>
-  <si>
-    <t>원중언니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
-  </si>
-  <si>
-    <t>63경 2623조 7103억 8416만</t>
-  </si>
-  <si>
-    <t>가을호떡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%84%ED%98%B8%EB%96%A1</t>
-  </si>
-  <si>
-    <t>55경 5523조 6632억 6782만</t>
-  </si>
-  <si>
-    <t>냠규리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>42경 4596조 4295억 7642만</t>
-  </si>
-  <si>
-    <t>김나뭉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
-  </si>
-  <si>
-    <t>36경 7909조 9998억 6145만</t>
-  </si>
-  <si>
-    <t>파퍼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
-  </si>
-  <si>
-    <t>34경 5592조 6400억 3832만</t>
-  </si>
-  <si>
-    <t>Hoood</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Hoood</t>
-  </si>
-  <si>
-    <t>30경 6712억 4376만</t>
-  </si>
-  <si>
-    <t>껌정색</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>20경 432조 4679억 2026만</t>
-  </si>
-  <si>
-    <t>찐맨듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
-  </si>
-  <si>
-    <t>17경 6019조 501억 4616만</t>
-  </si>
-  <si>
-    <t>다끝남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
-  </si>
-  <si>
-    <t>15경 6803조 9052억 3027만</t>
-  </si>
-  <si>
-    <t>이삼2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
-  </si>
-  <si>
-    <t>15경 1396조 8929억 8493만</t>
-  </si>
-  <si>
-    <t>악경</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B2%BD</t>
-  </si>
-  <si>
-    <t>10경 2388조 6776억 2691만</t>
-  </si>
-  <si>
-    <t>Rahee</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
-  </si>
-  <si>
-    <t>8경 4278조 2698억 8627만</t>
-  </si>
-  <si>
-    <t>고먀츠나나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
-  </si>
-  <si>
-    <t>7경 7681조 4092억 2482만</t>
-  </si>
-  <si>
-    <t>딤개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>6경 8742조 2511억 982만</t>
-  </si>
-  <si>
-    <t>히째히째</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
-  </si>
-  <si>
-    <t>5경 4655조 9844억 8425만</t>
-  </si>
-  <si>
-    <t>돌로레스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EB%A1%9C%EB%A0%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>4경 9014조 2749억 544만</t>
-  </si>
-  <si>
-    <t>통뼈1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
-  </si>
-  <si>
-    <t>4경 3909조 8818억 4974만</t>
-  </si>
-  <si>
-    <t>바람의새벽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
-  </si>
-  <si>
-    <t>2경 9221조 4290억 1767만</t>
-  </si>
-  <si>
-    <t>김도유니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2경 3599조 6934억 5371만</t>
-  </si>
-  <si>
-    <t>셀러문</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%9F%AC%EB%AC%B8</t>
-  </si>
-  <si>
-    <t>5219조 293억 2684만</t>
-  </si>
-  <si>
-    <t>해물만두야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
-  </si>
-  <si>
-    <t>308경 7498조 5371억 8363만</t>
-  </si>
-  <si>
-    <t>마옥지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
-  </si>
-  <si>
-    <t>302경 3995조 3295억 7935만</t>
-  </si>
-  <si>
-    <t>캐일리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>210경 4058조 3294억 9261만</t>
-  </si>
-  <si>
-    <t>설익은앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>105경 4731조 5416억 8730만</t>
-  </si>
-  <si>
-    <t>킹규봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
-  </si>
-  <si>
-    <t>85경 8894조 1952억 8378만</t>
-  </si>
-  <si>
-    <t>설함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>81경 1380조 9531억 7826만</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>48경 834조 2237억 8543만</t>
-  </si>
-  <si>
-    <t>루델밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>47경 6048조 4947억 5487만</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>46경 8028조 2449억 5700만</t>
-  </si>
-  <si>
-    <t>너굴얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
-  </si>
-  <si>
-    <t>44경 9169조 3146억 906만</t>
-  </si>
-  <si>
-    <t>싲프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
-  </si>
-  <si>
-    <t>42경 752조 5877억 8211만</t>
-  </si>
-  <si>
-    <t>시드리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>29경 7613조 5062억 2329만</t>
-  </si>
-  <si>
-    <t>셀렘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>29경 4933조 8598억 7698만</t>
-  </si>
-  <si>
-    <t>졸귀탱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>25경 284조 3598억 3895만</t>
-  </si>
-  <si>
-    <t>선콜은차가워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>21경 436조 3705억 8354만</t>
-  </si>
-  <si>
-    <t>마덕칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>21경 127조 2151억 9086만</t>
-  </si>
-  <si>
-    <t>설딩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
-  </si>
-  <si>
-    <t>19경 7396조 2622억 1029만</t>
-  </si>
-  <si>
-    <t>슐아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>13경 5408조 677억 8062만</t>
-  </si>
-  <si>
-    <t>설름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%A6%84</t>
-  </si>
-  <si>
-    <t>10경 8305조 4880억 3327만</t>
-  </si>
-  <si>
-    <t>경성2018</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
-  </si>
-  <si>
-    <t>10경 491조 6226억 4381만</t>
-  </si>
-  <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>7경 4948조 4629억 103만</t>
-  </si>
-  <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>7경 4772조 1310억 7065만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>7경 2830조 3342억 6906만</t>
-  </si>
-  <si>
-    <t>상구얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B5%AC%EC%96%8C</t>
-  </si>
-  <si>
-    <t>5경 4800조 2727억 5361만</t>
-  </si>
-  <si>
-    <t>애봉얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%B4%89%EC%96%8C</t>
-  </si>
-  <si>
-    <t>4경 3134조 5060억 9315만</t>
-  </si>
-  <si>
-    <t>설치는정상인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>2경 420조 1374억 5167만</t>
-  </si>
-  <si>
-    <t>설콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>1경 8903조 4165억 5232만</t>
-  </si>
-  <si>
-    <t>읏코츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>1경 6732조 697억 2331만</t>
-  </si>
-  <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>1경 4431조 7171억 1764만</t>
-  </si>
-  <si>
     <t>라온XR</t>
   </si>
   <si>
@@ -1551,7 +1539,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
   </si>
   <si>
-    <t>213경 4267조 5205억 8441만</t>
+    <t>215경 1594조 5464억 4871만</t>
   </si>
   <si>
     <t>하잉안파파</t>
@@ -1560,7 +1548,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>210경 671조 6890억 4287만</t>
+    <t>210경 967조 4017억 9820만</t>
   </si>
   <si>
     <t>미야고</t>
@@ -1584,7 +1572,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
   </si>
   <si>
-    <t>61경 5366조 8307억 6660만</t>
+    <t>61경 8131조 881억 2194만</t>
   </si>
   <si>
     <t>캔드릭</t>
@@ -1602,7 +1590,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>40경 19조 3971억 4625만</t>
+    <t>40경 352조 4944억 4741만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -1611,7 +1599,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
   </si>
   <si>
-    <t>27경 975조 2443억 7330만</t>
+    <t>27경 1636조 7187억 4799만</t>
   </si>
   <si>
     <t>똥갈</t>
@@ -1629,7 +1617,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%86%8D%EB%A1%B1</t>
   </si>
   <si>
-    <t>12경 8677조 1386억 5242만</t>
+    <t>12경 8749조 1994억 7023만</t>
   </si>
   <si>
     <t>도적왕대현</t>
@@ -1647,7 +1635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
   </si>
   <si>
-    <t>9경 6991조 1095억 6550만</t>
+    <t>9경 9011조 3697억 78만</t>
   </si>
   <si>
     <t>힐옹</t>
@@ -1656,7 +1644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%98%B9</t>
   </si>
   <si>
-    <t>9경 3146조 6570억 6418만</t>
+    <t>9경 6843조 1983억 2212만</t>
   </si>
   <si>
     <t>혜도로동</t>
@@ -1665,7 +1653,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>8경 1479조 6697억 5153만</t>
+    <t>8경 3075조 7622억 5434만</t>
+  </si>
+  <si>
+    <t>조명준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
+  </si>
+  <si>
+    <t>7경 4452조 6227억 9543만</t>
   </si>
   <si>
     <t>로생</t>
@@ -1674,7 +1671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
   </si>
   <si>
-    <t>7경 3227조 7292억 4635만</t>
+    <t>7경 3234조 6573억 3434만</t>
   </si>
   <si>
     <t>붕어줍</t>
@@ -1683,16 +1680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EC%96%B4%EC%A4%8D</t>
   </si>
   <si>
-    <t>7경 2005조 2221억 3118만</t>
-  </si>
-  <si>
-    <t>조명준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
-  </si>
-  <si>
-    <t>6경 8442조 8365억 2470만</t>
+    <t>7경 2239조 6627억 8531만</t>
   </si>
   <si>
     <t>이다연</t>
@@ -1701,7 +1689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
   </si>
   <si>
-    <t>6경 6850조 5020억 5856만</t>
+    <t>7경 486조 1461억 6119만</t>
   </si>
   <si>
     <t>망치반죽</t>
@@ -1710,7 +1698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
   </si>
   <si>
-    <t>6경 5735조 1037억 5946만</t>
+    <t>6경 9477조 303억 2394만</t>
   </si>
   <si>
     <t>Redwine</t>
@@ -1719,7 +1707,7 @@
     <t>https://mgf.gg/contents/character.php?n=Redwine</t>
   </si>
   <si>
-    <t>6경 986조 5392억 5124만</t>
+    <t>6경 1926조 7636억 249만</t>
   </si>
   <si>
     <t>유도로동</t>
@@ -1728,7 +1716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>4경 6616조 5737억 5703만</t>
+    <t>5경 174조 4078억 9299만</t>
   </si>
   <si>
     <t>메키메렁</t>
@@ -1746,7 +1734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>3경 1551조 4991억 3144만</t>
+    <t>3경 2163조 8947억 9574만</t>
   </si>
   <si>
     <t>루빙</t>
@@ -1755,7 +1743,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
   </si>
   <si>
-    <t>2경 5401조 216억 7335만</t>
+    <t>2경 5444조 8662억 4631만</t>
+  </si>
+  <si>
+    <t>spemi</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=spemi</t>
+  </si>
+  <si>
+    <t>2경 2494조 3407억 8152만</t>
   </si>
   <si>
     <t>우솝이</t>
@@ -1764,16 +1761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
   </si>
   <si>
-    <t>2경 1570조 9394억 6206만</t>
-  </si>
-  <si>
-    <t>spemi</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=spemi</t>
-  </si>
-  <si>
-    <t>2경 1035조 7156억 4787만</t>
+    <t>2경 1610조 9921억 4920만</t>
   </si>
   <si>
     <t>꽁꽁얼었다</t>
@@ -1818,7 +1806,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
   </si>
   <si>
-    <t>55경 950조 2776억 8244만</t>
+    <t>55경 1290조 9371억 566만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -1872,7 +1860,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>13경 2621조 9840억 9730만</t>
+    <t>13경 2761조 7251억 22만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -1893,6 +1881,15 @@
     <t>6경 9851조 7013억 3773만</t>
   </si>
   <si>
+    <t>어흥이다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>5경 8932조 2700억 5만</t>
+  </si>
+  <si>
     <t>홍시마로</t>
   </si>
   <si>
@@ -1902,15 +1899,6 @@
     <t>5경 7079조 9150억 7595만</t>
   </si>
   <si>
-    <t>어흥이다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>5경 6577조 3913억 9278만</t>
-  </si>
-  <si>
     <t>우꼬쨩</t>
   </si>
   <si>
@@ -1971,7 +1959,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
   </si>
   <si>
-    <t>2경 9378조 3887억 8430만</t>
+    <t>2경 9562조 5399억 1119만</t>
   </si>
   <si>
     <t>득츈</t>
@@ -1980,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
   </si>
   <si>
-    <t>2경 8003조 8450억 709만</t>
+    <t>2경 8013조 5886억 7300만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -1992,6 +1980,15 @@
     <t>2경 7597조 4601억 8690만</t>
   </si>
   <si>
+    <t>메론맛빵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
+  </si>
+  <si>
+    <t>2경 4452조 445억 7837만</t>
+  </si>
+  <si>
     <t>24년생정춘식</t>
   </si>
   <si>
@@ -2001,15 +1998,6 @@
     <t>2경 4378조 5712억 3689만</t>
   </si>
   <si>
-    <t>메론맛빵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
-  </si>
-  <si>
-    <t>2경 4061조 7847억 5872만</t>
-  </si>
-  <si>
     <t>시프님</t>
   </si>
   <si>
@@ -2034,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>1경 2217조 7789억 7437만</t>
+    <t>1경 2245조 7595억 8282만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -2043,7 +2031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>1경 793조 549억 6788만</t>
+    <t>1경 870조 2545억 6547만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -2070,7 +2058,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>21경 4602조 2880억 4838만</t>
+    <t>21경 5023조 1197억 311만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2079,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>15경 2682조 6704억 9270만</t>
+    <t>15경 2740조 864억 2274만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -2088,7 +2076,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>13경 7601조 2024억 355만</t>
+    <t>13경 9512조 8823억 8446만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -2106,7 +2094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>11경 6279조 9856억 8196만</t>
+    <t>11경 6482조 8557억 6748만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -2124,7 +2112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>11경 291조 4675억 896만</t>
+    <t>11경 2257조 8652억 5666만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -2133,7 +2121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>10경 8325조 7043억 8844만</t>
+    <t>10경 9321조 7447억 9515만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -2160,7 +2148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>3경 3178조 9781억 8699만</t>
+    <t>3경 3613조 4434억 8483만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -2169,7 +2157,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 8127조 9067억 203만</t>
+    <t>2경 9308조 5229억 9652만</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>2경 7146조 7225억 8149만</t>
   </si>
   <si>
     <t>오픈톡쌀숭E</t>
@@ -2181,15 +2178,6 @@
     <t>2경 6890조 4852억 886만</t>
   </si>
   <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>2경 5712조 7806억 9494만</t>
-  </si>
-  <si>
     <t>관리</t>
   </si>
   <si>
@@ -2205,7 +2193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>2경 3508조 3251억 6396만</t>
+    <t>2경 3735조 8934억 1056만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -2226,19 +2214,19 @@
     <t>2경 1323조 7490억 7475만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>2경 124조 7436억 1832만</t>
+  </si>
+  <si>
     <t>망겜감별사</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 9979조 9674억 5590만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>1경 9793조 2926억 2205만</t>
+    <t>1경 9989조 585억 9209만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -2247,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 5669조 3241억 5407만</t>
+    <t>1경 5773조 8073억 4323만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2256,7 +2244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 4122조 3481억 9881만</t>
+    <t>1경 4208조 4830억 3846만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -2283,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 1353조 1986억 6676만</t>
+    <t>1경 1436조 1287억 6107만</t>
   </si>
   <si>
     <t>초식왕</t>
@@ -2292,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%8B%9D%EC%99%95</t>
   </si>
   <si>
-    <t>8180조 6118억 3210만</t>
+    <t>9474조 4834억 1025만</t>
   </si>
   <si>
     <t>러너</t>
@@ -2301,7 +2289,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>7189조 6942억 6343만</t>
+    <t>7346조 6925억 44만</t>
   </si>
   <si>
     <t>해찬나래</t>
@@ -2322,7 +2310,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>2292조 5167억 1606만</t>
+    <t>2294조 3189억 3545만</t>
   </si>
 </sst>
 </file>
@@ -2803,10 +2791,10 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>30</v>
@@ -2847,48 +2835,48 @@
         <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>30</v>
@@ -3207,13 +3195,13 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3224,25 +3212,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>112</v>
@@ -3271,10 +3259,10 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>116</v>
@@ -3527,7 +3515,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>150</v>
@@ -3559,7 +3547,7 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>159</v>
@@ -3623,7 +3611,7 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>159</v>
@@ -3655,7 +3643,7 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>159</v>
@@ -3687,7 +3675,7 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>159</v>
@@ -3719,13 +3707,13 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3736,25 +3724,25 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>186</v>
@@ -3786,7 +3774,7 @@
         <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>190</v>
@@ -3847,7 +3835,7 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>194</v>
@@ -3911,10 +3899,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>208</v>
@@ -3943,10 +3931,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>212</v>
@@ -3975,10 +3963,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>216</v>
@@ -4007,7 +3995,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>194</v>
@@ -4039,7 +4027,7 @@
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>224</v>
@@ -4091,7 +4079,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4156,13 +4144,13 @@
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>228</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4176,25 +4164,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4208,25 +4196,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4240,25 +4228,25 @@
         <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4269,28 +4257,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4304,25 +4292,25 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4336,25 +4324,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4368,25 +4356,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4400,25 +4388,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>253</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4432,25 +4420,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4464,25 +4452,25 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4496,25 +4484,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4528,25 +4516,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4560,25 +4548,25 @@
         <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4592,25 +4580,25 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4624,25 +4612,25 @@
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4656,25 +4644,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4688,25 +4676,25 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4720,25 +4708,25 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>281</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4752,25 +4740,25 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4781,28 +4769,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4816,25 +4804,25 @@
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>253</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4848,22 +4836,22 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>293</v>
+        <v>33</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>293</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>294</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>295</v>
@@ -4895,7 +4883,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>298</v>
@@ -4924,13 +4912,13 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>301</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>288</v>
+        <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4944,22 +4932,22 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>304</v>
+        <v>184</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>288</v>
+        <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>305</v>
@@ -4988,13 +4976,13 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>228</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5008,25 +4996,25 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5040,96 +5028,32 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J32"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5160,8 +5084,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
-    <hyperlink ref="E32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5222,28 +5144,28 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5254,13 +5176,13 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
@@ -5272,10 +5194,10 @@
         <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5286,13 +5208,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -5304,10 +5226,10 @@
         <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5318,28 +5240,28 @@
         <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5347,31 +5269,31 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5382,28 +5304,28 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5414,28 +5336,28 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>342</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>342</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -5446,28 +5368,28 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5478,28 +5400,28 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5510,13 +5432,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -5528,10 +5450,10 @@
         <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5542,28 +5464,28 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5574,28 +5496,28 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5606,28 +5528,28 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5638,28 +5560,28 @@
         <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -5670,28 +5592,28 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>281</v>
+        <v>358</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -5702,28 +5624,28 @@
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>371</v>
+        <v>253</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -5734,28 +5656,28 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -5766,13 +5688,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
@@ -5784,10 +5706,10 @@
         <v>159</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -5798,13 +5720,13 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -5816,10 +5738,10 @@
         <v>159</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5830,13 +5752,13 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
@@ -5848,10 +5770,10 @@
         <v>203</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -5859,16 +5781,16 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -5880,10 +5802,10 @@
         <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5894,13 +5816,13 @@
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -5912,10 +5834,10 @@
         <v>203</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -5926,28 +5848,28 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>281</v>
+        <v>358</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -5958,13 +5880,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -5976,10 +5898,10 @@
         <v>203</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -5990,13 +5912,13 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -6008,10 +5930,10 @@
         <v>194</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6022,13 +5944,13 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
@@ -6037,13 +5959,13 @@
         <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -6054,13 +5976,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -6069,13 +5991,13 @@
         <v>149</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -6086,28 +6008,28 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6118,28 +6040,28 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>308</v>
+        <v>401</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -6181,7 +6103,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6228,31 +6150,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>304</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6260,31 +6182,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>304</v>
+        <v>184</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6292,31 +6214,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6324,31 +6246,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6356,31 +6278,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6388,31 +6310,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6420,31 +6342,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6452,31 +6374,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6484,31 +6406,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>371</v>
+        <v>100</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6516,31 +6438,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6548,31 +6470,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6580,31 +6502,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6612,31 +6534,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6644,31 +6566,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6676,31 +6598,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6708,31 +6630,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6740,31 +6662,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>460</v>
+        <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>460</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6772,31 +6694,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6804,31 +6726,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>358</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6836,31 +6758,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6868,31 +6790,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6900,31 +6822,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>371</v>
+        <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6932,31 +6854,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>51</v>
+        <v>468</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>468</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6964,19 +6886,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -6985,10 +6907,10 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6996,31 +6918,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>322</v>
+        <v>110</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7028,31 +6950,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>476</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7060,31 +6982,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>304</v>
+        <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7092,31 +7014,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7124,38 +7046,70 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -7186,6 +7140,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7246,25 +7201,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>60</v>
@@ -7278,13 +7233,13 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
@@ -7296,7 +7251,7 @@
         <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>60</v>
@@ -7310,13 +7265,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -7325,10 +7280,10 @@
         <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>60</v>
@@ -7342,13 +7297,13 @@
         <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -7360,7 +7315,7 @@
         <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>60</v>
@@ -7371,28 +7326,28 @@
         <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>60</v>
@@ -7406,25 +7361,25 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>60</v>
@@ -7444,19 +7399,19 @@
         <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>138</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>60</v>
@@ -7470,25 +7425,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>60</v>
@@ -7502,25 +7457,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>60</v>
@@ -7534,13 +7489,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -7552,7 +7507,7 @@
         <v>150</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>60</v>
@@ -7566,13 +7521,13 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
@@ -7581,10 +7536,10 @@
         <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>60</v>
@@ -7598,25 +7553,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>60</v>
@@ -7630,13 +7585,13 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
@@ -7648,7 +7603,7 @@
         <v>159</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>60</v>
@@ -7662,13 +7617,13 @@
         <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
@@ -7680,7 +7635,7 @@
         <v>203</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>60</v>
@@ -7694,13 +7649,13 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -7712,7 +7667,7 @@
         <v>159</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>60</v>
@@ -7726,25 +7681,25 @@
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>60</v>
@@ -7758,25 +7713,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>301</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>60</v>
@@ -7790,25 +7745,25 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>60</v>
@@ -7822,25 +7777,25 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>322</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>203</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>60</v>
@@ -7854,25 +7809,25 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>281</v>
+        <v>358</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>60</v>
@@ -7883,16 +7838,16 @@
         <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -7904,7 +7859,7 @@
         <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>60</v>
@@ -7918,25 +7873,25 @@
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>203</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>60</v>
@@ -7950,25 +7905,25 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>60</v>
@@ -7982,13 +7937,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -7997,10 +7952,10 @@
         <v>120</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>60</v>
@@ -8014,25 +7969,25 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>371</v>
+        <v>253</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>60</v>
@@ -8046,13 +8001,13 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
@@ -8064,7 +8019,7 @@
         <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>60</v>
@@ -8078,25 +8033,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>180</v>
+        <v>358</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>60</v>
@@ -8110,25 +8065,25 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>281</v>
+        <v>184</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>60</v>
@@ -8142,25 +8097,25 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>60</v>
@@ -8174,13 +8129,13 @@
         <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
@@ -8192,7 +8147,7 @@
         <v>224</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>60</v>
@@ -8291,25 +8246,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8323,25 +8278,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8361,7 +8316,7 @@
         <v>67</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>138</v>
@@ -8373,7 +8328,7 @@
         <v>144</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8387,25 +8342,25 @@
         <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8416,16 +8371,16 @@
         <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -8437,7 +8392,7 @@
         <v>150</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8451,25 +8406,25 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8483,25 +8438,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8515,25 +8470,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8547,13 +8502,13 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
@@ -8565,7 +8520,7 @@
         <v>159</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8579,25 +8534,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8611,25 +8566,25 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8643,25 +8598,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8675,25 +8630,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8707,25 +8662,25 @@
         <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>281</v>
+        <v>358</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8739,25 +8694,25 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>203</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8771,13 +8726,13 @@
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -8786,10 +8741,10 @@
         <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8803,25 +8758,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8835,25 +8790,25 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8867,25 +8822,25 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8899,25 +8854,25 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8928,16 +8883,16 @@
         <v>61</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -8949,7 +8904,7 @@
         <v>224</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8963,25 +8918,25 @@
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8995,25 +8950,25 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>281</v>
+        <v>149</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9027,25 +8982,25 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>149</v>
+        <v>358</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9059,25 +9014,25 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9091,13 +9046,13 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
@@ -9109,7 +9064,7 @@
         <v>224</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9123,13 +9078,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -9141,7 +9096,7 @@
         <v>224</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9155,25 +9110,25 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>288</v>
+        <v>476</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9187,25 +9142,25 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>288</v>
+        <v>224</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9303,13 +9258,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
@@ -9321,7 +9276,7 @@
         <v>144</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>60</v>
@@ -9335,13 +9290,13 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
@@ -9353,7 +9308,7 @@
         <v>159</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>60</v>
@@ -9367,13 +9322,13 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
@@ -9385,7 +9340,7 @@
         <v>150</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>60</v>
@@ -9399,13 +9354,13 @@
         <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -9417,7 +9372,7 @@
         <v>150</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>60</v>
@@ -9428,28 +9383,28 @@
         <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>60</v>
@@ -9463,25 +9418,25 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>60</v>
@@ -9495,13 +9450,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>87</v>
@@ -9513,7 +9468,7 @@
         <v>159</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>60</v>
@@ -9527,13 +9482,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
@@ -9545,7 +9500,7 @@
         <v>159</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>60</v>
@@ -9559,13 +9514,13 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
@@ -9577,7 +9532,7 @@
         <v>159</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>60</v>
@@ -9591,25 +9546,25 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>60</v>
@@ -9623,13 +9578,13 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
@@ -9641,7 +9596,7 @@
         <v>203</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>60</v>
@@ -9655,25 +9610,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>60</v>
@@ -9687,25 +9642,25 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>60</v>
@@ -9719,25 +9674,25 @@
         <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>60</v>
@@ -9751,25 +9706,25 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>60</v>
@@ -9783,25 +9738,25 @@
         <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>60</v>
@@ -9815,25 +9770,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>224</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>60</v>
@@ -9847,13 +9802,13 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>87</v>
@@ -9862,10 +9817,10 @@
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>288</v>
+        <v>476</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>60</v>
@@ -9879,13 +9834,13 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
@@ -9897,7 +9852,7 @@
         <v>194</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>60</v>
@@ -9911,25 +9866,25 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>731</v>
+        <v>75</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>731</v>
+        <v>75</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>60</v>
@@ -9940,28 +9895,28 @@
         <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>729</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>75</v>
+        <v>729</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>288</v>
+        <v>194</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>60</v>
@@ -9975,13 +9930,13 @@
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -9993,7 +9948,7 @@
         <v>224</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>60</v>
@@ -10007,25 +9962,25 @@
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>60</v>
@@ -10039,13 +9994,13 @@
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -10057,7 +10012,7 @@
         <v>224</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>60</v>
@@ -10071,13 +10026,13 @@
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -10089,7 +10044,7 @@
         <v>224</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>60</v>
@@ -10103,25 +10058,25 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>224</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>60</v>
@@ -10135,25 +10090,25 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>288</v>
+        <v>476</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>60</v>
@@ -10167,25 +10122,25 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>288</v>
+        <v>476</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>60</v>
@@ -10199,25 +10154,25 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>308</v>
+        <v>401</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>60</v>
@@ -10231,13 +10186,13 @@
         <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>87</v>
@@ -10246,10 +10201,10 @@
         <v>100</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>60</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -11,8 +11,8 @@
     <sheet name="레플리카셋" sheetId="2" r:id="rId2"/>
     <sheet name="설묘" sheetId="3" r:id="rId3"/>
     <sheet name="리안" sheetId="4" r:id="rId4"/>
-    <sheet name="브리또" sheetId="5" r:id="rId5"/>
-    <sheet name="점프킹" sheetId="6" r:id="rId6"/>
+    <sheet name="점프킹" sheetId="5" r:id="rId5"/>
+    <sheet name="브리또" sheetId="6" r:id="rId6"/>
     <sheet name="귀여미" sheetId="7" r:id="rId7"/>
     <sheet name="셀린느" sheetId="8" r:id="rId8"/>
   </sheets>
@@ -21,10 +21,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">귀여미!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">레플리카셋!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">리안!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">브리또!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">브리또!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">설묘!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">셀린느!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">점프킹!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">점프킹!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
     <t>Scania 32</t>
   </si>
   <si>
-    <t>45</t>
+    <t>44</t>
   </si>
   <si>
     <t>1위</t>
@@ -117,7 +117,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>48</t>
+    <t>47</t>
   </si>
   <si>
     <t>Lv.10</t>
@@ -147,7 +147,7 @@
     <t>59</t>
   </si>
   <si>
-    <t>7위</t>
+    <t>6위</t>
   </si>
   <si>
     <t>26명</t>
@@ -165,6 +165,33 @@
     <t>2026.09.22</t>
   </si>
   <si>
+    <t>점프킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
+  </si>
+  <si>
+    <t>Scania 5</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>1134경 3201조 9049억 7099만</t>
+  </si>
+  <si>
+    <t>뛰어</t>
+  </si>
+  <si>
+    <t>아크메이딩동</t>
+  </si>
+  <si>
+    <t>2026.09.21</t>
+  </si>
+  <si>
     <t>브리또</t>
   </si>
   <si>
@@ -174,7 +201,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>71</t>
+    <t>73</t>
   </si>
   <si>
     <t>2위</t>
@@ -189,33 +216,6 @@
     <t>안데일2</t>
   </si>
   <si>
-    <t>점프킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
-  </si>
-  <si>
-    <t>Scania 5</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>1134경 3201조 9049억 7099만</t>
-  </si>
-  <si>
-    <t>뛰어</t>
-  </si>
-  <si>
-    <t>아크메이딩동</t>
-  </si>
-  <si>
-    <t>2026.09.21</t>
-  </si>
-  <si>
     <t>귀여미</t>
   </si>
   <si>
@@ -246,7 +246,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>68</t>
+    <t>67</t>
   </si>
   <si>
     <t>3위</t>
@@ -321,7 +321,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>751경 3081조 8777억 5514만</t>
+    <t>771경 9450조 8753억 7070만</t>
   </si>
   <si>
     <t>3</t>
@@ -336,40 +336,40 @@
     <t>팔라딘</t>
   </si>
   <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>722경 5950조 87억 3458만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>라온A</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8A</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>473경 5821조 634억 9942만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>꾱환</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
+  </si>
+  <si>
     <t>126</t>
   </si>
   <si>
-    <t>645경 9997조 3244억 1619만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>꾱환</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
-  </si>
-  <si>
-    <t>473경 1188조 5302억 7047만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>라온A</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8A</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>462경 1350조 5798억 5105만</t>
+    <t>473경 4529조 2420억 9332만</t>
   </si>
   <si>
     <t>6</t>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
   </si>
   <si>
-    <t>453경 8852조 9934억 8203만</t>
+    <t>456경 9015조 1587억 8058만</t>
   </si>
   <si>
     <t>7</t>
@@ -396,7 +396,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>303경 2069조 2268억 5242만</t>
+    <t>303경 3936조 3292억 144만</t>
   </si>
   <si>
     <t>8</t>
@@ -438,7 +438,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
   </si>
   <si>
-    <t>89경 9862조 1727억 1627만</t>
+    <t>91경 5128조 6810억 8748만</t>
   </si>
   <si>
     <t>11</t>
@@ -486,7 +486,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>36경 1319조 7761억 5907만</t>
+    <t>36경 2081조 327억 1251만</t>
   </si>
   <si>
     <t>14</t>
@@ -510,22 +510,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9A%A0</t>
   </si>
   <si>
+    <t>25경 3607조 7527억 2543만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>쌰갈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%B0%EA%B0%88</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>25경 3316조 9144억 3489만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>쌰갈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%B0%EA%B0%88</t>
-  </si>
-  <si>
-    <t>23경 3828조 3785억 7962만</t>
+    <t>24경 2835조 320억 9740만</t>
   </si>
   <si>
     <t>17</t>
@@ -549,7 +549,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
   </si>
   <si>
-    <t>17경 6676조 6499억 7555만</t>
+    <t>18경 7437조 2391억 1384만</t>
   </si>
   <si>
     <t>19</t>
@@ -603,36 +603,36 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
   </si>
   <si>
-    <t>10경 6729조 1013억 4895만</t>
+    <t>11경 625조 7026억 244만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
+    <t>원탱구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>8경 4245조 7634억 4425만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>명품까칠공주</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
   </si>
   <si>
-    <t>117</t>
-  </si>
-  <si>
     <t>8경 328조 23억 6866만</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>원탱구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>7경 8121조 8129억 4732만</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -708,7 +708,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 8543조 1612억 6160만</t>
+    <t>1경 9524조 5592억 9076만</t>
   </si>
   <si>
     <t>해물만두야</t>
@@ -720,7 +720,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>311경 3611조 3158억 5220만</t>
+    <t>312경 5785조 7092억 4817만</t>
   </si>
   <si>
     <t>마옥지</t>
@@ -729,7 +729,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
   </si>
   <si>
-    <t>302경 3995조 3295억 7935만</t>
+    <t>304경 5361조 1288억 6283만</t>
   </si>
   <si>
     <t>캐일리</t>
@@ -738,7 +738,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>210경 4058조 3294억 9261만</t>
+    <t>210경 5297조 6065억 8205만</t>
   </si>
   <si>
     <t>설익은앵숭</t>
@@ -765,7 +765,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>81경 1380조 9531억 7826만</t>
+    <t>83경 4918조 3663억 1122만</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>48경 7508조 7573억 7589만</t>
   </si>
   <si>
     <t>설묘묘</t>
@@ -786,25 +798,13 @@
     <t>47경 6048조 4947억 5487만</t>
   </si>
   <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>47경 3154조 386억 1171만</t>
-  </si>
-  <si>
     <t>너굴얌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>44경 9169조 3146억 906만</t>
+    <t>45경 2556조 849억 321만</t>
   </si>
   <si>
     <t>싲프</t>
@@ -813,7 +813,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>42경 752조 5877억 8211만</t>
+    <t>43경 2903조 8250억 5856만</t>
+  </si>
+  <si>
+    <t>셀렘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>29경 8645조 6832억 9680만</t>
   </si>
   <si>
     <t>시드리안</t>
@@ -825,15 +834,6 @@
     <t>29경 7613조 5062억 2329만</t>
   </si>
   <si>
-    <t>셀렘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>29경 4933조 8598억 7698만</t>
-  </si>
-  <si>
     <t>졸귀탱이</t>
   </si>
   <si>
@@ -849,7 +849,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>21경 2055조 3477억 5841만</t>
+    <t>22경 4480조 9043억 8422만</t>
   </si>
   <si>
     <t>마덕칠</t>
@@ -903,7 +903,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>7경 8552조 1769억 220만</t>
+    <t>7경 8669조 8739억 8330만</t>
   </si>
   <si>
     <t>폰병</t>
@@ -948,7 +948,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%B9%98%EB%8A%94%EC%A0%95%EC%83%81%EC%9D%B8</t>
   </si>
   <si>
-    <t>2경 420조 1374억 5167만</t>
+    <t>2경 2676조 8138억 6796만</t>
   </si>
   <si>
     <t>설콩순</t>
@@ -957,7 +957,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 8903조 4165억 5232만</t>
+    <t>1경 9220조 489억 8804만</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -966,7 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 7082조 8310억 4105만</t>
+    <t>1경 7117조 902억 2574만</t>
   </si>
   <si>
     <t>네오메디</t>
@@ -975,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
   </si>
   <si>
-    <t>1경 4431조 7171억 1764만</t>
+    <t>1경 6027조 3167억 6584만</t>
   </si>
   <si>
     <t>군보</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>226경 3624조 9900억 8707만</t>
+    <t>241경 7943조 5008억 1645만</t>
   </si>
   <si>
     <t>눙키</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
   </si>
   <si>
-    <t>153경 8340조 6596억 4671만</t>
+    <t>155경 2043조 8427억 8848만</t>
   </si>
   <si>
     <t>5형사</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>122경 2058조 9957억 4528만</t>
+    <t>122경 2601조 6448억 7873만</t>
   </si>
   <si>
     <t>심천</t>
@@ -1011,7 +1011,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>96경 1288조 1360억 5581만</t>
+    <t>96경 8510조 5438억 9548만</t>
+  </si>
+  <si>
+    <t>또르뱅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
+  </si>
+  <si>
+    <t>89경 3143조 5849억 5120만</t>
   </si>
   <si>
     <t>총괄한석현</t>
@@ -1023,15 +1032,6 @@
     <t>88경 97조 324억 8358만</t>
   </si>
   <si>
-    <t>또르뱅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
-  </si>
-  <si>
-    <t>87경 7235조 1631억 5842만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
   </si>
   <si>
@@ -1053,7 +1053,7 @@
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>76경 1803조 128억 83만</t>
+    <t>76경 8539조 7189억 232만</t>
   </si>
   <si>
     <t>원중언니</t>
@@ -1062,7 +1062,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>63경 2623조 7103억 8416만</t>
+    <t>63경 3165조 7398억 3475만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1080,7 +1080,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>42경 4596조 4295억 7642만</t>
+    <t>42경 8688조 2278억 7710만</t>
   </si>
   <si>
     <t>김나뭉</t>
@@ -1089,7 +1089,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
   </si>
   <si>
-    <t>38경 2353조 9516억 8252만</t>
+    <t>38경 2799조 1852억 6764만</t>
   </si>
   <si>
     <t>파퍼</t>
@@ -1098,7 +1098,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>34경 7977조 2499억 5197만</t>
+    <t>34경 8571조 5437억 5842만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1113,22 +1113,22 @@
     <t>30경 6712억 4376만</t>
   </si>
   <si>
+    <t>찐맨듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
+  </si>
+  <si>
+    <t>21경 2751조 2698억 575만</t>
+  </si>
+  <si>
     <t>껌정색</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>20경 6481조 3192억 6128만</t>
-  </si>
-  <si>
-    <t>찐맨듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
-  </si>
-  <si>
-    <t>19경 3852조 9498억 8492만</t>
+    <t>20경 6630조 3622억 4711만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1137,7 +1137,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>15경 6963조 5144억 170만</t>
+    <t>15경 7120조 4313억 4793만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -1149,6 +1149,15 @@
     <t>15경 1396조 8929억 8493만</t>
   </si>
   <si>
+    <t>Rahee</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
+  </si>
+  <si>
+    <t>11경 3733조 8625억 7810만</t>
+  </si>
+  <si>
     <t>악경</t>
   </si>
   <si>
@@ -1158,15 +1167,6 @@
     <t>10경 2388조 6776억 2691만</t>
   </si>
   <si>
-    <t>Rahee</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rahee</t>
-  </si>
-  <si>
-    <t>8경 4278조 2698억 8627만</t>
-  </si>
-  <si>
     <t>고먀츠나나</t>
   </si>
   <si>
@@ -1209,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
   </si>
   <si>
-    <t>4경 5564조 7041억 204만</t>
+    <t>4경 5830조 2850억 1552만</t>
   </si>
   <si>
     <t>바람의새벽</t>
@@ -1218,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
   </si>
   <si>
-    <t>3경 655조 4594억 5626만</t>
+    <t>3경 712조 854억 4043만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1227,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 4606조 8331억 956만</t>
+    <t>2경 4984조 3282억 337만</t>
   </si>
   <si>
     <t>셀러문</t>
@@ -1239,7 +1239,274 @@
     <t>114</t>
   </si>
   <si>
-    <t>5329조 7290억 7632만</t>
+    <t>5715조 1971억 8580만</t>
+  </si>
+  <si>
+    <t>라온XR</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8XR</t>
+  </si>
+  <si>
+    <t>454경 1026조 4435억 4176만</t>
+  </si>
+  <si>
+    <t>매스몬스터</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%AA%AC%EC%8A%A4%ED%84%B0</t>
+  </si>
+  <si>
+    <t>310경 7797조 9067억 1436만</t>
+  </si>
+  <si>
+    <t>코코듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
+  </si>
+  <si>
+    <t>236경 5110조 9500억 7926만</t>
+  </si>
+  <si>
+    <t>하잉안파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>210경 967조 4017억 9820만</t>
+  </si>
+  <si>
+    <t>미야고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%95%BC%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>75경 6496조 2635억 7111만</t>
+  </si>
+  <si>
+    <t>타이슨에어랩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
+  </si>
+  <si>
+    <t>64경 9468조 1897억 1709만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
+  </si>
+  <si>
+    <t>61경 8131조 881억 2194만</t>
+  </si>
+  <si>
+    <t>캔드릭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
+  </si>
+  <si>
+    <t>55경 5521조 5327억 308만</t>
+  </si>
+  <si>
+    <t>용보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>40경 568조 866억 7168만</t>
+  </si>
+  <si>
+    <t>진압조</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
+  </si>
+  <si>
+    <t>27경 1636조 7187억 4799만</t>
+  </si>
+  <si>
+    <t>똥갈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
+  </si>
+  <si>
+    <t>22경 6071조 9791억 2753만</t>
+  </si>
+  <si>
+    <t>도농롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%86%8D%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>13경 6641조 1672억 5760만</t>
+  </si>
+  <si>
+    <t>도적왕대현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EC%99%95%EB%8C%80%ED%98%84</t>
+  </si>
+  <si>
+    <t>11경 6944조 1963억 7415만</t>
+  </si>
+  <si>
+    <t>반불</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
+  </si>
+  <si>
+    <t>9경 9946조 8133억 2348만</t>
+  </si>
+  <si>
+    <t>힐옹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%98%B9</t>
+  </si>
+  <si>
+    <t>9경 6843조 1983억 2212만</t>
+  </si>
+  <si>
+    <t>혜도로동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
+  </si>
+  <si>
+    <t>8경 3181조 4066억 8550만</t>
+  </si>
+  <si>
+    <t>조명준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
+  </si>
+  <si>
+    <t>7경 4452조 6227억 9543만</t>
+  </si>
+  <si>
+    <t>로생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
+  </si>
+  <si>
+    <t>7경 3270조 9119억 4886만</t>
+  </si>
+  <si>
+    <t>붕어줍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EC%96%B4%EC%A4%8D</t>
+  </si>
+  <si>
+    <t>7경 3182조 1520억 8819만</t>
+  </si>
+  <si>
+    <t>망치반죽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
+  </si>
+  <si>
+    <t>7경 2173조 1779억 765만</t>
+  </si>
+  <si>
+    <t>이다연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
+  </si>
+  <si>
+    <t>7경 668조 8218억 4404만</t>
+  </si>
+  <si>
+    <t>Redwine</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Redwine</t>
+  </si>
+  <si>
+    <t>6경 2671조 6983억 7075만</t>
+  </si>
+  <si>
+    <t>유도로동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
+  </si>
+  <si>
+    <t>5경 364조 447억 1448만</t>
+  </si>
+  <si>
+    <t>메키메렁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
+  </si>
+  <si>
+    <t>3경 7907조 5797억 6079만</t>
+  </si>
+  <si>
+    <t>그때그아이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3경 3557조 4573억 5775만</t>
+  </si>
+  <si>
+    <t>루빙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
+  </si>
+  <si>
+    <t>2경 5857조 3417억 9647만</t>
+  </si>
+  <si>
+    <t>spemi</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=spemi</t>
+  </si>
+  <si>
+    <t>2경 2564조 3871억 11만</t>
+  </si>
+  <si>
+    <t>우솝이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2경 1610조 9921억 4920만</t>
+  </si>
+  <si>
+    <t>꽁꽁얼었다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EC%96%BC%EC%97%88%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2경 415조 4230억 7944만</t>
+  </si>
+  <si>
+    <t>막또날드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
+  </si>
+  <si>
+    <t>1경 8603조 1535억 9902만</t>
   </si>
   <si>
     <t>강서구도적</t>
@@ -1248,7 +1515,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
   </si>
   <si>
-    <t>678경 6312조 2449억 1069만</t>
+    <t>679경 943조 6015억 8001만</t>
   </si>
   <si>
     <t>따코유</t>
@@ -1275,7 +1542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
   </si>
   <si>
-    <t>128경 8366조 7732억 1557만</t>
+    <t>134경 7012조 3547억 2108만</t>
   </si>
   <si>
     <t>귤놈펜</t>
@@ -1284,7 +1551,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
   </si>
   <si>
-    <t>92경 1753조 3969억 1373만</t>
+    <t>92경 4509조 1518억 9180만</t>
+  </si>
+  <si>
+    <t>퀸더쪼이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>37경 2318조 1068억 213만</t>
   </si>
   <si>
     <t>꿀서은</t>
@@ -1293,16 +1569,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
   </si>
   <si>
-    <t>36경 6947조 8154억 6849만</t>
-  </si>
-  <si>
-    <t>퀸더쪼이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>36경 1943조 204억 9997만</t>
+    <t>36경 7115조 3759억 971만</t>
+  </si>
+  <si>
+    <t>쿨쥐돌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
+  </si>
+  <si>
+    <t>26경 9042조 4204억 3073만</t>
   </si>
   <si>
     <t>게탕</t>
@@ -1311,16 +1587,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
   </si>
   <si>
-    <t>26경 7930조 4439억 3182만</t>
-  </si>
-  <si>
-    <t>쿨쥐돌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
-  </si>
-  <si>
-    <t>25경 7681조 8225억 532만</t>
+    <t>26경 8004조 3957억 9284만</t>
   </si>
   <si>
     <t>긴나라</t>
@@ -1329,7 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>25경 1558조 8648억 7196만</t>
+    <t>25경 1826조 3939억 4877만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -1338,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
   </si>
   <si>
-    <t>15경 3242조 2461억 2069만</t>
+    <t>16경 3407조 2583억 2586만</t>
   </si>
   <si>
     <t>류텐</t>
@@ -1347,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
   </si>
   <si>
-    <t>11경 883조 1950억 8681만</t>
+    <t>11경 967조 1228억 2416만</t>
   </si>
   <si>
     <t>철푸닥</t>
@@ -1374,7 +1641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>4경 1280조 7306억 4782만</t>
+    <t>4경 3761조 4402억 4259만</t>
   </si>
   <si>
     <t>무명장수</t>
@@ -1398,7 +1665,7 @@
     <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
   </si>
   <si>
-    <t>3경 1346조 5936억 4301만</t>
+    <t>3경 1970조 8270억 3578만</t>
   </si>
   <si>
     <t>오정구불독</t>
@@ -1410,22 +1677,22 @@
     <t>2경 5391조 9478억 8415만</t>
   </si>
   <si>
+    <t>구미적</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
+  </si>
+  <si>
+    <t>2경 3716조 4918억 7788만</t>
+  </si>
+  <si>
     <t>양덕하늘채</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8D%95%ED%95%98%EB%8A%98%EC%B1%84</t>
   </si>
   <si>
-    <t>2경 1791조 4950억 8951만</t>
-  </si>
-  <si>
-    <t>구미적</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
-  </si>
-  <si>
-    <t>2경 517조 7707억 1039만</t>
+    <t>2경 2355조 9466억 8668만</t>
   </si>
   <si>
     <t>검샷</t>
@@ -1434,7 +1701,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
   </si>
   <si>
-    <t>1경 6350조 814억 826만</t>
+    <t>1경 6362조 2357억 396만</t>
   </si>
   <si>
     <t>레드플레이어</t>
@@ -1443,7 +1710,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
   </si>
   <si>
-    <t>1경 6041조 8436억 8150만</t>
+    <t>1경 6193조 932억 131만</t>
   </si>
   <si>
     <t>주하사랑</t>
@@ -1452,7 +1719,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
   </si>
   <si>
-    <t>1경 5163조 9079억 2710만</t>
+    <t>1경 5655조 2869억 5063만</t>
   </si>
   <si>
     <t>장아린</t>
@@ -1464,7 +1731,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>1경 3399조 7861억 7097만</t>
+    <t>1경 3485조 9289억 7088만</t>
   </si>
   <si>
     <t>예슬a</t>
@@ -1500,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
   </si>
   <si>
-    <t>8736조 7457억 7565만</t>
+    <t>9012조 9049억 5937만</t>
   </si>
   <si>
     <t>어꼬</t>
@@ -1512,274 +1779,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>4262조 7358억 503만</t>
-  </si>
-  <si>
-    <t>라온XR</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8XR</t>
-  </si>
-  <si>
-    <t>454경 1026조 4435억 4176만</t>
-  </si>
-  <si>
-    <t>매스몬스터</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%AA%AC%EC%8A%A4%ED%84%B0</t>
-  </si>
-  <si>
-    <t>310경 7797조 9067억 1436만</t>
-  </si>
-  <si>
-    <t>코코듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
-  </si>
-  <si>
-    <t>215경 1594조 5464억 4871만</t>
-  </si>
-  <si>
-    <t>하잉안파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>210경 967조 4017억 9820만</t>
-  </si>
-  <si>
-    <t>미야고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%95%BC%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>75경 6496조 2635억 7111만</t>
-  </si>
-  <si>
-    <t>타이슨에어랩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
-  </si>
-  <si>
-    <t>64경 9468조 1897억 1709만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
-  </si>
-  <si>
-    <t>61경 8131조 881억 2194만</t>
-  </si>
-  <si>
-    <t>캔드릭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
-  </si>
-  <si>
-    <t>55경 5521조 5327억 308만</t>
-  </si>
-  <si>
-    <t>용보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>40경 352조 4944억 4741만</t>
-  </si>
-  <si>
-    <t>진압조</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
-  </si>
-  <si>
-    <t>27경 1636조 7187억 4799만</t>
-  </si>
-  <si>
-    <t>똥갈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
-  </si>
-  <si>
-    <t>22경 6071조 9791억 2753만</t>
-  </si>
-  <si>
-    <t>도농롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%86%8D%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>12경 8749조 1994억 7023만</t>
-  </si>
-  <si>
-    <t>도적왕대현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%A0%81%EC%99%95%EB%8C%80%ED%98%84</t>
-  </si>
-  <si>
-    <t>11경 6944조 1963억 7415만</t>
-  </si>
-  <si>
-    <t>반불</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
-  </si>
-  <si>
-    <t>9경 9011조 3697억 78만</t>
-  </si>
-  <si>
-    <t>힐옹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EC%98%B9</t>
-  </si>
-  <si>
-    <t>9경 6843조 1983억 2212만</t>
-  </si>
-  <si>
-    <t>혜도로동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
-  </si>
-  <si>
-    <t>8경 3075조 7622억 5434만</t>
-  </si>
-  <si>
-    <t>조명준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
-  </si>
-  <si>
-    <t>7경 4452조 6227억 9543만</t>
-  </si>
-  <si>
-    <t>로생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
-  </si>
-  <si>
-    <t>7경 3234조 6573억 3434만</t>
-  </si>
-  <si>
-    <t>붕어줍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EC%96%B4%EC%A4%8D</t>
-  </si>
-  <si>
-    <t>7경 2239조 6627억 8531만</t>
-  </si>
-  <si>
-    <t>이다연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
-  </si>
-  <si>
-    <t>7경 486조 1461억 6119만</t>
-  </si>
-  <si>
-    <t>망치반죽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
-  </si>
-  <si>
-    <t>6경 9477조 303억 2394만</t>
-  </si>
-  <si>
-    <t>Redwine</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Redwine</t>
-  </si>
-  <si>
-    <t>6경 1926조 7636억 249만</t>
-  </si>
-  <si>
-    <t>유도로동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
-  </si>
-  <si>
-    <t>5경 174조 4078억 9299만</t>
-  </si>
-  <si>
-    <t>메키메렁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
-  </si>
-  <si>
-    <t>3경 7907조 5797억 6079만</t>
-  </si>
-  <si>
-    <t>그때그아이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3경 2163조 8947억 9574만</t>
-  </si>
-  <si>
-    <t>루빙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
-  </si>
-  <si>
-    <t>2경 5444조 8662억 4631만</t>
-  </si>
-  <si>
-    <t>spemi</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=spemi</t>
-  </si>
-  <si>
-    <t>2경 2494조 3407억 8152만</t>
-  </si>
-  <si>
-    <t>우솝이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2경 1610조 9921억 4920만</t>
-  </si>
-  <si>
-    <t>꽁꽁얼었다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EC%96%BC%EC%97%88%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2경 415조 4230억 7944만</t>
-  </si>
-  <si>
-    <t>막또날드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
-  </si>
-  <si>
-    <t>1경 8603조 1535억 9902만</t>
+    <t>4380조 4821억 2206만</t>
   </si>
   <si>
     <t>금은동S2</t>
@@ -1824,7 +1824,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>37경 7632조 2543억 5046만</t>
+    <t>38경 5252조 9280억 3174만</t>
   </si>
   <si>
     <t>꿈넴</t>
@@ -1851,7 +1851,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%ED%9E%9D</t>
   </si>
   <si>
-    <t>14경 7878조 8409억 3060만</t>
+    <t>14경 8654조 5102억 3252만</t>
   </si>
   <si>
     <t>제껴</t>
@@ -1860,7 +1860,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>13경 2761조 7251억 22만</t>
+    <t>13경 3240조 9880억 4681만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -1869,7 +1869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%B8%8C%EB%A3%A8%EB%AF%80</t>
   </si>
   <si>
-    <t>10경 7247조 7705억 7370만</t>
+    <t>10경 7974조 5167억 8349만</t>
   </si>
   <si>
     <t>엘리자베타</t>
@@ -1896,7 +1896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>5경 7079조 9150억 7595만</t>
+    <t>5경 7960조 1793억 4161만</t>
   </si>
   <si>
     <t>우꼬쨩</t>
@@ -1905,7 +1905,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
   </si>
   <si>
-    <t>5경 5069조 4815억 6192만</t>
+    <t>5경 6343조 5570억 5250만</t>
   </si>
   <si>
     <t>누룽지룽누</t>
@@ -1941,7 +1941,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EC%9A%94S2</t>
   </si>
   <si>
-    <t>3경 4296조 6719억 5656만</t>
+    <t>3경 5201조 9327억 1655만</t>
   </si>
   <si>
     <t>지아라떼</t>
@@ -1959,7 +1959,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
   </si>
   <si>
-    <t>2경 9562조 5399억 1119만</t>
+    <t>2경 9772조 804억 7826만</t>
   </si>
   <si>
     <t>득츈</t>
@@ -1968,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
   </si>
   <si>
-    <t>2경 8013조 5886억 7300만</t>
+    <t>2경 8493조 1830억 1553만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -1986,7 +1986,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
   </si>
   <si>
-    <t>2경 4452조 445억 7837만</t>
+    <t>2경 4697조 2793억 3690만</t>
   </si>
   <si>
     <t>24년생정춘식</t>
@@ -2022,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>1경 2245조 7595억 8282만</t>
+    <t>1경 2307조 1136억 2622만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -2031,7 +2031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>1경 870조 2545억 6547만</t>
+    <t>1경 2301조 882억 5255만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -2040,7 +2040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>9235조 2239억 9662만</t>
+    <t>9939조 5019억 7240만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2058,7 +2058,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>21경 5023조 1197억 311만</t>
+    <t>21경 7020조 3459억 7096만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2067,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>15경 2740조 864억 2274만</t>
+    <t>15경 4700조 6711억 800만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -2076,7 +2076,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>13경 9512조 8823억 8446만</t>
+    <t>14경 58조 2490억 8844만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -2094,7 +2094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>11경 6482조 8557억 6748만</t>
+    <t>11경 8642조 6219억 7620만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -2148,7 +2148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>3경 3613조 4434억 8483만</t>
+    <t>3경 6499조 9571억 6070만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -2166,13 +2166,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 7146조 7225억 8149만</t>
-  </si>
-  <si>
-    <t>오픈톡쌀숭E</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%ED%94%88%ED%86%A1%EC%8C%80%EC%88%ADE</t>
+    <t>2경 7153조 3284억 9878만</t>
+  </si>
+  <si>
+    <t>햼쮸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%BC%EC%AE%B8</t>
   </si>
   <si>
     <t>2경 6890조 4852억 886만</t>
@@ -2193,7 +2193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>2경 3735조 8934억 1056만</t>
+    <t>2경 4866조 8388억 8718만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -2217,7 +2217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>2경 124조 7436억 1832만</t>
+    <t>2경 671조 7972억 7324만</t>
   </si>
   <si>
     <t>망겜감별사</t>
@@ -2226,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1경 9989조 585억 9209만</t>
+    <t>2경 163조 7355억 3124만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -2235,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 5773조 8073억 4323만</t>
+    <t>1경 6061조 5억 9691만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2244,7 +2244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>1경 4208조 4830억 3846만</t>
+    <t>1경 4429조 8789억 3038만</t>
   </si>
   <si>
     <t>오곤</t>
@@ -2271,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 1436조 1287억 6107만</t>
+    <t>1경 1990조 4206억 1101만</t>
   </si>
   <si>
     <t>초식왕</t>
@@ -2280,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%8B%9D%EC%99%95</t>
   </si>
   <si>
-    <t>9474조 4834억 1025만</t>
+    <t>9504조 155억 3557만</t>
   </si>
   <si>
     <t>러너</t>
@@ -2310,7 +2310,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>2294조 3189억 3545만</t>
+    <t>2324조 3357억 547만</t>
   </si>
 </sst>
 </file>
@@ -2873,13 +2873,13 @@
         <v>47</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>49</v>
@@ -2891,48 +2891,48 @@
         <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3014,7 +3014,7 @@
         <v>75</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3195,13 +3195,13 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3212,22 +3212,22 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>111</v>
@@ -3294,7 +3294,7 @@
         <v>120</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>121</v>
@@ -3515,7 +3515,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>150</v>
@@ -3547,13 +3547,13 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3564,16 +3564,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -3582,7 +3582,7 @@
         <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>164</v>
@@ -3611,10 +3611,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>168</v>
@@ -3643,10 +3643,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>172</v>
@@ -3675,10 +3675,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>176</v>
@@ -3803,7 +3803,7 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>194</v>
@@ -3835,7 +3835,7 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>194</v>
@@ -3899,7 +3899,7 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>185</v>
@@ -3931,7 +3931,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>185</v>
@@ -3963,7 +3963,7 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>185</v>
@@ -3995,7 +3995,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>194</v>
@@ -4027,7 +4027,7 @@
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>224</v>
@@ -4179,7 +4179,7 @@
         <v>228</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>232</v>
@@ -4208,7 +4208,7 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>95</v>
@@ -4257,7 +4257,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>239</v>
@@ -4336,13 +4336,13 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4356,25 +4356,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4388,22 +4388,22 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>253</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>254</v>
@@ -4435,7 +4435,7 @@
         <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>257</v>
@@ -4464,10 +4464,10 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>260</v>
@@ -4496,10 +4496,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>263</v>
@@ -4528,10 +4528,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>266</v>
@@ -4560,7 +4560,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>150</v>
@@ -4592,7 +4592,7 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>144</v>
@@ -4609,7 +4609,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>273</v>
@@ -4656,7 +4656,7 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>150</v>
@@ -4688,10 +4688,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>281</v>
@@ -4723,7 +4723,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>284</v>
@@ -4784,7 +4784,7 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>203</v>
@@ -4816,7 +4816,7 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>203</v>
@@ -4848,10 +4848,10 @@
         <v>138</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>295</v>
@@ -4979,7 +4979,7 @@
         <v>228</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>308</v>
@@ -5040,7 +5040,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>224</v>
@@ -5156,10 +5156,10 @@
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>301</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>317</v>
@@ -5191,7 +5191,7 @@
         <v>88</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>320</v>
@@ -5269,7 +5269,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>327</v>
@@ -5287,7 +5287,7 @@
         <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>329</v>
@@ -5319,7 +5319,7 @@
         <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>332</v>
@@ -5412,7 +5412,7 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>126</v>
@@ -5476,10 +5476,10 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>346</v>
@@ -5540,7 +5540,7 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>150</v>
@@ -5572,7 +5572,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>144</v>
@@ -5607,7 +5607,7 @@
         <v>358</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>359</v>
@@ -5621,7 +5621,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>360</v>
@@ -5636,10 +5636,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>253</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>362</v>
@@ -5668,10 +5668,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>365</v>
@@ -5703,7 +5703,7 @@
         <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>368</v>
@@ -5735,7 +5735,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>371</v>
@@ -5764,10 +5764,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>374</v>
@@ -5796,7 +5796,7 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>203</v>
@@ -6168,7 +6168,7 @@
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>301</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>111</v>
@@ -6177,7 +6177,7 @@
         <v>405</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6200,16 +6200,16 @@
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>408</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6232,16 +6232,16 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>411</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6264,7 +6264,7 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>126</v>
@@ -6273,7 +6273,7 @@
         <v>414</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6281,7 +6281,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>415</v>
@@ -6296,16 +6296,16 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>417</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6328,7 +6328,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>144</v>
@@ -6337,7 +6337,7 @@
         <v>420</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6348,28 +6348,28 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6380,28 +6380,28 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>426</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6412,28 +6412,28 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>429</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6444,28 +6444,28 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6476,28 +6476,28 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6508,28 +6508,28 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>438</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6540,28 +6540,28 @@
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>441</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6572,28 +6572,28 @@
         <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>444</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6604,28 +6604,28 @@
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>447</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6633,31 +6633,31 @@
         <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>450</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6668,28 +6668,28 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>450</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>450</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>451</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>184</v>
+        <v>301</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>452</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6712,16 +6712,16 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>455</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6744,16 +6744,16 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>358</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>458</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6779,13 +6779,13 @@
         <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>461</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6808,16 +6808,16 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>149</v>
+        <v>358</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>224</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>464</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6840,16 +6840,16 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>467</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6872,16 +6872,16 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>224</v>
+        <v>163</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>470</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6904,16 +6904,16 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>473</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -6936,16 +6936,16 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6956,28 +6956,28 @@
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -6988,28 +6988,28 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>483</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7020,28 +7020,28 @@
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>486</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7052,28 +7052,28 @@
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -7084,28 +7084,28 @@
         <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -7195,659 +7195,659 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>301</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>502</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>510</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>59</v>
+        <v>510</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>516</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>524</v>
-      </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>150</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>528</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>537</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>540</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>546</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>552</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
@@ -7856,301 +7856,301 @@
         <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>567</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>570</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>573</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>217</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>579</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>582</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -8258,7 +8258,7 @@
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>585</v>
@@ -8290,7 +8290,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>126</v>
@@ -8354,7 +8354,7 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>144</v>
@@ -8371,7 +8371,7 @@
         <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>595</v>
@@ -8418,10 +8418,10 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>600</v>
@@ -8450,10 +8450,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>603</v>
@@ -8482,10 +8482,10 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>606</v>
@@ -8517,7 +8517,7 @@
         <v>149</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>609</v>
@@ -8549,7 +8549,7 @@
         <v>228</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>612</v>
@@ -8578,10 +8578,10 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>615</v>
@@ -8610,7 +8610,7 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>203</v>
@@ -8642,7 +8642,7 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>185</v>
@@ -8677,7 +8677,7 @@
         <v>358</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>624</v>
@@ -8723,7 +8723,7 @@
         <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>628</v>
@@ -8802,7 +8802,7 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>194</v>
@@ -8834,7 +8834,7 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>185</v>
@@ -8866,7 +8866,7 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>194</v>
@@ -8901,7 +8901,7 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>645</v>
@@ -8930,7 +8930,7 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>185</v>
@@ -9026,7 +9026,7 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>224</v>
@@ -9122,10 +9122,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>476</v>
+        <v>224</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>666</v>
@@ -9154,7 +9154,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>224</v>
@@ -9279,7 +9279,7 @@
         <v>672</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -9305,13 +9305,13 @@
         <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>675</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -9343,7 +9343,7 @@
         <v>678</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -9375,7 +9375,7 @@
         <v>681</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -9383,7 +9383,7 @@
         <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>682</v>
@@ -9401,13 +9401,13 @@
         <v>184</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>684</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -9433,13 +9433,13 @@
         <v>301</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>687</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -9465,13 +9465,13 @@
         <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>690</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -9497,13 +9497,13 @@
         <v>125</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>693</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -9529,13 +9529,13 @@
         <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>696</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -9558,7 +9558,7 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>194</v>
@@ -9567,7 +9567,7 @@
         <v>699</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -9599,7 +9599,7 @@
         <v>702</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -9622,7 +9622,7 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>185</v>
@@ -9631,7 +9631,7 @@
         <v>705</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -9654,7 +9654,7 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>194</v>
@@ -9663,7 +9663,7 @@
         <v>708</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -9686,7 +9686,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>185</v>
@@ -9695,7 +9695,7 @@
         <v>711</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -9718,7 +9718,7 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>194</v>
@@ -9727,7 +9727,7 @@
         <v>714</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -9735,7 +9735,7 @@
         <v>68</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>715</v>
@@ -9750,7 +9750,7 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>194</v>
@@ -9759,7 +9759,7 @@
         <v>717</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -9782,16 +9782,16 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>720</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -9817,13 +9817,13 @@
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>476</v>
+        <v>565</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>723</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -9855,7 +9855,7 @@
         <v>726</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -9878,7 +9878,7 @@
         <v>138</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>224</v>
@@ -9887,7 +9887,7 @@
         <v>728</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -9910,7 +9910,7 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>194</v>
@@ -9919,7 +9919,7 @@
         <v>731</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -9951,7 +9951,7 @@
         <v>734</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -9974,7 +9974,7 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>194</v>
@@ -9983,7 +9983,7 @@
         <v>737</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -10015,7 +10015,7 @@
         <v>740</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -10047,7 +10047,7 @@
         <v>743</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -10070,7 +10070,7 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>224</v>
@@ -10079,7 +10079,7 @@
         <v>746</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -10102,16 +10102,16 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>476</v>
+        <v>565</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>749</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -10134,16 +10134,16 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>476</v>
+        <v>565</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>752</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -10166,7 +10166,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>401</v>
@@ -10175,7 +10175,7 @@
         <v>755</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -10207,7 +10207,7 @@
         <v>759</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -300,10 +300,10 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>4648경 5323조 2659억 1890만</t>
+    <t>130</t>
+  </si>
+  <si>
+    <t>4652경 9832조 6027억 4356만</t>
   </si>
   <si>
     <t>2</t>
@@ -321,7 +321,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>771경 9450조 8753억 7070만</t>
+    <t>772경 1763조 9808억 747만</t>
   </si>
   <si>
     <t>3</t>
@@ -339,12 +339,27 @@
     <t>127</t>
   </si>
   <si>
-    <t>722경 5950조 87억 3458만</t>
+    <t>724경 1110조 2565억 6251만</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>꾱환</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>524경 8406조 8126억 916만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>라온A</t>
   </si>
   <si>
@@ -357,21 +372,6 @@
     <t>473경 5821조 634억 9942만</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>꾱환</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>473경 4529조 2420억 9332만</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
   </si>
   <si>
-    <t>456경 9015조 1587억 8058만</t>
+    <t>457경 2033조 8056억 3611만</t>
   </si>
   <si>
     <t>7</t>
@@ -396,7 +396,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>303경 3936조 3292억 144만</t>
+    <t>303경 5181조 921억 7380만</t>
   </si>
   <si>
     <t>8</t>
@@ -438,7 +438,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
   </si>
   <si>
-    <t>91경 5128조 6810억 8748만</t>
+    <t>91경 5861조 7527억 789만</t>
   </si>
   <si>
     <t>11</t>
@@ -486,7 +486,7 @@
     <t>121</t>
   </si>
   <si>
-    <t>36경 2081조 327억 1251만</t>
+    <t>36경 3054조 2049억 1282만</t>
   </si>
   <si>
     <t>14</t>
@@ -510,7 +510,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9A%A0</t>
   </si>
   <si>
-    <t>25경 3607조 7527억 2543만</t>
+    <t>26경 5219조 9479억 5871만</t>
   </si>
   <si>
     <t>16</t>
@@ -525,7 +525,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>24경 2835조 320억 9740만</t>
+    <t>24경 5612조 9270억 2989만</t>
   </si>
   <si>
     <t>17</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
   </si>
   <si>
-    <t>19경 6218조 4556억 7817만</t>
+    <t>19경 7032조 4166억 6865만</t>
   </si>
   <si>
     <t>18</t>
@@ -549,7 +549,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
   </si>
   <si>
-    <t>18경 7437조 2391억 1384만</t>
+    <t>19경 1040조 5815억 6292만</t>
   </si>
   <si>
     <t>19</t>
@@ -573,7 +573,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8U</t>
   </si>
   <si>
-    <t>12경 4526조 6909억 8242만</t>
+    <t>12경 5581조 102억 3350만</t>
   </si>
   <si>
     <t>21</t>
@@ -591,7 +591,7 @@
     <t>118</t>
   </si>
   <si>
-    <t>12경 2006조 7135억 837만</t>
+    <t>12경 4834조 5424억 2903만</t>
   </si>
   <si>
     <t>22</t>
@@ -603,7 +603,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
   </si>
   <si>
-    <t>11경 625조 7026억 244만</t>
+    <t>11경 5748조 7434억 5787만</t>
   </si>
   <si>
     <t>23</t>
@@ -618,7 +618,7 @@
     <t>117</t>
   </si>
   <si>
-    <t>8경 4245조 7634억 4425만</t>
+    <t>8경 6138조 2822억 5094만</t>
   </si>
   <si>
     <t>24</t>
@@ -669,7 +669,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
   </si>
   <si>
-    <t>6경 2353조 7055억 9949만</t>
+    <t>6경 2419조 7292억 8393만</t>
   </si>
   <si>
     <t>28</t>
@@ -693,7 +693,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
   </si>
   <si>
-    <t>3경 1615조 7046억 2560만</t>
+    <t>3경 4052조 589억 7648만</t>
   </si>
   <si>
     <t>30</t>
@@ -720,7 +720,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>312경 5785조 7092억 4817만</t>
+    <t>327경 4776조 4624억 1168만</t>
   </si>
   <si>
     <t>마옥지</t>
@@ -729,7 +729,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
   </si>
   <si>
-    <t>304경 5361조 1288억 6283만</t>
+    <t>313경 455조 738억 2646만</t>
   </si>
   <si>
     <t>캐일리</t>
@@ -738,7 +738,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>210경 5297조 6065억 8205만</t>
+    <t>210경 6123조 7929억 6399만</t>
   </si>
   <si>
     <t>설익은앵숭</t>
@@ -765,7 +765,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>83경 4918조 3663억 1122만</t>
+    <t>84경 9267조 350억 9239만</t>
   </si>
   <si>
     <t>설봄a</t>
@@ -777,7 +777,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>48경 7508조 7573억 7589만</t>
+    <t>49경 7963조 6315억 5223만</t>
   </si>
   <si>
     <t>설묘묘</t>
@@ -804,7 +804,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>45경 2556조 849억 321만</t>
+    <t>45경 3070조 180억 2457만</t>
   </si>
   <si>
     <t>싲프</t>
@@ -813,7 +813,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>43경 2903조 8250억 5856만</t>
+    <t>43경 3521조 4818억 6066만</t>
   </si>
   <si>
     <t>셀렘이</t>
@@ -822,7 +822,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>29경 8645조 6832억 9680만</t>
+    <t>30경 8477조 3049억 8265만</t>
   </si>
   <si>
     <t>시드리안</t>
@@ -831,7 +831,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
   </si>
   <si>
-    <t>29경 7613조 5062억 2329만</t>
+    <t>29경 8815조 6254억 1077만</t>
   </si>
   <si>
     <t>졸귀탱이</t>
@@ -840,7 +840,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>25경 4104조 2759억 1048만</t>
+    <t>25경 7434조 5362억 6874만</t>
   </si>
   <si>
     <t>선콜은차가워</t>
@@ -849,7 +849,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>22경 4480조 9043억 8422만</t>
+    <t>22경 6600조 3273억 7460만</t>
   </si>
   <si>
     <t>마덕칠</t>
@@ -858,7 +858,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>21경 127조 2151억 9086만</t>
+    <t>21경 1083조 6548억 2511만</t>
   </si>
   <si>
     <t>설딩</t>
@@ -897,6 +897,15 @@
     <t>10경 491조 6226억 4381만</t>
   </si>
   <si>
+    <t>폰병</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
+  </si>
+  <si>
+    <t>8경 6365조 5071억 4773만</t>
+  </si>
+  <si>
     <t>다다익숍</t>
   </si>
   <si>
@@ -906,15 +915,6 @@
     <t>7경 8669조 8739억 8330만</t>
   </si>
   <si>
-    <t>폰병</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%B0%EB%B3%91</t>
-  </si>
-  <si>
-    <t>7경 4772조 1310억 7065만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>241경 7943조 5008억 1645만</t>
+    <t>241경 9034조 1134억 4587만</t>
   </si>
   <si>
     <t>눙키</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
   </si>
   <si>
-    <t>155경 2043조 8427억 8848만</t>
+    <t>155경 2124조 8650억 1880만</t>
   </si>
   <si>
     <t>5형사</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>122경 2601조 6448억 7873만</t>
+    <t>125경 7908조 7501억 1572만</t>
   </si>
   <si>
     <t>심천</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>96경 8510조 5438억 9548만</t>
+    <t>97경 1538조 6008억 9617만</t>
   </si>
   <si>
     <t>또르뱅</t>
@@ -1020,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>89경 3143조 5849억 5120만</t>
+    <t>90경 8755조 272억 1570만</t>
   </si>
   <si>
     <t>총괄한석현</t>
@@ -1038,6 +1038,15 @@
     <t>86경 50조 568억 3960만</t>
   </si>
   <si>
+    <t>Matter</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Matter</t>
+  </si>
+  <si>
+    <t>79경 1432조 4502억 656만</t>
+  </si>
+  <si>
     <t>혁수킹</t>
   </si>
   <si>
@@ -1047,22 +1056,13 @@
     <t>77경 7775조 9712억 658만</t>
   </si>
   <si>
-    <t>Matter</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Matter</t>
-  </si>
-  <si>
-    <t>76경 8539조 7189억 232만</t>
-  </si>
-  <si>
     <t>원중언니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>63경 3165조 7398억 3475만</t>
+    <t>63경 3184조 6519억 9192만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1089,7 +1089,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
   </si>
   <si>
-    <t>38경 2799조 1852억 6764만</t>
+    <t>38경 3412조 1308억 2922만</t>
   </si>
   <si>
     <t>파퍼</t>
@@ -1098,7 +1098,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>34경 8571조 5437억 5842만</t>
+    <t>35경 4539조 4314억 6832만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
   </si>
   <si>
-    <t>21경 2751조 2698억 575만</t>
+    <t>21경 2840조 2799억 4120만</t>
   </si>
   <si>
     <t>껌정색</t>
@@ -1128,7 +1128,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>20경 6630조 3622억 4711만</t>
+    <t>21경 558조 4879억 3565만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1137,7 +1137,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>15경 7120조 4313억 4793만</t>
+    <t>16경 669조 7431억 5151만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -1209,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
   </si>
   <si>
-    <t>4경 5830조 2850억 1552만</t>
+    <t>4경 5865조 4491억 3978만</t>
   </si>
   <si>
     <t>바람의새벽</t>
@@ -1218,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
   </si>
   <si>
-    <t>3경 712조 854억 4043만</t>
+    <t>3경 3005조 224억 1873만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1227,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 4984조 3282억 337만</t>
+    <t>2경 4995조 6278억 530만</t>
   </si>
   <si>
     <t>셀러문</t>
@@ -1239,7 +1239,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>5715조 1971억 8580만</t>
+    <t>5720조 4385억 5631만</t>
   </si>
   <si>
     <t>라온XR</t>
@@ -1266,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
   </si>
   <si>
-    <t>236경 5110조 9500억 7926만</t>
+    <t>271경 4872조 1237억 8091만</t>
   </si>
   <si>
     <t>하잉안파파</t>
@@ -1275,7 +1275,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>210경 967조 4017억 9820만</t>
+    <t>214경 8640조 8349억 94만</t>
   </si>
   <si>
     <t>미야고</t>
@@ -1293,13 +1293,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
   </si>
   <si>
-    <t>64경 9468조 1897억 1709만</t>
+    <t>65경 2398조 5777억 7860만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
   </si>
   <si>
-    <t>61경 8131조 881억 2194만</t>
+    <t>63경 7536조 6392억 240만</t>
   </si>
   <si>
     <t>캔드릭</t>
@@ -1308,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
   </si>
   <si>
-    <t>55경 5521조 5327억 308만</t>
+    <t>55경 7456조 4185억 4050만</t>
   </si>
   <si>
     <t>용보이</t>
@@ -1317,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>40경 568조 866억 7168만</t>
+    <t>40경 1808조 7292억 5672만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -1362,7 +1362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
   </si>
   <si>
-    <t>9경 9946조 8133억 2348만</t>
+    <t>10경 4347조 7092억 1106만</t>
   </si>
   <si>
     <t>힐옹</t>
@@ -1380,7 +1380,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>8경 3181조 4066억 8550만</t>
+    <t>8경 3467조 394억 1386만</t>
+  </si>
+  <si>
+    <t>로생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
+  </si>
+  <si>
+    <t>8경 637조 1812억 1337만</t>
   </si>
   <si>
     <t>조명준</t>
@@ -1389,16 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
   </si>
   <si>
-    <t>7경 4452조 6227억 9543만</t>
-  </si>
-  <si>
-    <t>로생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
-  </si>
-  <si>
-    <t>7경 3270조 9119억 4886만</t>
+    <t>8경 231조 8243억 62만</t>
   </si>
   <si>
     <t>붕어줍</t>
@@ -1407,7 +1407,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EC%96%B4%EC%A4%8D</t>
   </si>
   <si>
-    <t>7경 3182조 1520억 8819만</t>
+    <t>7경 9371조 9978억 5340만</t>
+  </si>
+  <si>
+    <t>이다연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
+  </si>
+  <si>
+    <t>7경 5117조 6651억 2785만</t>
   </si>
   <si>
     <t>망치반죽</t>
@@ -1416,16 +1425,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
   </si>
   <si>
-    <t>7경 2173조 1779억 765만</t>
-  </si>
-  <si>
-    <t>이다연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
-  </si>
-  <si>
-    <t>7경 668조 8218억 4404만</t>
+    <t>7경 4699조 2289억 8513만</t>
   </si>
   <si>
     <t>Redwine</t>
@@ -1434,7 +1434,7 @@
     <t>https://mgf.gg/contents/character.php?n=Redwine</t>
   </si>
   <si>
-    <t>6경 2671조 6983억 7075만</t>
+    <t>6경 4285조 9023억 3568만</t>
   </si>
   <si>
     <t>유도로동</t>
@@ -1443,7 +1443,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>5경 364조 447억 1448만</t>
+    <t>5경 1251조 9582억 734만</t>
   </si>
   <si>
     <t>메키메렁</t>
@@ -1461,7 +1461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>3경 3557조 4573억 5775만</t>
+    <t>3경 3569조 7127억 1943만</t>
   </si>
   <si>
     <t>루빙</t>
@@ -1470,7 +1470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
   </si>
   <si>
-    <t>2경 5857조 3417억 9647만</t>
+    <t>2경 6370조 4168억 6332만</t>
   </si>
   <si>
     <t>spemi</t>
@@ -1479,7 +1479,7 @@
     <t>https://mgf.gg/contents/character.php?n=spemi</t>
   </si>
   <si>
-    <t>2경 2564조 3871억 11만</t>
+    <t>2경 3473조 1307억 4807만</t>
   </si>
   <si>
     <t>우솝이</t>
@@ -1524,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EC%BD%94%EC%9C%A0</t>
   </si>
   <si>
-    <t>521경 9622조 8287억 9803만</t>
+    <t>522경 3546조 7664억 309만</t>
   </si>
   <si>
     <t>뚱털</t>
@@ -1551,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
   </si>
   <si>
-    <t>92경 4509조 1518억 9180만</t>
+    <t>93경 7321조 9719억 7004만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>37경 2318조 1068억 213만</t>
+    <t>37경 2711조 860억 7892만</t>
   </si>
   <si>
     <t>꿀서은</t>
@@ -1569,7 +1569,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
   </si>
   <si>
-    <t>36경 7115조 3759억 971만</t>
+    <t>36경 7205조 9075억 4186만</t>
   </si>
   <si>
     <t>쿨쥐돌</t>
@@ -1578,7 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
   </si>
   <si>
-    <t>26경 9042조 4204억 3073만</t>
+    <t>28경 617조 3727억 4589만</t>
   </si>
   <si>
     <t>게탕</t>
@@ -1587,7 +1587,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
   </si>
   <si>
-    <t>26경 8004조 3957억 9284만</t>
+    <t>26경 8012조 8701억 5274만</t>
   </si>
   <si>
     <t>긴나라</t>
@@ -1596,7 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>25경 1826조 3939억 4877만</t>
+    <t>25경 2727조 4212억 3136만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -1605,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
   </si>
   <si>
-    <t>16경 3407조 2583억 2586만</t>
+    <t>16경 3482조 2917억 4038만</t>
   </si>
   <si>
     <t>류텐</t>
@@ -1614,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
   </si>
   <si>
-    <t>11경 967조 1228억 2416만</t>
+    <t>11경 1134조 9782억 9886만</t>
   </si>
   <si>
     <t>철푸닥</t>
@@ -1641,7 +1641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>4경 3761조 4402억 4259만</t>
+    <t>4경 3775조 2422억 1501만</t>
   </si>
   <si>
     <t>무명장수</t>
@@ -1653,19 +1653,19 @@
     <t>3경 8230조 129억 3942만</t>
   </si>
   <si>
+    <t>ShellyCake</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
+  </si>
+  <si>
+    <t>3경 8008조 8507억 885만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
   </si>
   <si>
-    <t>3경 7517조 5238억 1395만</t>
-  </si>
-  <si>
-    <t>ShellyCake</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
-  </si>
-  <si>
-    <t>3경 1970조 8270억 3578만</t>
+    <t>3경 7541조 5343억 8574만</t>
   </si>
   <si>
     <t>오정구불독</t>
@@ -1674,7 +1674,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>2경 5391조 9478억 8415만</t>
+    <t>2경 6796조 5271억 834만</t>
   </si>
   <si>
     <t>구미적</t>
@@ -1701,7 +1701,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
   </si>
   <si>
-    <t>1경 6362조 2357억 396만</t>
+    <t>1경 6373조 1001억 1267만</t>
   </si>
   <si>
     <t>레드플레이어</t>
@@ -1731,7 +1731,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>1경 3485조 9289억 7088만</t>
+    <t>1경 3498조 1228억 8245만</t>
   </si>
   <si>
     <t>예슬a</t>
@@ -1758,7 +1758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
   </si>
   <si>
-    <t>9832조 2838억 3594만</t>
+    <t>1경 104조 6351억 3267만</t>
   </si>
   <si>
     <t>l빠다코코낫l</t>
@@ -1767,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
   </si>
   <si>
-    <t>9012조 9049억 5937만</t>
+    <t>9351조 5087억 2092만</t>
   </si>
   <si>
     <t>어꼬</t>
@@ -1806,7 +1806,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
   </si>
   <si>
-    <t>55경 1290조 9371억 566만</t>
+    <t>60경 1250조 6799억 3364만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -1824,7 +1824,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>38경 5252조 9280억 3174만</t>
+    <t>40경 4304조 1828억 2346만</t>
   </si>
   <si>
     <t>꿈넴</t>
@@ -1842,7 +1842,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>17경 759조 2722억 483만</t>
+    <t>17경 3074조 3031억 9529만</t>
   </si>
   <si>
     <t>쵸힝</t>
@@ -1851,7 +1851,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%ED%9E%9D</t>
   </si>
   <si>
-    <t>14경 8654조 5102억 3252만</t>
+    <t>15경 451조 9967억 4190만</t>
   </si>
   <si>
     <t>제껴</t>
@@ -1878,7 +1878,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A6%AC%EC%9E%90%EB%B2%A0%ED%83%80</t>
   </si>
   <si>
-    <t>6경 9851조 7013억 3773만</t>
+    <t>7경 2935조 8909억 2794만</t>
   </si>
   <si>
     <t>어흥이다</t>
@@ -1887,7 +1887,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>5경 8932조 2700억 5만</t>
+    <t>5경 9930조 7546억 7646만</t>
   </si>
   <si>
     <t>홍시마로</t>
@@ -1896,7 +1896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>5경 7960조 1793억 4161만</t>
+    <t>5경 9754조 8817억 6533만</t>
   </si>
   <si>
     <t>우꼬쨩</t>
@@ -1905,7 +1905,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
   </si>
   <si>
-    <t>5경 6343조 5570억 5250만</t>
+    <t>5경 7802조 7005억 849만</t>
+  </si>
+  <si>
+    <t>비밀키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
+  </si>
+  <si>
+    <t>5경 2218조 9204억 6242만</t>
   </si>
   <si>
     <t>누룽지룽누</t>
@@ -1917,15 +1926,6 @@
     <t>5경 1934조 9124억 872만</t>
   </si>
   <si>
-    <t>비밀키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B0%80%ED%82%A4</t>
-  </si>
-  <si>
-    <t>5경 1246조 2137억 2761만</t>
-  </si>
-  <si>
     <t>붙잡아</t>
   </si>
   <si>
@@ -1941,7 +1941,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EC%9A%94S2</t>
   </si>
   <si>
-    <t>3경 5201조 9327억 1655만</t>
+    <t>3경 5428조 8961억 2094만</t>
   </si>
   <si>
     <t>지아라떼</t>
@@ -1959,7 +1959,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
   </si>
   <si>
-    <t>2경 9772조 804억 7826만</t>
+    <t>3경 617조 6126억 28만</t>
   </si>
   <si>
     <t>득츈</t>
@@ -1968,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
   </si>
   <si>
-    <t>2경 8493조 1830억 1553만</t>
+    <t>2경 8563조 9501억 803만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -1977,7 +1977,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 7597조 4601억 8690만</t>
+    <t>2경 7627조 2560억 2545만</t>
   </si>
   <si>
     <t>메론맛빵</t>
@@ -1986,7 +1986,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
   </si>
   <si>
-    <t>2경 4697조 2793억 3690만</t>
+    <t>2경 4893조 2763억 3297만</t>
   </si>
   <si>
     <t>24년생정춘식</t>
@@ -2022,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>1경 2307조 1136억 2622만</t>
+    <t>1경 2412조 3771억 75만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -2031,7 +2031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>1경 2301조 882억 5255만</t>
+    <t>1경 2374조 5933억 2657만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -2040,7 +2040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>9939조 5019억 7240만</t>
+    <t>1경 1880조 2401억 581만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2058,7 +2058,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>21경 7020조 3459억 7096만</t>
+    <t>21경 7302조 4833억 6339만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2067,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>15경 4700조 6711억 800만</t>
+    <t>15경 5730조 448억 1455만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -2076,7 +2076,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>14경 58조 2490억 8844만</t>
+    <t>14경 690조 1312억 2596만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -2094,7 +2094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>11경 8642조 6219억 7620만</t>
+    <t>11경 8825조 5534억 2796만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -2103,7 +2103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>11경 4888조 1019억 6279만</t>
+    <t>11경 6866조 9746억 2508만</t>
   </si>
   <si>
     <t>약어</t>
@@ -2130,7 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>10경 5819조 998억 2162만</t>
+    <t>10경 7190조 7291억 7532만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -2148,7 +2148,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>3경 6499조 9571억 6070만</t>
+    <t>3경 7450조 581억 7381만</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>2경 9367조 1222억 1298만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -2160,15 +2169,6 @@
     <t>2경 9308조 5229억 9652만</t>
   </si>
   <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>2경 7153조 3284억 9878만</t>
-  </si>
-  <si>
     <t>햼쮸</t>
   </si>
   <si>
@@ -2178,6 +2178,15 @@
     <t>2경 6890조 4852억 886만</t>
   </si>
   <si>
+    <t>반가성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
+  </si>
+  <si>
+    <t>2경 5134조 9400억 165만</t>
+  </si>
+  <si>
     <t>관리</t>
   </si>
   <si>
@@ -2187,13 +2196,10 @@
     <t>2경 5040조 3923억 9599만</t>
   </si>
   <si>
-    <t>반가성</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
-  </si>
-  <si>
-    <t>2경 4866조 8388억 8718만</t>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>2경 2547조 8575억 1164만</t>
   </si>
   <si>
     <t>쌉새</t>
@@ -2214,19 +2220,13 @@
     <t>2경 1323조 7490억 7475만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>2경 671조 7972억 7324만</t>
-  </si>
-  <si>
     <t>망겜감별사</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>2경 163조 7355억 3124만</t>
+    <t>2경 172조 9067억 3680만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -2235,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 6061조 5억 9691만</t>
+    <t>1경 7267조 2707억 6942만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2280,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%8B%9D%EC%99%95</t>
   </si>
   <si>
-    <t>9504조 155억 3557만</t>
+    <t>9681조 3069억 4008만</t>
   </si>
   <si>
     <t>러너</t>
@@ -3195,10 +3195,10 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>107</v>
@@ -3227,10 +3227,10 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>112</v>
@@ -3294,7 +3294,7 @@
         <v>120</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>121</v>
@@ -3515,7 +3515,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>150</v>
@@ -3547,7 +3547,7 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>150</v>
@@ -3611,10 +3611,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>168</v>
@@ -3643,7 +3643,7 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>163</v>
@@ -3675,7 +3675,7 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>163</v>
@@ -3803,7 +3803,7 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>194</v>
@@ -3899,7 +3899,7 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>185</v>
@@ -3931,7 +3931,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>185</v>
@@ -3963,7 +3963,7 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>185</v>
@@ -3995,7 +3995,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>194</v>
@@ -4027,7 +4027,7 @@
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>224</v>
@@ -4208,7 +4208,7 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>95</v>
@@ -4368,7 +4368,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>139</v>
@@ -4400,7 +4400,7 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>139</v>
@@ -4464,7 +4464,7 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>144</v>
@@ -4560,7 +4560,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>150</v>
@@ -4592,7 +4592,7 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>144</v>
@@ -4656,7 +4656,7 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>150</v>
@@ -4688,7 +4688,7 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>163</v>
@@ -4784,7 +4784,7 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>203</v>
@@ -4816,7 +4816,7 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>247</v>
+        <v>111</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>203</v>
@@ -4848,7 +4848,7 @@
         <v>138</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>203</v>
@@ -5040,10 +5040,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>314</v>
@@ -5159,7 +5159,7 @@
         <v>301</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>317</v>
@@ -5380,10 +5380,10 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>337</v>
@@ -5412,10 +5412,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>340</v>
@@ -5476,7 +5476,7 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>139</v>
@@ -5540,7 +5540,7 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>150</v>
@@ -5572,7 +5572,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>144</v>
@@ -5636,7 +5636,7 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>163</v>
@@ -6171,7 +6171,7 @@
         <v>301</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>405</v>
@@ -6267,7 +6267,7 @@
         <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>414</v>
@@ -6296,7 +6296,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>144</v>
@@ -6328,7 +6328,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>144</v>
@@ -6360,7 +6360,7 @@
         <v>138</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>139</v>
@@ -6520,7 +6520,7 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>150</v>
@@ -6648,7 +6648,7 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>163</v>
@@ -6680,7 +6680,7 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>301</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>163</v>
@@ -6712,7 +6712,7 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>301</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>163</v>
@@ -6776,10 +6776,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>100</v>
+        <v>358</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>461</v>
@@ -6808,10 +6808,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>358</v>
+        <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>464</v>
@@ -6840,7 +6840,7 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>203</v>
@@ -6872,7 +6872,7 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>163</v>
@@ -7064,7 +7064,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>194</v>
@@ -7099,7 +7099,7 @@
         <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>491</v>
@@ -7248,7 +7248,7 @@
         <v>184</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>497</v>
@@ -7277,7 +7277,7 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>126</v>
@@ -7309,7 +7309,7 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>126</v>
@@ -7341,7 +7341,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>95</v>
@@ -7373,7 +7373,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>144</v>
@@ -7440,7 +7440,7 @@
         <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>515</v>
@@ -7469,7 +7469,7 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>139</v>
@@ -7597,7 +7597,7 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>163</v>
@@ -7629,7 +7629,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>185</v>
@@ -7693,7 +7693,7 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>203</v>
@@ -7713,25 +7713,25 @@
         <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7745,22 +7745,22 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>542</v>
+        <v>60</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>542</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>543</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>544</v>
@@ -7917,7 +7917,7 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>224</v>
@@ -7981,7 +7981,7 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>565</v>
@@ -8045,7 +8045,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>565</v>
@@ -8080,7 +8080,7 @@
         <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>565</v>
+        <v>224</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>575</v>
@@ -8109,7 +8109,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>565</v>
@@ -8258,7 +8258,7 @@
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>585</v>
@@ -8290,7 +8290,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>126</v>
@@ -8354,7 +8354,7 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>144</v>
@@ -8418,7 +8418,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>163</v>
@@ -8450,7 +8450,7 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>163</v>
@@ -8482,7 +8482,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>163</v>
@@ -8578,7 +8578,7 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>163</v>
@@ -8610,7 +8610,7 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>203</v>
@@ -8642,7 +8642,7 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>185</v>
@@ -8706,10 +8706,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>228</v>
+        <v>100</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>627</v>
@@ -8738,10 +8738,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
+        <v>228</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>630</v>
@@ -8802,7 +8802,7 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>194</v>
@@ -8834,7 +8834,7 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>185</v>
@@ -8866,7 +8866,7 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>194</v>
@@ -8930,7 +8930,7 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>185</v>
@@ -9026,7 +9026,7 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>224</v>
@@ -9122,7 +9122,7 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>224</v>
@@ -9154,7 +9154,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>224</v>
@@ -9558,7 +9558,7 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>194</v>
@@ -9622,7 +9622,7 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>185</v>
@@ -9654,10 +9654,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>708</v>
@@ -9686,10 +9686,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>711</v>
@@ -9718,7 +9718,7 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>194</v>
@@ -9750,7 +9750,7 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>194</v>
@@ -9782,7 +9782,7 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>194</v>
@@ -9802,25 +9802,25 @@
         <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>52</v>
@@ -9834,25 +9834,25 @@
         <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>52</v>
@@ -9866,22 +9866,22 @@
         <v>177</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>726</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>75</v>
+        <v>726</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>727</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>728</v>
@@ -9910,7 +9910,7 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>194</v>
@@ -9974,7 +9974,7 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>194</v>
@@ -10070,7 +10070,7 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>224</v>
@@ -10102,7 +10102,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>565</v>
@@ -10134,7 +10134,7 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>565</v>
@@ -10166,7 +10166,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>401</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -84,7 +84,7 @@
     <t>Scania 32</t>
   </si>
   <si>
-    <t>44</t>
+    <t>45</t>
   </si>
   <si>
     <t>1위</t>
@@ -117,66 +117,66 @@
     <t>Scania 25</t>
   </si>
   <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>1089경 6103조 5933억 8200만</t>
+  </si>
+  <si>
+    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
+  </si>
+  <si>
+    <t>설익은체리</t>
+  </si>
+  <si>
+    <t>리안</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>6위</t>
+  </si>
+  <si>
+    <t>26명</t>
+  </si>
+  <si>
+    <t>815경 6691조 2701억 4039만</t>
+  </si>
+  <si>
+    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
+  </si>
+  <si>
+    <t>예습2</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
+    <t>점프킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
+  </si>
+  <si>
+    <t>Scania 5</t>
+  </si>
+  <si>
     <t>47</t>
   </si>
   <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>1089경 6103조 5933억 8200만</t>
-  </si>
-  <si>
-    <t>랭킹 98위권이내 용사를 상시 모집중 문의는 설익은체리, 설앵숭, 너굴얌 귓주세요</t>
-  </si>
-  <si>
-    <t>설익은체리</t>
-  </si>
-  <si>
-    <t>리안</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A6%AC%EC%95%88</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>6위</t>
-  </si>
-  <si>
-    <t>26명</t>
-  </si>
-  <si>
-    <t>815경 6691조 2701억 4039만</t>
-  </si>
-  <si>
-    <t>길갑 문의 : 예습2 // 리안, 리원, 일식, Link 연합에 오실분 언제든지 귓주세요!</t>
-  </si>
-  <si>
-    <t>예습2</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
-    <t>점프킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A0%90%ED%94%84%ED%82%B9</t>
-  </si>
-  <si>
-    <t>Scania 5</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
     <t>28명</t>
   </si>
   <si>
@@ -225,7 +225,7 @@
     <t>Scania 34</t>
   </si>
   <si>
-    <t>52</t>
+    <t>54</t>
   </si>
   <si>
     <t>989경 8536조 5822억 5369만</t>
@@ -246,7 +246,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>67</t>
+    <t>68</t>
   </si>
   <si>
     <t>3위</t>
@@ -303,7 +303,7 @@
     <t>130</t>
   </si>
   <si>
-    <t>4652경 9832조 6027억 4356만</t>
+    <t>5387경 2122조 4703억 4705만</t>
   </si>
   <si>
     <t>2</t>
@@ -321,7 +321,7 @@
     <t>125</t>
   </si>
   <si>
-    <t>772경 1763조 9808억 747만</t>
+    <t>794경 837조 8313억 1001만</t>
   </si>
   <si>
     <t>3</t>
@@ -339,7 +339,7 @@
     <t>127</t>
   </si>
   <si>
-    <t>724경 1110조 2565억 6251만</t>
+    <t>737경 3162조 9417억 5869만</t>
   </si>
   <si>
     <t>4</t>
@@ -354,12 +354,24 @@
     <t>126</t>
   </si>
   <si>
-    <t>524경 8406조 8126억 916만</t>
+    <t>525경 5080조 4189억 3579만</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>루졔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
+  </si>
+  <si>
+    <t>493경 8108조 2877억 987만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>라온A</t>
   </si>
   <si>
@@ -372,18 +384,6 @@
     <t>473경 5821조 634억 9942만</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>루졔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
-  </si>
-  <si>
-    <t>457경 2033조 8056억 3611만</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -396,7 +396,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>303경 5181조 921억 7380만</t>
+    <t>306경 187조 364억 4234만</t>
   </si>
   <si>
     <t>8</t>
@@ -438,7 +438,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
   </si>
   <si>
-    <t>91경 5861조 7527억 789만</t>
+    <t>91경 6422조 5970억 8239만</t>
   </si>
   <si>
     <t>11</t>
@@ -468,7 +468,7 @@
     <t>122</t>
   </si>
   <si>
-    <t>39경 5201조 5822억 3551만</t>
+    <t>39경 5704조 2621억 6901만</t>
   </si>
   <si>
     <t>13</t>
@@ -480,348 +480,348 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%B8%8C%EC%AB%91</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>37경 8395조 8185억 9337만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>다다른</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EB%A5%B8</t>
+  </si>
+  <si>
+    <t>36경 5066조 5387억 1446만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>기뚠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9A%A0</t>
+  </si>
+  <si>
+    <t>27경 862조 3243억 9566만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>쌰갈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%B0%EA%B0%88</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>24경 5612조 9270억 2989만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>하싱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
+  </si>
+  <si>
+    <t>20경 6128조 605억 8781만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>911TurboS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
+  </si>
+  <si>
+    <t>20경 979조 9647억 4262만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>권도권</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B6%8C%EB%8F%84%EA%B6%8C</t>
+  </si>
+  <si>
+    <t>16경 3501조 8170억 5538만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>어쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EC%93%B0</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>12경 6570조 169억 9335만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>라온U</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8U</t>
+  </si>
+  <si>
+    <t>12경 5743조 1364억 3405만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>김라이트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>11경 5748조 7434억 5787만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>원탱구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>8경 9652조 2023억 1795만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>명품까칠공주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>8경 2767조 5503억 792만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>뿔피리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>7경 4867조 7844억 1323만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>최슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>6경 6287조 6681억 6245만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>오이겐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
+  </si>
+  <si>
+    <t>6경 4444조 6793억 932만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>탄지로네즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>5경 6305조 245억 4529만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>이솔빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>3경 4537조 2540억 5626만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>멀해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%80%ED%95%B4</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>2경 1774조 6860억 5595만</t>
+  </si>
+  <si>
+    <t>해물만두야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>328경 6580조 3693억 2845만</t>
+  </si>
+  <si>
+    <t>마옥지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
+  </si>
+  <si>
+    <t>313경 455조 738억 2646만</t>
+  </si>
+  <si>
+    <t>캐일리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>211경 2891조 6943억 5522만</t>
+  </si>
+  <si>
+    <t>설익은앵숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
+  </si>
+  <si>
+    <t>108경 7264조 7216억 8733만</t>
+  </si>
+  <si>
+    <t>킹규봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
+  </si>
+  <si>
+    <t>85경 8894조 1952억 8378만</t>
+  </si>
+  <si>
+    <t>설함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>85경 1758조 7933억 6869만</t>
+  </si>
+  <si>
+    <t>설봄a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>52경 6503조 4117억 4012만</t>
+  </si>
+  <si>
+    <t>루델밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>49경 6849조 3542억 4149만</t>
+  </si>
+  <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>48경 834조 2237억 8543만</t>
+  </si>
+  <si>
+    <t>너굴얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
+  </si>
+  <si>
+    <t>46경 1234조 9547억 1589만</t>
+  </si>
+  <si>
+    <t>싲프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
+  </si>
+  <si>
+    <t>43경 4087조 2616억 8828만</t>
+  </si>
+  <si>
+    <t>셀렘이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
+  </si>
+  <si>
     <t>섀도어</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>36경 3054조 2049억 1282만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>다다른</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EB%A5%B8</t>
-  </si>
-  <si>
-    <t>34경 7227조 6576억 9472만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>기뚠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9A%A0</t>
-  </si>
-  <si>
-    <t>26경 5219조 9479억 5871만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>쌰갈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%B0%EA%B0%88</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>24경 5612조 9270억 2989만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>911TurboS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
-  </si>
-  <si>
-    <t>19경 7032조 4166억 6865만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>하싱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
-  </si>
-  <si>
-    <t>19경 1040조 5815억 6292만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>권도권</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B6%8C%EB%8F%84%EA%B6%8C</t>
-  </si>
-  <si>
-    <t>15경 9952조 8757억 421만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>라온U</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8U</t>
-  </si>
-  <si>
-    <t>12경 5581조 102억 3350만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>어쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EC%93%B0</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>12경 4834조 5424억 2903만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>김라이트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>11경 5748조 7434억 5787만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>원탱구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>8경 6138조 2822억 5094만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>명품까칠공주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%ED%92%88%EA%B9%8C%EC%B9%A0%EA%B3%B5%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>8경 328조 23억 6866만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>뿔피리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>7경 2362조 8510억 5890만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>최슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>6경 6287조 6681억 6245만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>오이겐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
-  </si>
-  <si>
-    <t>6경 2419조 7292억 8393만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>탄지로네즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
-  </si>
-  <si>
-    <t>4경 7182조 1964억 3201만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>이솔빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>3경 4052조 589억 7648만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>멀해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%80%ED%95%B4</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>1경 9524조 5592억 9076만</t>
-  </si>
-  <si>
-    <t>해물만두야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>327경 4776조 4624억 1168만</t>
-  </si>
-  <si>
-    <t>마옥지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%98%A5%EC%A7%80</t>
-  </si>
-  <si>
-    <t>313경 455조 738억 2646만</t>
-  </si>
-  <si>
-    <t>캐일리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>210경 6123조 7929억 6399만</t>
-  </si>
-  <si>
-    <t>설익은앵숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
-  </si>
-  <si>
-    <t>105경 4731조 5416억 8730만</t>
-  </si>
-  <si>
-    <t>킹규봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EA%B7%9C%EB%B4%89</t>
-  </si>
-  <si>
-    <t>85경 8894조 1952억 8378만</t>
-  </si>
-  <si>
-    <t>설함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>84경 9267조 350억 9239만</t>
-  </si>
-  <si>
-    <t>설봄a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%B4%84a</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>49경 7963조 6315억 5223만</t>
-  </si>
-  <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>48경 834조 2237억 8543만</t>
-  </si>
-  <si>
-    <t>루델밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%8D%B8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>47경 6048조 4947억 5487만</t>
-  </si>
-  <si>
-    <t>너굴얌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
-  </si>
-  <si>
-    <t>45경 3070조 180억 2457만</t>
-  </si>
-  <si>
-    <t>싲프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
-  </si>
-  <si>
-    <t>43경 3521조 4818억 6066만</t>
-  </si>
-  <si>
-    <t>셀렘이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%85%80%EB%A0%98%EC%9D%B4</t>
-  </si>
-  <si>
     <t>30경 8477조 3049억 8265만</t>
   </si>
   <si>
@@ -831,7 +831,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
   </si>
   <si>
-    <t>29경 8815조 6254억 1077만</t>
+    <t>29경 9000조 7691억 9845만</t>
   </si>
   <si>
     <t>졸귀탱이</t>
@@ -840,7 +840,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>25경 7434조 5362억 6874만</t>
+    <t>25경 9048조 9137억 6237만</t>
   </si>
   <si>
     <t>선콜은차가워</t>
@@ -849,7 +849,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>22경 6600조 3273억 7460만</t>
+    <t>23경 271조 740억 6844만</t>
+  </si>
+  <si>
+    <t>설딩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
+  </si>
+  <si>
+    <t>22경 53조 2786억 4093만</t>
   </si>
   <si>
     <t>마덕칠</t>
@@ -858,16 +867,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
   </si>
   <si>
-    <t>21경 1083조 6548억 2511만</t>
-  </si>
-  <si>
-    <t>설딩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%94%A9</t>
-  </si>
-  <si>
-    <t>19경 7396조 2622억 1029만</t>
+    <t>21경 1097조 1193억 3732만</t>
   </si>
   <si>
     <t>슐아</t>
@@ -879,6 +879,15 @@
     <t>13경 5408조 677억 8062만</t>
   </si>
   <si>
+    <t>경성2018</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
+  </si>
+  <si>
+    <t>11경 3511조 6915억 9639만</t>
+  </si>
+  <si>
     <t>설름</t>
   </si>
   <si>
@@ -888,15 +897,6 @@
     <t>11경 597조 4783억 2861만</t>
   </si>
   <si>
-    <t>경성2018</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%84%B12018</t>
-  </si>
-  <si>
-    <t>10경 491조 6226억 4381만</t>
-  </si>
-  <si>
     <t>폰병</t>
   </si>
   <si>
@@ -912,7 +912,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
   </si>
   <si>
-    <t>7경 8669조 8739억 8330만</t>
+    <t>8경 4860조 7935억 5465만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
@@ -939,7 +939,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>4경 3134조 5060억 9315만</t>
+    <t>4경 4496조 5506억 6769만</t>
   </si>
   <si>
     <t>설치는정상인</t>
@@ -957,7 +957,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1경 9220조 489억 8804만</t>
+    <t>2경 2575조 1502억 1996만</t>
+  </si>
+  <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>2경 1203조 8776억 9257만</t>
   </si>
   <si>
     <t>읏코츠</t>
@@ -966,16 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%8F%EC%BD%94%EC%B8%A0</t>
   </si>
   <si>
-    <t>1경 7117조 902억 2574만</t>
-  </si>
-  <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>1경 6027조 3167억 6584만</t>
+    <t>1경 7890조 1857억 5839만</t>
   </si>
   <si>
     <t>군보</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>241경 9034조 1134억 4587만</t>
+    <t>242경 4492조 5481억 5041만</t>
   </si>
   <si>
     <t>눙키</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
   </si>
   <si>
-    <t>155경 2124조 8650억 1880만</t>
+    <t>159경 6237조 412억 6304만</t>
   </si>
   <si>
     <t>5형사</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>125경 7908조 7501억 1572만</t>
+    <t>130경 6841조 1416억 2597만</t>
   </si>
   <si>
     <t>심천</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%B2%9C</t>
   </si>
   <si>
-    <t>97경 1538조 6008억 9617만</t>
+    <t>112경 3155조 1555억 4633만</t>
   </si>
   <si>
     <t>또르뱅</t>
@@ -1044,7 +1044,7 @@
     <t>https://mgf.gg/contents/character.php?n=Matter</t>
   </si>
   <si>
-    <t>79경 1432조 4502억 656만</t>
+    <t>79경 6985조 8943억 295만</t>
   </si>
   <si>
     <t>혁수킹</t>
@@ -1062,7 +1062,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>63경 3184조 6519억 9192만</t>
+    <t>63경 4075조 3875억 532만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1080,7 +1080,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>42경 8688조 2278억 7710만</t>
+    <t>45경 4543조 4529억 2283만</t>
   </si>
   <si>
     <t>김나뭉</t>
@@ -1089,7 +1089,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
   </si>
   <si>
-    <t>38경 3412조 1308억 2922만</t>
+    <t>43경 3364조 9068억 9748만</t>
   </si>
   <si>
     <t>파퍼</t>
@@ -1098,7 +1098,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>35경 4539조 4314억 6832만</t>
+    <t>35경 5809조 5994억 5303만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
   </si>
   <si>
-    <t>21경 2840조 2799억 4120만</t>
+    <t>22경 5106조 4794억 8592만</t>
   </si>
   <si>
     <t>껌정색</t>
@@ -1128,7 +1128,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>21경 558조 4879억 3565만</t>
+    <t>21경 4606조 2985억 6200만</t>
+  </si>
+  <si>
+    <t>이삼2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
+  </si>
+  <si>
+    <t>17경 7868조 8541억 7857만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1137,16 +1146,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>16경 669조 7431억 5151만</t>
-  </si>
-  <si>
-    <t>이삼2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
-  </si>
-  <si>
-    <t>15경 1396조 8929억 8493만</t>
+    <t>16경 8826조 4748억 6178만</t>
   </si>
   <si>
     <t>Rahee</t>
@@ -1173,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EB%A8%80%EC%B8%A0%EB%82%98%EB%82%98</t>
   </si>
   <si>
-    <t>7경 7681조 4092억 2482만</t>
+    <t>10경 1273조 8713억 2283만</t>
   </si>
   <si>
     <t>딤개</t>
@@ -1182,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%A4%EA%B0%9C</t>
   </si>
   <si>
-    <t>6경 8742조 2511억 982만</t>
+    <t>7경 2731조 5749억 454만</t>
   </si>
   <si>
     <t>히째히째</t>
@@ -1191,7 +1191,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%A7%B8%ED%9E%88%EC%A7%B8</t>
   </si>
   <si>
-    <t>5경 4655조 9844억 8425만</t>
+    <t>5경 6976조 4397억 4712만</t>
   </si>
   <si>
     <t>돌로레스</t>
@@ -1209,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EB%BC%881</t>
   </si>
   <si>
-    <t>4경 5865조 4491억 3978만</t>
+    <t>4경 5875조 1960억 1913만</t>
   </si>
   <si>
     <t>바람의새벽</t>
@@ -1218,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EB%9E%8C%EC%9D%98%EC%83%88%EB%B2%BD</t>
   </si>
   <si>
-    <t>3경 3005조 224억 1873만</t>
+    <t>3경 5713조 1148억 7277만</t>
   </si>
   <si>
     <t>김도유니</t>
@@ -1227,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 4995조 6278억 530만</t>
+    <t>2경 5108조 6499억 745만</t>
   </si>
   <si>
     <t>셀러문</t>
@@ -1239,7 +1239,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>5720조 4385억 5631만</t>
+    <t>6797조 5335억 192만</t>
   </si>
   <si>
     <t>라온XR</t>
@@ -1248,7 +1248,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8XR</t>
   </si>
   <si>
-    <t>454경 1026조 4435억 4176만</t>
+    <t>454경 5472조 3155억 6098만</t>
   </si>
   <si>
     <t>매스몬스터</t>
@@ -1257,7 +1257,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%AA%AC%EC%8A%A4%ED%84%B0</t>
   </si>
   <si>
-    <t>310경 7797조 9067억 1436만</t>
+    <t>320경 3624조 3323억 5290만</t>
   </si>
   <si>
     <t>코코듀</t>
@@ -1266,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EB%93%80</t>
   </si>
   <si>
-    <t>271경 4872조 1237억 8091만</t>
+    <t>310경 8777조 36억 2277만</t>
   </si>
   <si>
     <t>하잉안파파</t>
@@ -1275,7 +1275,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>214경 8640조 8349억 94만</t>
+    <t>215경 4240조 1784억 5997만</t>
   </si>
   <si>
     <t>미야고</t>
@@ -1287,19 +1287,19 @@
     <t>75경 6496조 2635억 7111만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
+  </si>
+  <si>
+    <t>68경 1747조 6461억 7855만</t>
+  </si>
+  <si>
     <t>타이슨에어랩</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
   </si>
   <si>
-    <t>65경 2398조 5777억 7860만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
-  </si>
-  <si>
-    <t>63경 7536조 6392억 240만</t>
+    <t>66경 7741조 9342억 6599만</t>
   </si>
   <si>
     <t>캔드릭</t>
@@ -1308,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%93%9C%EB%A6%AD</t>
   </si>
   <si>
-    <t>55경 7456조 4185억 4050만</t>
+    <t>60경 4389조 204억 5041만</t>
   </si>
   <si>
     <t>용보이</t>
@@ -1317,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>40경 1808조 7292억 5672만</t>
+    <t>41경 1142조 6638억 7569만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -1326,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
   </si>
   <si>
-    <t>27경 1636조 7187억 4799만</t>
+    <t>28경 5937조 9272억 363만</t>
   </si>
   <si>
     <t>똥갈</t>
@@ -1335,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
   </si>
   <si>
-    <t>22경 6071조 9791억 2753만</t>
+    <t>22경 9082조 2323억 40만</t>
   </si>
   <si>
     <t>도농롱</t>
@@ -1362,7 +1362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B6%88</t>
   </si>
   <si>
-    <t>10경 4347조 7092억 1106만</t>
+    <t>10경 5538조 9382억 9588만</t>
   </si>
   <si>
     <t>힐옹</t>
@@ -1374,13 +1374,40 @@
     <t>9경 6843조 1983억 2212만</t>
   </si>
   <si>
+    <t>망치반죽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
+  </si>
+  <si>
+    <t>8경 9988조 8441억 435만</t>
+  </si>
+  <si>
     <t>혜도로동</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>8경 3467조 394억 1386만</t>
+    <t>8경 5957조 769억 8735만</t>
+  </si>
+  <si>
+    <t>조명준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
+  </si>
+  <si>
+    <t>8경 4714조 9464억 2292만</t>
+  </si>
+  <si>
+    <t>붕어줍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EC%96%B4%EC%A4%8D</t>
+  </si>
+  <si>
+    <t>8경 2905조 1142억 9827만</t>
   </si>
   <si>
     <t>로생</t>
@@ -1389,25 +1416,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
   </si>
   <si>
-    <t>8경 637조 1812억 1337만</t>
-  </si>
-  <si>
-    <t>조명준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EB%AA%85%EC%A4%80</t>
-  </si>
-  <si>
-    <t>8경 231조 8243억 62만</t>
-  </si>
-  <si>
-    <t>붕어줍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EC%96%B4%EC%A4%8D</t>
-  </si>
-  <si>
-    <t>7경 9371조 9978억 5340만</t>
+    <t>8경 688조 2694억 1162만</t>
   </si>
   <si>
     <t>이다연</t>
@@ -1416,16 +1425,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8B%A4%EC%97%B0</t>
   </si>
   <si>
-    <t>7경 5117조 6651억 2785만</t>
-  </si>
-  <si>
-    <t>망치반죽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%B0%98%EC%A3%BD</t>
-  </si>
-  <si>
-    <t>7경 4699조 2289억 8513만</t>
+    <t>7경 9155조 6068억 8038만</t>
   </si>
   <si>
     <t>Redwine</t>
@@ -1437,13 +1437,22 @@
     <t>6경 4285조 9023억 3568만</t>
   </si>
   <si>
+    <t>슬램걸고싶다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%AC%EB%9E%A8%EA%B1%B8%EA%B3%A0%EC%8B%B6%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>5경 6578조 5456억 2553만</t>
+  </si>
+  <si>
     <t>유도로동</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>5경 1251조 9582억 734만</t>
+    <t>5경 3121조 3619억 4625만</t>
   </si>
   <si>
     <t>메키메렁</t>
@@ -1452,7 +1461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%A9%94%EB%A0%81</t>
   </si>
   <si>
-    <t>3경 7907조 5797억 6079만</t>
+    <t>4경 7731조 3789억 8389만</t>
   </si>
   <si>
     <t>그때그아이</t>
@@ -1461,7 +1470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C%EA%B7%B8%EC%95%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>3경 3569조 7127억 1943만</t>
+    <t>3경 4260조 922억 9279만</t>
   </si>
   <si>
     <t>루빙</t>
@@ -1470,7 +1479,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%B9%99</t>
   </si>
   <si>
-    <t>2경 6370조 4168억 6332만</t>
+    <t>2경 7517조 5334억 7995만</t>
   </si>
   <si>
     <t>spemi</t>
@@ -1479,7 +1488,7 @@
     <t>https://mgf.gg/contents/character.php?n=spemi</t>
   </si>
   <si>
-    <t>2경 3473조 1307억 4807만</t>
+    <t>2경 4358조 7712억 372만</t>
   </si>
   <si>
     <t>우솝이</t>
@@ -1488,7 +1497,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%86%9D%EC%9D%B4</t>
   </si>
   <si>
-    <t>2경 1610조 9921억 4920만</t>
+    <t>2경 2053조 5195억 1167만</t>
   </si>
   <si>
     <t>꽁꽁얼었다</t>
@@ -1500,22 +1509,13 @@
     <t>2경 415조 4230억 7944만</t>
   </si>
   <si>
-    <t>막또날드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EB%98%90%EB%82%A0%EB%93%9C</t>
-  </si>
-  <si>
-    <t>1경 8603조 1535억 9902만</t>
-  </si>
-  <si>
     <t>강서구도적</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
   </si>
   <si>
-    <t>679경 943조 6015억 8001만</t>
+    <t>706경 991조 751억 258만</t>
   </si>
   <si>
     <t>따코유</t>
@@ -1524,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EC%BD%94%EC%9C%A0</t>
   </si>
   <si>
-    <t>522경 3546조 7664억 309만</t>
+    <t>544경 1300조 2761억 1854만</t>
   </si>
   <si>
     <t>뚱털</t>
@@ -1533,7 +1533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%ED%84%B8</t>
   </si>
   <si>
-    <t>181경 6712조 2417억 2927만</t>
+    <t>205경 5491조 7303억 6657만</t>
   </si>
   <si>
     <t>뽀로로남편</t>
@@ -1542,7 +1542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%A1%9C%EB%A1%9C%EB%82%A8%ED%8E%B8</t>
   </si>
   <si>
-    <t>134경 7012조 3547억 2108만</t>
+    <t>136경 9217조 2501억 9713만</t>
   </si>
   <si>
     <t>귤놈펜</t>
@@ -1551,7 +1551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
   </si>
   <si>
-    <t>93경 7321조 9719억 7004만</t>
+    <t>94경 2583조 6202억 8642만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -1560,7 +1560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>37경 2711조 860억 7892만</t>
+    <t>37경 3180조 5239억 8831만</t>
   </si>
   <si>
     <t>꿀서은</t>
@@ -1578,7 +1578,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
   </si>
   <si>
-    <t>28경 617조 3727억 4589만</t>
+    <t>31경 8709조 9997억 7176만</t>
+  </si>
+  <si>
+    <t>긴나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>27경 4046조 5855억 40만</t>
   </si>
   <si>
     <t>게탕</t>
@@ -1587,16 +1596,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
   </si>
   <si>
-    <t>26경 8012조 8701억 5274만</t>
-  </si>
-  <si>
-    <t>긴나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B4%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>25경 2727조 4212억 3136만</t>
+    <t>27경 2777조 7266억 7081만</t>
   </si>
   <si>
     <t>우둉</t>
@@ -1605,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
   </si>
   <si>
-    <t>16경 3482조 2917억 4038만</t>
+    <t>16경 3697조 1170억 5197만</t>
   </si>
   <si>
     <t>류텐</t>
@@ -1614,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
   </si>
   <si>
-    <t>11경 1134조 9782억 9886만</t>
+    <t>11경 1334조 2299억 8589만</t>
   </si>
   <si>
     <t>철푸닥</t>
@@ -1641,7 +1641,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>4경 3775조 2422억 1501만</t>
+    <t>4경 5657조 9888억 5026만</t>
+  </si>
+  <si>
+    <t>ShellyCake</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
+  </si>
+  <si>
+    <t>4경 155조 6311억 7109만</t>
   </si>
   <si>
     <t>무명장수</t>
@@ -1653,15 +1662,6 @@
     <t>3경 8230조 129억 3942만</t>
   </si>
   <si>
-    <t>ShellyCake</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ShellyCake</t>
-  </si>
-  <si>
-    <t>3경 8008조 8507억 885만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
   </si>
   <si>
@@ -1674,7 +1674,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>2경 6796조 5271억 834만</t>
+    <t>2경 7345조 5580억 8128만</t>
   </si>
   <si>
     <t>구미적</t>
@@ -1683,7 +1683,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
   </si>
   <si>
-    <t>2경 3716조 4918억 7788만</t>
+    <t>2경 6274조 6582억 7329만</t>
   </si>
   <si>
     <t>양덕하늘채</t>
@@ -1692,7 +1692,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%8D%95%ED%95%98%EB%8A%98%EC%B1%84</t>
   </si>
   <si>
-    <t>2경 2355조 9466억 8668만</t>
+    <t>2경 2746조 1840억 1492만</t>
+  </si>
+  <si>
+    <t>레드플레이어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
+  </si>
+  <si>
+    <t>1경 7457조 4642억 7972만</t>
   </si>
   <si>
     <t>검샷</t>
@@ -1704,22 +1713,13 @@
     <t>1경 6373조 1001억 1267만</t>
   </si>
   <si>
-    <t>레드플레이어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
-  </si>
-  <si>
-    <t>1경 6193조 932억 131만</t>
-  </si>
-  <si>
     <t>주하사랑</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
   </si>
   <si>
-    <t>1경 5655조 2869억 5063만</t>
+    <t>1경 5703조 8094억 4499만</t>
   </si>
   <si>
     <t>장아린</t>
@@ -1731,7 +1731,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>1경 3498조 1228억 8245만</t>
+    <t>1경 4048조 6845억 80만</t>
   </si>
   <si>
     <t>예슬a</t>
@@ -1752,6 +1752,15 @@
     <t>1경 2238조 8084억 982만</t>
   </si>
   <si>
+    <t>l빠다코코낫l</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
+  </si>
+  <si>
+    <t>1경 569조 4651억 2938만</t>
+  </si>
+  <si>
     <t>꼬기갓</t>
   </si>
   <si>
@@ -1761,15 +1770,6 @@
     <t>1경 104조 6351억 3267만</t>
   </si>
   <si>
-    <t>l빠다코코낫l</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=l%EB%B9%A0%EB%8B%A4%EC%BD%94%EC%BD%94%EB%82%ABl</t>
-  </si>
-  <si>
-    <t>9351조 5087억 2092만</t>
-  </si>
-  <si>
     <t>어꼬</t>
   </si>
   <si>
@@ -1779,7 +1779,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>4380조 4821억 2206만</t>
+    <t>4459조 1427억 6199만</t>
   </si>
   <si>
     <t>금은동S2</t>
@@ -1800,13 +1800,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>92경 5900조 2551억 7147만</t>
+    <t>95경 455조 5952억 2475만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
   </si>
   <si>
-    <t>60경 1250조 6799억 3364만</t>
+    <t>62경 2180조 2928억 8211만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -1815,7 +1815,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
   </si>
   <si>
-    <t>44경 1846조 225억 1643만</t>
+    <t>45경 4192조 3310억 5895만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -1824,7 +1824,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>40경 4304조 1828억 2346만</t>
+    <t>40경 4833조 5385억 5875만</t>
+  </si>
+  <si>
+    <t>임홀리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>19경 9600조 7967억 5258만</t>
   </si>
   <si>
     <t>꿈넴</t>
@@ -1836,22 +1845,13 @@
     <t>18경 6696조 2939억 1690만</t>
   </si>
   <si>
-    <t>임홀리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>17경 3074조 3031억 9529만</t>
-  </si>
-  <si>
     <t>쵸힝</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%B8%ED%9E%9D</t>
   </si>
   <si>
-    <t>15경 451조 9967억 4190만</t>
+    <t>15경 5537조 184억 5066만</t>
   </si>
   <si>
     <t>제껴</t>
@@ -1860,7 +1860,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>13경 3240조 9880억 4681만</t>
+    <t>13경 3733조 5109억 1126만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -1869,7 +1869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%B8%8C%EB%A3%A8%EB%AF%80</t>
   </si>
   <si>
-    <t>10경 7974조 5167억 8349만</t>
+    <t>11경 5115조 4054억 503만</t>
   </si>
   <si>
     <t>엘리자베타</t>
@@ -1881,13 +1881,22 @@
     <t>7경 2935조 8909억 2794만</t>
   </si>
   <si>
+    <t>우꼬쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>6경 6789조 8345억 1257만</t>
+  </si>
+  <si>
     <t>어흥이다</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>5경 9930조 7546억 7646만</t>
+    <t>6경 2418조 8011억 6602만</t>
   </si>
   <si>
     <t>홍시마로</t>
@@ -1896,16 +1905,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>5경 9754조 8817억 6533만</t>
-  </si>
-  <si>
-    <t>우꼬쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EA%BC%AC%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>5경 7802조 7005억 849만</t>
+    <t>6경 225조 2279억 5188만</t>
   </si>
   <si>
     <t>비밀키</t>
@@ -1941,7 +1941,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EC%9A%94S2</t>
   </si>
   <si>
-    <t>3경 5428조 8961억 2094만</t>
+    <t>3경 5785조 6974억 2480만</t>
   </si>
   <si>
     <t>지아라떼</t>
@@ -1950,7 +1950,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%84%EB%9D%BC%EB%96%BC</t>
   </si>
   <si>
-    <t>3경 2561조 2843억 5580만</t>
+    <t>3경 3692조 9777억 2081만</t>
   </si>
   <si>
     <t>o엔젤o</t>
@@ -1959,7 +1959,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
   </si>
   <si>
-    <t>3경 617조 6126억 28만</t>
+    <t>3경 885조 6927억 5847만</t>
   </si>
   <si>
     <t>득츈</t>
@@ -1968,7 +1968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
   </si>
   <si>
-    <t>2경 8563조 9501억 803만</t>
+    <t>2경 9496조 7293억 5394만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -1977,7 +1977,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 7627조 2560억 2545만</t>
+    <t>2경 7705조 3970억 8456만</t>
   </si>
   <si>
     <t>메론맛빵</t>
@@ -1986,7 +1986,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
   </si>
   <si>
-    <t>2경 4893조 2763억 3297만</t>
+    <t>2경 5860조 6045억 1625만</t>
   </si>
   <si>
     <t>24년생정춘식</t>
@@ -2004,7 +2004,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
   </si>
   <si>
-    <t>1경 9561조 2569억 6775만</t>
+    <t>2경 1430조 5034억 5137만</t>
   </si>
   <si>
     <t>야옹이다</t>
@@ -2013,7 +2013,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>1경 4460조 4049억 9777만</t>
+    <t>1경 4641조 2961억 1660만</t>
+  </si>
+  <si>
+    <t>쏨열무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>1경 3819조 1163억 3040만</t>
+  </si>
+  <si>
+    <t>김똔똔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
+  </si>
+  <si>
+    <t>1경 3164조 452억 8533만</t>
   </si>
   <si>
     <t>출장괴물</t>
@@ -2022,25 +2040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>1경 2412조 3771억 75만</t>
-  </si>
-  <si>
-    <t>쏨열무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>1경 2374조 5933억 2657만</t>
-  </si>
-  <si>
-    <t>김똔똔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
-  </si>
-  <si>
-    <t>1경 1880조 2401억 581만</t>
+    <t>1경 2904조 6670억 4809만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2058,7 +2058,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>21경 7302조 4833억 6339만</t>
+    <t>22경 2505조 4602억 7523만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2067,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>15경 5730조 448억 1455만</t>
+    <t>17경 52조 8420억 7637만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -2076,7 +2076,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>14경 690조 1312억 2596만</t>
+    <t>15경 597조 6267억 475만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -2094,7 +2094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>11경 8825조 5534억 2796만</t>
+    <t>12경 5826조 5892억 4855만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -2103,7 +2103,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>11경 6866조 9746억 2508만</t>
+    <t>11경 6917조 3716억 5120만</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>11경 6350조 3056억 807만</t>
   </si>
   <si>
     <t>약어</t>
@@ -2112,16 +2121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>11경 2257조 8652억 5666만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>10경 9321조 7447억 9515만</t>
+    <t>11경 3842조 9237억 9346만</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -2148,7 +2148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>3경 7450조 581억 7381만</t>
+    <t>3경 8632조 99억 5133만</t>
   </si>
   <si>
     <t>세아수호지호</t>
@@ -2157,7 +2157,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
   </si>
   <si>
-    <t>2경 9367조 1222억 1298만</t>
+    <t>3경 1701조 3081억 8178만</t>
   </si>
   <si>
     <t>핫잇</t>
@@ -2166,7 +2166,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>2경 9308조 5229억 9652만</t>
+    <t>3경 840조 2334억 2295만</t>
   </si>
   <si>
     <t>햼쮸</t>
@@ -2184,7 +2184,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>2경 5134조 9400억 165만</t>
+    <t>2경 6498조 7288억 2348만</t>
   </si>
   <si>
     <t>관리</t>
@@ -2226,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>2경 172조 9067억 3680만</t>
+    <t>2경 587조 4899억 6523만</t>
   </si>
   <si>
     <t>니뚜</t>
@@ -2235,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 7267조 2707억 6942만</t>
+    <t>1경 8285조 5498억 2142만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2271,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 1990조 4206억 1101만</t>
+    <t>1경 2003조 3345억 4261만</t>
   </si>
   <si>
     <t>초식왕</t>
@@ -2280,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%8B%9D%EC%99%95</t>
   </si>
   <si>
-    <t>9681조 3069억 4008만</t>
+    <t>9689조 32억 7248만</t>
   </si>
   <si>
     <t>러너</t>
@@ -2289,7 +2289,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>7346조 6925억 44만</t>
+    <t>7704조 70억 5986만</t>
   </si>
   <si>
     <t>해찬나래</t>
@@ -2310,7 +2310,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>2324조 3357억 547만</t>
+    <t>2336조 587억 4111만</t>
   </si>
 </sst>
 </file>
@@ -3227,13 +3227,13 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3244,25 +3244,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>116</v>
@@ -3483,13 +3483,13 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3500,28 +3500,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3532,28 +3532,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3564,16 +3564,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>87</v>
@@ -3582,10 +3582,10 @@
         <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3596,28 +3596,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3628,28 +3628,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3660,28 +3660,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3692,28 +3692,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3724,28 +3724,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3756,16 +3756,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>87</v>
@@ -3774,10 +3774,10 @@
         <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3788,28 +3788,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3820,16 +3820,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -3838,10 +3838,10 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3852,16 +3852,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -3870,10 +3870,10 @@
         <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3884,28 +3884,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3916,28 +3916,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3948,28 +3948,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3980,28 +3980,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4012,28 +4012,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4132,25 +4132,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4164,25 +4164,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4196,25 +4196,25 @@
         <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="F4" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4228,13 +4228,13 @@
         <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>87</v>
@@ -4246,7 +4246,7 @@
         <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4260,13 +4260,13 @@
         <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -4278,7 +4278,7 @@
         <v>139</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4289,16 +4289,16 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -4310,7 +4310,7 @@
         <v>139</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4324,25 +4324,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4356,25 +4356,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4388,25 +4388,25 @@
         <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="F10" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4420,13 +4420,13 @@
         <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>87</v>
@@ -4438,7 +4438,7 @@
         <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4452,25 +4452,25 @@
         <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="F12" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4484,22 +4484,22 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>263</v>
@@ -4545,7 +4545,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>267</v>
@@ -4560,10 +4560,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>269</v>
@@ -4577,7 +4577,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>270</v>
@@ -4592,7 +4592,7 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>144</v>
@@ -4609,7 +4609,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>273</v>
@@ -4624,10 +4624,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>275</v>
@@ -4641,7 +4641,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>276</v>
@@ -4656,10 +4656,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>278</v>
@@ -4673,7 +4673,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>279</v>
@@ -4688,10 +4688,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>281</v>
@@ -4705,7 +4705,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>282</v>
@@ -4720,10 +4720,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>284</v>
@@ -4737,7 +4737,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>285</v>
@@ -4752,10 +4752,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>287</v>
@@ -4769,7 +4769,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>288</v>
@@ -4784,10 +4784,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>290</v>
@@ -4801,7 +4801,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>291</v>
@@ -4816,10 +4816,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>293</v>
@@ -4833,7 +4833,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>33</v>
@@ -4848,10 +4848,10 @@
         <v>138</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>295</v>
@@ -4865,7 +4865,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>296</v>
@@ -4883,7 +4883,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>298</v>
@@ -4897,7 +4897,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>299</v>
@@ -4915,7 +4915,7 @@
         <v>301</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>302</v>
@@ -4929,7 +4929,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>303</v>
@@ -4944,10 +4944,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>305</v>
@@ -4961,7 +4961,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>306</v>
@@ -4976,10 +4976,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>308</v>
@@ -4993,7 +4993,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>309</v>
@@ -5008,10 +5008,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>311</v>
@@ -5025,7 +5025,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>312</v>
@@ -5040,10 +5040,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>314</v>
@@ -5301,7 +5301,7 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>330</v>
@@ -5348,7 +5348,7 @@
         <v>138</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>139</v>
@@ -5380,7 +5380,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>126</v>
@@ -5476,7 +5476,7 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>139</v>
@@ -5511,7 +5511,7 @@
         <v>120</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>349</v>
@@ -5540,10 +5540,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>352</v>
@@ -5557,7 +5557,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>353</v>
@@ -5572,7 +5572,7 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>144</v>
@@ -5589,7 +5589,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>356</v>
@@ -5621,7 +5621,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>360</v>
@@ -5636,10 +5636,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>362</v>
@@ -5653,7 +5653,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>363</v>
@@ -5668,10 +5668,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>365</v>
@@ -5685,7 +5685,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>366</v>
@@ -5700,10 +5700,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>368</v>
@@ -5717,7 +5717,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>369</v>
@@ -5732,10 +5732,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>371</v>
@@ -5749,7 +5749,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>372</v>
@@ -5767,7 +5767,7 @@
         <v>125</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>374</v>
@@ -5781,7 +5781,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>375</v>
@@ -5799,7 +5799,7 @@
         <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>377</v>
@@ -5813,7 +5813,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>378</v>
@@ -5831,7 +5831,7 @@
         <v>120</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>380</v>
@@ -5845,7 +5845,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>381</v>
@@ -5863,7 +5863,7 @@
         <v>358</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>383</v>
@@ -5877,7 +5877,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>384</v>
@@ -5895,7 +5895,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>386</v>
@@ -5909,7 +5909,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>387</v>
@@ -5927,7 +5927,7 @@
         <v>125</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>389</v>
@@ -5941,7 +5941,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>390</v>
@@ -5959,7 +5959,7 @@
         <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>392</v>
@@ -5973,7 +5973,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>393</v>
@@ -5988,10 +5988,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>395</v>
@@ -6005,7 +6005,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>396</v>
@@ -6023,7 +6023,7 @@
         <v>301</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>398</v>
@@ -6037,7 +6037,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>399</v>
@@ -6052,7 +6052,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>401</v>
@@ -6296,7 +6296,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>144</v>
@@ -6313,28 +6313,28 @@
         <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>52</v>
@@ -6348,22 +6348,22 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>420</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>420</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>421</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>422</v>
@@ -6392,7 +6392,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>144</v>
@@ -6459,7 +6459,7 @@
         <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>431</v>
@@ -6491,7 +6491,7 @@
         <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>434</v>
@@ -6520,10 +6520,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>437</v>
@@ -6555,7 +6555,7 @@
         <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>440</v>
@@ -6569,7 +6569,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>441</v>
@@ -6587,7 +6587,7 @@
         <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>443</v>
@@ -6601,7 +6601,7 @@
         <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>444</v>
@@ -6619,7 +6619,7 @@
         <v>125</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>446</v>
@@ -6633,7 +6633,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>447</v>
@@ -6648,10 +6648,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>449</v>
@@ -6665,7 +6665,7 @@
         <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>450</v>
@@ -6680,10 +6680,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>452</v>
@@ -6697,7 +6697,7 @@
         <v>44</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>453</v>
@@ -6715,7 +6715,7 @@
         <v>301</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>455</v>
@@ -6729,7 +6729,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>456</v>
@@ -6747,7 +6747,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>458</v>
@@ -6761,7 +6761,7 @@
         <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>459</v>
@@ -6776,10 +6776,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>358</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>461</v>
@@ -6793,7 +6793,7 @@
         <v>44</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>462</v>
@@ -6808,10 +6808,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
+        <v>358</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>464</v>
@@ -6825,7 +6825,7 @@
         <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>465</v>
@@ -6840,10 +6840,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>467</v>
@@ -6857,7 +6857,7 @@
         <v>44</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>468</v>
@@ -6872,10 +6872,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>470</v>
@@ -6889,7 +6889,7 @@
         <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>471</v>
@@ -6904,10 +6904,10 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>473</v>
@@ -6921,7 +6921,7 @@
         <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>474</v>
@@ -6936,10 +6936,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>247</v>
+        <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>476</v>
@@ -6953,7 +6953,7 @@
         <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>477</v>
@@ -6968,10 +6968,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>125</v>
+        <v>246</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>479</v>
@@ -6985,7 +6985,7 @@
         <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>480</v>
@@ -7000,10 +7000,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>358</v>
+        <v>125</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>482</v>
@@ -7017,7 +7017,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>483</v>
@@ -7032,10 +7032,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>184</v>
+        <v>358</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>485</v>
@@ -7049,7 +7049,7 @@
         <v>44</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>486</v>
@@ -7064,10 +7064,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>488</v>
@@ -7081,7 +7081,7 @@
         <v>44</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>489</v>
@@ -7096,10 +7096,10 @@
         <v>87</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>491</v>
@@ -7245,7 +7245,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>106</v>
@@ -7277,7 +7277,7 @@
         <v>87</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>126</v>
@@ -7309,7 +7309,7 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>126</v>
@@ -7341,7 +7341,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>95</v>
@@ -7358,7 +7358,7 @@
         <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>507</v>
@@ -7373,7 +7373,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>144</v>
@@ -7405,7 +7405,7 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>144</v>
@@ -7440,7 +7440,7 @@
         <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>515</v>
@@ -7469,10 +7469,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>518</v>
@@ -7501,10 +7501,10 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>521</v>
@@ -7536,7 +7536,7 @@
         <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>524</v>
@@ -7568,7 +7568,7 @@
         <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>527</v>
@@ -7597,10 +7597,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>530</v>
@@ -7614,7 +7614,7 @@
         <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>531</v>
@@ -7629,10 +7629,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>533</v>
@@ -7646,7 +7646,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>534</v>
@@ -7661,10 +7661,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>536</v>
@@ -7678,7 +7678,7 @@
         <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>537</v>
@@ -7693,10 +7693,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>539</v>
@@ -7710,7 +7710,7 @@
         <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>540</v>
@@ -7725,10 +7725,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>542</v>
@@ -7742,7 +7742,7 @@
         <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>60</v>
@@ -7757,10 +7757,10 @@
         <v>138</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>544</v>
@@ -7774,7 +7774,7 @@
         <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>545</v>
@@ -7792,7 +7792,7 @@
         <v>358</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>547</v>
@@ -7806,7 +7806,7 @@
         <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>548</v>
@@ -7821,10 +7821,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>550</v>
@@ -7838,7 +7838,7 @@
         <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>551</v>
@@ -7856,7 +7856,7 @@
         <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>553</v>
@@ -7870,7 +7870,7 @@
         <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>554</v>
@@ -7885,10 +7885,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>556</v>
@@ -7902,7 +7902,7 @@
         <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>557</v>
@@ -7917,10 +7917,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>559</v>
@@ -7934,7 +7934,7 @@
         <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>560</v>
@@ -7952,7 +7952,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>562</v>
@@ -7966,7 +7966,7 @@
         <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>563</v>
@@ -7981,7 +7981,7 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>565</v>
@@ -7998,7 +7998,7 @@
         <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>567</v>
@@ -8013,7 +8013,7 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>565</v>
@@ -8030,7 +8030,7 @@
         <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>570</v>
@@ -8045,7 +8045,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>565</v>
@@ -8062,7 +8062,7 @@
         <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>573</v>
@@ -8077,10 +8077,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>224</v>
+        <v>565</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>575</v>
@@ -8094,7 +8094,7 @@
         <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>576</v>
@@ -8109,10 +8109,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>565</v>
+        <v>223</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>578</v>
@@ -8126,7 +8126,7 @@
         <v>53</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>579</v>
@@ -8258,7 +8258,7 @@
         <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>585</v>
@@ -8290,7 +8290,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>126</v>
@@ -8322,7 +8322,7 @@
         <v>138</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>144</v>
@@ -8354,7 +8354,7 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>144</v>
@@ -8389,7 +8389,7 @@
         <v>125</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>597</v>
@@ -8403,7 +8403,7 @@
         <v>61</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>598</v>
@@ -8418,10 +8418,10 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>600</v>
@@ -8450,10 +8450,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>603</v>
@@ -8482,10 +8482,10 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>606</v>
@@ -8514,10 +8514,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>609</v>
@@ -8546,10 +8546,10 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>612</v>
@@ -8578,10 +8578,10 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>615</v>
@@ -8610,10 +8610,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>111</v>
+        <v>358</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>618</v>
@@ -8642,10 +8642,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>621</v>
@@ -8659,7 +8659,7 @@
         <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>622</v>
@@ -8674,10 +8674,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>358</v>
+        <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>624</v>
@@ -8691,7 +8691,7 @@
         <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>625</v>
@@ -8709,7 +8709,7 @@
         <v>100</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>627</v>
@@ -8723,7 +8723,7 @@
         <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>628</v>
@@ -8738,10 +8738,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>630</v>
@@ -8755,7 +8755,7 @@
         <v>61</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>631</v>
@@ -8770,10 +8770,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>633</v>
@@ -8787,7 +8787,7 @@
         <v>61</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>634</v>
@@ -8802,10 +8802,10 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>636</v>
@@ -8819,7 +8819,7 @@
         <v>61</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>637</v>
@@ -8834,10 +8834,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>639</v>
@@ -8851,7 +8851,7 @@
         <v>61</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>640</v>
@@ -8866,10 +8866,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>642</v>
@@ -8883,7 +8883,7 @@
         <v>61</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>643</v>
@@ -8901,7 +8901,7 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>645</v>
@@ -8915,7 +8915,7 @@
         <v>61</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>646</v>
@@ -8930,10 +8930,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>648</v>
@@ -8947,7 +8947,7 @@
         <v>61</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>649</v>
@@ -8962,10 +8962,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>651</v>
@@ -8979,7 +8979,7 @@
         <v>61</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>652</v>
@@ -8997,7 +8997,7 @@
         <v>358</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>654</v>
@@ -9011,7 +9011,7 @@
         <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>655</v>
@@ -9026,10 +9026,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>657</v>
@@ -9043,7 +9043,7 @@
         <v>61</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>658</v>
@@ -9061,7 +9061,7 @@
         <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>660</v>
@@ -9075,7 +9075,7 @@
         <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>661</v>
@@ -9090,10 +9090,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>663</v>
@@ -9107,7 +9107,7 @@
         <v>61</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>664</v>
@@ -9122,10 +9122,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>666</v>
@@ -9139,7 +9139,7 @@
         <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>667</v>
@@ -9154,10 +9154,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>669</v>
@@ -9305,7 +9305,7 @@
         <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>675</v>
@@ -9337,7 +9337,7 @@
         <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>678</v>
@@ -9366,10 +9366,10 @@
         <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>681</v>
@@ -9398,10 +9398,10 @@
         <v>87</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>684</v>
@@ -9415,7 +9415,7 @@
         <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>685</v>
@@ -9433,7 +9433,7 @@
         <v>301</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>687</v>
@@ -9465,7 +9465,7 @@
         <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>690</v>
@@ -9494,10 +9494,10 @@
         <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>693</v>
@@ -9526,10 +9526,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>696</v>
@@ -9558,10 +9558,10 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>699</v>
@@ -9590,10 +9590,10 @@
         <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>702</v>
@@ -9622,10 +9622,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>705</v>
@@ -9654,10 +9654,10 @@
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>708</v>
@@ -9671,7 +9671,7 @@
         <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>709</v>
@@ -9686,10 +9686,10 @@
         <v>87</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>711</v>
@@ -9703,7 +9703,7 @@
         <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>712</v>
@@ -9718,10 +9718,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>714</v>
@@ -9735,7 +9735,7 @@
         <v>68</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>715</v>
@@ -9750,10 +9750,10 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>717</v>
@@ -9767,7 +9767,7 @@
         <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>718</v>
@@ -9782,10 +9782,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>720</v>
@@ -9799,7 +9799,7 @@
         <v>68</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>75</v>
@@ -9814,10 +9814,10 @@
         <v>138</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>722</v>
@@ -9831,7 +9831,7 @@
         <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>723</v>
@@ -9863,7 +9863,7 @@
         <v>68</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>726</v>
@@ -9881,7 +9881,7 @@
         <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>728</v>
@@ -9895,7 +9895,7 @@
         <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>729</v>
@@ -9910,10 +9910,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>731</v>
@@ -9927,7 +9927,7 @@
         <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>732</v>
@@ -9945,7 +9945,7 @@
         <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>734</v>
@@ -9959,7 +9959,7 @@
         <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>735</v>
@@ -9974,10 +9974,10 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>737</v>
@@ -9991,7 +9991,7 @@
         <v>68</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>738</v>
@@ -10009,7 +10009,7 @@
         <v>125</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>740</v>
@@ -10023,7 +10023,7 @@
         <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>741</v>
@@ -10041,7 +10041,7 @@
         <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>743</v>
@@ -10055,7 +10055,7 @@
         <v>68</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>744</v>
@@ -10070,10 +10070,10 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>746</v>
@@ -10087,7 +10087,7 @@
         <v>68</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>747</v>
@@ -10102,10 +10102,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>565</v>
+        <v>223</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>749</v>
@@ -10119,7 +10119,7 @@
         <v>68</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>750</v>
@@ -10134,7 +10134,7 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>565</v>
@@ -10151,7 +10151,7 @@
         <v>68</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>753</v>
@@ -10166,7 +10166,7 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>401</v>
@@ -10183,7 +10183,7 @@
         <v>68</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>756</v>

--- a/reports/셀린느/셀린느_training_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_training_mgf_report.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="761">
   <si>
     <t>guild_name</t>
   </si>
@@ -201,7 +201,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>71</t>
+    <t>72</t>
   </si>
   <si>
     <t>2위</t>
@@ -246,7 +246,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>66</t>
+    <t>65</t>
   </si>
   <si>
     <t>3위</t>
@@ -303,7 +303,7 @@
     <t>130</t>
   </si>
   <si>
-    <t>5888경 2060조 5086억 6719만</t>
+    <t>6096경 1451조 2394억 580만</t>
   </si>
   <si>
     <t>2</t>
@@ -318,52 +318,52 @@
     <t>나이트로드</t>
   </si>
   <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>850경 2661조 8082억 3665만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>유이파더</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%9D%B4%ED%8C%8C%EB%8D%94</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>776경 1942조 7427억 7170만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>꾱환</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
+  </si>
+  <si>
+    <t>546경 9844조 5866억 8124만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>루졔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
+  </si>
+  <si>
     <t>125</t>
   </si>
   <si>
-    <t>794경 837조 8313억 1001만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>유이파더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%9D%B4%ED%8C%8C%EB%8D%94</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>775경 9270조 3786억 4678만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>꾱환</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B1%ED%99%98</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>546경 9844조 5866억 8124만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>루졔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%A1%94</t>
-  </si>
-  <si>
-    <t>494경 1199조 3500억 2740만</t>
+    <t>500경 5402조 5615억 1892만</t>
   </si>
   <si>
     <t>6</t>
@@ -435,7 +435,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%ED%88%AC%EA%B8%B0%EB%A6%BF</t>
   </si>
   <si>
-    <t>91경 7006조 7620억 6328만</t>
+    <t>91경 7807조 5138억 3000만</t>
   </si>
   <si>
     <t>11</t>
@@ -456,6 +456,24 @@
     <t>12</t>
   </si>
   <si>
+    <t>데브쫑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%B8%8C%EC%AB%91</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>44경 3558조 5025억 3175만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>라온J</t>
   </si>
   <si>
@@ -465,25 +483,7 @@
     <t>122</t>
   </si>
   <si>
-    <t>39경 5704조 2621억 6901만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>데브쫑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%B8%8C%EC%AB%91</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>37경 8395조 8185억 9337만</t>
+    <t>39경 5771조 5037억 5874만</t>
   </si>
   <si>
     <t>14</t>
@@ -495,7 +495,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EB%A5%B8</t>
   </si>
   <si>
-    <t>36경 5066조 5387억 1446만</t>
+    <t>37경 5828조 9444억 5335만</t>
   </si>
   <si>
     <t>15</t>
@@ -507,7 +507,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9A%A0</t>
   </si>
   <si>
-    <t>29경 2914조 6749억 7868만</t>
+    <t>30경 1834조 8965억 3649만</t>
   </si>
   <si>
     <t>16</t>
@@ -534,7 +534,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%8B%B1</t>
   </si>
   <si>
-    <t>20경 8995조 8732억 958만</t>
+    <t>21경 3564조 5261억 1001만</t>
   </si>
   <si>
     <t>18</t>
@@ -546,7 +546,7 @@
     <t>https://mgf.gg/contents/character.php?n=911TurboS</t>
   </si>
   <si>
-    <t>20경 990조 753억 8757만</t>
+    <t>20경 1348조 2894억 2744만</t>
   </si>
   <si>
     <t>19</t>
@@ -573,37 +573,40 @@
     <t>캡틴</t>
   </si>
   <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>14경 3584조 136억 3259만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>라온U</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8U</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>12경 5743조 1364억 3405만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>김라이트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
+  </si>
+  <si>
     <t>118</t>
   </si>
   <si>
-    <t>12경 9139조 5865억 4488만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>라온U</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%98%A8U</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>12경 5743조 1364억 3405만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>김라이트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%9D%BC%EC%9D%B4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>11경 5748조 7434억 5787만</t>
+    <t>11경 6213조 5426억 5830만</t>
   </si>
   <si>
     <t>23</t>
@@ -615,7 +618,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%83%B1%EA%B5%AC</t>
   </si>
   <si>
-    <t>9경 44조 696억 3647만</t>
+    <t>9경 9322조 2236억 3751만</t>
   </si>
   <si>
     <t>24</t>
@@ -642,9 +645,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%94%ED%94%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>119</t>
-  </si>
-  <si>
     <t>7경 4867조 7844억 1323만</t>
   </si>
   <si>
@@ -657,7 +657,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9D%B4%EA%B2%90</t>
   </si>
   <si>
-    <t>6경 6536조 1543억 997만</t>
+    <t>6경 6614조 156억 3068만</t>
   </si>
   <si>
     <t>27</t>
@@ -681,7 +681,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%84%EC%A7%80%EB%A1%9C%EB%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>5경 9875조 2824억 6922만</t>
+    <t>6경 553조 3237억 7872만</t>
   </si>
   <si>
     <t>29</t>
@@ -693,7 +693,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%86%94%EB%B9%A0</t>
   </si>
   <si>
-    <t>3경 6947조 6463억 7525만</t>
+    <t>3경 7085조 4299억 3753만</t>
   </si>
   <si>
     <t>30</t>
@@ -708,7 +708,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>2경 2076조 6560억 2748만</t>
+    <t>2경 3143조 3585억 4969만</t>
   </si>
   <si>
     <t>람볼기니</t>
@@ -720,7 +720,7 @@
     <t>128</t>
   </si>
   <si>
-    <t>1598경 1016조 3592억 2191만</t>
+    <t>1598경 7969조 9194억 869만</t>
   </si>
   <si>
     <t>무과금선포</t>
@@ -777,7 +777,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9E%89%EC%95%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>220경 2301조 6477억 4589만</t>
+    <t>220경 7028조 1257억 8292만</t>
   </si>
   <si>
     <t>밍카누</t>
@@ -786,7 +786,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%B9%B4%EB%88%84</t>
   </si>
   <si>
-    <t>149경 2061조 1942억 8500만</t>
+    <t>172경 7538조 5505억 6623만</t>
   </si>
   <si>
     <t>봉띤</t>
@@ -813,22 +813,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%99%ED%8B%B0</t>
   </si>
   <si>
-    <t>71경 6277조 7709억 6100만</t>
+    <t>72경 4602조 7414억 424만</t>
+  </si>
+  <si>
+    <t>타이슨에어랩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
+  </si>
+  <si>
+    <t>68경 6665조 8978억 7294만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%81%AC%EB%A9%94%EC%9D%B4%EB%94%A9%EB%8F%99</t>
   </si>
   <si>
-    <t>68경 2142조 5232억 2669만</t>
-  </si>
-  <si>
-    <t>타이슨에어랩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EC%9D%B4%EC%8A%A8%EC%97%90%EC%96%B4%EB%9E%A9</t>
-  </si>
-  <si>
-    <t>66경 8983조 917억 3167만</t>
+    <t>68경 2938조 8231억 8278만</t>
   </si>
   <si>
     <t>캔드릭</t>
@@ -840,7 +840,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>61경 1575조 7096억 3731만</t>
+    <t>62경 5780조 4764억 2356만</t>
   </si>
   <si>
     <t>후뢰쉬맨</t>
@@ -867,7 +867,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%B3%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>44경 5193조 3357억 3709만</t>
+    <t>46경 1721조 4823억 418만</t>
   </si>
   <si>
     <t>황해면선생</t>
@@ -876,7 +876,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%ED%95%B4%EB%A9%B4%EC%84%A0%EC%83%9D</t>
   </si>
   <si>
-    <t>36경 4158조 1755억 65만</t>
+    <t>36경 4187조 9016억 1584만</t>
   </si>
   <si>
     <t>레몬깜바뉴</t>
@@ -885,7 +885,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%AA%AC%EA%B9%9C%EB%B0%94%EB%89%B4</t>
   </si>
   <si>
-    <t>31경 4771조 4217억 3408만</t>
+    <t>32경 9724조 5587억 2736만</t>
   </si>
   <si>
     <t>진압조</t>
@@ -894,7 +894,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%95%95%EC%A1%B0</t>
   </si>
   <si>
-    <t>28경 5963조 7794억 7500만</t>
+    <t>28경 8668조 9210억 2814만</t>
   </si>
   <si>
     <t>공주쏭</t>
@@ -912,7 +912,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EA%B0%88</t>
   </si>
   <si>
-    <t>23경 2869조 5947억 2013만</t>
+    <t>25경 5048조 3160억 1647만</t>
   </si>
   <si>
     <t>밍모리</t>
@@ -921,7 +921,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EB%AA%A8%EB%A6%AC</t>
   </si>
   <si>
-    <t>14경 4424조 4855억 9906만</t>
+    <t>14경 5260조 5083억 9375만</t>
   </si>
   <si>
     <t>도적왕대현</t>
@@ -948,7 +948,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%95%EC%96%B4%EC%A4%8D</t>
   </si>
   <si>
-    <t>8경 9404조 1610억 6726만</t>
+    <t>9경 6347조 4596억 2272만</t>
   </si>
   <si>
     <t>로생</t>
@@ -957,7 +957,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%83%9D</t>
   </si>
   <si>
-    <t>8경 6363조 2000억 6564만</t>
+    <t>8경 9032조 1922억 3106만</t>
   </si>
   <si>
     <t>혜도로동</t>
@@ -966,7 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>8경 6124조 7010억 3445만</t>
+    <t>8경 6666조 5099억 9049만</t>
   </si>
   <si>
     <t>똑순</t>
@@ -975,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%91%EC%88%9C</t>
   </si>
   <si>
-    <t>7경 4736조 8183억 2546만</t>
+    <t>7경 5943조 6071억 130만</t>
   </si>
   <si>
     <t>유도로동</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8F%84%EB%A1%9C%EB%8F%99</t>
   </si>
   <si>
-    <t>5경 6483조 568억 902만</t>
+    <t>5경 6525조 4938억 9190만</t>
   </si>
   <si>
     <t>군보</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>253경 103조 2412억 8730만</t>
+    <t>254경 641조 565억 1463만</t>
   </si>
   <si>
     <t>여보슈</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%99%ED%82%A4</t>
   </si>
   <si>
-    <t>165경 4901조 955억 9690만</t>
+    <t>169경 8479조 9648억 2500만</t>
   </si>
   <si>
     <t>5형사</t>
@@ -1020,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=5%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>131경 1786조 3951억 3764만</t>
+    <t>131경 2365조 6115억 4620만</t>
   </si>
   <si>
     <t>심천</t>
@@ -1038,7 +1038,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>90경 8755조 272억 1570만</t>
+    <t>92경 6360조 9605억 6440만</t>
+  </si>
+  <si>
+    <t>혁수킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
+  </si>
+  <si>
+    <t>88경 8880조 1071억 5331만</t>
   </si>
   <si>
     <t>총괄한석현</t>
@@ -1053,7 +1062,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%B52</t>
   </si>
   <si>
-    <t>86경 50조 568억 3960만</t>
+    <t>86경 3231조 5906억 2016만</t>
   </si>
   <si>
     <t>Matter</t>
@@ -1065,22 +1074,13 @@
     <t>79경 7077조 5812억 6799만</t>
   </si>
   <si>
-    <t>혁수킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EC%88%98%ED%82%B9</t>
-  </si>
-  <si>
-    <t>77경 7775조 9712억 658만</t>
-  </si>
-  <si>
     <t>원중언니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A4%91%EC%96%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>63경 4106조 5855억 9175만</t>
+    <t>63경 4859조 3973억 885만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1107,7 +1107,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EA%B7%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>46경 3785조 4773억 4959만</t>
+    <t>46경 6320조 9539억 6412만</t>
   </si>
   <si>
     <t>김나뭉</t>
@@ -1116,7 +1116,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%82%98%EB%AD%89</t>
   </si>
   <si>
-    <t>43경 3739조 8481억 5791만</t>
+    <t>43경 3852조 7272억 4677만</t>
   </si>
   <si>
     <t>파퍼</t>
@@ -1125,7 +1125,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8D%BC</t>
   </si>
   <si>
-    <t>37경 5452조 8216억 200만</t>
+    <t>37경 5938조 2515억 8710만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1140,25 +1140,25 @@
     <t>30경 6712억 4376만</t>
   </si>
   <si>
+    <t>껌정색</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>23경 663조 1619억 1749만</t>
+  </si>
+  <si>
     <t>찐맨듀</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EB%A7%A8%EB%93%80</t>
   </si>
   <si>
-    <t>22경 5239조 2304억 4036만</t>
-  </si>
-  <si>
-    <t>껌정색</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>21경 4909조 2159억 6850만</t>
+    <t>22경 5269조 1530억 6541만</t>
   </si>
   <si>
     <t>이삼2</t>
@@ -1167,7 +1167,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%82%BC2</t>
   </si>
   <si>
-    <t>18경 8057조 6726억 7627만</t>
+    <t>18경 8227조 9729억 6383만</t>
   </si>
   <si>
     <t>다끝남</t>
@@ -1176,7 +1176,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%81%9D%EB%82%A8</t>
   </si>
   <si>
-    <t>17경 2064조 642억 8464만</t>
+    <t>17경 2375조 7991억 2522만</t>
   </si>
   <si>
     <t>Rahee</t>
@@ -1230,7 +1230,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EB%A1%9C%EB%A0%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>4경 9014조 2749억 544만</t>
+    <t>5경 1007조 9738억 3661만</t>
   </si>
   <si>
     <t>통뼈1</t>
@@ -1257,7 +1257,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8F%84%EC%9C%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>2경 5133조 4044억 5872만</t>
+    <t>2경 5139조 6928억 6610만</t>
   </si>
   <si>
     <t>해물만두야</t>
@@ -1266,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%AC%BC%EB%A7%8C%EB%91%90%EC%95%BC</t>
   </si>
   <si>
-    <t>328경 6580조 3693억 2845만</t>
+    <t>328경 9020조 6365억 5767만</t>
   </si>
   <si>
     <t>마옥지</t>
@@ -1284,7 +1284,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%9D%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>211경 3305조 9512억 6696만</t>
+    <t>211경 5566조 2876억 3170만</t>
   </si>
   <si>
     <t>설익은앵숭</t>
@@ -1293,7 +1293,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%95%B5%EC%88%AD</t>
   </si>
   <si>
-    <t>108경 7264조 7216억 8733만</t>
+    <t>112경 4690조 2431억 3125만</t>
   </si>
   <si>
     <t>설함마</t>
@@ -1302,7 +1302,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%ED%95%A8%EB%A7%88</t>
   </si>
   <si>
-    <t>93경 2334조 435억 8019만</t>
+    <t>101경 8853조 8604억 6088만</t>
   </si>
   <si>
     <t>킹규봉</t>
@@ -1323,6 +1323,15 @@
     <t>52경 6503조 4117억 4012만</t>
   </si>
   <si>
+    <t>설묘묘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
+  </si>
+  <si>
+    <t>50경 4616조 1114억 5626만</t>
+  </si>
+  <si>
     <t>루델밍</t>
   </si>
   <si>
@@ -1332,22 +1341,13 @@
     <t>49경 6849조 3542억 4149만</t>
   </si>
   <si>
-    <t>설묘묘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EB%AC%98%EB%AC%98</t>
-  </si>
-  <si>
-    <t>48경 8952조 5422억 484만</t>
-  </si>
-  <si>
     <t>너굴얌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%84%88%EA%B5%B4%EC%96%8C</t>
   </si>
   <si>
-    <t>46경 1234조 9547억 1589만</t>
+    <t>47경 8158조 1694억 1797만</t>
   </si>
   <si>
     <t>싲프</t>
@@ -1356,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B2%ED%94%84</t>
   </si>
   <si>
-    <t>43경 4649조 5410억 6877만</t>
+    <t>45경 5027조 7256억 8779만</t>
   </si>
   <si>
     <t>셀렘이</t>
@@ -1374,7 +1374,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%93%9C%EB%A6%AC%EC%95%88</t>
   </si>
   <si>
-    <t>30경 4255조 6412억 9736만</t>
+    <t>31경 805조 9309억 8041만</t>
   </si>
   <si>
     <t>졸귀탱이</t>
@@ -1383,7 +1383,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80%ED%83%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>25경 9048조 9137억 6237만</t>
+    <t>26경 6807조 9677억 2516만</t>
   </si>
   <si>
     <t>선콜은차가워</t>
@@ -1392,7 +1392,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EC%BD%9C%EC%9D%80%EC%B0%A8%EA%B0%80%EC%9B%8C</t>
   </si>
   <si>
-    <t>23경 8842조 3034억 4140만</t>
+    <t>24경 1296조 660억 5293만</t>
+  </si>
+  <si>
+    <t>마덕칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>22경 5635조 4028억 6320만</t>
   </si>
   <si>
     <t>설딩</t>
@@ -1404,22 +1413,13 @@
     <t>22경 53조 2786억 4093만</t>
   </si>
   <si>
-    <t>마덕칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8D%95%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>21경 1117조 3492억 7082만</t>
-  </si>
-  <si>
     <t>슐아</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%90%EC%95%84</t>
   </si>
   <si>
-    <t>13경 5408조 677억 8062만</t>
+    <t>14경 9802조 2239억 2518만</t>
   </si>
   <si>
     <t>경성2018</t>
@@ -1440,6 +1440,15 @@
     <t>11경 597조 4783억 2861만</t>
   </si>
   <si>
+    <t>다다익숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
+  </si>
+  <si>
+    <t>9경 410조 8334억 9964만</t>
+  </si>
+  <si>
     <t>폰병</t>
   </si>
   <si>
@@ -1449,15 +1458,6 @@
     <t>8경 6365조 5071억 4773만</t>
   </si>
   <si>
-    <t>다다익숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%88%8D</t>
-  </si>
-  <si>
-    <t>8경 4860조 7935억 5465만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%9D%B5%EC%9D%80%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
@@ -1491,6 +1491,15 @@
     <t>2경 3215조 155억 8178만</t>
   </si>
   <si>
+    <t>네오메디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
+  </si>
+  <si>
+    <t>2경 2949조 6419억 4730만</t>
+  </si>
+  <si>
     <t>설치는정상인</t>
   </si>
   <si>
@@ -1500,15 +1509,6 @@
     <t>2경 2676조 8138억 6796만</t>
   </si>
   <si>
-    <t>네오메디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%98%A4%EB%A9%94%EB%94%94</t>
-  </si>
-  <si>
-    <t>2경 1203조 8776억 9257만</t>
-  </si>
-  <si>
     <t>읏코츠</t>
   </si>
   <si>
@@ -1524,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%84%9C%EA%B5%AC%EB%8F%84%EC%A0%81</t>
   </si>
   <si>
-    <t>717경 8557조 8194억 5723만</t>
+    <t>719경 9122조 1049억 2092만</t>
   </si>
   <si>
     <t>따코유</t>
@@ -1542,7 +1542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%ED%84%B8</t>
   </si>
   <si>
-    <t>205경 5491조 7303억 6657만</t>
+    <t>205경 6333조 9706억 6650만</t>
   </si>
   <si>
     <t>뽀로로남편</t>
@@ -1560,7 +1560,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%A4%EB%86%88%ED%8E%9C</t>
   </si>
   <si>
-    <t>94경 8169조 714억 7877만</t>
+    <t>95경 6458조 9616억 9395만</t>
+  </si>
+  <si>
+    <t>꿀서은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
+  </si>
+  <si>
+    <t>38경 8766조 3274억 1165만</t>
   </si>
   <si>
     <t>퀸더쪼이</t>
@@ -1569,16 +1578,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EB%8D%94%EC%AA%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>37경 3344조 2233억 1838만</t>
-  </si>
-  <si>
-    <t>꿀서은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%84%9C%EC%9D%80</t>
-  </si>
-  <si>
-    <t>36경 7205조 9075억 4186만</t>
+    <t>37경 3706조 5641억 4987만</t>
   </si>
   <si>
     <t>쿨쥐돌</t>
@@ -1587,7 +1587,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A8%EC%A5%90%EB%8F%8C</t>
   </si>
   <si>
-    <t>31경 9413조 48억 100만</t>
+    <t>34경 7127조 5951억 6748만</t>
+  </si>
+  <si>
+    <t>게탕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
+  </si>
+  <si>
+    <t>27경 6251조 3492억 7078만</t>
   </si>
   <si>
     <t>긴나라</t>
@@ -1599,22 +1608,13 @@
     <t>27경 4046조 5855억 40만</t>
   </si>
   <si>
-    <t>게탕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%ED%83%95</t>
-  </si>
-  <si>
-    <t>27경 2777조 7266억 7081만</t>
-  </si>
-  <si>
     <t>우둉</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%91%89</t>
   </si>
   <si>
-    <t>16경 3697조 1170억 5197만</t>
+    <t>17경 8599조 1602억 7066만</t>
   </si>
   <si>
     <t>류텐</t>
@@ -1623,7 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%90</t>
   </si>
   <si>
-    <t>11경 1466조 4532억 6588만</t>
+    <t>11경 3456조 4350억 6674만</t>
   </si>
   <si>
     <t>철푸닥</t>
@@ -1650,13 +1650,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%93%9C%EC%9B%A8%EC%96%B4</t>
   </si>
   <si>
-    <t>4경 5657조 9888억 5026만</t>
+    <t>4경 5801조 2971억 31만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%8D%B0%EC%9D%BC2</t>
   </si>
   <si>
-    <t>4경 1487조 6369억 4781만</t>
+    <t>4경 1957조 3331억 1099만</t>
   </si>
   <si>
     <t>ShellyCake</t>
@@ -1677,22 +1677,22 @@
     <t>3경 8230조 129억 3942만</t>
   </si>
   <si>
+    <t>구미적</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
+  </si>
+  <si>
+    <t>2경 9259조 4377억 5892만</t>
+  </si>
+  <si>
     <t>오정구불독</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%A0%95%EA%B5%AC%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>2경 7345조 5580억 8128만</t>
-  </si>
-  <si>
-    <t>구미적</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%AF%B8%EC%A0%81</t>
-  </si>
-  <si>
-    <t>2경 6934조 6741억 5404만</t>
+    <t>2경 7628조 304억 5546만</t>
   </si>
   <si>
     <t>양덕하늘채</t>
@@ -1704,13 +1704,22 @@
     <t>2경 2746조 1840억 1492만</t>
   </si>
   <si>
+    <t>예슬a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%ACa</t>
+  </si>
+  <si>
+    <t>2경 2448조 9054억 575만</t>
+  </si>
+  <si>
     <t>레드플레이어</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%93%9C%ED%94%8C%EB%A0%88%EC%9D%B4%EC%96%B4</t>
   </si>
   <si>
-    <t>1경 7457조 4642억 7972만</t>
+    <t>1경 7536조 7536억 6812만</t>
   </si>
   <si>
     <t>검샷</t>
@@ -1719,7 +1728,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%EC%83%B7</t>
   </si>
   <si>
-    <t>1경 6398조 8698억 3888만</t>
+    <t>1경 6692조 8284억 2246만</t>
   </si>
   <si>
     <t>주하사랑</t>
@@ -1728,7 +1737,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%ED%95%98%EC%82%AC%EB%9E%91</t>
   </si>
   <si>
-    <t>1경 5703조 8094억 4499만</t>
+    <t>1경 6042조 9846억 7343만</t>
   </si>
   <si>
     <t>장아린</t>
@@ -1740,24 +1749,15 @@
     <t>1경 5450조 9714억 5644만</t>
   </si>
   <si>
-    <t>예슬a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%8A%ACa</t>
+    <t>브리또강철중</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A6%AC%EB%98%90%EA%B0%95%EC%B2%A0%EC%A4%91</t>
   </si>
   <si>
     <t>115</t>
   </si>
   <si>
-    <t>1경 3695조 7828억 603만</t>
-  </si>
-  <si>
-    <t>브리또강철중</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A6%AC%EB%98%90%EA%B0%95%EC%B2%A0%EC%A4%91</t>
-  </si>
-  <si>
     <t>1경 2238조 8084억 982만</t>
   </si>
   <si>
@@ -1767,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EA%B8%B0%EA%B0%93</t>
   </si>
   <si>
-    <t>1경 856조 6831억 3532만</t>
+    <t>1경 869조 1464억 1581만</t>
   </si>
   <si>
     <t>l빠다코코낫l</t>
@@ -1785,10 +1785,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EA%BC%AC</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>4498조 273억 6219만</t>
+    <t>113</t>
+  </si>
+  <si>
+    <t>4507조 2554억 4740만</t>
   </si>
   <si>
     <t>금은동S2</t>
@@ -1806,7 +1806,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>96경 5118조 1596억 7180만</t>
+    <t>100경 1265조 8727억 4286만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EB%9E%84</t>
@@ -1821,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
   </si>
   <si>
-    <t>45경 4192조 3310억 5895만</t>
+    <t>45경 7839조 4830억 7389만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -1830,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>40경 4856조 569억 6949만</t>
+    <t>40경 6568조 7350억 1949만</t>
   </si>
   <si>
     <t>임홀리</t>
@@ -1839,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%99%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>20경 8632조 3117억 538만</t>
+    <t>22경 9242조 1969억 7961만</t>
   </si>
   <si>
     <t>꿈넴</t>
@@ -1866,7 +1866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EA%BB%B4</t>
   </si>
   <si>
-    <t>13경 4450조 4251억 3750만</t>
+    <t>13경 7290조 5761억 3708만</t>
   </si>
   <si>
     <t>리브루므</t>
@@ -1875,7 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%B8%8C%EB%A3%A8%EB%AF%80</t>
   </si>
   <si>
-    <t>12경 4079조 4544억 6322만</t>
+    <t>12경 8108조 4496억 8778만</t>
   </si>
   <si>
     <t>엘리자베타</t>
@@ -1884,7 +1884,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A6%AC%EC%9E%90%EB%B2%A0%ED%83%80</t>
   </si>
   <si>
-    <t>7경 2935조 8909억 2794만</t>
+    <t>7경 3139조 7080억 3387만</t>
+  </si>
+  <si>
+    <t>어흥이다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>6경 7415조 3547억 8561만</t>
   </si>
   <si>
     <t>우꼬쨩</t>
@@ -1896,22 +1905,13 @@
     <t>6경 6789조 8345억 1257만</t>
   </si>
   <si>
-    <t>어흥이다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%9D%A5%EC%9D%B4%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>6경 4033조 8918억 5782만</t>
-  </si>
-  <si>
     <t>홍시마로</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9C%EB%A7%88%EB%A1%9C</t>
   </si>
   <si>
-    <t>6경 225조 2279억 5188만</t>
+    <t>6경 2210조 5066억 9044만</t>
   </si>
   <si>
     <t>비밀키</t>
@@ -1947,7 +1947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%80%EC%9A%94S2</t>
   </si>
   <si>
-    <t>3경 9138조 7940억 8718만</t>
+    <t>3경 9974조 4263억 4277만</t>
   </si>
   <si>
     <t>지아라떼</t>
@@ -1965,7 +1965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9D%EC%B8%88</t>
   </si>
   <si>
-    <t>3경 2432조 9335억 5748만</t>
+    <t>3경 3019조 4431억 1332만</t>
   </si>
   <si>
     <t>o엔젤o</t>
@@ -1974,7 +1974,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%94%EC%A0%A4o</t>
   </si>
   <si>
-    <t>3경 885조 6927억 5847만</t>
+    <t>3경 958조 5435억 6752만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -1983,7 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>2경 7819조 591억 1395만</t>
+    <t>2경 8781조 2624억 7964만</t>
   </si>
   <si>
     <t>메론맛빵</t>
@@ -1992,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EB%A1%A0%EB%A7%9B%EB%B9%B5</t>
   </si>
   <si>
-    <t>2경 7068조 3626억 4500만</t>
+    <t>2경 7690조 8104억 9364만</t>
   </si>
   <si>
     <t>24년생정춘식</t>
@@ -2019,7 +2019,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>1경 5417조 6110억 6101만</t>
+    <t>1경 5892조 1014억 4872만</t>
   </si>
   <si>
     <t>쏨열무</t>
@@ -2028,7 +2028,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8F%A8%EC%97%B4%EB%AC%B4</t>
   </si>
   <si>
-    <t>1경 5405조 309억 5363만</t>
+    <t>1경 5755조 9965억 8104만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -2037,7 +2037,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>1경 3251조 5694억 5794만</t>
+    <t>1경 3322조 3921억 5137만</t>
   </si>
   <si>
     <t>출장괴물</t>
@@ -2046,7 +2046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%9C%EC%9E%A5%EA%B4%B4%EB%AC%BC</t>
   </si>
   <si>
-    <t>1경 2913조 8252억 2837만</t>
+    <t>1경 2942조 5666억 2969만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -2055,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>31경 2254조 2005억 6399만</t>
+    <t>32경 404조 953억 4123만</t>
   </si>
   <si>
     <t>부엉이형</t>
@@ -2064,7 +2064,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>22경 4338조 4311억 2690만</t>
+    <t>22경 4383조 2379억 4418만</t>
   </si>
   <si>
     <t>국의</t>
@@ -2073,7 +2073,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EC%9D%98</t>
   </si>
   <si>
-    <t>17경 5733조 2687억 247만</t>
+    <t>18경 1071조 8894억 93만</t>
   </si>
   <si>
     <t>걸음</t>
@@ -2082,7 +2082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B8%EC%9D%8C</t>
   </si>
   <si>
-    <t>15경 5474조 2635억 7953만</t>
+    <t>15경 8128조 6296억 3206만</t>
   </si>
   <si>
     <t>니달리신</t>
@@ -2100,7 +2100,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>12경 6106조 8016억 2962만</t>
+    <t>12경 7747조 4306억 9939만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>12경 5952조 4640억 2596만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -2121,15 +2130,6 @@
     <t>11경 6350조 3056억 807만</t>
   </si>
   <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>11경 6138조 6704억 1468만</t>
-  </si>
-  <si>
     <t>킹몬</t>
   </si>
   <si>
@@ -2154,7 +2154,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>4경 791조 5739억 5472만</t>
+    <t>4경 798조 2870억 9878만</t>
+  </si>
+  <si>
+    <t>세아수호지호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
+  </si>
+  <si>
+    <t>3경 3158조 651억 6053만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -2166,22 +2175,13 @@
     <t>3경 2373조 4968억 9766만</t>
   </si>
   <si>
-    <t>세아수호지호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%95%84%EC%88%98%ED%98%B8%EC%A7%80%ED%98%B8</t>
-  </si>
-  <si>
-    <t>3경 1709조 664억 225만</t>
-  </si>
-  <si>
     <t>핫잇</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EC%9E%87</t>
   </si>
   <si>
-    <t>3경 954조 3408억 7516만</t>
+    <t>3경 1905조 6295억 6099만</t>
   </si>
   <si>
     <t>반가성</t>
@@ -2190,7 +2190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EA%B0%80%EC%84%B1</t>
   </si>
   <si>
-    <t>2경 8420조 3096억 4562만</t>
+    <t>2경 8427조 3482억 4340만</t>
   </si>
   <si>
     <t>관리</t>
@@ -2211,13 +2211,31 @@
     <t>2경 3738조 4429억 3955만</t>
   </si>
   <si>
+    <t>호날두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%82%A0%EB%91%90</t>
+  </si>
+  <si>
+    <t>2경 3665조 8326억 1067만</t>
+  </si>
+  <si>
+    <t>아이스꾸임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
+  </si>
+  <si>
+    <t>2경 3522조 834억 2642만</t>
+  </si>
+  <si>
     <t>망겜감별사</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
-    <t>2경 2901조 206억 5980만</t>
+    <t>2경 3431조 9019억 5634만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
@@ -2232,7 +2250,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%9A%9C</t>
   </si>
   <si>
-    <t>1경 8791조 7224억 3541만</t>
+    <t>1경 9186조 5768억 3625만</t>
+  </si>
+  <si>
+    <t>오곤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
+  </si>
+  <si>
+    <t>1경 5652조 4635억 9184만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -2244,24 +2271,6 @@
     <t>1경 4932조 152억 2027만</t>
   </si>
   <si>
-    <t>호날두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%82%A0%EB%91%90</t>
-  </si>
-  <si>
-    <t>1경 4528조 6392억 7421만</t>
-  </si>
-  <si>
-    <t>오곤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EA%B3%A4</t>
-  </si>
-  <si>
-    <t>1경 4402조 5350억 6084만</t>
-  </si>
-  <si>
     <t>라똥이</t>
   </si>
   <si>
@@ -2277,7 +2286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%B3%A4%EB%83%A5</t>
   </si>
   <si>
-    <t>1경 2893조 8032억 5991만</t>
+    <t>1경 2904조 5499억 45만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -2286,7 +2295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>1경 2003조 3345억 4261만</t>
+    <t>1경 2056조 7692억 1857만</t>
   </si>
   <si>
     <t>초식왕</t>
@@ -2295,7 +2304,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%8B%9D%EC%99%95</t>
   </si>
   <si>
-    <t>9689조 32억 7248만</t>
+    <t>1경 713조 4122억 4840만</t>
   </si>
   <si>
     <t>러너</t>
@@ -2304,19 +2313,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%AC%EB%84%88</t>
   </si>
   <si>
-    <t>7704조 70억 5986만</t>
-  </si>
-  <si>
-    <t>해찬나래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%B0%AC%EB%82%98%EB%9E%98</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>7516조 9035억 6492만</t>
+    <t>7953조 2900억 3963만</t>
   </si>
 </sst>
 </file>
@@ -3049,7 +3046,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3204,10 +3201,10 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3218,16 +3215,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>87</v>
@@ -3236,7 +3233,7 @@
         <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>110</v>
@@ -3300,7 +3297,7 @@
         <v>119</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>120</v>
@@ -3457,13 +3454,13 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3474,22 +3471,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>149</v>
@@ -3556,7 +3553,7 @@
         <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>158</v>
@@ -3652,7 +3649,7 @@
         <v>114</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>171</v>
@@ -3748,7 +3745,7 @@
         <v>185</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>186</v>
@@ -3780,10 +3777,10 @@
         <v>185</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3794,16 +3791,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>87</v>
@@ -3812,10 +3809,10 @@
         <v>114</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3826,16 +3823,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>87</v>
@@ -3844,10 +3841,10 @@
         <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3858,16 +3855,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
@@ -3876,7 +3873,7 @@
         <v>185</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>204</v>
@@ -3908,7 +3905,7 @@
         <v>114</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>208</v>
@@ -3940,7 +3937,7 @@
         <v>114</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>212</v>
@@ -3972,7 +3969,7 @@
         <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>216</v>
@@ -4004,7 +4001,7 @@
         <v>114</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>220</v>
@@ -4094,7 +4091,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4217,7 +4214,7 @@
         <v>235</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>236</v>
@@ -4263,7 +4260,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>240</v>
@@ -4281,7 +4278,7 @@
         <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>242</v>
@@ -4345,7 +4342,7 @@
         <v>88</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>248</v>
@@ -4441,7 +4438,7 @@
         <v>114</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>257</v>
@@ -4490,25 +4487,25 @@
         <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>261</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>261</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>114</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>33</v>
@@ -4519,25 +4516,25 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>263</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>263</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>264</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>265</v>
@@ -4569,7 +4566,7 @@
         <v>268</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>269</v>
@@ -4601,7 +4598,7 @@
         <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>272</v>
@@ -4665,7 +4662,7 @@
         <v>235</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>278</v>
@@ -4697,7 +4694,7 @@
         <v>114</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>281</v>
@@ -4729,7 +4726,7 @@
         <v>114</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>284</v>
@@ -4793,7 +4790,7 @@
         <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>290</v>
@@ -4825,7 +4822,7 @@
         <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>293</v>
@@ -4839,7 +4836,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>294</v>
@@ -4871,7 +4868,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>297</v>
@@ -4889,7 +4886,7 @@
         <v>124</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>299</v>
@@ -4903,7 +4900,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>300</v>
@@ -4921,7 +4918,7 @@
         <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>302</v>
@@ -5049,7 +5046,7 @@
         <v>268</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>314</v>
@@ -5198,7 +5195,7 @@
         <v>235</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>320</v>
@@ -5262,7 +5259,7 @@
         <v>185</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>326</v>
@@ -5308,7 +5305,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>330</v>
@@ -5387,10 +5384,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>185</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>338</v>
@@ -5407,25 +5404,25 @@
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>339</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>43</v>
+        <v>339</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>44</v>
@@ -5439,22 +5436,22 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>341</v>
+        <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>341</v>
+        <v>43</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>342</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>343</v>
@@ -5483,7 +5480,7 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>125</v>
@@ -5564,7 +5561,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>353</v>
@@ -5582,7 +5579,7 @@
         <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>355</v>
@@ -5614,7 +5611,7 @@
         <v>119</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>358</v>
@@ -5646,7 +5643,7 @@
         <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>361</v>
@@ -5678,7 +5675,7 @@
         <v>114</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>364</v>
@@ -5710,7 +5707,7 @@
         <v>367</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>368</v>
@@ -5739,13 +5736,13 @@
         <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>114</v>
+        <v>371</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>162</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>44</v>
@@ -5759,19 +5756,19 @@
         <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>374</v>
+        <v>114</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>162</v>
@@ -5838,7 +5835,7 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>381</v>
@@ -5884,7 +5881,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>385</v>
@@ -5902,7 +5899,7 @@
         <v>185</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>387</v>
@@ -5916,7 +5913,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>388</v>
@@ -5948,7 +5945,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>391</v>
@@ -5966,7 +5963,7 @@
         <v>367</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>393</v>
@@ -6030,7 +6027,7 @@
         <v>124</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>399</v>
@@ -6091,10 +6088,10 @@
         <v>87</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>405</v>
@@ -6126,7 +6123,7 @@
         <v>235</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>408</v>
@@ -6243,7 +6240,7 @@
         <v>268</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>411</v>
@@ -6275,7 +6272,7 @@
         <v>268</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>414</v>
@@ -6307,7 +6304,7 @@
         <v>114</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>417</v>
@@ -6353,7 +6350,7 @@
         <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>421</v>
@@ -6432,10 +6429,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>429</v>
@@ -6563,7 +6560,7 @@
         <v>114</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>441</v>
@@ -6592,10 +6589,10 @@
         <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>444</v>
@@ -6609,7 +6606,7 @@
         <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>445</v>
@@ -6627,7 +6624,7 @@
         <v>124</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>447</v>
@@ -6659,7 +6656,7 @@
         <v>114</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>450</v>
@@ -6691,7 +6688,7 @@
         <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>453</v>
@@ -6720,7 +6717,7 @@
         <v>87</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>149</v>
@@ -6752,10 +6749,10 @@
         <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>459</v>
@@ -6819,7 +6816,7 @@
         <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>465</v>
@@ -6880,10 +6877,10 @@
         <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>374</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>471</v>
@@ -6912,10 +6909,10 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>114</v>
+        <v>371</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>474</v>
@@ -6929,7 +6926,7 @@
         <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>52</v>
@@ -6947,7 +6944,7 @@
         <v>114</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>476</v>
@@ -6961,7 +6958,7 @@
         <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>477</v>
@@ -6979,7 +6976,7 @@
         <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>479</v>
@@ -6993,7 +6990,7 @@
         <v>45</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>480</v>
@@ -7011,7 +7008,7 @@
         <v>235</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>482</v>
@@ -7043,7 +7040,7 @@
         <v>268</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>485</v>
@@ -7072,10 +7069,10 @@
         <v>87</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>488</v>
@@ -7104,10 +7101,10 @@
         <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>491</v>
@@ -7139,7 +7136,7 @@
         <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>494</v>
@@ -7287,7 +7284,7 @@
         <v>179</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>500</v>
@@ -7365,7 +7362,7 @@
         <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>507</v>
@@ -7383,7 +7380,7 @@
         <v>114</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>509</v>
@@ -7412,10 +7409,10 @@
         <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>512</v>
@@ -7444,10 +7441,10 @@
         <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>515</v>
@@ -7479,7 +7476,7 @@
         <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>518</v>
@@ -7508,10 +7505,10 @@
         <v>87</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>521</v>
@@ -7540,10 +7537,10 @@
         <v>87</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>524</v>
@@ -7575,7 +7572,7 @@
         <v>185</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>527</v>
@@ -7621,7 +7618,7 @@
         <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>531</v>
@@ -7639,7 +7636,7 @@
         <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>533</v>
@@ -7671,7 +7668,7 @@
         <v>114</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>536</v>
@@ -7700,10 +7697,10 @@
         <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>539</v>
@@ -7735,7 +7732,7 @@
         <v>179</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>541</v>
@@ -7767,7 +7764,7 @@
         <v>114</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>544</v>
@@ -7799,7 +7796,7 @@
         <v>114</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>547</v>
@@ -7828,10 +7825,10 @@
         <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>367</v>
+        <v>143</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>550</v>
@@ -7860,10 +7857,10 @@
         <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>148</v>
+        <v>367</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>553</v>
@@ -7895,7 +7892,7 @@
         <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>556</v>
@@ -7924,7 +7921,7 @@
         <v>87</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>114</v>
+        <v>268</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>224</v>
@@ -7941,7 +7938,7 @@
         <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>560</v>
@@ -7956,7 +7953,7 @@
         <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>224</v>
@@ -7973,7 +7970,7 @@
         <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>563</v>
@@ -7988,10 +7985,10 @@
         <v>87</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>565</v>
@@ -8005,7 +8002,7 @@
         <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>566</v>
@@ -8020,10 +8017,10 @@
         <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>568</v>
@@ -8052,13 +8049,13 @@
         <v>87</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>268</v>
+        <v>114</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>572</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8072,13 +8069,13 @@
         <v>209</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>87</v>
@@ -8087,7 +8084,7 @@
         <v>114</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>575</v>
@@ -8151,7 +8148,7 @@
         <v>114</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>581</v>